--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
@@ -787,7 +787,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q2" t="n">
         <v>2.14</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>2.24</v>
       </c>
       <c r="G3" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="H3" t="n">
         <v>2.96</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.04</v>
+        <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
         <v>2.02</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -1339,23 +1339,23 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="G5" t="n">
-        <v>5.4</v>
+        <v>3.95</v>
       </c>
       <c r="H5" t="n">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="I5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K5" t="n">
         <v>3.25</v>
       </c>
-      <c r="J5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.5</v>
-      </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -1536,19 +1536,19 @@
         <v>3.3</v>
       </c>
       <c r="G6" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="H6" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="I6" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="J6" t="n">
         <v>2.64</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1927,7 @@
         <v>8.6</v>
       </c>
       <c r="H8" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="I8" t="n">
         <v>1.57</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q8" t="n">
         <v>1.76</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -2318,13 +2318,13 @@
         <v>1.74</v>
       </c>
       <c r="I10" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J10" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>5.9</v>
+        <v>4.1</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="G13" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="H13" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
@@ -2924,7 +2924,7 @@
         <v>1.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="H15" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="J15" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -3476,13 +3476,13 @@
         <v>2.2</v>
       </c>
       <c r="G16" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="H16" t="n">
         <v>3.05</v>
       </c>
       <c r="I16" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J16" t="n">
         <v>3.65</v>
@@ -3506,7 +3506,7 @@
         <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
         <v>1.74</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R17" t="n">
         <v>1.27</v>
@@ -3712,7 +3712,7 @@
         <v>1.98</v>
       </c>
       <c r="U17" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3724,7 +3724,7 @@
         <v>12</v>
       </c>
       <c r="Y17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z17" t="n">
         <v>26</v>
@@ -3739,25 +3739,25 @@
         <v>7.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF17" t="n">
         <v>13</v>
       </c>
       <c r="AG17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH17" t="n">
         <v>23</v>
       </c>
       <c r="AI17" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK17" t="n">
         <v>29</v>
@@ -3769,7 +3769,7 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO17" t="n">
         <v>75</v>
@@ -3787,16 +3787,16 @@
         <v>32</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV17" t="n">
         <v>14</v>
       </c>
       <c r="AW17" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="AX17" t="n">
         <v>11.5</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
         <v>2.44</v>
       </c>
       <c r="H18" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I18" t="n">
         <v>3.45</v>
@@ -3885,7 +3885,7 @@
         <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O18" t="n">
         <v>1.38</v>
@@ -3930,7 +3930,7 @@
         <v>9.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD18" t="n">
         <v>14.5</v>
@@ -3951,7 +3951,7 @@
         <v>55</v>
       </c>
       <c r="AJ18" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK18" t="n">
         <v>28</v>
@@ -3966,7 +3966,7 @@
         <v>24</v>
       </c>
       <c r="AO18" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP18" t="n">
         <v>10.5</v>
@@ -3984,7 +3984,7 @@
         <v>8.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV18" t="n">
         <v>12.5</v>
@@ -3996,7 +3996,7 @@
         <v>13.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ18" t="n">
         <v>16</v>
@@ -4011,10 +4011,10 @@
         <v>24</v>
       </c>
       <c r="BD18" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BE18" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF18" t="n">
         <v>18</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G19" t="n">
         <v>3.35</v>
@@ -4064,7 +4064,7 @@
         <v>2.46</v>
       </c>
       <c r="I19" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J19" t="n">
         <v>3.35</v>
@@ -4082,25 +4082,25 @@
         <v>3.55</v>
       </c>
       <c r="O19" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P19" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R19" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S19" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T19" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U19" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4112,7 +4112,7 @@
         <v>13</v>
       </c>
       <c r="Y19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z19" t="n">
         <v>15.5</v>
@@ -4124,7 +4124,7 @@
         <v>12</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD19" t="n">
         <v>12</v>
@@ -4145,7 +4145,7 @@
         <v>44</v>
       </c>
       <c r="AJ19" t="n">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="AK19" t="n">
         <v>46</v>
@@ -4157,16 +4157,16 @@
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AO19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP19" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR19" t="n">
         <v>13</v>
@@ -4178,7 +4178,7 @@
         <v>10.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV19" t="n">
         <v>10.5</v>
@@ -4193,10 +4193,10 @@
         <v>12.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA19" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB19" t="n">
         <v>48</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
@@ -760,16 +760,16 @@
         <v>1.57</v>
       </c>
       <c r="G2" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J2" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="K2" t="n">
         <v>4.3</v>
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.25</v>
+        <v>2.02</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -1536,16 +1536,16 @@
         <v>3.3</v>
       </c>
       <c r="G6" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I6" t="n">
-        <v>2.98</v>
+        <v>3.35</v>
       </c>
       <c r="J6" t="n">
-        <v>2.64</v>
+        <v>2.44</v>
       </c>
       <c r="K6" t="n">
         <v>2.92</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="G8" t="n">
         <v>8.6</v>
       </c>
       <c r="H8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="I8" t="n">
         <v>1.57</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>2.38</v>
       </c>
       <c r="G9" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="H9" t="n">
         <v>3.05</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="H10" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="I10" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="J10" t="n">
         <v>3.5</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="G12" t="n">
-        <v>2.76</v>
+        <v>2.42</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I12" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="K12" t="n">
-        <v>5.9</v>
+        <v>4.3</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -2894,19 +2894,19 @@
         <v>1.32</v>
       </c>
       <c r="G13" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="H13" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="J13" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q13" t="n">
         <v>2.04</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.76</v>
+        <v>3.05</v>
       </c>
       <c r="G14" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="H14" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="I14" t="n">
         <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="K14" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -3279,19 +3279,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="G15" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="H15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J15" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="K15" t="n">
         <v>3.25</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G16" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H16" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I16" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J16" t="n">
         <v>3.65</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G17" t="n">
         <v>2.24</v>
@@ -3682,7 +3682,7 @@
         <v>3.45</v>
       </c>
       <c r="K17" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3700,7 +3700,7 @@
         <v>1.74</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R17" t="n">
         <v>1.27</v>
@@ -3712,7 +3712,7 @@
         <v>1.98</v>
       </c>
       <c r="U17" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3739,7 +3739,7 @@
         <v>7.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE17" t="n">
         <v>55</v>
@@ -3769,7 +3769,7 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO17" t="n">
         <v>75</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
         <v>2.44</v>
       </c>
       <c r="H18" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I18" t="n">
         <v>3.45</v>
@@ -3879,7 +3879,7 @@
         <v>3.45</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M18" t="n">
         <v>1.08</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
         <v>3.35</v>
       </c>
       <c r="H19" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="I19" t="n">
         <v>2.54</v>
@@ -4085,7 +4085,7 @@
         <v>1.37</v>
       </c>
       <c r="P19" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q19" t="n">
         <v>2.18</v>
@@ -4145,7 +4145,7 @@
         <v>44</v>
       </c>
       <c r="AJ19" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="AK19" t="n">
         <v>46</v>
@@ -4196,7 +4196,7 @@
         <v>16</v>
       </c>
       <c r="BA19" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="BB19" t="n">
         <v>48</v>
@@ -4211,14 +4211,14 @@
         <v>38</v>
       </c>
       <c r="BF19" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="BG19" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH20"/>
+  <dimension ref="A1:BH21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="G2" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="H2" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="I2" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="K2" t="n">
         <v>4.3</v>
@@ -790,7 +790,7 @@
         <v>1.76</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H3" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="I3" t="n">
         <v>3.45</v>
@@ -981,7 +981,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q3" t="n">
         <v>1.77</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="G4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H4" t="n">
         <v>12.5</v>
@@ -1160,7 +1160,7 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="H6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J6" t="n">
         <v>2.72</v>
       </c>
-      <c r="I6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.44</v>
-      </c>
       <c r="K6" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
@@ -2118,10 +2118,10 @@
         <v>2.38</v>
       </c>
       <c r="G9" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="H9" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="I9" t="n">
         <v>3.35</v>
@@ -2130,7 +2130,7 @@
         <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="H10" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="I10" t="n">
         <v>2.04</v>
@@ -2324,7 +2324,7 @@
         <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,31 +2494,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Crvena Zvezda</t>
+          <t>Erokspor A.S</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FK Spartak</t>
+          <t>Amed Sportif Faaliyetler</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>2.44</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="J11" t="n">
-        <v>1.02</v>
+        <v>3.55</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.07</v>
+        <v>2.18</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,31 +2688,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Erokspor A.S</t>
+          <t>Crvena Zvezda</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Amed Sportif Faaliyetler</t>
+          <t>FK Spartak</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.14</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>2.42</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>3.55</v>
+        <v>1.02</v>
       </c>
       <c r="K12" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.18</v>
+        <v>1.07</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,36 +2877,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PFC Levski Sofia</t>
+          <t>Cukaricki</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>FK Radnicki 1923</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>4.7</v>
+        <v>1.02</v>
       </c>
       <c r="K13" t="n">
-        <v>5.7</v>
+        <v>950</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.77</v>
+        <v>1.07</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,36 +3071,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>PFC Levski Sofia</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ZED FC</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.05</v>
+        <v>1.34</v>
       </c>
       <c r="G14" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="H14" t="n">
-        <v>2.74</v>
+        <v>8.6</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>18.5</v>
       </c>
       <c r="J14" t="n">
-        <v>2.68</v>
+        <v>4.6</v>
       </c>
       <c r="K14" t="n">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.44</v>
+        <v>1.77</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.92</v>
+        <v>2.06</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
@@ -3270,31 +3270,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>ZED FC</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.97</v>
+        <v>3.05</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="H15" t="n">
-        <v>4.9</v>
+        <v>2.74</v>
       </c>
       <c r="I15" t="n">
-        <v>6.4</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="K15" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,50 +3464,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.18</v>
+        <v>1.97</v>
       </c>
       <c r="G16" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="H16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Q16" t="n">
         <v>3.1</v>
       </c>
-      <c r="I16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.77</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -3636,14 +3636,14 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,66 +3653,66 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Al-Ettifaq</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>Al Riyadh SC</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G17" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="H17" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="I17" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="J17" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K17" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="R17" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3721,116 +3721,116 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>2.4</v>
       </c>
       <c r="G18" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H18" t="n">
         <v>3.4</v>
@@ -3885,7 +3885,7 @@
         <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O18" t="n">
         <v>1.38</v>
@@ -3903,7 +3903,7 @@
         <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U18" t="n">
         <v>2.06</v>
@@ -3912,7 +3912,7 @@
         <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X18" t="n">
         <v>12.5</v>
@@ -3939,7 +3939,7 @@
         <v>42</v>
       </c>
       <c r="AF18" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG18" t="n">
         <v>12</v>
@@ -3960,7 +3960,7 @@
         <v>44</v>
       </c>
       <c r="AM18" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
         <v>24</v>
@@ -3981,7 +3981,7 @@
         <v>50</v>
       </c>
       <c r="AT18" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU18" t="n">
         <v>7</v>
@@ -4011,20 +4011,20 @@
         <v>24</v>
       </c>
       <c r="BD18" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="BE18" t="n">
-        <v>14.5</v>
+        <v>40</v>
       </c>
       <c r="BF18" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BG18" t="n">
         <v>34</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
         <v>3.2</v>
       </c>
       <c r="G19" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H19" t="n">
         <v>2.5</v>
@@ -4085,7 +4085,7 @@
         <v>1.37</v>
       </c>
       <c r="P19" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q19" t="n">
         <v>2.18</v>
@@ -4130,7 +4130,7 @@
         <v>12</v>
       </c>
       <c r="AE19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF19" t="n">
         <v>23</v>
@@ -4142,13 +4142,13 @@
         <v>18.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ19" t="n">
         <v>350</v>
       </c>
       <c r="AK19" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AL19" t="n">
         <v>55</v>
@@ -4196,7 +4196,7 @@
         <v>16</v>
       </c>
       <c r="BA19" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BB19" t="n">
         <v>48</v>
@@ -4218,201 +4218,395 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Nottm Forest</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:21:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Colombian Primera B</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>18:00:00</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Union Magdalena</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Envigado</t>
         </is>
       </c>
-      <c r="F20" t="n">
+      <c r="F21" t="n">
         <v>1.04</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G21" t="n">
         <v>1000</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H21" t="n">
         <v>1.04</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I21" t="n">
         <v>1000</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>1.03</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K21" t="n">
         <v>950</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q21" t="n">
         <v>1.01</v>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH20" t="inlineStr">
-        <is>
-          <t>2026-04-07 05:12:08</t>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH21"/>
+  <dimension ref="A1:BH29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="H2" t="n">
         <v>6.4</v>
       </c>
       <c r="I2" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K2" t="n">
         <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P2" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-07 07:21:26</t>
+          <t>2026-04-07 22:09:25</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G3" t="n">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="H3" t="n">
         <v>2.94</v>
       </c>
       <c r="I3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J3" t="n">
         <v>3.45</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.4</v>
       </c>
       <c r="K3" t="n">
         <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P3" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-07 07:21:26</t>
+          <t>2026-04-07 22:09:25</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="G4" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="H4" t="n">
         <v>12.5</v>
       </c>
       <c r="I4" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="J4" t="n">
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-07 07:21:26</t>
+          <t>2026-04-07 22:09:25</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G5" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="H5" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="J5" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="P5" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-07 07:21:26</t>
+          <t>2026-04-07 22:09:25</t>
         </is>
       </c>
     </row>
@@ -1536,167 +1536,167 @@
         <v>3.25</v>
       </c>
       <c r="G6" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="I6" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="J6" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="K6" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="P6" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-07 07:21:26</t>
+          <t>2026-04-07 22:09:25</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>3.2</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.07</v>
+        <v>1.84</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-07 07:21:26</t>
+          <t>2026-04-07 22:09:25</t>
         </is>
       </c>
     </row>
@@ -1921,177 +1921,177 @@
         </is>
       </c>
       <c r="F8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>9</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>270</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>130</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>140</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT8" t="n">
         <v>6.6</v>
       </c>
-      <c r="G8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-07 07:21:26</t>
+          <t>2026-04-07 22:09:25</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:20:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Al-Ula FC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.38</v>
+        <v>1.82</v>
       </c>
       <c r="G9" t="n">
-        <v>2.52</v>
+        <v>2.02</v>
       </c>
       <c r="H9" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="I9" t="n">
-        <v>3.35</v>
+        <v>5.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P9" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-07 07:21:26</t>
+          <t>2026-04-07 22:09:25</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:20:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Istanbulspor</t>
+          <t>Al Orubah</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Erzurum BB</t>
+          <t>Al Faisaly ( KSA )</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.2</v>
+        <v>2.98</v>
       </c>
       <c r="G10" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="H10" t="n">
-        <v>1.83</v>
+        <v>2.26</v>
       </c>
       <c r="I10" t="n">
-        <v>2.04</v>
+        <v>2.48</v>
       </c>
       <c r="J10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X10" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>3.5</v>
       </c>
-      <c r="K10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-07 07:21:26</t>
+          <t>2026-04-07 22:09:25</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Erokspor A.S</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Amed Sportif Faaliyetler</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="G11" t="n">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="H11" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="I11" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="J11" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K11" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P11" t="n">
-        <v>2.18</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.67</v>
+        <v>2.28</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-07 07:21:26</t>
+          <t>2026-04-07 22:09:25</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Crvena Zvezda</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FK Spartak</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>2.42</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="J12" t="n">
-        <v>1.02</v>
+        <v>3.45</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P12" t="n">
-        <v>1.07</v>
+        <v>1.93</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-07 07:21:26</t>
+          <t>2026-04-07 22:09:25</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cukaricki</t>
+          <t>Erokspor A.S</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FK Radnicki 1923</t>
+          <t>Amed Sportif Faaliyetler</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>2.38</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="J13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
         <v>1.02</v>
       </c>
-      <c r="K13" t="n">
-        <v>950</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P13" t="n">
-        <v>1.07</v>
+        <v>2.18</v>
       </c>
       <c r="Q13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T13" t="n">
         <v>1.01</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-07 07:21:26</t>
+          <t>2026-04-07 22:09:25</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PFC Levski Sofia</t>
+          <t>Istanbulspor</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Erzurum BB</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L14" t="n">
         <v>1.34</v>
       </c>
-      <c r="G14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="H14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="I14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="J14" t="n">
+      <c r="M14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA14" t="n">
         <v>4.6</v>
       </c>
-      <c r="K14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0</v>
-      </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-07 07:21:26</t>
+          <t>2026-04-07 22:09:25</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Cukaricki</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ZED FC</t>
+          <t>FK Radnicki 1923</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H15" t="n">
         <v>3.05</v>
       </c>
-      <c r="G15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2.74</v>
-      </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="K15" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P15" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.92</v>
+        <v>1.72</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-07 07:21:26</t>
+          <t>2026-04-07 22:09:25</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Crvena Zvezda</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>FK Spartak</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.97</v>
+        <v>1.07</v>
       </c>
       <c r="G16" t="n">
-        <v>2.26</v>
+        <v>1.1</v>
       </c>
       <c r="H16" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="I16" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>2.84</v>
+        <v>15</v>
       </c>
       <c r="K16" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="P16" t="n">
-        <v>1.37</v>
+        <v>4.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.1</v>
+        <v>1.19</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-07 07:21:26</t>
+          <t>2026-04-07 22:09:25</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>PFC Levski Sofia</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.18</v>
+        <v>1.35</v>
       </c>
       <c r="G17" t="n">
-        <v>2.38</v>
+        <v>1.45</v>
       </c>
       <c r="H17" t="n">
-        <v>3.1</v>
+        <v>11</v>
       </c>
       <c r="I17" t="n">
-        <v>3.5</v>
+        <v>17.5</v>
       </c>
       <c r="J17" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="K17" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.77</v>
+        <v>2.06</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-07 07:21:26</t>
+          <t>2026-04-07 22:09:25</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:40:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Al-Adalh</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Al Batin</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="G18" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S18" t="n">
         <v>2.42</v>
       </c>
-      <c r="H18" t="n">
+      <c r="T18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X18" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT18" t="n">
         <v>3.4</v>
-      </c>
-      <c r="I18" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S18" t="n">
-        <v>4</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>8.6</v>
       </c>
       <c r="AU18" t="n">
         <v>7</v>
       </c>
       <c r="AV18" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AW18" t="n">
-        <v>36</v>
+        <v>3.85</v>
       </c>
       <c r="AX18" t="n">
-        <v>13.5</v>
+        <v>3.6</v>
       </c>
       <c r="AY18" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ18" t="n">
-        <v>16</v>
+        <v>3.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>46</v>
+        <v>3.9</v>
       </c>
       <c r="BB18" t="n">
-        <v>29</v>
+        <v>3.9</v>
       </c>
       <c r="BC18" t="n">
-        <v>24</v>
+        <v>3.8</v>
       </c>
       <c r="BD18" t="n">
-        <v>26</v>
+        <v>3.9</v>
       </c>
       <c r="BE18" t="n">
-        <v>40</v>
+        <v>4.1</v>
       </c>
       <c r="BF18" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="BG18" t="n">
-        <v>34</v>
+        <v>3.65</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-07 07:21:26</t>
+          <t>2026-04-07 22:09:25</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>ZED FC</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="G19" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="I19" t="n">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>3.35</v>
+        <v>2.74</v>
       </c>
       <c r="K19" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M19" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="N19" t="n">
-        <v>3.55</v>
+        <v>2.34</v>
       </c>
       <c r="O19" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="P19" t="n">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.18</v>
+        <v>2.96</v>
       </c>
       <c r="R19" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="T19" t="n">
-        <v>1.86</v>
+        <v>2.22</v>
       </c>
       <c r="U19" t="n">
-        <v>2.08</v>
+        <v>1.7</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X19" t="n">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z19" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AB19" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD19" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AF19" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG19" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AH19" t="n">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="AI19" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AJ19" t="n">
-        <v>350</v>
+        <v>70</v>
       </c>
       <c r="AK19" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AL19" t="n">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN19" t="n">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="AO19" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="AP19" t="n">
-        <v>11</v>
+        <v>5.7</v>
       </c>
       <c r="AQ19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA19" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AR19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>36</v>
-      </c>
       <c r="BB19" t="n">
-        <v>48</v>
+        <v>8.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>32</v>
+        <v>8.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>42</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE19" t="n">
-        <v>38</v>
+        <v>9.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>23</v>
+        <v>8.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>21</v>
+        <v>8.4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-07 07:21:26</t>
+          <t>2026-04-07 22:09:25</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,378 +4235,1930 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="G20" t="n">
         <v>2.24</v>
       </c>
       <c r="H20" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="I20" t="n">
-        <v>3.85</v>
+        <v>5.9</v>
       </c>
       <c r="J20" t="n">
-        <v>3.45</v>
+        <v>2.76</v>
       </c>
       <c r="K20" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M20" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="N20" t="n">
-        <v>3.2</v>
+        <v>2.14</v>
       </c>
       <c r="O20" t="n">
-        <v>1.43</v>
+        <v>1.7</v>
       </c>
       <c r="P20" t="n">
-        <v>1.74</v>
+        <v>1.37</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.3</v>
+        <v>3.15</v>
       </c>
       <c r="R20" t="n">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="S20" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="T20" t="n">
-        <v>1.98</v>
+        <v>2.44</v>
       </c>
       <c r="U20" t="n">
-        <v>1.96</v>
+        <v>1.55</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="X20" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Y20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="AA20" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB20" t="n">
-        <v>8.6</v>
+        <v>6</v>
       </c>
       <c r="AC20" t="n">
         <v>7.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>16.5</v>
+        <v>25</v>
       </c>
       <c r="AE20" t="n">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="AF20" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AJ20" t="n">
         <v>32</v>
       </c>
       <c r="AK20" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AL20" t="n">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AN20" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AO20" t="n">
-        <v>65</v>
+        <v>290</v>
       </c>
       <c r="AP20" t="n">
-        <v>10.5</v>
+        <v>5.7</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AR20" t="n">
-        <v>16.5</v>
+        <v>7.8</v>
       </c>
       <c r="AS20" t="n">
-        <v>34</v>
+        <v>9.4</v>
       </c>
       <c r="AT20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ20" t="n">
         <v>7.6</v>
       </c>
-      <c r="AU20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BA20" t="n">
-        <v>50</v>
+        <v>9.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>19</v>
+        <v>7.6</v>
       </c>
       <c r="BC20" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="BD20" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="BE20" t="n">
-        <v>42</v>
+        <v>9.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>20</v>
+        <v>7.8</v>
       </c>
       <c r="BG20" t="n">
-        <v>50</v>
+        <v>9.6</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-07 07:21:26</t>
+          <t>2026-04-07 22:09:25</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Al-Ettifaq</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Al Riyadh SC</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X21" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:09:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Nottm Forest</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:09:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Algerian Ligue 1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>MC Alger</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>MC El Bayadh</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="H23" t="n">
+        <v>10</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:09:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:09:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Crystal Palace</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I25" t="n">
+        <v>6</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>70</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:09:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Shakhtar</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AZ Alkmaar</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X26" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>36</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>19</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:09:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X27" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>40</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:09:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X28" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>36</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>22</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:09:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Colombian Primera B</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>18:00:00</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Union Magdalena</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Envigado</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="F29" t="n">
         <v>1.04</v>
       </c>
-      <c r="G21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H21" t="n">
+      <c r="G29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H29" t="n">
         <v>1.04</v>
       </c>
-      <c r="I21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="K21" t="n">
+      <c r="I29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K29" t="n">
         <v>950</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
+      <c r="L29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P29" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S29" t="n">
         <v>1.01</v>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>2026-04-07 07:21:26</t>
+      <c r="T29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:09:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
@@ -766,7 +766,7 @@
         <v>6.4</v>
       </c>
       <c r="I2" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J2" t="n">
         <v>3.8</v>
@@ -796,7 +796,7 @@
         <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="T2" t="n">
         <v>2.04</v>
@@ -805,7 +805,7 @@
         <v>1.8</v>
       </c>
       <c r="V2" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W2" t="n">
         <v>2.42</v>
@@ -877,10 +877,10 @@
         <v>4.9</v>
       </c>
       <c r="AT2" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
         <v>20</v>
@@ -892,10 +892,10 @@
         <v>7</v>
       </c>
       <c r="AY2" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.2</v>
+        <v>18.5</v>
       </c>
       <c r="BA2" t="n">
         <v>4.8</v>
@@ -913,14 +913,14 @@
         <v>4.9</v>
       </c>
       <c r="BF2" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG2" t="n">
         <v>4.9</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -954,22 +954,22 @@
         <v>2.28</v>
       </c>
       <c r="G3" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H3" t="n">
         <v>2.94</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J3" t="n">
         <v>3.45</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
@@ -996,10 +996,10 @@
         <v>1.65</v>
       </c>
       <c r="U3" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W3" t="n">
         <v>1.64</v>
@@ -1008,10 +1008,10 @@
         <v>19.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA3" t="n">
         <v>55</v>
@@ -1020,7 +1020,7 @@
         <v>12.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3" t="n">
         <v>16</v>
@@ -1056,7 +1056,7 @@
         <v>20</v>
       </c>
       <c r="AO3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AP3" t="n">
         <v>13</v>
@@ -1068,7 +1068,7 @@
         <v>19</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AT3" t="n">
         <v>10</v>
@@ -1080,7 +1080,7 @@
         <v>11.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AX3" t="n">
         <v>12.5</v>
@@ -1092,29 +1092,29 @@
         <v>13.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BC3" t="n">
         <v>20</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF3" t="n">
         <v>14.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O4" t="n">
         <v>1.29</v>
@@ -1202,7 +1202,7 @@
         <v>20</v>
       </c>
       <c r="Y4" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Z4" t="n">
         <v>150</v>
@@ -1241,7 +1241,7 @@
         <v>20</v>
       </c>
       <c r="AL4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="n">
         <v>310</v>
@@ -1259,10 +1259,10 @@
         <v>4.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT4" t="n">
         <v>6.2</v>
@@ -1271,10 +1271,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX4" t="n">
         <v>6.2</v>
@@ -1283,10 +1283,10 @@
         <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB4" t="n">
         <v>8.800000000000001</v>
@@ -1298,17 +1298,17 @@
         <v>4.7</v>
       </c>
       <c r="BE4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF4" t="n">
         <v>5.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -1342,16 +1342,16 @@
         <v>3.15</v>
       </c>
       <c r="G5" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H5" t="n">
         <v>2.56</v>
       </c>
       <c r="I5" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="K5" t="n">
         <v>3.2</v>
@@ -1381,7 +1381,7 @@
         <v>5.6</v>
       </c>
       <c r="T5" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U5" t="n">
         <v>1.71</v>
@@ -1390,7 +1390,7 @@
         <v>1.52</v>
       </c>
       <c r="W5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X5" t="n">
         <v>8.199999999999999</v>
@@ -1405,7 +1405,7 @@
         <v>50</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC5" t="n">
         <v>7.4</v>
@@ -1423,7 +1423,7 @@
         <v>16.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI5" t="n">
         <v>75</v>
@@ -1441,22 +1441,22 @@
         <v>230</v>
       </c>
       <c r="AN5" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AO5" t="n">
         <v>55</v>
       </c>
       <c r="AP5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ5" t="n">
         <v>6.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT5" t="n">
         <v>7.6</v>
@@ -1465,44 +1465,44 @@
         <v>6</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="AX5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AZ5" t="n">
         <v>20</v>
       </c>
       <c r="BA5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC5" t="n">
         <v>8</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BD5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>50</v>
+      </c>
+      <c r="BG5" t="n">
         <v>8</v>
       </c>
-      <c r="BC5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G6" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H6" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I6" t="n">
         <v>2.92</v>
@@ -1557,7 +1557,7 @@
         <v>1.16</v>
       </c>
       <c r="N6" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O6" t="n">
         <v>1.66</v>
@@ -1569,7 +1569,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S6" t="n">
         <v>6.4</v>
@@ -1578,7 +1578,7 @@
         <v>2.28</v>
       </c>
       <c r="U6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V6" t="n">
         <v>1.52</v>
@@ -1638,7 +1638,7 @@
         <v>120</v>
       </c>
       <c r="AO6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP6" t="n">
         <v>6.2</v>
@@ -1650,7 +1650,7 @@
         <v>14</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT6" t="n">
         <v>7.6</v>
@@ -1671,7 +1671,7 @@
         <v>14</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BA6" t="n">
         <v>6.6</v>
@@ -1680,23 +1680,23 @@
         <v>6.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>50</v>
+        <v>6.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE6" t="n">
         <v>7</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG6" t="n">
         <v>6.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H7" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="I7" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="J7" t="n">
         <v>3.2</v>
@@ -1745,7 +1745,7 @@
         <v>3.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
@@ -1775,10 +1775,10 @@
         <v>2.24</v>
       </c>
       <c r="V7" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -1805,7 +1805,7 @@
         <v>42</v>
       </c>
       <c r="AF7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG7" t="n">
         <v>970</v>
@@ -1817,10 +1817,10 @@
         <v>65</v>
       </c>
       <c r="AJ7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL7" t="n">
         <v>46</v>
@@ -1829,7 +1829,7 @@
         <v>85</v>
       </c>
       <c r="AN7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO7" t="n">
         <v>32</v>
@@ -1841,10 +1841,10 @@
         <v>10</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AT7" t="n">
         <v>8.6</v>
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AY7" t="n">
         <v>9</v>
@@ -1868,29 +1868,29 @@
         <v>10.5</v>
       </c>
       <c r="BA7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC7" t="n">
         <v>4.6</v>
       </c>
-      <c r="BB7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BD7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF7" t="n">
         <v>4.5</v>
       </c>
-      <c r="BE7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BG7" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -1924,13 +1924,13 @@
         <v>7.2</v>
       </c>
       <c r="G8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H8" t="n">
         <v>1.42</v>
       </c>
       <c r="I8" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="J8" t="n">
         <v>4.7</v>
@@ -1945,19 +1945,19 @@
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O8" t="n">
         <v>1.21</v>
       </c>
       <c r="P8" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q8" t="n">
         <v>1.63</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S8" t="n">
         <v>2.58</v>
@@ -1966,10 +1966,10 @@
         <v>1.81</v>
       </c>
       <c r="U8" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V8" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="W8" t="n">
         <v>1.12</v>
@@ -2014,7 +2014,7 @@
         <v>270</v>
       </c>
       <c r="AK8" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AL8" t="n">
         <v>110</v>
@@ -2056,7 +2056,7 @@
         <v>7.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AZ8" t="n">
         <v>6.2</v>
@@ -2071,7 +2071,7 @@
         <v>8</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE8" t="n">
         <v>8</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="O10" t="n">
         <v>1.24</v>
@@ -2360,28 +2360,28 @@
         <v>1.67</v>
       </c>
       <c r="W10" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X10" t="n">
         <v>24</v>
       </c>
       <c r="Y10" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="Z10" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AA10" t="n">
         <v>38</v>
       </c>
       <c r="AB10" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AD10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AE10" t="n">
         <v>28</v>
@@ -2390,10 +2390,10 @@
         <v>29</v>
       </c>
       <c r="AG10" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AI10" t="n">
         <v>40</v>
@@ -2417,62 +2417,62 @@
         <v>18</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.55</v>
+        <v>5.3</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.8</v>
+        <v>6.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="AW10" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="BA10" t="n">
-        <v>3.85</v>
+        <v>6.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.85</v>
+        <v>6.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.9</v>
+        <v>6.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.45</v>
+        <v>5.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
         <v>3.2</v>
       </c>
       <c r="O11" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P11" t="n">
         <v>1.73</v>
@@ -2542,16 +2542,16 @@
         <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
         <v>1.92</v>
       </c>
       <c r="V11" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W11" t="n">
         <v>1.91</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>2.3</v>
       </c>
       <c r="G12" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H12" t="n">
         <v>3.35</v>
@@ -2748,7 +2748,7 @@
         <v>1.39</v>
       </c>
       <c r="W12" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="X12" t="n">
         <v>14</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -3085,19 +3085,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="G14" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="H14" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="I14" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K14" t="n">
         <v>4.2</v>
@@ -3109,34 +3109,34 @@
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O14" t="n">
         <v>1.3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
         <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U14" t="n">
         <v>2.02</v>
       </c>
       <c r="V14" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="W14" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X14" t="n">
         <v>17.5</v>
@@ -3145,10 +3145,10 @@
         <v>10.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AB14" t="n">
         <v>19</v>
@@ -3160,7 +3160,7 @@
         <v>12</v>
       </c>
       <c r="AE14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF14" t="n">
         <v>40</v>
@@ -3190,7 +3190,7 @@
         <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AP14" t="n">
         <v>11.5</v>
@@ -3208,7 +3208,7 @@
         <v>12.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV14" t="n">
         <v>8</v>
@@ -3217,7 +3217,7 @@
         <v>15.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AY14" t="n">
         <v>13.5</v>
@@ -3226,29 +3226,29 @@
         <v>14</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BG14" t="n">
         <v>10</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="G15" t="n">
         <v>2.42</v>
@@ -3288,7 +3288,7 @@
         <v>3.05</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="J15" t="n">
         <v>3.1</v>
@@ -3327,7 +3327,7 @@
         <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W15" t="n">
         <v>1.7</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3718,7 @@
         <v>1.06</v>
       </c>
       <c r="W17" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X17" t="n">
         <v>15.5</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>2.32</v>
       </c>
       <c r="G18" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="H18" t="n">
         <v>2.72</v>
@@ -3879,7 +3879,7 @@
         <v>4.3</v>
       </c>
       <c r="L18" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
         <v>1.03</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -4070,13 +4070,13 @@
         <v>2.74</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="L19" t="n">
         <v>1.56</v>
       </c>
       <c r="M19" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="N19" t="n">
         <v>2.34</v>
@@ -4106,7 +4106,7 @@
         <v>1.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X19" t="n">
         <v>8.4</v>
@@ -4142,7 +4142,7 @@
         <v>26</v>
       </c>
       <c r="AI19" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ19" t="n">
         <v>70</v>
@@ -4163,7 +4163,7 @@
         <v>65</v>
       </c>
       <c r="AP19" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AQ19" t="n">
         <v>6.8</v>
@@ -4178,13 +4178,13 @@
         <v>7.4</v>
       </c>
       <c r="AU19" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV19" t="n">
         <v>12.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX19" t="n">
         <v>17.5</v>
@@ -4199,13 +4199,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BB19" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC19" t="n">
         <v>8.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BE19" t="n">
         <v>9.4</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
         <v>7.2</v>
       </c>
       <c r="T20" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="U20" t="n">
         <v>1.55</v>
@@ -4303,7 +4303,7 @@
         <v>1.81</v>
       </c>
       <c r="X20" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Y20" t="n">
         <v>11.5</v>
@@ -4315,7 +4315,7 @@
         <v>200</v>
       </c>
       <c r="AB20" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AC20" t="n">
         <v>7.6</v>
@@ -4363,10 +4363,10 @@
         <v>9.4</v>
       </c>
       <c r="AR20" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS20" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AT20" t="n">
         <v>5</v>
@@ -4378,7 +4378,7 @@
         <v>20</v>
       </c>
       <c r="AW20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX20" t="n">
         <v>9.4</v>
@@ -4387,32 +4387,32 @@
         <v>11</v>
       </c>
       <c r="AZ20" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BA20" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BB20" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BC20" t="n">
         <v>30</v>
       </c>
       <c r="BD20" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF20" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -4446,13 +4446,13 @@
         <v>2.18</v>
       </c>
       <c r="G21" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="H21" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="I21" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J21" t="n">
         <v>3.65</v>
@@ -4491,10 +4491,10 @@
         <v>2.28</v>
       </c>
       <c r="V21" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="X21" t="n">
         <v>970</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -4640,10 +4640,10 @@
         <v>2.2</v>
       </c>
       <c r="G22" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H22" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I22" t="n">
         <v>3.85</v>
@@ -4655,7 +4655,7 @@
         <v>3.5</v>
       </c>
       <c r="L22" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="M22" t="n">
         <v>1.09</v>
@@ -4670,16 +4670,16 @@
         <v>1.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S22" t="n">
         <v>4.3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U22" t="n">
         <v>1.97</v>
@@ -4688,7 +4688,7 @@
         <v>1.35</v>
       </c>
       <c r="W22" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X22" t="n">
         <v>11.5</v>
@@ -4742,7 +4742,7 @@
         <v>23</v>
       </c>
       <c r="AO22" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP22" t="n">
         <v>10.5</v>
@@ -4763,7 +4763,7 @@
         <v>7.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW22" t="n">
         <v>27</v>
@@ -4796,11 +4796,11 @@
         <v>20</v>
       </c>
       <c r="BG22" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -5025,19 +5025,19 @@
         </is>
       </c>
       <c r="F24" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G24" t="n">
         <v>2.1</v>
       </c>
-      <c r="G24" t="n">
-        <v>2.16</v>
-      </c>
       <c r="H24" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J24" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K24" t="n">
         <v>3.7</v>
@@ -5067,16 +5067,16 @@
         <v>3.4</v>
       </c>
       <c r="T24" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U24" t="n">
         <v>2.18</v>
       </c>
       <c r="V24" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W24" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="X24" t="n">
         <v>14.5</v>
@@ -5094,7 +5094,7 @@
         <v>10</v>
       </c>
       <c r="AC24" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD24" t="n">
         <v>16.5</v>
@@ -5106,13 +5106,13 @@
         <v>13</v>
       </c>
       <c r="AG24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH24" t="n">
         <v>18</v>
       </c>
       <c r="AI24" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ24" t="n">
         <v>26</v>
@@ -5142,10 +5142,10 @@
         <v>24</v>
       </c>
       <c r="AS24" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT24" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU24" t="n">
         <v>7.4</v>
@@ -5154,7 +5154,7 @@
         <v>15</v>
       </c>
       <c r="AW24" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX24" t="n">
         <v>11.5</v>
@@ -5166,7 +5166,7 @@
         <v>16</v>
       </c>
       <c r="BA24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB24" t="n">
         <v>23</v>
@@ -5178,17 +5178,17 @@
         <v>30</v>
       </c>
       <c r="BE24" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BF24" t="n">
         <v>13.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
         <v>1.97</v>
       </c>
       <c r="U25" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V25" t="n">
         <v>1.2</v>
@@ -5300,7 +5300,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AG25" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH25" t="n">
         <v>22</v>
@@ -5333,7 +5333,7 @@
         <v>15.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS25" t="n">
         <v>13</v>
@@ -5354,13 +5354,13 @@
         <v>9</v>
       </c>
       <c r="AY25" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ25" t="n">
         <v>17.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BB25" t="n">
         <v>16</v>
@@ -5369,20 +5369,20 @@
         <v>17</v>
       </c>
       <c r="BD25" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BE25" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF25" t="n">
         <v>11</v>
       </c>
       <c r="BG25" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -5613,7 +5613,7 @@
         <v>2.38</v>
       </c>
       <c r="H27" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I27" t="n">
         <v>3.55</v>
@@ -5706,7 +5706,7 @@
         <v>42</v>
       </c>
       <c r="AM27" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN27" t="n">
         <v>23</v>
@@ -5718,7 +5718,7 @@
         <v>11</v>
       </c>
       <c r="AQ27" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR27" t="n">
         <v>21</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5810,7 @@
         <v>2.5</v>
       </c>
       <c r="I28" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J28" t="n">
         <v>3.35</v>
@@ -5942,7 +5942,7 @@
         <v>17.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB28" t="n">
         <v>50</v>
@@ -5951,7 +5951,7 @@
         <v>36</v>
       </c>
       <c r="BD28" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BE28" t="n">
         <v>38</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
@@ -760,13 +760,13 @@
         <v>1.59</v>
       </c>
       <c r="G2" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H2" t="n">
         <v>6.4</v>
       </c>
       <c r="I2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J2" t="n">
         <v>3.8</v>
@@ -775,7 +775,7 @@
         <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="M2" t="n">
         <v>1.08</v>
@@ -805,7 +805,7 @@
         <v>1.8</v>
       </c>
       <c r="V2" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W2" t="n">
         <v>2.42</v>
@@ -877,10 +877,10 @@
         <v>4.9</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV2" t="n">
         <v>20</v>
@@ -895,7 +895,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>18.5</v>
+        <v>4.2</v>
       </c>
       <c r="BA2" t="n">
         <v>4.8</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G3" t="n">
         <v>2.58</v>
@@ -969,7 +969,7 @@
         <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
@@ -978,13 +978,13 @@
         <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P3" t="n">
         <v>2.02</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R3" t="n">
         <v>1.4</v>
@@ -1023,7 +1023,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE3" t="n">
         <v>36</v>
@@ -1080,7 +1080,7 @@
         <v>11.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX3" t="n">
         <v>12.5</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="G4" t="n">
         <v>1.37</v>
@@ -1154,13 +1154,13 @@
         <v>12.5</v>
       </c>
       <c r="I4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J4" t="n">
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L4" t="n">
         <v>1.31</v>
@@ -1223,7 +1223,7 @@
         <v>330</v>
       </c>
       <c r="AF4" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG4" t="n">
         <v>11.5</v>
@@ -1238,7 +1238,7 @@
         <v>11</v>
       </c>
       <c r="AK4" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL4" t="n">
         <v>55</v>
@@ -1256,13 +1256,13 @@
         <v>14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AR4" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AT4" t="n">
         <v>6.2</v>
@@ -1271,10 +1271,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.8</v>
+        <v>34</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AX4" t="n">
         <v>6.2</v>
@@ -1283,32 +1283,32 @@
         <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BB4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BC4" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.7</v>
+        <v>34</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BF4" t="n">
         <v>5.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -1342,55 +1342,55 @@
         <v>3.15</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="H5" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="J5" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L5" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="M5" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N5" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="P5" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="R5" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
         <v>5.6</v>
       </c>
       <c r="T5" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="U5" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="V5" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W5" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X5" t="n">
         <v>8.199999999999999</v>
@@ -1402,7 +1402,7 @@
         <v>17</v>
       </c>
       <c r="AA5" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB5" t="n">
         <v>9.199999999999999</v>
@@ -1417,46 +1417,46 @@
         <v>44</v>
       </c>
       <c r="AF5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG5" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI5" t="n">
         <v>75</v>
       </c>
       <c r="AJ5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN5" t="n">
         <v>75</v>
       </c>
-      <c r="AK5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>85</v>
-      </c>
       <c r="AO5" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AQ5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR5" t="n">
         <v>6.6</v>
       </c>
-      <c r="AR5" t="n">
-        <v>6</v>
-      </c>
       <c r="AS5" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AT5" t="n">
         <v>7.6</v>
@@ -1465,44 +1465,44 @@
         <v>6</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>34</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX5" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AZ5" t="n">
         <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BE5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG5" t="n">
         <v>9</v>
       </c>
-      <c r="BF5" t="n">
-        <v>50</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>8</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -1539,16 +1539,16 @@
         <v>3.65</v>
       </c>
       <c r="H6" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="I6" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="J6" t="n">
         <v>2.74</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="L6" t="n">
         <v>1.66</v>
@@ -1560,13 +1560,13 @@
         <v>2.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="P6" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R6" t="n">
         <v>1.15</v>
@@ -1578,13 +1578,13 @@
         <v>2.28</v>
       </c>
       <c r="U6" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V6" t="n">
         <v>1.52</v>
       </c>
       <c r="W6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X6" t="n">
         <v>7.2</v>
@@ -1599,7 +1599,7 @@
         <v>60</v>
       </c>
       <c r="AB6" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AC6" t="n">
         <v>7</v>
@@ -1620,22 +1620,22 @@
         <v>30</v>
       </c>
       <c r="AI6" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ6" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AK6" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AL6" t="n">
         <v>120</v>
       </c>
       <c r="AM6" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AN6" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AO6" t="n">
         <v>60</v>
@@ -1650,7 +1650,7 @@
         <v>14</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT6" t="n">
         <v>7.6</v>
@@ -1671,32 +1671,32 @@
         <v>14</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -1727,34 +1727,34 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I7" t="n">
         <v>2.88</v>
       </c>
-      <c r="G7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2.72</v>
-      </c>
       <c r="J7" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L7" t="n">
         <v>1.39</v>
       </c>
       <c r="M7" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P7" t="n">
         <v>1.84</v>
@@ -1763,22 +1763,22 @@
         <v>1.94</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S7" t="n">
         <v>3.25</v>
       </c>
       <c r="T7" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U7" t="n">
         <v>2.24</v>
       </c>
       <c r="V7" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="W7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -1796,7 +1796,7 @@
         <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD7" t="n">
         <v>970</v>
@@ -1823,7 +1823,7 @@
         <v>36</v>
       </c>
       <c r="AL7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM7" t="n">
         <v>85</v>
@@ -1838,13 +1838,13 @@
         <v>9.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AT7" t="n">
         <v>8.6</v>
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AY7" t="n">
         <v>9</v>
@@ -1868,29 +1868,29 @@
         <v>10.5</v>
       </c>
       <c r="BA7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD7" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB7" t="n">
+      <c r="BE7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF7" t="n">
         <v>4.7</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BG7" t="n">
         <v>4.6</v>
       </c>
-      <c r="BD7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="G8" t="n">
         <v>8.800000000000001</v>
@@ -1930,7 +1930,7 @@
         <v>1.42</v>
       </c>
       <c r="I8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>4.7</v>
@@ -1963,13 +1963,13 @@
         <v>2.58</v>
       </c>
       <c r="T8" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U8" t="n">
         <v>2</v>
       </c>
       <c r="V8" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="W8" t="n">
         <v>1.12</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -2133,28 +2133,28 @@
         <v>5.1</v>
       </c>
       <c r="L9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N9" t="n">
         <v>1.01</v>
       </c>
-      <c r="M9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.05</v>
-      </c>
       <c r="O9" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P9" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="T9" t="n">
         <v>1.66</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
         <v>4.1</v>
       </c>
       <c r="L10" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2533,7 @@
         <v>1.42</v>
       </c>
       <c r="P11" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q11" t="n">
         <v>2.28</v>
@@ -2545,7 +2545,7 @@
         <v>4.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U11" t="n">
         <v>1.92</v>
@@ -2572,7 +2572,7 @@
         <v>8</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD11" t="n">
         <v>18</v>
@@ -2602,10 +2602,10 @@
         <v>46</v>
       </c>
       <c r="AM11" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN11" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO11" t="n">
         <v>100</v>
@@ -2620,22 +2620,22 @@
         <v>27</v>
       </c>
       <c r="AS11" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT11" t="n">
         <v>7.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV11" t="n">
         <v>16</v>
       </c>
       <c r="AW11" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
@@ -2644,7 +2644,7 @@
         <v>18.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB11" t="n">
         <v>22</v>
@@ -2656,17 +2656,17 @@
         <v>36</v>
       </c>
       <c r="BE11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BF11" t="n">
         <v>17</v>
       </c>
       <c r="BG11" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G12" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I12" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J12" t="n">
         <v>3.45</v>
@@ -2730,7 +2730,7 @@
         <v>1.93</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="R12" t="n">
         <v>1.34</v>
@@ -2745,22 +2745,22 @@
         <v>2.16</v>
       </c>
       <c r="V12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="X12" t="n">
         <v>14</v>
       </c>
       <c r="Y12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z12" t="n">
         <v>24</v>
       </c>
       <c r="AA12" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB12" t="n">
         <v>11</v>
@@ -2772,7 +2772,7 @@
         <v>15</v>
       </c>
       <c r="AE12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF12" t="n">
         <v>15.5</v>
@@ -2784,7 +2784,7 @@
         <v>17.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ12" t="n">
         <v>32</v>
@@ -2802,7 +2802,7 @@
         <v>21</v>
       </c>
       <c r="AO12" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP12" t="n">
         <v>12</v>
@@ -2811,10 +2811,10 @@
         <v>11.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AS12" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT12" t="n">
         <v>9.199999999999999</v>
@@ -2847,10 +2847,10 @@
         <v>22</v>
       </c>
       <c r="BD12" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BE12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF12" t="n">
         <v>16.5</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G13" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H13" t="n">
         <v>3.1</v>
@@ -2912,149 +2912,149 @@
         <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>2.18</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P13" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
         <v>1.67</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="S13" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U13" t="n">
         <v>2.34</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.01</v>
       </c>
       <c r="V13" t="n">
         <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -3091,10 +3091,10 @@
         <v>5.5</v>
       </c>
       <c r="H14" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="I14" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="J14" t="n">
         <v>3.55</v>
@@ -3115,7 +3115,7 @@
         <v>1.3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q14" t="n">
         <v>1.87</v>
@@ -3127,13 +3127,13 @@
         <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U14" t="n">
         <v>2.02</v>
       </c>
       <c r="V14" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="W14" t="n">
         <v>1.22</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="G15" t="n">
         <v>2.42</v>
@@ -3288,7 +3288,7 @@
         <v>3.05</v>
       </c>
       <c r="I15" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="J15" t="n">
         <v>3.1</v>
@@ -3327,7 +3327,7 @@
         <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
         <v>1.7</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
         <v>1.44</v>
       </c>
       <c r="T16" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U16" t="n">
         <v>1.63</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -3703,7 +3703,7 @@
         <v>2.06</v>
       </c>
       <c r="R17" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
         <v>3.75</v>
@@ -3718,7 +3718,7 @@
         <v>1.06</v>
       </c>
       <c r="W17" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="X17" t="n">
         <v>15.5</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>2.32</v>
       </c>
       <c r="G18" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H18" t="n">
         <v>2.72</v>
@@ -3882,7 +3882,7 @@
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
         <v>2.2</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -4058,10 +4058,10 @@
         <v>3.05</v>
       </c>
       <c r="G19" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H19" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I19" t="n">
         <v>3</v>
@@ -4070,7 +4070,7 @@
         <v>2.74</v>
       </c>
       <c r="K19" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L19" t="n">
         <v>1.56</v>
@@ -4079,19 +4079,19 @@
         <v>1.15</v>
       </c>
       <c r="N19" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="O19" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="P19" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="Q19" t="n">
         <v>2.96</v>
       </c>
       <c r="R19" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S19" t="n">
         <v>6.4</v>
@@ -4100,13 +4100,13 @@
         <v>2.22</v>
       </c>
       <c r="U19" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V19" t="n">
         <v>1.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X19" t="n">
         <v>8.4</v>
@@ -4151,10 +4151,10 @@
         <v>60</v>
       </c>
       <c r="AL19" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AM19" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AN19" t="n">
         <v>80</v>
@@ -4172,7 +4172,7 @@
         <v>15</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT19" t="n">
         <v>7.4</v>
@@ -4211,14 +4211,14 @@
         <v>9.4</v>
       </c>
       <c r="BF19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG19" t="n">
         <v>8.6</v>
       </c>
-      <c r="BG19" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -4252,19 +4252,19 @@
         <v>2.04</v>
       </c>
       <c r="G20" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H20" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="I20" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J20" t="n">
         <v>2.76</v>
       </c>
       <c r="K20" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L20" t="n">
         <v>1.61</v>
@@ -4273,16 +4273,16 @@
         <v>1.15</v>
       </c>
       <c r="N20" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="O20" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="P20" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="R20" t="n">
         <v>1.12</v>
@@ -4291,16 +4291,16 @@
         <v>7.2</v>
       </c>
       <c r="T20" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="U20" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="V20" t="n">
         <v>1.21</v>
       </c>
       <c r="W20" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="X20" t="n">
         <v>6.8</v>
@@ -4339,7 +4339,7 @@
         <v>190</v>
       </c>
       <c r="AJ20" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK20" t="n">
         <v>38</v>
@@ -4357,16 +4357,16 @@
         <v>290</v>
       </c>
       <c r="AP20" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AQ20" t="n">
         <v>9.4</v>
       </c>
       <c r="AR20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AS20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT20" t="n">
         <v>5</v>
@@ -4378,7 +4378,7 @@
         <v>20</v>
       </c>
       <c r="AW20" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX20" t="n">
         <v>9.4</v>
@@ -4387,10 +4387,10 @@
         <v>11</v>
       </c>
       <c r="AZ20" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB20" t="n">
         <v>8</v>
@@ -4399,20 +4399,20 @@
         <v>30</v>
       </c>
       <c r="BD20" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BE20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="G21" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H21" t="n">
         <v>3.3</v>
       </c>
       <c r="I21" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J21" t="n">
         <v>3.65</v>
@@ -4491,19 +4491,19 @@
         <v>2.28</v>
       </c>
       <c r="V21" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W21" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="X21" t="n">
         <v>970</v>
       </c>
       <c r="Y21" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA21" t="n">
         <v>60</v>
@@ -4518,7 +4518,7 @@
         <v>970</v>
       </c>
       <c r="AE21" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AF21" t="n">
         <v>970</v>
@@ -4548,19 +4548,19 @@
         <v>970</v>
       </c>
       <c r="AO21" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AP21" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AQ21" t="n">
         <v>12.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AS21" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AT21" t="n">
         <v>10</v>
@@ -4569,44 +4569,44 @@
         <v>7.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="AW21" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AX21" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AY21" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ21" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="BB21" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BD21" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF21" t="n">
         <v>13</v>
       </c>
       <c r="BG21" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="G22" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="H22" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="I22" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="J22" t="n">
         <v>3.45</v>
       </c>
       <c r="K22" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L22" t="n">
         <v>1.48</v>
@@ -4661,7 +4661,7 @@
         <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
         <v>1.42</v>
@@ -4670,46 +4670,46 @@
         <v>1.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R22" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S22" t="n">
         <v>4.3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U22" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="V22" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W22" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="X22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA22" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB22" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC22" t="n">
         <v>7.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE22" t="n">
         <v>55</v>
@@ -4727,10 +4727,10 @@
         <v>70</v>
       </c>
       <c r="AJ22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL22" t="n">
         <v>46</v>
@@ -4739,7 +4739,7 @@
         <v>130</v>
       </c>
       <c r="AN22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO22" t="n">
         <v>65</v>
@@ -4757,7 +4757,7 @@
         <v>34</v>
       </c>
       <c r="AT22" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AU22" t="n">
         <v>7.2</v>
@@ -4766,41 +4766,41 @@
         <v>15</v>
       </c>
       <c r="AW22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY22" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ22" t="n">
         <v>19</v>
       </c>
       <c r="BA22" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="BB22" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BC22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD22" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BE22" t="n">
         <v>42</v>
       </c>
       <c r="BF22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BG22" t="n">
         <v>55</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
         <v>1.26</v>
       </c>
       <c r="G23" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="H23" t="n">
         <v>10</v>
@@ -4855,22 +4855,22 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="O23" t="n">
         <v>1.36</v>
       </c>
       <c r="P23" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R23" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S23" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T23" t="n">
         <v>1.01</v>
@@ -4882,7 +4882,7 @@
         <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -5025,13 +5025,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G24" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="I24" t="n">
         <v>4.1</v>
@@ -5040,7 +5040,7 @@
         <v>3.6</v>
       </c>
       <c r="K24" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -5055,13 +5055,13 @@
         <v>1.31</v>
       </c>
       <c r="P24" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q24" t="n">
         <v>1.98</v>
       </c>
       <c r="R24" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
         <v>3.4</v>
@@ -5076,7 +5076,7 @@
         <v>1.32</v>
       </c>
       <c r="W24" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="X24" t="n">
         <v>14.5</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -5225,10 +5225,10 @@
         <v>1.77</v>
       </c>
       <c r="H25" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="I25" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J25" t="n">
         <v>3.8</v>
@@ -5240,7 +5240,7 @@
         <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N25" t="n">
         <v>3.7</v>
@@ -5249,10 +5249,10 @@
         <v>1.34</v>
       </c>
       <c r="P25" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R25" t="n">
         <v>1.34</v>
@@ -5261,7 +5261,7 @@
         <v>3.7</v>
       </c>
       <c r="T25" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U25" t="n">
         <v>1.97</v>
@@ -5276,7 +5276,7 @@
         <v>15.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z25" t="n">
         <v>46</v>
@@ -5294,7 +5294,7 @@
         <v>23</v>
       </c>
       <c r="AE25" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF25" t="n">
         <v>9.800000000000001</v>
@@ -5303,13 +5303,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI25" t="n">
         <v>100</v>
       </c>
       <c r="AJ25" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AK25" t="n">
         <v>18</v>
@@ -5318,7 +5318,7 @@
         <v>40</v>
       </c>
       <c r="AM25" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN25" t="n">
         <v>12</v>
@@ -5348,7 +5348,7 @@
         <v>19</v>
       </c>
       <c r="AW25" t="n">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="AX25" t="n">
         <v>9</v>
@@ -5357,10 +5357,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ25" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BB25" t="n">
         <v>16</v>
@@ -5378,11 +5378,11 @@
         <v>11</v>
       </c>
       <c r="BG25" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -5452,10 +5452,10 @@
         <v>1.44</v>
       </c>
       <c r="S26" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U26" t="n">
         <v>2.4</v>
@@ -5488,7 +5488,7 @@
         <v>12.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AF26" t="n">
         <v>19.5</v>
@@ -5497,7 +5497,7 @@
         <v>12</v>
       </c>
       <c r="AH26" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI26" t="n">
         <v>38</v>
@@ -5512,16 +5512,16 @@
         <v>38</v>
       </c>
       <c r="AM26" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN26" t="n">
         <v>22</v>
       </c>
       <c r="AO26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP26" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ26" t="n">
         <v>12</v>
@@ -5566,17 +5566,17 @@
         <v>32</v>
       </c>
       <c r="BE26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF26" t="n">
         <v>18.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -5637,7 +5637,7 @@
         <v>1.38</v>
       </c>
       <c r="P27" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q27" t="n">
         <v>2.18</v>
@@ -5706,7 +5706,7 @@
         <v>42</v>
       </c>
       <c r="AM27" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN27" t="n">
         <v>23</v>
@@ -5718,7 +5718,7 @@
         <v>11</v>
       </c>
       <c r="AQ27" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR27" t="n">
         <v>21</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5822,7 @@
         <v>1.47</v>
       </c>
       <c r="M28" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N28" t="n">
         <v>3.55</v>
@@ -5918,7 +5918,7 @@
         <v>13.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AT28" t="n">
         <v>11</v>
@@ -5942,7 +5942,7 @@
         <v>17.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB28" t="n">
         <v>50</v>
@@ -5951,7 +5951,7 @@
         <v>36</v>
       </c>
       <c r="BD28" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BE28" t="n">
         <v>38</v>
@@ -5960,11 +5960,11 @@
         <v>36</v>
       </c>
       <c r="BG28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="H2" t="n">
         <v>6.4</v>
@@ -805,10 +805,10 @@
         <v>1.8</v>
       </c>
       <c r="V2" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W2" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="X2" t="n">
         <v>15.5</v>
@@ -877,13 +877,13 @@
         <v>4.9</v>
       </c>
       <c r="AT2" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>20</v>
+        <v>4.3</v>
       </c>
       <c r="AW2" t="n">
         <v>4.8</v>
@@ -892,10 +892,10 @@
         <v>7</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.2</v>
+        <v>18.5</v>
       </c>
       <c r="BA2" t="n">
         <v>4.8</v>
@@ -913,14 +913,14 @@
         <v>4.9</v>
       </c>
       <c r="BF2" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG2" t="n">
         <v>4.9</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
         <v>1.87</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S4" t="n">
         <v>3.2</v>
@@ -1223,7 +1223,7 @@
         <v>330</v>
       </c>
       <c r="AF4" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AG4" t="n">
         <v>11.5</v>
@@ -1256,13 +1256,13 @@
         <v>14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AT4" t="n">
         <v>6.2</v>
@@ -1271,10 +1271,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV4" t="n">
-        <v>34</v>
+        <v>4.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AX4" t="n">
         <v>6.2</v>
@@ -1286,7 +1286,7 @@
         <v>4.7</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BB4" t="n">
         <v>8.800000000000001</v>
@@ -1298,17 +1298,17 @@
         <v>34</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF4" t="n">
         <v>5.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
         <v>1.13</v>
       </c>
       <c r="N5" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O5" t="n">
         <v>1.56</v>
@@ -1384,7 +1384,7 @@
         <v>2.12</v>
       </c>
       <c r="U5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V5" t="n">
         <v>1.53</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -1557,10 +1557,10 @@
         <v>1.16</v>
       </c>
       <c r="N6" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="P6" t="n">
         <v>1.43</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -1727,85 +1727,85 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="G7" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="H7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I7" t="n">
         <v>2.44</v>
       </c>
-      <c r="I7" t="n">
-        <v>2.88</v>
-      </c>
       <c r="J7" t="n">
-        <v>2.94</v>
+        <v>3.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="O7" t="n">
         <v>1.31</v>
       </c>
       <c r="P7" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="Q7" t="n">
         <v>1.94</v>
       </c>
       <c r="R7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S7" t="n">
         <v>3.25</v>
       </c>
       <c r="T7" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="U7" t="n">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="W7" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
       </c>
       <c r="Y7" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Z7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AA7" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AB7" t="n">
         <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="AD7" t="n">
         <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AF7" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AG7" t="n">
         <v>970</v>
@@ -1814,7 +1814,7 @@
         <v>970</v>
       </c>
       <c r="AI7" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="AJ7" t="n">
         <v>55</v>
@@ -1823,74 +1823,74 @@
         <v>36</v>
       </c>
       <c r="AL7" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AM7" t="n">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="AN7" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AO7" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AP7" t="n">
-        <v>9.4</v>
+        <v>4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="AR7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS7" t="n">
         <v>4.4</v>
       </c>
-      <c r="AS7" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AT7" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AV7" t="n">
         <v>11</v>
       </c>
       <c r="AW7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE7" t="n">
         <v>4.8</v>
       </c>
-      <c r="AX7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BF7" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
         <v>12</v>
       </c>
       <c r="AX8" t="n">
-        <v>7.6</v>
+        <v>55</v>
       </c>
       <c r="AY8" t="n">
         <v>6.8</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
         <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="T9" t="n">
         <v>1.66</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="G10" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H10" t="n">
         <v>2.26</v>
@@ -2321,7 +2321,7 @@
         <v>2.48</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
         <v>4.1</v>
@@ -2333,16 +2333,16 @@
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="O10" t="n">
         <v>1.24</v>
       </c>
       <c r="P10" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="R10" t="n">
         <v>1.48</v>
@@ -2360,28 +2360,28 @@
         <v>1.67</v>
       </c>
       <c r="W10" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X10" t="n">
         <v>24</v>
       </c>
       <c r="Y10" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AA10" t="n">
         <v>38</v>
       </c>
       <c r="AB10" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AD10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE10" t="n">
         <v>28</v>
@@ -2390,10 +2390,10 @@
         <v>29</v>
       </c>
       <c r="AG10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AH10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
         <v>40</v>
@@ -2408,7 +2408,7 @@
         <v>46</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN10" t="n">
         <v>30</v>
@@ -2417,62 +2417,62 @@
         <v>18</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.6</v>
+        <v>3.65</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.8</v>
+        <v>3.35</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.3</v>
+        <v>3.55</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.4</v>
+        <v>3.85</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="AU10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE10" t="n">
         <v>4.1</v>
       </c>
-      <c r="AV10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>7</v>
-      </c>
       <c r="BF10" t="n">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.4</v>
+        <v>3.45</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -2527,7 +2527,7 @@
         <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
         <v>1.42</v>
@@ -2536,7 +2536,7 @@
         <v>1.74</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R11" t="n">
         <v>1.27</v>
@@ -2545,10 +2545,10 @@
         <v>4.3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U11" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V11" t="n">
         <v>1.28</v>
@@ -2572,7 +2572,7 @@
         <v>8</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD11" t="n">
         <v>18</v>
@@ -2620,7 +2620,7 @@
         <v>27</v>
       </c>
       <c r="AS11" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT11" t="n">
         <v>7.2</v>
@@ -2632,7 +2632,7 @@
         <v>16</v>
       </c>
       <c r="AW11" t="n">
-        <v>14.5</v>
+        <v>55</v>
       </c>
       <c r="AX11" t="n">
         <v>10.5</v>
@@ -2656,17 +2656,17 @@
         <v>36</v>
       </c>
       <c r="BE11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BF11" t="n">
         <v>17</v>
       </c>
       <c r="BG11" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2715,7 @@
         <v>3.55</v>
       </c>
       <c r="L12" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
@@ -2733,7 +2733,7 @@
         <v>1.94</v>
       </c>
       <c r="R12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S12" t="n">
         <v>3.4</v>
@@ -2850,7 +2850,7 @@
         <v>10</v>
       </c>
       <c r="BE12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF12" t="n">
         <v>16.5</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2909,7 @@
         <v>4.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
@@ -2930,7 +2930,7 @@
         <v>1.48</v>
       </c>
       <c r="S13" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="T13" t="n">
         <v>1.61</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -3088,13 +3088,13 @@
         <v>4.4</v>
       </c>
       <c r="G14" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H14" t="n">
         <v>1.79</v>
       </c>
       <c r="I14" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="J14" t="n">
         <v>3.55</v>
@@ -3109,7 +3109,7 @@
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O14" t="n">
         <v>1.3</v>
@@ -3133,10 +3133,10 @@
         <v>2.02</v>
       </c>
       <c r="V14" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="W14" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X14" t="n">
         <v>17.5</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -3282,10 +3282,10 @@
         <v>1.99</v>
       </c>
       <c r="G15" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H15" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
         <v>4</v>
@@ -3294,7 +3294,7 @@
         <v>3.1</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1</v>
+        <v>85</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -3327,10 +3327,10 @@
         <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>1.07</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="H16" t="n">
         <v>1.04</v>
@@ -3485,7 +3485,7 @@
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -3497,34 +3497,34 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="P16" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="R16" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="S16" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T16" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="U16" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="V16" t="n">
         <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3581,62 +3581,62 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA16" t="n">
         <v>5.9</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>6.2</v>
       </c>
       <c r="BB16" t="n">
         <v>7.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -3667,64 +3667,64 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="G17" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="I17" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="J17" t="n">
         <v>4.2</v>
       </c>
       <c r="K17" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V17" t="n">
         <v>1.07</v>
       </c>
-      <c r="N17" t="n">
+      <c r="W17" t="n">
         <v>3.15</v>
       </c>
-      <c r="O17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W17" t="n">
-        <v>3.35</v>
-      </c>
       <c r="X17" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="Y17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z17" t="n">
         <v>160</v>
@@ -3733,10 +3733,10 @@
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AD17" t="n">
         <v>65</v>
@@ -3757,7 +3757,7 @@
         <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AK17" t="n">
         <v>22</v>
@@ -3769,68 +3769,68 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AS17" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AT17" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AV17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW17" t="n">
         <v>6.4</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>7</v>
       </c>
       <c r="AX17" t="n">
         <v>5.7</v>
       </c>
       <c r="AY17" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AZ17" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BA17" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BB17" t="n">
-        <v>4.3</v>
+        <v>9</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.4</v>
+        <v>15.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BE17" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -3882,10 +3882,10 @@
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N18" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="O18" t="n">
         <v>1.22</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4067,7 @@
         <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="K19" t="n">
         <v>3.05</v>
@@ -4112,7 +4112,7 @@
         <v>8.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z19" t="n">
         <v>17.5</v>
@@ -4121,7 +4121,7 @@
         <v>55</v>
       </c>
       <c r="AB19" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC19" t="n">
         <v>7</v>
@@ -4130,22 +4130,22 @@
         <v>14.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF19" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH19" t="n">
         <v>26</v>
       </c>
       <c r="AI19" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AJ19" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK19" t="n">
         <v>60</v>
@@ -4157,7 +4157,7 @@
         <v>260</v>
       </c>
       <c r="AN19" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AO19" t="n">
         <v>65</v>
@@ -4172,7 +4172,7 @@
         <v>15</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT19" t="n">
         <v>7.4</v>
@@ -4184,7 +4184,7 @@
         <v>12.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX19" t="n">
         <v>17.5</v>
@@ -4193,32 +4193,32 @@
         <v>13.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA19" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB19" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC19" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD19" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BF19" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
         <v>2.22</v>
       </c>
       <c r="H20" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I20" t="n">
         <v>5.8</v>
@@ -4264,7 +4264,7 @@
         <v>2.76</v>
       </c>
       <c r="K20" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L20" t="n">
         <v>1.61</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="G21" t="n">
         <v>2.24</v>
       </c>
       <c r="H21" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I21" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="J21" t="n">
         <v>3.65</v>
@@ -4491,7 +4491,7 @@
         <v>2.28</v>
       </c>
       <c r="V21" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W21" t="n">
         <v>1.81</v>
@@ -4560,7 +4560,7 @@
         <v>7</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT21" t="n">
         <v>10</v>
@@ -4569,31 +4569,31 @@
         <v>7.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AW21" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AX21" t="n">
         <v>6</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BA21" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BB21" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC21" t="n">
         <v>6.8</v>
       </c>
       <c r="BD21" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE21" t="n">
         <v>8.800000000000001</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -4637,25 +4637,25 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G22" t="n">
         <v>2.18</v>
       </c>
       <c r="H22" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I22" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J22" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K22" t="n">
         <v>3.55</v>
       </c>
       <c r="L22" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M22" t="n">
         <v>1.09</v>
@@ -4679,13 +4679,13 @@
         <v>4.3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U22" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="V22" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W22" t="n">
         <v>1.84</v>
@@ -4694,7 +4694,7 @@
         <v>11</v>
       </c>
       <c r="Y22" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z22" t="n">
         <v>26</v>
@@ -4703,7 +4703,7 @@
         <v>85</v>
       </c>
       <c r="AB22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC22" t="n">
         <v>7.6</v>
@@ -4736,7 +4736,7 @@
         <v>46</v>
       </c>
       <c r="AM22" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
         <v>21</v>
@@ -4757,7 +4757,7 @@
         <v>34</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU22" t="n">
         <v>7.2</v>
@@ -4766,13 +4766,13 @@
         <v>15</v>
       </c>
       <c r="AW22" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="AX22" t="n">
         <v>11</v>
       </c>
       <c r="AY22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ22" t="n">
         <v>19</v>
@@ -4787,7 +4787,7 @@
         <v>23</v>
       </c>
       <c r="BD22" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE22" t="n">
         <v>42</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -4831,64 +4831,64 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="G23" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="H23" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="K23" t="n">
-        <v>9.4</v>
+        <v>5.9</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>2.38</v>
+        <v>2.84</v>
       </c>
       <c r="O23" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P23" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="R23" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="S23" t="n">
-        <v>2.78</v>
+        <v>3.55</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W23" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Z23" t="n">
         <v>1000</v>
@@ -4897,104 +4897,104 @@
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AE23" t="n">
         <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AI23" t="n">
         <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM23" t="n">
         <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO23" t="n">
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.03</v>
+        <v>2.96</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -5025,19 +5025,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G24" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H24" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I24" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K24" t="n">
         <v>3.75</v>
@@ -5055,7 +5055,7 @@
         <v>1.31</v>
       </c>
       <c r="P24" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q24" t="n">
         <v>1.98</v>
@@ -5067,16 +5067,16 @@
         <v>3.4</v>
       </c>
       <c r="T24" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U24" t="n">
         <v>2.18</v>
       </c>
       <c r="V24" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W24" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="X24" t="n">
         <v>14.5</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -5219,13 +5219,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G25" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="H25" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I25" t="n">
         <v>5.9</v>
@@ -5249,13 +5249,13 @@
         <v>1.34</v>
       </c>
       <c r="P25" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q25" t="n">
         <v>2.04</v>
       </c>
       <c r="R25" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
         <v>3.7</v>
@@ -5273,43 +5273,43 @@
         <v>2.28</v>
       </c>
       <c r="X25" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Y25" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z25" t="n">
         <v>46</v>
       </c>
       <c r="AA25" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC25" t="n">
         <v>8.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE25" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AF25" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG25" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AH25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>21</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>20</v>
       </c>
       <c r="AK25" t="n">
         <v>18</v>
@@ -5321,10 +5321,10 @@
         <v>150</v>
       </c>
       <c r="AN25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP25" t="n">
         <v>12</v>
@@ -5333,7 +5333,7 @@
         <v>15.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>11.5</v>
+        <v>38</v>
       </c>
       <c r="AS25" t="n">
         <v>13</v>
@@ -5348,7 +5348,7 @@
         <v>19</v>
       </c>
       <c r="AW25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX25" t="n">
         <v>9</v>
@@ -5360,7 +5360,7 @@
         <v>18.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BB25" t="n">
         <v>16</v>
@@ -5369,7 +5369,7 @@
         <v>17</v>
       </c>
       <c r="BD25" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="BE25" t="n">
         <v>13</v>
@@ -5378,11 +5378,11 @@
         <v>11</v>
       </c>
       <c r="BG25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -5446,16 +5446,16 @@
         <v>2.12</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="R26" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T26" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U26" t="n">
         <v>2.4</v>
@@ -5545,7 +5545,7 @@
         <v>25</v>
       </c>
       <c r="AX26" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY26" t="n">
         <v>11</v>
@@ -5557,7 +5557,7 @@
         <v>32</v>
       </c>
       <c r="BB26" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BC26" t="n">
         <v>25</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -5703,7 +5703,7 @@
         <v>27</v>
       </c>
       <c r="AL27" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -5822,13 +5822,13 @@
         <v>1.47</v>
       </c>
       <c r="M28" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N28" t="n">
         <v>3.55</v>
       </c>
       <c r="O28" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P28" t="n">
         <v>1.83</v>
@@ -5876,7 +5876,7 @@
         <v>11.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF28" t="n">
         <v>21</v>
@@ -5918,7 +5918,7 @@
         <v>13.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT28" t="n">
         <v>11</v>
@@ -5942,7 +5942,7 @@
         <v>17.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB28" t="n">
         <v>50</v>
@@ -5951,20 +5951,20 @@
         <v>36</v>
       </c>
       <c r="BD28" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BE28" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="BF28" t="n">
         <v>36</v>
       </c>
       <c r="BG28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="G2" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="H2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L2" t="n">
         <v>1.38</v>
@@ -787,7 +787,7 @@
         <v>1.36</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q2" t="n">
         <v>2.04</v>
@@ -796,43 +796,43 @@
         <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V2" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W2" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="X2" t="n">
         <v>15.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z2" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AA2" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD2" t="n">
         <v>32</v>
       </c>
       <c r="AE2" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AF2" t="n">
         <v>10.5</v>
@@ -844,7 +844,7 @@
         <v>29</v>
       </c>
       <c r="AI2" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AJ2" t="n">
         <v>18.5</v>
@@ -853,74 +853,74 @@
         <v>22</v>
       </c>
       <c r="AL2" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AN2" t="n">
         <v>13.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AP2" t="n">
         <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW2" t="n">
         <v>4.6</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>4.8</v>
       </c>
       <c r="AX2" t="n">
         <v>7</v>
       </c>
       <c r="AY2" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BB2" t="n">
         <v>12</v>
       </c>
       <c r="BC2" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BF2" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="G3" t="n">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="H3" t="n">
-        <v>2.94</v>
+        <v>2.74</v>
       </c>
       <c r="I3" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="J3" t="n">
         <v>3.45</v>
@@ -972,7 +972,7 @@
         <v>1.32</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
         <v>4</v>
@@ -990,7 +990,7 @@
         <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
         <v>1.65</v>
@@ -999,10 +999,10 @@
         <v>2.24</v>
       </c>
       <c r="V3" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W3" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="X3" t="n">
         <v>19.5</v>
@@ -1023,13 +1023,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE3" t="n">
         <v>36</v>
       </c>
       <c r="AF3" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AG3" t="n">
         <v>12.5</v>
@@ -1038,13 +1038,13 @@
         <v>19</v>
       </c>
       <c r="AI3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AK3" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AL3" t="n">
         <v>38</v>
@@ -1056,7 +1056,7 @@
         <v>20</v>
       </c>
       <c r="AO3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP3" t="n">
         <v>13</v>
@@ -1065,10 +1065,10 @@
         <v>11.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
         <v>10</v>
@@ -1080,7 +1080,7 @@
         <v>11.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AX3" t="n">
         <v>12.5</v>
@@ -1092,29 +1092,29 @@
         <v>13.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BB3" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BC3" t="n">
         <v>20</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF3" t="n">
         <v>14.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.9</v>
+        <v>20</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="G4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="H4" t="n">
         <v>12.5</v>
       </c>
       <c r="I4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J4" t="n">
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L4" t="n">
         <v>1.31</v>
@@ -1169,7 +1169,7 @@
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O4" t="n">
         <v>1.29</v>
@@ -1184,10 +1184,10 @@
         <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="U4" t="n">
         <v>1.64</v>
@@ -1196,13 +1196,13 @@
         <v>1.07</v>
       </c>
       <c r="W4" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="X4" t="n">
         <v>20</v>
       </c>
       <c r="Y4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z4" t="n">
         <v>150</v>
@@ -1211,7 +1211,7 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AC4" t="n">
         <v>15</v>
@@ -1238,7 +1238,7 @@
         <v>11</v>
       </c>
       <c r="AK4" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL4" t="n">
         <v>55</v>
@@ -1256,13 +1256,13 @@
         <v>14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.6</v>
+        <v>24</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AT4" t="n">
         <v>6.2</v>
@@ -1271,10 +1271,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AX4" t="n">
         <v>6.2</v>
@@ -1283,10 +1283,10 @@
         <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BB4" t="n">
         <v>8.800000000000001</v>
@@ -1298,17 +1298,17 @@
         <v>34</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF4" t="n">
         <v>5.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -1342,37 +1342,37 @@
         <v>3.15</v>
       </c>
       <c r="G5" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="H5" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="I5" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J5" t="n">
         <v>2.88</v>
       </c>
-      <c r="J5" t="n">
-        <v>2.82</v>
-      </c>
       <c r="K5" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="L5" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="M5" t="n">
         <v>1.13</v>
       </c>
       <c r="N5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q5" t="n">
         <v>2.52</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.66</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
@@ -1381,40 +1381,40 @@
         <v>5.6</v>
       </c>
       <c r="T5" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="U5" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="V5" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y5" t="n">
         <v>8</v>
       </c>
       <c r="Z5" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA5" t="n">
         <v>48</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF5" t="n">
         <v>22</v>
@@ -1426,7 +1426,7 @@
         <v>24</v>
       </c>
       <c r="AI5" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ5" t="n">
         <v>70</v>
@@ -1441,7 +1441,7 @@
         <v>220</v>
       </c>
       <c r="AN5" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AO5" t="n">
         <v>50</v>
@@ -1453,56 +1453,56 @@
         <v>7</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AS5" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU5" t="n">
         <v>6</v>
       </c>
       <c r="AV5" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AW5" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AY5" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AZ5" t="n">
         <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.6</v>
+        <v>48</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE5" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG5" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>3.3</v>
       </c>
       <c r="G6" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H6" t="n">
         <v>2.7</v>
@@ -1548,37 +1548,37 @@
         <v>2.74</v>
       </c>
       <c r="K6" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="L6" t="n">
         <v>1.66</v>
       </c>
       <c r="M6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="R6" t="n">
         <v>1.16</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.15</v>
       </c>
       <c r="S6" t="n">
         <v>6.4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="U6" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="V6" t="n">
         <v>1.52</v>
@@ -1587,10 +1587,10 @@
         <v>1.38</v>
       </c>
       <c r="X6" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="Z6" t="n">
         <v>19</v>
@@ -1599,10 +1599,10 @@
         <v>60</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AC6" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AD6" t="n">
         <v>16.5</v>
@@ -1626,13 +1626,13 @@
         <v>90</v>
       </c>
       <c r="AK6" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AL6" t="n">
         <v>120</v>
       </c>
       <c r="AM6" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AN6" t="n">
         <v>110</v>
@@ -1644,13 +1644,13 @@
         <v>6.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AR6" t="n">
         <v>14</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="AT6" t="n">
         <v>7.6</v>
@@ -1671,32 +1671,32 @@
         <v>14</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.8</v>
+        <v>5.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.8</v>
+        <v>5.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.05</v>
+        <v>2.64</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="H7" t="n">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="I7" t="n">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K7" t="n">
         <v>4.4</v>
@@ -1751,146 +1751,146 @@
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="R7" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S7" t="n">
         <v>3.25</v>
       </c>
       <c r="T7" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
       </c>
       <c r="Y7" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AA7" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AB7" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AD7" t="n">
         <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AF7" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AG7" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH7" t="n">
         <v>970</v>
       </c>
       <c r="AI7" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AJ7" t="n">
         <v>55</v>
       </c>
       <c r="AK7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL7" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AM7" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AN7" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AO7" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AP7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AU7" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV7" t="n">
         <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AX7" t="n">
         <v>4.2</v>
       </c>
       <c r="AY7" t="n">
-        <v>10.5</v>
+        <v>3.75</v>
       </c>
       <c r="AZ7" t="n">
         <v>4.1</v>
       </c>
       <c r="BA7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC7" t="n">
         <v>4.5</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4.4</v>
       </c>
       <c r="BD7" t="n">
         <v>4.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1996,7 @@
         <v>10.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AF8" t="n">
         <v>75</v>
@@ -2026,10 +2026,10 @@
         <v>140</v>
       </c>
       <c r="AO8" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AP8" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ8" t="n">
         <v>8.199999999999999</v>
@@ -2041,7 +2041,7 @@
         <v>11.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU8" t="n">
         <v>9.800000000000001</v>
@@ -2056,35 +2056,35 @@
         <v>55</v>
       </c>
       <c r="AY8" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC8" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BD8" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BG8" t="n">
         <v>5.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         <v>5.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="K9" t="n">
         <v>5.1</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -2321,19 +2321,19 @@
         <v>2.48</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
         <v>4.1</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
         <v>1.24</v>
@@ -2360,7 +2360,7 @@
         <v>1.67</v>
       </c>
       <c r="W10" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X10" t="n">
         <v>24</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>2.06</v>
       </c>
       <c r="G11" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H11" t="n">
         <v>4.2</v>
@@ -2527,16 +2527,16 @@
         <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P11" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R11" t="n">
         <v>1.27</v>
@@ -2545,16 +2545,16 @@
         <v>4.3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="U11" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V11" t="n">
         <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="X11" t="n">
         <v>11</v>
@@ -2608,7 +2608,7 @@
         <v>19.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AP11" t="n">
         <v>10</v>
@@ -2653,7 +2653,7 @@
         <v>21</v>
       </c>
       <c r="BD11" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BE11" t="n">
         <v>16</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -2697,40 +2697,40 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G12" t="n">
         <v>2.42</v>
       </c>
       <c r="H12" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I12" t="n">
         <v>3.5</v>
       </c>
       <c r="J12" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
         <v>3.55</v>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P12" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R12" t="n">
         <v>1.35</v>
@@ -2739,7 +2739,7 @@
         <v>3.4</v>
       </c>
       <c r="T12" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U12" t="n">
         <v>2.16</v>
@@ -2760,13 +2760,13 @@
         <v>24</v>
       </c>
       <c r="AA12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB12" t="n">
         <v>11</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD12" t="n">
         <v>15</v>
@@ -2799,7 +2799,7 @@
         <v>95</v>
       </c>
       <c r="AN12" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AO12" t="n">
         <v>38</v>
@@ -2814,7 +2814,7 @@
         <v>21</v>
       </c>
       <c r="AS12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT12" t="n">
         <v>9.199999999999999</v>
@@ -2847,10 +2847,10 @@
         <v>22</v>
       </c>
       <c r="BD12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF12" t="n">
         <v>16.5</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="G14" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="H14" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="I14" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="J14" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L14" t="n">
         <v>1.34</v>
@@ -3133,10 +3133,10 @@
         <v>2.02</v>
       </c>
       <c r="V14" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="W14" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X14" t="n">
         <v>17.5</v>
@@ -3145,10 +3145,10 @@
         <v>10.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB14" t="n">
         <v>19</v>
@@ -3190,7 +3190,7 @@
         <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AP14" t="n">
         <v>11.5</v>
@@ -3217,7 +3217,7 @@
         <v>15.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AY14" t="n">
         <v>13.5</v>
@@ -3226,29 +3226,29 @@
         <v>14</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC14" t="n">
         <v>5.2</v>
       </c>
-      <c r="BC14" t="n">
-        <v>5</v>
-      </c>
       <c r="BD14" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BG14" t="n">
         <v>10</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="G15" t="n">
         <v>2.4</v>
@@ -3288,13 +3288,13 @@
         <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="J15" t="n">
         <v>3.1</v>
       </c>
       <c r="K15" t="n">
-        <v>85</v>
+        <v>4.1</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3524,7 @@
         <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -3667,170 +3667,170 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="G17" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="H17" t="n">
         <v>11.5</v>
       </c>
       <c r="I17" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="J17" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="L17" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="M17" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="O17" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="P17" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.28</v>
+        <v>1.96</v>
       </c>
       <c r="R17" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="T17" t="n">
-        <v>2.68</v>
+        <v>2.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="V17" t="n">
         <v>1.07</v>
       </c>
       <c r="W17" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="X17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y17" t="n">
         <v>32</v>
       </c>
       <c r="Z17" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AC17" t="n">
         <v>970</v>
       </c>
       <c r="AD17" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG17" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AI17" t="n">
         <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL17" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="AQ17" t="n">
         <v>5.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AS17" t="n">
         <v>6.6</v>
       </c>
       <c r="AT17" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AU17" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AW17" t="n">
         <v>6.4</v>
       </c>
       <c r="AX17" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AY17" t="n">
         <v>4.2</v>
       </c>
       <c r="AZ17" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BA17" t="n">
         <v>6.4</v>
       </c>
       <c r="BB17" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BC17" t="n">
-        <v>15.5</v>
+        <v>4.9</v>
       </c>
       <c r="BD17" t="n">
         <v>6</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BG17" t="n">
         <v>6.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>2.32</v>
       </c>
       <c r="G18" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="H18" t="n">
         <v>2.72</v>
@@ -3885,7 +3885,7 @@
         <v>1.02</v>
       </c>
       <c r="N18" t="n">
-        <v>3.4</v>
+        <v>2.34</v>
       </c>
       <c r="O18" t="n">
         <v>1.22</v>
@@ -3912,7 +3912,7 @@
         <v>1.45</v>
       </c>
       <c r="W18" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="X18" t="n">
         <v>25</v>
@@ -3981,7 +3981,7 @@
         <v>4</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.4</v>
+        <v>10</v>
       </c>
       <c r="AU18" t="n">
         <v>7</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -4055,19 +4055,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G19" t="n">
         <v>3.3</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="J19" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K19" t="n">
         <v>3.05</v>
@@ -4103,7 +4103,7 @@
         <v>1.71</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W19" t="n">
         <v>1.43</v>
@@ -4163,7 +4163,7 @@
         <v>65</v>
       </c>
       <c r="AP19" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AQ19" t="n">
         <v>6.8</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -4252,19 +4252,19 @@
         <v>2.04</v>
       </c>
       <c r="G20" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H20" t="n">
         <v>4.9</v>
       </c>
       <c r="I20" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J20" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="K20" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L20" t="n">
         <v>1.61</v>
@@ -4375,7 +4375,7 @@
         <v>6.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>20</v>
+        <v>7.6</v>
       </c>
       <c r="AW20" t="n">
         <v>10</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G21" t="n">
         <v>2.24</v>
@@ -4452,7 +4452,7 @@
         <v>3.35</v>
       </c>
       <c r="I21" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="J21" t="n">
         <v>3.65</v>
@@ -4491,7 +4491,7 @@
         <v>2.28</v>
       </c>
       <c r="V21" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W21" t="n">
         <v>1.81</v>
@@ -4500,7 +4500,7 @@
         <v>970</v>
       </c>
       <c r="Y21" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="Z21" t="n">
         <v>26</v>
@@ -4533,7 +4533,7 @@
         <v>44</v>
       </c>
       <c r="AJ21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK21" t="n">
         <v>23</v>
@@ -4542,7 +4542,7 @@
         <v>34</v>
       </c>
       <c r="AM21" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN21" t="n">
         <v>970</v>
@@ -4551,16 +4551,16 @@
         <v>32</v>
       </c>
       <c r="AP21" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT21" t="n">
         <v>10</v>
@@ -4569,44 +4569,44 @@
         <v>7.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AW21" t="n">
-        <v>7.8</v>
+        <v>30</v>
       </c>
       <c r="AX21" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AY21" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BA21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB21" t="n">
         <v>7.8</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BC21" t="n">
         <v>7.2</v>
       </c>
-      <c r="BC21" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BD21" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE21" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF21" t="n">
         <v>13</v>
       </c>
       <c r="BG21" t="n">
-        <v>7.4</v>
+        <v>26</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -4637,25 +4637,25 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="G22" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="H22" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="I22" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J22" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K22" t="n">
         <v>3.5</v>
       </c>
-      <c r="K22" t="n">
-        <v>3.55</v>
-      </c>
       <c r="L22" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M22" t="n">
         <v>1.09</v>
@@ -4667,40 +4667,40 @@
         <v>1.42</v>
       </c>
       <c r="P22" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q22" t="n">
         <v>2.28</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S22" t="n">
         <v>4.3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U22" t="n">
         <v>1.97</v>
       </c>
       <c r="V22" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W22" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="X22" t="n">
         <v>11</v>
       </c>
       <c r="Y22" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA22" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB22" t="n">
         <v>8.4</v>
@@ -4709,7 +4709,7 @@
         <v>7.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE22" t="n">
         <v>55</v>
@@ -4727,10 +4727,10 @@
         <v>70</v>
       </c>
       <c r="AJ22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL22" t="n">
         <v>46</v>
@@ -4739,7 +4739,7 @@
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO22" t="n">
         <v>65</v>
@@ -4751,7 +4751,7 @@
         <v>11</v>
       </c>
       <c r="AR22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS22" t="n">
         <v>34</v>
@@ -4766,7 +4766,7 @@
         <v>15</v>
       </c>
       <c r="AW22" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AX22" t="n">
         <v>11</v>
@@ -4778,7 +4778,7 @@
         <v>19</v>
       </c>
       <c r="BA22" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BB22" t="n">
         <v>24</v>
@@ -4796,11 +4796,11 @@
         <v>19</v>
       </c>
       <c r="BG22" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -4834,16 +4834,16 @@
         <v>1.28</v>
       </c>
       <c r="G23" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="H23" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="I23" t="n">
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="K23" t="n">
         <v>5.9</v>
@@ -4882,7 +4882,7 @@
         <v>1.04</v>
       </c>
       <c r="W23" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="X23" t="n">
         <v>14.5</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G24" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="H24" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J24" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K24" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -5055,16 +5055,16 @@
         <v>1.31</v>
       </c>
       <c r="P24" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R24" t="n">
         <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T24" t="n">
         <v>1.79</v>
@@ -5073,31 +5073,31 @@
         <v>2.18</v>
       </c>
       <c r="V24" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W24" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="X24" t="n">
         <v>14.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z24" t="n">
         <v>28</v>
       </c>
       <c r="AA24" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB24" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD24" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE24" t="n">
         <v>48</v>
@@ -5112,10 +5112,10 @@
         <v>18</v>
       </c>
       <c r="AI24" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK24" t="n">
         <v>23</v>
@@ -5127,10 +5127,10 @@
         <v>95</v>
       </c>
       <c r="AN24" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP24" t="n">
         <v>13</v>
@@ -5139,22 +5139,22 @@
         <v>13</v>
       </c>
       <c r="AR24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS24" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AT24" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU24" t="n">
         <v>7.4</v>
       </c>
       <c r="AV24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW24" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="AX24" t="n">
         <v>11.5</v>
@@ -5166,7 +5166,7 @@
         <v>16</v>
       </c>
       <c r="BA24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB24" t="n">
         <v>23</v>
@@ -5178,17 +5178,17 @@
         <v>30</v>
       </c>
       <c r="BE24" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BF24" t="n">
         <v>13.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -5222,19 +5222,19 @@
         <v>1.75</v>
       </c>
       <c r="G25" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H25" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I25" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J25" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K25" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -5246,22 +5246,22 @@
         <v>3.7</v>
       </c>
       <c r="O25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R25" t="n">
         <v>1.34</v>
       </c>
-      <c r="P25" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.35</v>
-      </c>
       <c r="S25" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T25" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U25" t="n">
         <v>1.97</v>
@@ -5279,7 +5279,7 @@
         <v>17.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA25" t="n">
         <v>170</v>
@@ -5306,28 +5306,28 @@
         <v>22</v>
       </c>
       <c r="AI25" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AJ25" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AK25" t="n">
         <v>18</v>
       </c>
       <c r="AL25" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM25" t="n">
         <v>150</v>
       </c>
       <c r="AN25" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO25" t="n">
         <v>120</v>
       </c>
       <c r="AP25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ25" t="n">
         <v>15.5</v>
@@ -5336,7 +5336,7 @@
         <v>38</v>
       </c>
       <c r="AS25" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AT25" t="n">
         <v>7.4</v>
@@ -5348,7 +5348,7 @@
         <v>19</v>
       </c>
       <c r="AW25" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AX25" t="n">
         <v>9</v>
@@ -5360,7 +5360,7 @@
         <v>18.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BB25" t="n">
         <v>16</v>
@@ -5372,17 +5372,17 @@
         <v>27</v>
       </c>
       <c r="BE25" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BF25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="G26" t="n">
         <v>2.74</v>
@@ -5431,7 +5431,7 @@
         <v>3.7</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M26" t="n">
         <v>1.06</v>
@@ -5446,22 +5446,22 @@
         <v>2.12</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R26" t="n">
         <v>1.45</v>
       </c>
       <c r="S26" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="T26" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U26" t="n">
         <v>2.4</v>
       </c>
       <c r="V26" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W26" t="n">
         <v>1.57</v>
@@ -5560,7 +5560,7 @@
         <v>34</v>
       </c>
       <c r="BC26" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="BD26" t="n">
         <v>32</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -5607,16 +5607,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="G27" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="H27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I27" t="n">
         <v>3.45</v>
-      </c>
-      <c r="I27" t="n">
-        <v>3.55</v>
       </c>
       <c r="J27" t="n">
         <v>3.4</v>
@@ -5655,10 +5655,10 @@
         <v>2.06</v>
       </c>
       <c r="V27" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W27" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="X27" t="n">
         <v>12</v>
@@ -5709,7 +5709,7 @@
         <v>110</v>
       </c>
       <c r="AN27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO27" t="n">
         <v>46</v>
@@ -5718,13 +5718,13 @@
         <v>11</v>
       </c>
       <c r="AQ27" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS27" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AT27" t="n">
         <v>8.6</v>
@@ -5733,7 +5733,7 @@
         <v>7</v>
       </c>
       <c r="AV27" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW27" t="n">
         <v>38</v>
@@ -5748,7 +5748,7 @@
         <v>17.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="BB27" t="n">
         <v>20</v>
@@ -5766,11 +5766,11 @@
         <v>20</v>
       </c>
       <c r="BG27" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -5801,16 +5801,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G28" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="H28" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="I28" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="J28" t="n">
         <v>3.35</v>
@@ -5828,7 +5828,7 @@
         <v>3.55</v>
       </c>
       <c r="O28" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P28" t="n">
         <v>1.83</v>
@@ -5849,10 +5849,10 @@
         <v>2.08</v>
       </c>
       <c r="V28" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W28" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="X28" t="n">
         <v>12</v>
@@ -5864,7 +5864,7 @@
         <v>15</v>
       </c>
       <c r="AA28" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB28" t="n">
         <v>12</v>
@@ -5876,7 +5876,7 @@
         <v>11.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF28" t="n">
         <v>21</v>
@@ -5903,7 +5903,7 @@
         <v>110</v>
       </c>
       <c r="AN28" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AO28" t="n">
         <v>25</v>
@@ -5918,7 +5918,7 @@
         <v>13.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AT28" t="n">
         <v>11</v>
@@ -5927,7 +5927,7 @@
         <v>7</v>
       </c>
       <c r="AV28" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW28" t="n">
         <v>25</v>
@@ -5942,7 +5942,7 @@
         <v>17.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB28" t="n">
         <v>50</v>
@@ -5951,10 +5951,10 @@
         <v>36</v>
       </c>
       <c r="BD28" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BE28" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BF28" t="n">
         <v>36</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -6019,22 +6019,22 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="O29" t="n">
         <v>1.38</v>
       </c>
       <c r="P29" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R29" t="n">
         <v>1.13</v>
       </c>
       <c r="S29" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="T29" t="n">
         <v>1.01</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
@@ -766,7 +766,7 @@
         <v>6.6</v>
       </c>
       <c r="I2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J2" t="n">
         <v>3.85</v>
@@ -775,7 +775,7 @@
         <v>4.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="M2" t="n">
         <v>1.08</v>
@@ -808,7 +808,7 @@
         <v>1.14</v>
       </c>
       <c r="W2" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="X2" t="n">
         <v>15.5</v>
@@ -823,7 +823,7 @@
         <v>280</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC2" t="n">
         <v>11</v>
@@ -847,7 +847,7 @@
         <v>140</v>
       </c>
       <c r="AJ2" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK2" t="n">
         <v>22</v>
@@ -859,7 +859,7 @@
         <v>200</v>
       </c>
       <c r="AN2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO2" t="n">
         <v>220</v>
@@ -871,13 +871,13 @@
         <v>15</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AU2" t="n">
         <v>7.2</v>
@@ -886,41 +886,41 @@
         <v>21</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AX2" t="n">
         <v>7</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AZ2" t="n">
         <v>19</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF2" t="n">
         <v>8.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -960,10 +960,10 @@
         <v>2.74</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
         <v>4</v>
@@ -978,13 +978,13 @@
         <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P3" t="n">
         <v>2.02</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R3" t="n">
         <v>1.4</v>
@@ -993,7 +993,7 @@
         <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U3" t="n">
         <v>2.24</v>
@@ -1008,7 +1008,7 @@
         <v>19.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z3" t="n">
         <v>24</v>
@@ -1017,10 +1017,10 @@
         <v>55</v>
       </c>
       <c r="AB3" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD3" t="n">
         <v>15</v>
@@ -1029,10 +1029,10 @@
         <v>36</v>
       </c>
       <c r="AF3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AG3" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AH3" t="n">
         <v>19</v>
@@ -1041,19 +1041,19 @@
         <v>46</v>
       </c>
       <c r="AJ3" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AK3" t="n">
         <v>32</v>
       </c>
       <c r="AL3" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AM3" t="n">
         <v>90</v>
       </c>
       <c r="AN3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AO3" t="n">
         <v>28</v>
@@ -1062,59 +1062,59 @@
         <v>13</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="AT3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV3" t="n">
         <v>10</v>
       </c>
-      <c r="AU3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AW3" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="AX3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>12.5</v>
       </c>
-      <c r="AY3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BA3" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="BC3" t="n">
         <v>20</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="BF3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BG3" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="G4" t="n">
         <v>1.38</v>
@@ -1154,19 +1154,19 @@
         <v>12.5</v>
       </c>
       <c r="I4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="J4" t="n">
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L4" t="n">
         <v>1.31</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
         <v>3.8</v>
@@ -1175,22 +1175,22 @@
         <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="T4" t="n">
         <v>2.28</v>
       </c>
       <c r="U4" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="V4" t="n">
         <v>1.07</v>
@@ -1202,7 +1202,7 @@
         <v>20</v>
       </c>
       <c r="Y4" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="Z4" t="n">
         <v>150</v>
@@ -1211,7 +1211,7 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AC4" t="n">
         <v>15</v>
@@ -1226,89 +1226,89 @@
         <v>8.6</v>
       </c>
       <c r="AG4" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AI4" t="n">
         <v>260</v>
       </c>
       <c r="AJ4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AK4" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM4" t="n">
         <v>310</v>
       </c>
       <c r="AN4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO4" t="n">
-        <v>580</v>
+        <v>590</v>
       </c>
       <c r="AP4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AQ4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="AS4" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="AU4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY4" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AV4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>5.3</v>
+        <v>26</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>34</v>
+        <v>4.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         <v>3.55</v>
       </c>
       <c r="H5" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I5" t="n">
         <v>2.76</v>
@@ -1354,37 +1354,37 @@
         <v>2.88</v>
       </c>
       <c r="K5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="M5" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
       <c r="O5" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="P5" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S5" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="U5" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="V5" t="n">
         <v>1.56</v>
@@ -1393,37 +1393,37 @@
         <v>1.39</v>
       </c>
       <c r="X5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z5" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC5" t="n">
         <v>7.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AG5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI5" t="n">
         <v>70</v>
@@ -1432,77 +1432,77 @@
         <v>70</v>
       </c>
       <c r="AK5" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL5" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM5" t="n">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="AN5" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AO5" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AP5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD5" t="n">
         <v>7</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX5" t="n">
+      <c r="BE5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF5" t="n">
         <v>6.8</v>
       </c>
-      <c r="AY5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BG5" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="G6" t="n">
         <v>3.6</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="I6" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="J6" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="K6" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="M6" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="O6" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="P6" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="R6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S6" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W6" t="n">
         <v>1.38</v>
       </c>
       <c r="X6" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA6" t="n">
         <v>60</v>
       </c>
       <c r="AB6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AD6" t="n">
         <v>16.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG6" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AH6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI6" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AJ6" t="n">
         <v>90</v>
       </c>
       <c r="AK6" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AL6" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AM6" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AN6" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AO6" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP6" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AR6" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="AT6" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU6" t="n">
         <v>6</v>
       </c>
       <c r="AV6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW6" t="n">
         <v>32</v>
       </c>
       <c r="AX6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.8</v>
+        <v>17.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -1727,49 +1727,49 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H7" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="J7" t="n">
         <v>3.65</v>
       </c>
       <c r="K7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="R7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="T7" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="U7" t="n">
         <v>2.08</v>
@@ -1778,7 +1778,7 @@
         <v>1.56</v>
       </c>
       <c r="W7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -1790,31 +1790,31 @@
         <v>970</v>
       </c>
       <c r="AA7" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC7" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
         <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AF7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG7" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH7" t="n">
         <v>970</v>
       </c>
       <c r="AI7" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AJ7" t="n">
         <v>55</v>
@@ -1826,7 +1826,7 @@
         <v>42</v>
       </c>
       <c r="AM7" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN7" t="n">
         <v>30</v>
@@ -1835,62 +1835,62 @@
         <v>25</v>
       </c>
       <c r="AP7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>4.1</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AR7" t="n">
-        <v>10.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>4.6</v>
       </c>
-      <c r="AT7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BA7" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="G8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="H8" t="n">
         <v>1.42</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="J8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K8" t="n">
         <v>5.6</v>
@@ -1951,70 +1951,70 @@
         <v>1.21</v>
       </c>
       <c r="P8" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S8" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T8" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="U8" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V8" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="W8" t="n">
         <v>1.12</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z8" t="n">
         <v>10</v>
       </c>
-      <c r="Z8" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AA8" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AC8" t="n">
         <v>12.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AE8" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AG8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AH8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AI8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AJ8" t="n">
         <v>270</v>
       </c>
       <c r="AK8" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AL8" t="n">
         <v>110</v>
@@ -2029,62 +2029,62 @@
         <v>6.6</v>
       </c>
       <c r="AP8" t="n">
-        <v>6.6</v>
+        <v>19</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR8" t="n">
         <v>8</v>
       </c>
       <c r="AS8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT8" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AU8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AV8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AW8" t="n">
         <v>12</v>
       </c>
       <c r="AX8" t="n">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="AY8" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6.6</v>
+        <v>17.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="G9" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="H9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I9" t="n">
         <v>5.1</v>
@@ -2130,22 +2130,22 @@
         <v>3.5</v>
       </c>
       <c r="K9" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
         <v>1.23</v>
       </c>
       <c r="P9" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q9" t="n">
         <v>1.63</v>
@@ -2154,13 +2154,13 @@
         <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="T9" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U9" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V9" t="n">
         <v>1.24</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="G10" t="n">
         <v>3.3</v>
@@ -2321,7 +2321,7 @@
         <v>2.48</v>
       </c>
       <c r="J10" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
         <v>4.1</v>
@@ -2333,40 +2333,40 @@
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P10" t="n">
         <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="R10" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S10" t="n">
-        <v>2.48</v>
+        <v>2.68</v>
       </c>
       <c r="T10" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="U10" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V10" t="n">
         <v>1.67</v>
       </c>
       <c r="W10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y10" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z10" t="n">
         <v>21</v>
@@ -2375,7 +2375,7 @@
         <v>38</v>
       </c>
       <c r="AB10" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AC10" t="n">
         <v>11</v>
@@ -2396,7 +2396,7 @@
         <v>19</v>
       </c>
       <c r="AI10" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ10" t="n">
         <v>65</v>
@@ -2408,13 +2408,13 @@
         <v>46</v>
       </c>
       <c r="AM10" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO10" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AP10" t="n">
         <v>3.65</v>
@@ -2432,47 +2432,47 @@
         <v>3.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AW10" t="n">
         <v>3.7</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AZ10" t="n">
         <v>3.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BB10" t="n">
         <v>4</v>
       </c>
       <c r="BC10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD10" t="n">
         <v>3.9</v>
       </c>
-      <c r="BD10" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BE10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -2506,10 +2506,10 @@
         <v>2.06</v>
       </c>
       <c r="G11" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I11" t="n">
         <v>4.5</v>
@@ -2530,7 +2530,7 @@
         <v>3.2</v>
       </c>
       <c r="O11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P11" t="n">
         <v>1.73</v>
@@ -2542,10 +2542,10 @@
         <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="U11" t="n">
         <v>1.92</v>
@@ -2554,7 +2554,7 @@
         <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="X11" t="n">
         <v>11</v>
@@ -2587,10 +2587,10 @@
         <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AJ11" t="n">
         <v>25</v>
@@ -2611,7 +2611,7 @@
         <v>85</v>
       </c>
       <c r="AP11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ11" t="n">
         <v>12</v>
@@ -2620,7 +2620,7 @@
         <v>27</v>
       </c>
       <c r="AS11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AT11" t="n">
         <v>7.2</v>
@@ -2635,13 +2635,13 @@
         <v>55</v>
       </c>
       <c r="AX11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA11" t="n">
         <v>15</v>
@@ -2653,10 +2653,10 @@
         <v>21</v>
       </c>
       <c r="BD11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE11" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BF11" t="n">
         <v>17</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G12" t="n">
         <v>2.42</v>
@@ -2706,16 +2706,16 @@
         <v>3.35</v>
       </c>
       <c r="I12" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J12" t="n">
         <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L12" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
@@ -2742,7 +2742,7 @@
         <v>1.71</v>
       </c>
       <c r="U12" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V12" t="n">
         <v>1.4</v>
@@ -2757,19 +2757,19 @@
         <v>13.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA12" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC12" t="n">
         <v>8</v>
       </c>
       <c r="AD12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE12" t="n">
         <v>40</v>
@@ -2781,7 +2781,7 @@
         <v>11.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AI12" t="n">
         <v>50</v>
@@ -2799,13 +2799,13 @@
         <v>95</v>
       </c>
       <c r="AN12" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AO12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP12" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ12" t="n">
         <v>11.5</v>
@@ -2814,10 +2814,10 @@
         <v>21</v>
       </c>
       <c r="AS12" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AT12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU12" t="n">
         <v>7.2</v>
@@ -2826,10 +2826,10 @@
         <v>13</v>
       </c>
       <c r="AW12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AX12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY12" t="n">
         <v>10</v>
@@ -2838,19 +2838,19 @@
         <v>16</v>
       </c>
       <c r="BA12" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="BB12" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BC12" t="n">
         <v>22</v>
       </c>
       <c r="BD12" t="n">
-        <v>10.5</v>
+        <v>32</v>
       </c>
       <c r="BE12" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF12" t="n">
         <v>16.5</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
         <v>2.36</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I13" t="n">
         <v>3.65</v>
@@ -2906,7 +2906,7 @@
         <v>3.6</v>
       </c>
       <c r="K13" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L13" t="n">
         <v>1.27</v>
@@ -2921,7 +2921,7 @@
         <v>1.23</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q13" t="n">
         <v>1.67</v>
@@ -2933,7 +2933,7 @@
         <v>2.66</v>
       </c>
       <c r="T13" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U13" t="n">
         <v>2.34</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -3088,10 +3088,10 @@
         <v>4.6</v>
       </c>
       <c r="G14" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="I14" t="n">
         <v>1.92</v>
@@ -3103,7 +3103,7 @@
         <v>4.3</v>
       </c>
       <c r="L14" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
@@ -3112,49 +3112,49 @@
         <v>3.7</v>
       </c>
       <c r="O14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P14" t="n">
         <v>1.93</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R14" t="n">
         <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T14" t="n">
         <v>1.79</v>
       </c>
       <c r="U14" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
         <v>2.08</v>
       </c>
       <c r="W14" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X14" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y14" t="n">
         <v>10.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA14" t="n">
         <v>23</v>
       </c>
       <c r="AB14" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD14" t="n">
         <v>12</v>
@@ -3163,13 +3163,13 @@
         <v>23</v>
       </c>
       <c r="AF14" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AG14" t="n">
         <v>21</v>
       </c>
       <c r="AH14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI14" t="n">
         <v>42</v>
@@ -3178,7 +3178,7 @@
         <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL14" t="n">
         <v>1000</v>
@@ -3190,65 +3190,65 @@
         <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AP14" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AS14" t="n">
         <v>16.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AY14" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BD14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE14" t="n">
         <v>5.3</v>
       </c>
-      <c r="BE14" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BF14" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BG14" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -3279,58 +3279,58 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="I15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K15" t="n">
         <v>4.6</v>
       </c>
-      <c r="J15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.1</v>
-      </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M15" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>2.96</v>
+        <v>3.65</v>
       </c>
       <c r="O15" t="n">
         <v>1.27</v>
       </c>
       <c r="P15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="R15" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V15" t="n">
         <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3435,14 +3435,14 @@
         <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="G16" t="n">
         <v>1.09</v>
@@ -3485,7 +3485,7 @@
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -3506,16 +3506,16 @@
         <v>4.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="R16" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="S16" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T16" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U16" t="n">
         <v>1.66</v>
@@ -3524,7 +3524,7 @@
         <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3575,68 +3575,68 @@
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.7</v>
+        <v>3.05</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5.8</v>
+        <v>3.1</v>
       </c>
       <c r="AR16" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="AS16" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="AT16" t="n">
-        <v>4.8</v>
+        <v>2.82</v>
       </c>
       <c r="AU16" t="n">
-        <v>5.4</v>
+        <v>2.96</v>
       </c>
       <c r="AV16" t="n">
-        <v>5.8</v>
+        <v>3.05</v>
       </c>
       <c r="AW16" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AY16" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="AZ16" t="n">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.9</v>
+        <v>3.1</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.9</v>
+        <v>3.1</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="BG16" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -3667,76 +3667,76 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="G17" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="H17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="I17" t="n">
         <v>15.5</v>
       </c>
       <c r="J17" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K17" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="L17" t="n">
         <v>1.44</v>
       </c>
       <c r="M17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O17" t="n">
         <v>1.38</v>
       </c>
       <c r="P17" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="R17" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U17" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="V17" t="n">
         <v>1.07</v>
       </c>
       <c r="W17" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="X17" t="n">
         <v>15</v>
       </c>
       <c r="Y17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Z17" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AC17" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AD17" t="n">
         <v>55</v>
@@ -3745,7 +3745,7 @@
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AG17" t="n">
         <v>11.5</v>
@@ -3754,83 +3754,83 @@
         <v>44</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AJ17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AK17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL17" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="AR17" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="AT17" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AU17" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AV17" t="n">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="AW17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX17" t="n">
         <v>6.4</v>
       </c>
-      <c r="AX17" t="n">
-        <v>5.9</v>
-      </c>
       <c r="AY17" t="n">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BD17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="BF17" t="n">
         <v>7</v>
       </c>
       <c r="BG17" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -3861,43 +3861,43 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G18" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="H18" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I18" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J18" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M18" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>2.34</v>
+        <v>3.9</v>
       </c>
       <c r="O18" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P18" t="n">
         <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="R18" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S18" t="n">
         <v>2.42</v>
@@ -3906,7 +3906,7 @@
         <v>1.61</v>
       </c>
       <c r="U18" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V18" t="n">
         <v>1.45</v>
@@ -3915,7 +3915,7 @@
         <v>1.59</v>
       </c>
       <c r="X18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y18" t="n">
         <v>970</v>
@@ -3948,7 +3948,7 @@
         <v>970</v>
       </c>
       <c r="AI18" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ18" t="n">
         <v>40</v>
@@ -3975,56 +3975,56 @@
         <v>3.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AS18" t="n">
         <v>4</v>
       </c>
       <c r="AT18" t="n">
-        <v>10</v>
+        <v>3.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>7</v>
+        <v>3.15</v>
       </c>
       <c r="AV18" t="n">
-        <v>10</v>
+        <v>3.45</v>
       </c>
       <c r="AW18" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AX18" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.199999999999999</v>
+        <v>3.35</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BB18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BC18" t="n">
         <v>3.8</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BE18" t="n">
         <v>4.1</v>
       </c>
       <c r="BF18" t="n">
-        <v>11</v>
+        <v>3.55</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G19" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H19" t="n">
         <v>2.72</v>
@@ -4082,22 +4082,22 @@
         <v>2.38</v>
       </c>
       <c r="O19" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="P19" t="n">
         <v>1.46</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="R19" t="n">
         <v>1.16</v>
       </c>
       <c r="S19" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="T19" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
         <v>1.71</v>
@@ -4106,34 +4106,34 @@
         <v>1.51</v>
       </c>
       <c r="W19" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X19" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="Y19" t="n">
         <v>7.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA19" t="n">
         <v>55</v>
       </c>
       <c r="AB19" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD19" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AE19" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AF19" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AG19" t="n">
         <v>15.5</v>
@@ -4142,83 +4142,83 @@
         <v>26</v>
       </c>
       <c r="AI19" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AJ19" t="n">
         <v>65</v>
       </c>
       <c r="AK19" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AL19" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AM19" t="n">
         <v>260</v>
       </c>
       <c r="AN19" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AO19" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX19" t="n">
         <v>5.9</v>
       </c>
-      <c r="AQ19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT19" t="n">
+      <c r="AY19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB19" t="n">
         <v>7.4</v>
       </c>
-      <c r="AU19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ19" t="n">
+      <c r="BC19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE19" t="n">
         <v>8</v>
       </c>
-      <c r="BA19" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>11</v>
-      </c>
       <c r="BF19" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>9.800000000000001</v>
+        <v>40</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -4258,79 +4258,79 @@
         <v>4.9</v>
       </c>
       <c r="I20" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J20" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K20" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L20" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="M20" t="n">
         <v>1.15</v>
       </c>
       <c r="N20" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="O20" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="P20" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R20" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S20" t="n">
         <v>7.2</v>
       </c>
       <c r="T20" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V20" t="n">
         <v>1.21</v>
       </c>
       <c r="W20" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X20" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="Y20" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Z20" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AA20" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AB20" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AE20" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AF20" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH20" t="n">
         <v>34</v>
@@ -4339,80 +4339,80 @@
         <v>190</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AK20" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AL20" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AM20" t="n">
         <v>400</v>
       </c>
       <c r="AN20" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AO20" t="n">
         <v>290</v>
       </c>
       <c r="AP20" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AR20" t="n">
-        <v>8.6</v>
+        <v>4.8</v>
       </c>
       <c r="AS20" t="n">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="AT20" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>7.6</v>
+        <v>18.5</v>
       </c>
       <c r="AW20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY20" t="n">
         <v>10</v>
       </c>
-      <c r="AX20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>11</v>
-      </c>
       <c r="AZ20" t="n">
-        <v>8.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="BA20" t="n">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="BB20" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="BC20" t="n">
-        <v>30</v>
+        <v>4.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>10</v>
+        <v>5.1</v>
       </c>
       <c r="BE20" t="n">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="BF20" t="n">
-        <v>8.6</v>
+        <v>4.8</v>
       </c>
       <c r="BG20" t="n">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -4446,22 +4446,22 @@
         <v>2.12</v>
       </c>
       <c r="G21" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H21" t="n">
         <v>3.35</v>
       </c>
       <c r="I21" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J21" t="n">
         <v>3.7</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.65</v>
       </c>
       <c r="K21" t="n">
         <v>4.1</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M21" t="n">
         <v>1.05</v>
@@ -4473,19 +4473,19 @@
         <v>1.26</v>
       </c>
       <c r="P21" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q21" t="n">
         <v>1.77</v>
       </c>
       <c r="R21" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
         <v>2.96</v>
       </c>
       <c r="T21" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U21" t="n">
         <v>2.28</v>
@@ -4497,116 +4497,116 @@
         <v>1.81</v>
       </c>
       <c r="X21" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="Y21" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Z21" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AA21" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AB21" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AE21" t="n">
         <v>46</v>
       </c>
       <c r="AF21" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AI21" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AJ21" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AK21" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AL21" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AM21" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN21" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AO21" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AP21" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="AQ21" t="n">
         <v>13.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AT21" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU21" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="AW21" t="n">
-        <v>30</v>
+        <v>3.9</v>
       </c>
       <c r="AX21" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>6.4</v>
+        <v>14</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.6</v>
+        <v>3.95</v>
       </c>
       <c r="BB21" t="n">
-        <v>7.8</v>
+        <v>3.8</v>
       </c>
       <c r="BC21" t="n">
-        <v>7.2</v>
+        <v>3.7</v>
       </c>
       <c r="BD21" t="n">
-        <v>8</v>
+        <v>3.85</v>
       </c>
       <c r="BE21" t="n">
-        <v>9.4</v>
+        <v>4.1</v>
       </c>
       <c r="BF21" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>26</v>
+        <v>3.85</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G22" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H22" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I22" t="n">
         <v>3.8</v>
@@ -4655,7 +4655,7 @@
         <v>3.5</v>
       </c>
       <c r="L22" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M22" t="n">
         <v>1.09</v>
@@ -4667,28 +4667,28 @@
         <v>1.42</v>
       </c>
       <c r="P22" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q22" t="n">
         <v>2.28</v>
       </c>
       <c r="R22" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S22" t="n">
         <v>4.3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U22" t="n">
         <v>1.97</v>
       </c>
       <c r="V22" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W22" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X22" t="n">
         <v>11</v>
@@ -4700,7 +4700,7 @@
         <v>25</v>
       </c>
       <c r="AA22" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB22" t="n">
         <v>8.4</v>
@@ -4709,19 +4709,19 @@
         <v>7.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE22" t="n">
         <v>55</v>
       </c>
       <c r="AF22" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG22" t="n">
         <v>11</v>
       </c>
       <c r="AH22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI22" t="n">
         <v>70</v>
@@ -4730,22 +4730,22 @@
         <v>28</v>
       </c>
       <c r="AK22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL22" t="n">
         <v>46</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN22" t="n">
         <v>23</v>
       </c>
       <c r="AO22" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP22" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ22" t="n">
         <v>11</v>
@@ -4769,7 +4769,7 @@
         <v>44</v>
       </c>
       <c r="AX22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY22" t="n">
         <v>10.5</v>
@@ -4781,10 +4781,10 @@
         <v>55</v>
       </c>
       <c r="BB22" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC22" t="n">
         <v>24</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>23</v>
       </c>
       <c r="BD22" t="n">
         <v>40</v>
@@ -4793,14 +4793,14 @@
         <v>42</v>
       </c>
       <c r="BF22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BG22" t="n">
         <v>50</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -4840,16 +4840,16 @@
         <v>11.5</v>
       </c>
       <c r="I23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K23" t="n">
         <v>5.9</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M23" t="n">
         <v>1.08</v>
@@ -4861,7 +4861,7 @@
         <v>1.38</v>
       </c>
       <c r="P23" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q23" t="n">
         <v>2.02</v>
@@ -4888,7 +4888,7 @@
         <v>14.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Z23" t="n">
         <v>1000</v>
@@ -4897,10 +4897,10 @@
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AD23" t="n">
         <v>85</v>
@@ -4909,10 +4909,10 @@
         <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AG23" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH23" t="n">
         <v>65</v>
@@ -4921,10 +4921,10 @@
         <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL23" t="n">
         <v>95</v>
@@ -4933,68 +4933,68 @@
         <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO23" t="n">
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>3.9</v>
+        <v>5.6</v>
       </c>
       <c r="AQ23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB23" t="n">
         <v>4.7</v>
       </c>
-      <c r="AR23" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>3.65</v>
-      </c>
       <c r="BC23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF23" t="n">
         <v>4.3</v>
       </c>
-      <c r="BD23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BG23" t="n">
-        <v>5.3</v>
+        <v>9</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -5025,31 +5025,31 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G24" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H24" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I24" t="n">
         <v>3.95</v>
       </c>
       <c r="J24" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K24" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M24" t="n">
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="O24" t="n">
         <v>1.31</v>
@@ -5058,31 +5058,31 @@
         <v>1.97</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R24" t="n">
         <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T24" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="U24" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V24" t="n">
         <v>1.34</v>
       </c>
       <c r="W24" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="X24" t="n">
         <v>14.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Z24" t="n">
         <v>28</v>
@@ -5091,7 +5091,7 @@
         <v>75</v>
       </c>
       <c r="AB24" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC24" t="n">
         <v>8</v>
@@ -5109,13 +5109,13 @@
         <v>10.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI24" t="n">
         <v>55</v>
       </c>
       <c r="AJ24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK24" t="n">
         <v>23</v>
@@ -5124,7 +5124,7 @@
         <v>36</v>
       </c>
       <c r="AM24" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AN24" t="n">
         <v>15.5</v>
@@ -5139,25 +5139,25 @@
         <v>13</v>
       </c>
       <c r="AR24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS24" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AT24" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU24" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW24" t="n">
         <v>30</v>
       </c>
       <c r="AX24" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY24" t="n">
         <v>9.800000000000001</v>
@@ -5178,17 +5178,17 @@
         <v>30</v>
       </c>
       <c r="BE24" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BF24" t="n">
         <v>13.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -5222,22 +5222,22 @@
         <v>1.75</v>
       </c>
       <c r="G25" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="H25" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I25" t="n">
         <v>6</v>
       </c>
       <c r="J25" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K25" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M25" t="n">
         <v>1.07</v>
@@ -5252,64 +5252,64 @@
         <v>1.91</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
         <v>1.34</v>
       </c>
       <c r="S25" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T25" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="U25" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V25" t="n">
         <v>1.2</v>
       </c>
       <c r="W25" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X25" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z25" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA25" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AB25" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC25" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD25" t="n">
         <v>22</v>
       </c>
       <c r="AE25" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF25" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG25" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AH25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI25" t="n">
         <v>85</v>
       </c>
       <c r="AJ25" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK25" t="n">
         <v>18</v>
@@ -5318,49 +5318,49 @@
         <v>38</v>
       </c>
       <c r="AM25" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AN25" t="n">
         <v>12</v>
       </c>
       <c r="AO25" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AP25" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ25" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR25" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AS25" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AT25" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU25" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV25" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AX25" t="n">
         <v>9</v>
       </c>
       <c r="AY25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA25" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="BB25" t="n">
         <v>16</v>
@@ -5369,20 +5369,20 @@
         <v>17</v>
       </c>
       <c r="BD25" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="BE25" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BF25" t="n">
         <v>10.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
         <v>2.68</v>
       </c>
       <c r="G26" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H26" t="n">
         <v>2.78</v>
@@ -5440,22 +5440,22 @@
         <v>4.4</v>
       </c>
       <c r="O26" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P26" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R26" t="n">
         <v>1.45</v>
       </c>
       <c r="S26" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="T26" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U26" t="n">
         <v>2.4</v>
@@ -5464,10 +5464,10 @@
         <v>1.54</v>
       </c>
       <c r="W26" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X26" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="Y26" t="n">
         <v>13.5</v>
@@ -5482,7 +5482,7 @@
         <v>13.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD26" t="n">
         <v>12.5</v>
@@ -5497,31 +5497,31 @@
         <v>12</v>
       </c>
       <c r="AH26" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI26" t="n">
         <v>38</v>
       </c>
       <c r="AJ26" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL26" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM26" t="n">
         <v>75</v>
       </c>
       <c r="AN26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO26" t="n">
         <v>22</v>
       </c>
       <c r="AP26" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ26" t="n">
         <v>12</v>
@@ -5560,23 +5560,23 @@
         <v>34</v>
       </c>
       <c r="BC26" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BD26" t="n">
         <v>32</v>
       </c>
       <c r="BE26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF26" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BG26" t="n">
         <v>18.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -5607,10 +5607,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G27" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H27" t="n">
         <v>3.4</v>
@@ -5652,7 +5652,7 @@
         <v>1.87</v>
       </c>
       <c r="U27" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V27" t="n">
         <v>1.4</v>
@@ -5667,13 +5667,13 @@
         <v>12</v>
       </c>
       <c r="Z27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA27" t="n">
         <v>65</v>
       </c>
       <c r="AB27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC27" t="n">
         <v>7.4</v>
@@ -5682,7 +5682,7 @@
         <v>14.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF27" t="n">
         <v>14</v>
@@ -5691,7 +5691,7 @@
         <v>11.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI27" t="n">
         <v>55</v>
@@ -5739,19 +5739,19 @@
         <v>38</v>
       </c>
       <c r="AX27" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY27" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA27" t="n">
         <v>48</v>
       </c>
       <c r="BB27" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="BC27" t="n">
         <v>24</v>
@@ -5763,14 +5763,14 @@
         <v>40</v>
       </c>
       <c r="BF27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG27" t="n">
         <v>25</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -5843,7 +5843,7 @@
         <v>4</v>
       </c>
       <c r="T28" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="U28" t="n">
         <v>2.08</v>
@@ -5861,7 +5861,7 @@
         <v>9.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA28" t="n">
         <v>34</v>
@@ -5906,7 +5906,7 @@
         <v>42</v>
       </c>
       <c r="AO28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP28" t="n">
         <v>11</v>
@@ -5933,7 +5933,7 @@
         <v>25</v>
       </c>
       <c r="AX28" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AY28" t="n">
         <v>13</v>
@@ -5954,17 +5954,17 @@
         <v>46</v>
       </c>
       <c r="BE28" t="n">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="BF28" t="n">
         <v>36</v>
       </c>
       <c r="BG28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -5995,145 +5995,145 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="G29" t="n">
-        <v>1000</v>
+        <v>2.66</v>
       </c>
       <c r="H29" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="I29" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="J29" t="n">
-        <v>1.03</v>
+        <v>2.98</v>
       </c>
       <c r="K29" t="n">
-        <v>950</v>
+        <v>3.55</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M29" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N29" t="n">
-        <v>1.28</v>
+        <v>2.82</v>
       </c>
       <c r="O29" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="P29" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.39</v>
+        <v>2.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="S29" t="n">
-        <v>1.39</v>
+        <v>4</v>
       </c>
       <c r="T29" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U29" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG29" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL29" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM29" t="n">
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AS29" t="n">
         <v>1.03</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AW29" t="n">
         <v>1.03</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BA29" t="n">
         <v>1.03</v>
@@ -6151,14 +6151,14 @@
         <v>1.03</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BG29" t="n">
         <v>1.01</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH29"/>
+  <dimension ref="A1:BH31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,16 +760,16 @@
         <v>1.57</v>
       </c>
       <c r="G2" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I2" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J2" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K2" t="n">
         <v>4.4</v>
@@ -787,10 +787,10 @@
         <v>1.36</v>
       </c>
       <c r="P2" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R2" t="n">
         <v>1.3</v>
@@ -802,13 +802,13 @@
         <v>2.06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V2" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="X2" t="n">
         <v>15.5</v>
@@ -877,10 +877,10 @@
         <v>4.9</v>
       </c>
       <c r="AT2" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV2" t="n">
         <v>21</v>
@@ -907,7 +907,7 @@
         <v>14</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.5</v>
+        <v>32</v>
       </c>
       <c r="BE2" t="n">
         <v>4.8</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -951,52 +951,52 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.44</v>
+        <v>1.09</v>
       </c>
       <c r="G3" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="H3" t="n">
-        <v>2.74</v>
+        <v>1.09</v>
       </c>
       <c r="I3" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>1.03</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>950</v>
       </c>
       <c r="L3" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="P3" t="n">
-        <v>2.02</v>
+        <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.8</v>
+        <v>1.29</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>1.29</v>
       </c>
       <c r="T3" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
         <v>1.48</v>
@@ -1005,116 +1005,116 @@
         <v>1.57</v>
       </c>
       <c r="X3" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -1160,19 +1160,19 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.8</v>
+        <v>1.96</v>
       </c>
       <c r="O4" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="P4" t="n">
         <v>1.96</v>
@@ -1184,19 +1184,19 @@
         <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
         <v>1.07</v>
       </c>
       <c r="W4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="X4" t="n">
         <v>20</v>
@@ -1229,7 +1229,7 @@
         <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AI4" t="n">
         <v>260</v>
@@ -1238,7 +1238,7 @@
         <v>13</v>
       </c>
       <c r="AK4" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AL4" t="n">
         <v>60</v>
@@ -1253,62 +1253,62 @@
         <v>590</v>
       </c>
       <c r="AP4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AQ4" t="n">
         <v>23</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AU4" t="n">
         <v>10.5</v>
       </c>
       <c r="AV4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>4.1</v>
       </c>
-      <c r="AW4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>26</v>
-      </c>
       <c r="BA4" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BC4" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.1</v>
+        <v>40</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BF4" t="n">
         <v>5.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>2.76</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>2.88</v>
+        <v>1.03</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
         <v>1.48</v>
       </c>
       <c r="M5" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P5" t="n">
         <v>1.49</v>
       </c>
-      <c r="P5" t="n">
-        <v>1.59</v>
-      </c>
       <c r="Q5" t="n">
-        <v>2.38</v>
+        <v>1.48</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="T5" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.25</v>
+        <v>1.52</v>
       </c>
       <c r="G6" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>2.66</v>
+        <v>1.09</v>
       </c>
       <c r="I6" t="n">
-        <v>2.88</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>2.78</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
-        <v>3.05</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
         <v>1.53</v>
@@ -1557,28 +1557,28 @@
         <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.54</v>
+        <v>2.24</v>
       </c>
       <c r="O6" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="P6" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.84</v>
+        <v>1.02</v>
       </c>
       <c r="R6" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>1.02</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="V6" t="n">
         <v>1.53</v>
@@ -1587,116 +1587,116 @@
         <v>1.38</v>
       </c>
       <c r="X6" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -1727,52 +1727,52 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="G7" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H7" t="n">
-        <v>2.46</v>
+        <v>2.26</v>
       </c>
       <c r="I7" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J7" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="K7" t="n">
         <v>4.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.75</v>
+        <v>1.08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="P7" t="n">
-        <v>1.94</v>
+        <v>1.08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.84</v>
+        <v>1.27</v>
       </c>
       <c r="R7" t="n">
-        <v>1.38</v>
+        <v>1.08</v>
       </c>
       <c r="S7" t="n">
-        <v>2.94</v>
+        <v>1.85</v>
       </c>
       <c r="T7" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
         <v>1.56</v>
@@ -1781,116 +1781,116 @@
         <v>1.47</v>
       </c>
       <c r="X7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
         <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -1921,170 +1921,170 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="K8" t="n">
-        <v>5.6</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>4.7</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.62</v>
+        <v>1.2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.52</v>
+        <v>1.19</v>
       </c>
       <c r="S8" t="n">
-        <v>2.56</v>
+        <v>1.63</v>
       </c>
       <c r="T8" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="W8" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -2115,58 +2115,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.76</v>
+        <v>1.09</v>
       </c>
       <c r="G9" t="n">
-        <v>2.12</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="I9" t="n">
-        <v>5.1</v>
+        <v>65</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5</v>
+        <v>1.03</v>
       </c>
       <c r="K9" t="n">
-        <v>6.4</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>3.8</v>
+        <v>1.15</v>
       </c>
       <c r="O9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P9" t="n">
-        <v>2.08</v>
+        <v>1.15</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.63</v>
+        <v>1.22</v>
       </c>
       <c r="R9" t="n">
-        <v>1.45</v>
+        <v>1.08</v>
       </c>
       <c r="S9" t="n">
-        <v>2.58</v>
+        <v>1.22</v>
       </c>
       <c r="T9" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2184,7 +2184,7 @@
         <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -2309,170 +2309,170 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.96</v>
+        <v>1.34</v>
       </c>
       <c r="G10" t="n">
-        <v>3.3</v>
+        <v>970</v>
       </c>
       <c r="H10" t="n">
-        <v>2.26</v>
+        <v>1.34</v>
       </c>
       <c r="I10" t="n">
-        <v>2.48</v>
+        <v>970</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>1.09</v>
       </c>
       <c r="K10" t="n">
         <v>4.1</v>
       </c>
       <c r="L10" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>1.24</v>
       </c>
       <c r="O10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="R10" t="n">
-        <v>1.49</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>2.68</v>
+        <v>1.22</v>
       </c>
       <c r="T10" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G11" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H11" t="n">
         <v>4.3</v>
@@ -2521,7 +2521,7 @@
         <v>3.5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
         <v>1.09</v>
@@ -2530,37 +2530,37 @@
         <v>3.2</v>
       </c>
       <c r="O11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P11" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="R11" t="n">
         <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="U11" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V11" t="n">
         <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="X11" t="n">
         <v>11</v>
       </c>
       <c r="Y11" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Z11" t="n">
         <v>32</v>
@@ -2569,10 +2569,10 @@
         <v>110</v>
       </c>
       <c r="AB11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC11" t="n">
         <v>8</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>7.8</v>
       </c>
       <c r="AD11" t="n">
         <v>18</v>
@@ -2587,10 +2587,10 @@
         <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI11" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ11" t="n">
         <v>25</v>
@@ -2599,28 +2599,28 @@
         <v>25</v>
       </c>
       <c r="AL11" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AN11" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AO11" t="n">
         <v>85</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="AQ11" t="n">
         <v>12</v>
       </c>
       <c r="AR11" t="n">
-        <v>27</v>
+        <v>9.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="AT11" t="n">
         <v>7.2</v>
@@ -2632,48 +2632,48 @@
         <v>16</v>
       </c>
       <c r="AW11" t="n">
-        <v>55</v>
+        <v>7.4</v>
       </c>
       <c r="AX11" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
       </c>
       <c r="AZ11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC11" t="n">
         <v>18</v>
       </c>
-      <c r="BA11" t="n">
-        <v>15</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>21</v>
-      </c>
       <c r="BD11" t="n">
-        <v>30</v>
+        <v>10.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>15.5</v>
+        <v>3.95</v>
       </c>
       <c r="BF11" t="n">
         <v>17</v>
       </c>
       <c r="BG11" t="n">
-        <v>15.5</v>
+        <v>3.85</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Istanbulspor</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Erzurum BB</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.34</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>2.42</v>
+        <v>7.8</v>
       </c>
       <c r="H12" t="n">
-        <v>3.35</v>
+        <v>1.58</v>
       </c>
       <c r="I12" t="n">
-        <v>3.45</v>
+        <v>2.96</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>1.03</v>
       </c>
       <c r="K12" t="n">
-        <v>3.6</v>
+        <v>950</v>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>3.75</v>
+        <v>1.25</v>
       </c>
       <c r="O12" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="P12" t="n">
-        <v>1.94</v>
+        <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.96</v>
+        <v>1.28</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>3.4</v>
+        <v>1.28</v>
       </c>
       <c r="T12" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4</v>
+        <v>2.08</v>
       </c>
       <c r="W12" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -2891,177 +2891,177 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.12</v>
+        <v>1.09</v>
       </c>
       <c r="G13" t="n">
-        <v>2.36</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>3.15</v>
+        <v>1.29</v>
       </c>
       <c r="I13" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>3.6</v>
+        <v>1.39</v>
       </c>
       <c r="K13" t="n">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L13" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P13" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="R13" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.66</v>
+        <v>2.32</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
         <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,179 +3076,179 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Istanbulspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Erzurum BB</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>2.44</v>
       </c>
       <c r="H14" t="n">
-        <v>1.75</v>
+        <v>3.35</v>
       </c>
       <c r="I14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N14" t="n">
         <v>1.92</v>
       </c>
-      <c r="J14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.7</v>
-      </c>
       <c r="O14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.93</v>
+        <v>1.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2</v>
+        <v>1.02</v>
       </c>
       <c r="T14" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>2.08</v>
+        <v>1.41</v>
       </c>
       <c r="W14" t="n">
-        <v>1.21</v>
+        <v>1.69</v>
       </c>
       <c r="X14" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Y14" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="Z14" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AA14" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="AB14" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AD14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE14" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="AF14" t="n">
-        <v>46</v>
+        <v>15.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AH14" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AI14" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK14" t="n">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO14" t="n">
-        <v>12.5</v>
+        <v>40</v>
       </c>
       <c r="AP14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ14" t="n">
         <v>11.5</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AR14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT14" t="n">
         <v>9.6</v>
       </c>
-      <c r="AS14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AU14" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>8.6</v>
+        <v>4.8</v>
       </c>
       <c r="AW14" t="n">
-        <v>14.5</v>
+        <v>6.2</v>
       </c>
       <c r="AX14" t="n">
         <v>4.9</v>
       </c>
       <c r="AY14" t="n">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BB14" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF14" t="n">
         <v>5.3</v>
       </c>
-      <c r="BC14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BG14" t="n">
-        <v>9.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -3279,58 +3279,58 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="G15" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="H15" t="n">
-        <v>3.25</v>
+        <v>2.32</v>
       </c>
       <c r="I15" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2</v>
+        <v>2.28</v>
       </c>
       <c r="K15" t="n">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L15" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>3.65</v>
+        <v>1.08</v>
       </c>
       <c r="O15" t="n">
         <v>1.27</v>
       </c>
       <c r="P15" t="n">
-        <v>1.91</v>
+        <v>1.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.08</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8</v>
+        <v>1.27</v>
       </c>
       <c r="T15" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3435,14 +3435,14 @@
         <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="G16" t="n">
-        <v>1.09</v>
+        <v>1000</v>
       </c>
       <c r="H16" t="n">
         <v>1.04</v>
@@ -3485,46 +3485,46 @@
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>17.5</v>
+        <v>1.02</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
       </c>
       <c r="L16" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>12.5</v>
+        <v>1.08</v>
       </c>
       <c r="O16" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="P16" t="n">
-        <v>4.8</v>
+        <v>1.08</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="R16" t="n">
-        <v>2.62</v>
+        <v>1.08</v>
       </c>
       <c r="S16" t="n">
-        <v>1.44</v>
+        <v>1.03</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
         <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>12</v>
+        <v>2.46</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3575,68 +3575,68 @@
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.02</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.82</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -3667,31 +3667,31 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="G17" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I17" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="J17" t="n">
         <v>4.5</v>
       </c>
       <c r="K17" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.44</v>
       </c>
       <c r="M17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>3.2</v>
+        <v>1.78</v>
       </c>
       <c r="O17" t="n">
         <v>1.38</v>
@@ -3700,34 +3700,34 @@
         <v>1.78</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S17" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="T17" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U17" t="n">
         <v>1.58</v>
       </c>
       <c r="V17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W17" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="X17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="Z17" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
@@ -3739,31 +3739,31 @@
         <v>13.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH17" t="n">
         <v>44</v>
       </c>
       <c r="AI17" t="n">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="AJ17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AK17" t="n">
         <v>21</v>
       </c>
       <c r="AL17" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
@@ -3775,16 +3775,16 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AT17" t="n">
         <v>5.3</v>
@@ -3793,44 +3793,44 @@
         <v>9</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AX17" t="n">
         <v>6.4</v>
       </c>
       <c r="AY17" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BF17" t="n">
         <v>7</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -3861,170 +3861,170 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.34</v>
+        <v>1.33</v>
       </c>
       <c r="G18" t="n">
-        <v>2.68</v>
+        <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>2.74</v>
+        <v>1.33</v>
       </c>
       <c r="I18" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>3.15</v>
+        <v>1.03</v>
       </c>
       <c r="K18" t="n">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L18" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N18" t="n">
-        <v>3.9</v>
+        <v>1.24</v>
       </c>
       <c r="O18" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>1.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="R18" t="n">
-        <v>1.48</v>
+        <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>2.42</v>
+        <v>1.22</v>
       </c>
       <c r="T18" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -4055,52 +4055,52 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="G19" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="H19" t="n">
-        <v>2.72</v>
+        <v>1.09</v>
       </c>
       <c r="I19" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J19" t="n">
-        <v>2.82</v>
+        <v>1.03</v>
       </c>
       <c r="K19" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="L19" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="N19" t="n">
-        <v>2.38</v>
+        <v>1.25</v>
       </c>
       <c r="O19" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="P19" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.9</v>
+        <v>1.57</v>
       </c>
       <c r="R19" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="S19" t="n">
-        <v>5.6</v>
+        <v>1.57</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="U19" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
         <v>1.51</v>
@@ -4109,116 +4109,116 @@
         <v>1.42</v>
       </c>
       <c r="X19" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR19" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV19" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD19" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE19" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -4249,170 +4249,170 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="G20" t="n">
-        <v>2.2</v>
+        <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>2.84</v>
+        <v>1.03</v>
       </c>
       <c r="K20" t="n">
-        <v>3.15</v>
+        <v>980</v>
       </c>
       <c r="L20" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
         <v>1.15</v>
       </c>
       <c r="N20" t="n">
-        <v>2.2</v>
+        <v>1.25</v>
       </c>
       <c r="O20" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="P20" t="n">
         <v>1.39</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="R20" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S20" t="n">
-        <v>7.2</v>
+        <v>1.68</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="U20" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -4443,170 +4443,170 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G21" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="H21" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="I21" t="n">
         <v>3.65</v>
       </c>
       <c r="J21" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="K21" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
         <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="O21" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>1.16</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.77</v>
+        <v>1.24</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="S21" t="n">
-        <v>2.96</v>
+        <v>1.24</v>
       </c>
       <c r="T21" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="U21" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="V21" t="n">
         <v>1.37</v>
       </c>
       <c r="W21" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="X21" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF21" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -4637,16 +4637,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G22" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H22" t="n">
         <v>3.7</v>
       </c>
       <c r="I22" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J22" t="n">
         <v>3.45</v>
@@ -4673,7 +4673,7 @@
         <v>2.28</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S22" t="n">
         <v>4.3</v>
@@ -4688,16 +4688,16 @@
         <v>1.36</v>
       </c>
       <c r="W22" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X22" t="n">
         <v>11</v>
       </c>
       <c r="Y22" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Z22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA22" t="n">
         <v>75</v>
@@ -4706,37 +4706,37 @@
         <v>8.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD22" t="n">
         <v>15.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF22" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG22" t="n">
         <v>11</v>
       </c>
       <c r="AH22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI22" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK22" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="AL22" t="n">
-        <v>46</v>
+        <v>190</v>
       </c>
       <c r="AM22" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
         <v>23</v>
@@ -4745,7 +4745,7 @@
         <v>60</v>
       </c>
       <c r="AP22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ22" t="n">
         <v>11</v>
@@ -4754,10 +4754,10 @@
         <v>22</v>
       </c>
       <c r="AS22" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU22" t="n">
         <v>7.2</v>
@@ -4769,13 +4769,13 @@
         <v>44</v>
       </c>
       <c r="AX22" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY22" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA22" t="n">
         <v>55</v>
@@ -4784,30 +4784,30 @@
         <v>27</v>
       </c>
       <c r="BC22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD22" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE22" t="n">
         <v>42</v>
       </c>
       <c r="BF22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG22" t="n">
         <v>50</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,186 +4822,186 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MC El Bayadh</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.28</v>
+        <v>3.3</v>
       </c>
       <c r="G23" t="n">
-        <v>1.34</v>
+        <v>3.4</v>
       </c>
       <c r="H23" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X23" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD23" t="n">
         <v>11.5</v>
       </c>
-      <c r="I23" t="n">
-        <v>22</v>
-      </c>
-      <c r="J23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K23" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="X23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Y23" t="n">
+      <c r="AE23" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA23" t="n">
         <v>38</v>
       </c>
-      <c r="Z23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>85</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>65</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AK23" t="n">
+      <c r="BB23" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>36</v>
+      </c>
+      <c r="BG23" t="n">
         <v>21</v>
       </c>
-      <c r="AL23" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>9</v>
-      </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,179 +5016,179 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="G24" t="n">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="H24" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="I24" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="J24" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="K24" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="L24" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="M24" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N24" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R24" t="n">
         <v>1.31</v>
       </c>
-      <c r="P24" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.38</v>
-      </c>
       <c r="S24" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="T24" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="U24" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V24" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="X24" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD24" t="n">
         <v>14.5</v>
       </c>
-      <c r="Y24" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AE24" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AF24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG24" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AI24" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ24" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AK24" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AL24" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
       </c>
       <c r="AN24" t="n">
-        <v>15.5</v>
+        <v>32</v>
       </c>
       <c r="AO24" t="n">
         <v>46</v>
       </c>
       <c r="AP24" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ24" t="n">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW24" t="n">
         <v>24</v>
       </c>
-      <c r="AS24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>30</v>
-      </c>
       <c r="AX24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA24" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="BB24" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BC24" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BD24" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BE24" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="BF24" t="n">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="BG24" t="n">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -5210,179 +5210,179 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="G25" t="n">
-        <v>1.79</v>
+        <v>2.16</v>
       </c>
       <c r="H25" t="n">
-        <v>5.5</v>
+        <v>3.85</v>
       </c>
       <c r="I25" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="J25" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="K25" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="L25" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
         <v>1.07</v>
       </c>
       <c r="N25" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="O25" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V25" t="n">
         <v>1.33</v>
       </c>
-      <c r="P25" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.2</v>
-      </c>
       <c r="W25" t="n">
-        <v>2.26</v>
+        <v>1.86</v>
       </c>
       <c r="X25" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="Z25" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AA25" t="n">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="AB25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV25" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AC25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF25" t="n">
+      <c r="AW25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY25" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AG25" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ25" t="n">
+      <c r="AZ25" t="n">
         <v>16</v>
       </c>
-      <c r="AR25" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>19</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>19</v>
-      </c>
       <c r="BA25" t="n">
-        <v>19</v>
+        <v>7.2</v>
       </c>
       <c r="BB25" t="n">
-        <v>16</v>
+        <v>10.5</v>
       </c>
       <c r="BC25" t="n">
         <v>17</v>
       </c>
       <c r="BD25" t="n">
-        <v>34</v>
+        <v>6.6</v>
       </c>
       <c r="BE25" t="n">
-        <v>19</v>
+        <v>7.4</v>
       </c>
       <c r="BF25" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -5404,186 +5404,186 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Shakhtar</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.68</v>
+        <v>1.75</v>
       </c>
       <c r="G26" t="n">
-        <v>2.72</v>
+        <v>1.8</v>
       </c>
       <c r="H26" t="n">
-        <v>2.78</v>
+        <v>5.5</v>
       </c>
       <c r="I26" t="n">
-        <v>2.82</v>
+        <v>6</v>
       </c>
       <c r="J26" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K26" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N26" t="n">
         <v>3.7</v>
       </c>
-      <c r="L26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="X26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS26" t="n">
         <v>4.4</v>
       </c>
-      <c r="O26" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="X26" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF26" t="n">
+      <c r="AT26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV26" t="n">
         <v>19.5</v>
       </c>
-      <c r="AG26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH26" t="n">
+      <c r="AW26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD26" t="n">
         <v>15.5</v>
       </c>
-      <c r="AI26" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>32</v>
-      </c>
       <c r="BE26" t="n">
-        <v>13</v>
+        <v>4.3</v>
       </c>
       <c r="BF26" t="n">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>18.5</v>
+        <v>4.3</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5598,186 +5598,186 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>MC El Bayadh</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.4</v>
+        <v>1.28</v>
       </c>
       <c r="G27" t="n">
-        <v>2.44</v>
+        <v>1.34</v>
       </c>
       <c r="H27" t="n">
-        <v>3.4</v>
+        <v>16.5</v>
       </c>
       <c r="I27" t="n">
-        <v>3.45</v>
+        <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="K27" t="n">
-        <v>3.45</v>
+        <v>5.9</v>
       </c>
       <c r="L27" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N27" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="O27" t="n">
         <v>1.38</v>
       </c>
       <c r="P27" t="n">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="R27" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T27" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="U27" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="W27" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="X27" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="Z27" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>85</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH27" t="n">
         <v>65</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY27" t="n">
         <v>9.4</v>
       </c>
-      <c r="AC27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AZ27" t="n">
-        <v>16.5</v>
+        <v>8</v>
       </c>
       <c r="BA27" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="BB27" t="n">
-        <v>30</v>
+        <v>4.7</v>
       </c>
       <c r="BC27" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="BD27" t="n">
-        <v>38</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE27" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="BF27" t="n">
-        <v>21</v>
+        <v>6.2</v>
       </c>
       <c r="BG27" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5792,373 +5792,761 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.3</v>
+        <v>2.68</v>
       </c>
       <c r="G28" t="n">
-        <v>3.4</v>
+        <v>2.72</v>
       </c>
       <c r="H28" t="n">
-        <v>2.44</v>
+        <v>2.78</v>
       </c>
       <c r="I28" t="n">
-        <v>2.48</v>
+        <v>2.82</v>
       </c>
       <c r="J28" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="K28" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="L28" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="N28" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="O28" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="P28" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="R28" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="T28" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="U28" t="n">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="V28" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="W28" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="X28" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG28" t="n">
         <v>12</v>
       </c>
-      <c r="Y28" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Z28" t="n">
+      <c r="AH28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ28" t="n">
         <v>14</v>
       </c>
-      <c r="AA28" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BA28" t="n">
-        <v>38</v>
+        <v>5.9</v>
       </c>
       <c r="BB28" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="BC28" t="n">
-        <v>36</v>
+        <v>9.4</v>
       </c>
       <c r="BD28" t="n">
-        <v>46</v>
+        <v>5.9</v>
       </c>
       <c r="BE28" t="n">
-        <v>38</v>
+        <v>6.4</v>
       </c>
       <c r="BF28" t="n">
-        <v>36</v>
+        <v>5.3</v>
       </c>
       <c r="BG28" t="n">
-        <v>21</v>
+        <v>3.85</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Juticalpa</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Olancho</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-04-08 11:09:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Colombian Primera B</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>18:00:00</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Union Magdalena</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Envigado</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G29" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="H29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I29" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="K29" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S29" t="n">
-        <v>4</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS29" t="n">
+      <c r="F30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J30" t="n">
         <v>1.03</v>
       </c>
-      <c r="AT29" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW29" t="n">
+      <c r="K30" t="n">
+        <v>950</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
         <v>1.03</v>
       </c>
-      <c r="AX29" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA29" t="n">
+      <c r="AQ30" t="n">
         <v>1.03</v>
       </c>
-      <c r="BB29" t="n">
+      <c r="AR30" t="n">
         <v>1.03</v>
       </c>
-      <c r="BC29" t="n">
+      <c r="AS30" t="n">
         <v>1.03</v>
       </c>
-      <c r="BD29" t="n">
+      <c r="AT30" t="n">
         <v>1.03</v>
       </c>
-      <c r="BE29" t="n">
+      <c r="AU30" t="n">
         <v>1.03</v>
       </c>
-      <c r="BF29" t="n">
-        <v>23</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH29" t="inlineStr">
-        <is>
-          <t>2026-04-08 08:59:19</t>
+      <c r="AV30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-04-08 11:09:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CD Marathon</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>CD Motagua</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
@@ -766,7 +766,7 @@
         <v>6.8</v>
       </c>
       <c r="I2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J2" t="n">
         <v>3.9</v>
@@ -775,7 +775,7 @@
         <v>4.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="M2" t="n">
         <v>1.08</v>
@@ -796,7 +796,7 @@
         <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="T2" t="n">
         <v>2.06</v>
@@ -805,10 +805,10 @@
         <v>1.8</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="W2" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="X2" t="n">
         <v>15.5</v>
@@ -877,7 +877,7 @@
         <v>4.9</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AU2" t="n">
         <v>7.4</v>
@@ -889,7 +889,7 @@
         <v>4.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AY2" t="n">
         <v>7.8</v>
@@ -907,7 +907,7 @@
         <v>14</v>
       </c>
       <c r="BD2" t="n">
-        <v>32</v>
+        <v>4.5</v>
       </c>
       <c r="BE2" t="n">
         <v>4.8</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.09</v>
+        <v>2.48</v>
       </c>
       <c r="G3" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H3" t="n">
-        <v>1.09</v>
+        <v>2.82</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>3.95</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>1.25</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.29</v>
+        <v>1.79</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>1.29</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V3" t="n">
         <v>1.48</v>
       </c>
       <c r="W3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="G4" t="n">
         <v>1.38</v>
@@ -1157,28 +1157,28 @@
         <v>14.5</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>1.96</v>
+        <v>3.8</v>
       </c>
       <c r="O4" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="P4" t="n">
         <v>1.96</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="R4" t="n">
         <v>1.36</v>
@@ -1187,10 +1187,10 @@
         <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="V4" t="n">
         <v>1.07</v>
@@ -1229,7 +1229,7 @@
         <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AI4" t="n">
         <v>260</v>
@@ -1238,7 +1238,7 @@
         <v>13</v>
       </c>
       <c r="AK4" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
         <v>60</v>
@@ -1256,25 +1256,25 @@
         <v>14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AT4" t="n">
         <v>6.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AX4" t="n">
         <v>6.2</v>
@@ -1283,32 +1283,32 @@
         <v>9</v>
       </c>
       <c r="AZ4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD4" t="n">
         <v>4.1</v>
       </c>
-      <c r="BA4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>40</v>
-      </c>
       <c r="BE4" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BF4" t="n">
         <v>5.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="J5" t="n">
-        <v>1.03</v>
+        <v>2.84</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>3.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="O5" t="n">
         <v>1.48</v>
       </c>
       <c r="P5" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.48</v>
+        <v>2.42</v>
       </c>
       <c r="R5" t="n">
         <v>1.21</v>
       </c>
       <c r="S5" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -1533,49 +1533,49 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.52</v>
+        <v>3.25</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="H6" t="n">
-        <v>1.09</v>
+        <v>2.7</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>2.78</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>3.05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="M6" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="N6" t="n">
-        <v>2.24</v>
+        <v>2.52</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.02</v>
+        <v>2.78</v>
       </c>
       <c r="R6" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="S6" t="n">
-        <v>1.02</v>
+        <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
         <v>1.78</v>
@@ -1584,119 +1584,119 @@
         <v>1.53</v>
       </c>
       <c r="W6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="G7" t="n">
         <v>3.2</v>
       </c>
       <c r="H7" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="I7" t="n">
-        <v>2.76</v>
+        <v>2.42</v>
       </c>
       <c r="J7" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="K7" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>1.08</v>
+        <v>3.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.08</v>
+        <v>1.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.27</v>
+        <v>1.92</v>
       </c>
       <c r="R7" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>1.85</v>
+        <v>3.25</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="V7" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="W7" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC7" t="n">
         <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -1921,170 +1921,170 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="J8" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>5.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M8" t="n">
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>4.7</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>2.28</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.2</v>
+        <v>1.63</v>
       </c>
       <c r="R8" t="n">
-        <v>1.19</v>
+        <v>1.52</v>
       </c>
       <c r="S8" t="n">
-        <v>1.63</v>
+        <v>2.58</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V8" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -2115,58 +2115,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.09</v>
+        <v>1.81</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>2.12</v>
       </c>
       <c r="H9" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="I9" t="n">
-        <v>65</v>
+        <v>5.1</v>
       </c>
       <c r="J9" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>6.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>1.15</v>
+        <v>4.3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P9" t="n">
-        <v>1.15</v>
+        <v>2.14</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.22</v>
+        <v>1.69</v>
       </c>
       <c r="R9" t="n">
-        <v>1.08</v>
+        <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>1.22</v>
+        <v>2.6</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2184,7 +2184,7 @@
         <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.34</v>
+        <v>2.98</v>
       </c>
       <c r="G10" t="n">
-        <v>970</v>
+        <v>3.3</v>
       </c>
       <c r="H10" t="n">
-        <v>1.34</v>
+        <v>2.24</v>
       </c>
       <c r="I10" t="n">
-        <v>970</v>
+        <v>2.46</v>
       </c>
       <c r="J10" t="n">
-        <v>1.09</v>
+        <v>3.65</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2333,146 +2333,146 @@
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>1.24</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.22</v>
+        <v>1.68</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>1.49</v>
       </c>
       <c r="S10" t="n">
-        <v>1.22</v>
+        <v>2.72</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G11" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H11" t="n">
         <v>4.3</v>
@@ -2515,25 +2515,25 @@
         <v>4.5</v>
       </c>
       <c r="J11" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K11" t="n">
         <v>3.5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M11" t="n">
         <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P11" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
         <v>2.28</v>
@@ -2554,13 +2554,13 @@
         <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="X11" t="n">
         <v>11</v>
       </c>
       <c r="Y11" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Z11" t="n">
         <v>32</v>
@@ -2569,7 +2569,7 @@
         <v>110</v>
       </c>
       <c r="AB11" t="n">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC11" t="n">
         <v>8</v>
@@ -2587,10 +2587,10 @@
         <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ11" t="n">
         <v>25</v>
@@ -2599,28 +2599,28 @@
         <v>25</v>
       </c>
       <c r="AL11" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM11" t="n">
         <v>170</v>
       </c>
       <c r="AN11" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AO11" t="n">
         <v>85</v>
       </c>
       <c r="AP11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AQ11" t="n">
         <v>12</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.4</v>
+        <v>27</v>
       </c>
       <c r="AS11" t="n">
-        <v>4</v>
+        <v>15.5</v>
       </c>
       <c r="AT11" t="n">
         <v>7.2</v>
@@ -2632,41 +2632,41 @@
         <v>16</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.4</v>
+        <v>14</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.6</v>
+        <v>14.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.6</v>
+        <v>22</v>
       </c>
       <c r="BC11" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BD11" t="n">
-        <v>10.5</v>
+        <v>30</v>
       </c>
       <c r="BE11" t="n">
-        <v>3.95</v>
+        <v>14.5</v>
       </c>
       <c r="BF11" t="n">
         <v>17</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.85</v>
+        <v>13.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="G12" t="n">
-        <v>7.8</v>
+        <v>5.7</v>
       </c>
       <c r="H12" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="I12" t="n">
-        <v>2.96</v>
+        <v>1.9</v>
       </c>
       <c r="J12" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2721,70 +2721,70 @@
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>1.25</v>
+        <v>3.7</v>
       </c>
       <c r="O12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.94</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.28</v>
+        <v>1.87</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>1.28</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V12" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ12" t="n">
         <v>1000</v>
@@ -2802,65 +2802,65 @@
         <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -2891,25 +2891,25 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.09</v>
+        <v>2.2</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>2.38</v>
       </c>
       <c r="H13" t="n">
-        <v>1.29</v>
+        <v>3.55</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="J13" t="n">
-        <v>1.39</v>
+        <v>3.25</v>
       </c>
       <c r="K13" t="n">
-        <v>950</v>
+        <v>3.75</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
@@ -2918,37 +2918,37 @@
         <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P13" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="S13" t="n">
-        <v>2.32</v>
+        <v>2.68</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="V13" t="n">
         <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z13" t="n">
         <v>1000</v>
@@ -2957,25 +2957,25 @@
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE13" t="n">
         <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI13" t="n">
         <v>1000</v>
@@ -2984,7 +2984,7 @@
         <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL13" t="n">
         <v>1000</v>
@@ -2993,68 +2993,68 @@
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -3109,28 +3109,28 @@
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>1.92</v>
+        <v>3.75</v>
       </c>
       <c r="O14" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25</v>
+        <v>1.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R14" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>1.02</v>
+        <v>3.5</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V14" t="n">
         <v>1.41</v>
@@ -3142,7 +3142,7 @@
         <v>14</v>
       </c>
       <c r="Y14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z14" t="n">
         <v>23</v>
@@ -3151,28 +3151,28 @@
         <v>60</v>
       </c>
       <c r="AB14" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>970</v>
+        <v>7.8</v>
       </c>
       <c r="AD14" t="n">
         <v>14</v>
       </c>
       <c r="AE14" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF14" t="n">
         <v>15.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AI14" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AJ14" t="n">
         <v>32</v>
@@ -3181,28 +3181,28 @@
         <v>26</v>
       </c>
       <c r="AL14" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM14" t="n">
         <v>95</v>
       </c>
       <c r="AN14" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AO14" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AP14" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="AQ14" t="n">
         <v>11.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="AT14" t="n">
         <v>9.6</v>
@@ -3211,13 +3211,13 @@
         <v>7.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>4.8</v>
+        <v>12.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.2</v>
+        <v>32</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.9</v>
+        <v>13.5</v>
       </c>
       <c r="AY14" t="n">
         <v>10</v>
@@ -3226,29 +3226,29 @@
         <v>16</v>
       </c>
       <c r="BA14" t="n">
-        <v>6.4</v>
+        <v>34</v>
       </c>
       <c r="BB14" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="BC14" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.2</v>
+        <v>32</v>
       </c>
       <c r="BE14" t="n">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="BF14" t="n">
-        <v>5.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.7</v>
+        <v>12.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -3279,58 +3279,58 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="G15" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="H15" t="n">
-        <v>2.32</v>
+        <v>3.35</v>
       </c>
       <c r="I15" t="n">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
       <c r="J15" t="n">
-        <v>2.28</v>
+        <v>3.2</v>
       </c>
       <c r="K15" t="n">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>1.08</v>
+        <v>3.65</v>
       </c>
       <c r="O15" t="n">
         <v>1.27</v>
       </c>
       <c r="P15" t="n">
-        <v>1.08</v>
+        <v>1.99</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.27</v>
+        <v>1.81</v>
       </c>
       <c r="R15" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>1.27</v>
+        <v>2.82</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3435,14 +3435,14 @@
         <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BG15" t="n">
         <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>1.1</v>
       </c>
       <c r="H16" t="n">
         <v>1.04</v>
@@ -3485,7 +3485,7 @@
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.02</v>
+        <v>17.5</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -3497,34 +3497,34 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.08</v>
+        <v>12</v>
       </c>
       <c r="O16" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="P16" t="n">
-        <v>1.08</v>
+        <v>4.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="R16" t="n">
-        <v>1.08</v>
+        <v>2.72</v>
       </c>
       <c r="S16" t="n">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="V16" t="n">
         <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>2.46</v>
+        <v>11</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3575,68 +3575,68 @@
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>2.06</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -3667,170 +3667,170 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="G17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L17" t="n">
         <v>1.46</v>
       </c>
-      <c r="H17" t="n">
-        <v>10</v>
-      </c>
-      <c r="I17" t="n">
-        <v>13</v>
-      </c>
-      <c r="J17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.44</v>
-      </c>
       <c r="M17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>1.78</v>
+        <v>3.1</v>
       </c>
       <c r="O17" t="n">
         <v>1.38</v>
       </c>
       <c r="P17" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R17" t="n">
         <v>1.27</v>
       </c>
       <c r="S17" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="U17" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="V17" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="W17" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="X17" t="n">
         <v>14.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="Z17" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AD17" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AF17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>210</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW17" t="n">
         <v>8.4</v>
       </c>
-      <c r="AG17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>44</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>270</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AX17" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AY17" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.4</v>
+        <v>15</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -3861,170 +3861,170 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.33</v>
+        <v>2.36</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="H18" t="n">
-        <v>1.33</v>
+        <v>2.74</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="J18" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="K18" t="n">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>1.24</v>
+        <v>4.1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="P18" t="n">
-        <v>1.24</v>
+        <v>2.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.22</v>
+        <v>1.75</v>
       </c>
       <c r="R18" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>1.22</v>
+        <v>2.76</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="H19" t="n">
-        <v>1.09</v>
+        <v>2.8</v>
       </c>
       <c r="I19" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="J19" t="n">
-        <v>1.03</v>
+        <v>2.82</v>
       </c>
       <c r="K19" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4079,28 +4079,28 @@
         <v>1.13</v>
       </c>
       <c r="N19" t="n">
-        <v>1.25</v>
+        <v>2.4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="P19" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.57</v>
+        <v>2.88</v>
       </c>
       <c r="R19" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="S19" t="n">
-        <v>1.57</v>
+        <v>6.2</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V19" t="n">
         <v>1.51</v>
@@ -4109,116 +4109,116 @@
         <v>1.42</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -4249,170 +4249,170 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="G20" t="n">
-        <v>1000</v>
+        <v>2.18</v>
       </c>
       <c r="H20" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="J20" t="n">
-        <v>1.03</v>
+        <v>2.84</v>
       </c>
       <c r="K20" t="n">
-        <v>980</v>
+        <v>3.15</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="M20" t="n">
         <v>1.15</v>
       </c>
       <c r="N20" t="n">
-        <v>1.25</v>
+        <v>2.18</v>
       </c>
       <c r="O20" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="P20" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R20" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S20" t="n">
-        <v>1.68</v>
+        <v>7.2</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="G21" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="H21" t="n">
         <v>3.2</v>
       </c>
       <c r="I21" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="J21" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="K21" t="n">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -4467,146 +4467,146 @@
         <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="O21" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P21" t="n">
-        <v>1.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.24</v>
+        <v>1.76</v>
       </c>
       <c r="R21" t="n">
-        <v>1.15</v>
+        <v>1.43</v>
       </c>
       <c r="S21" t="n">
-        <v>1.24</v>
+        <v>2.96</v>
       </c>
       <c r="T21" t="n">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="U21" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="V21" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
         <v>2.26</v>
       </c>
       <c r="G22" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H22" t="n">
         <v>3.7</v>
@@ -4649,10 +4649,10 @@
         <v>3.75</v>
       </c>
       <c r="J22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K22" t="n">
         <v>3.45</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.5</v>
       </c>
       <c r="L22" t="n">
         <v>1.49</v>
@@ -4670,13 +4670,13 @@
         <v>1.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T22" t="n">
         <v>1.96</v>
@@ -4688,13 +4688,13 @@
         <v>1.36</v>
       </c>
       <c r="W22" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="X22" t="n">
         <v>11</v>
       </c>
       <c r="Y22" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Z22" t="n">
         <v>24</v>
@@ -4715,28 +4715,28 @@
         <v>50</v>
       </c>
       <c r="AF22" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG22" t="n">
         <v>11</v>
       </c>
       <c r="AH22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ22" t="n">
         <v>29</v>
       </c>
       <c r="AK22" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="AL22" t="n">
-        <v>190</v>
+        <v>46</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN22" t="n">
         <v>23</v>
@@ -4760,13 +4760,13 @@
         <v>8</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV22" t="n">
         <v>15</v>
       </c>
       <c r="AW22" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AX22" t="n">
         <v>12</v>
@@ -4784,7 +4784,7 @@
         <v>27</v>
       </c>
       <c r="BC22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD22" t="n">
         <v>42</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -4831,16 +4831,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="G23" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H23" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I23" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="J23" t="n">
         <v>3.35</v>
@@ -4855,34 +4855,34 @@
         <v>1.09</v>
       </c>
       <c r="N23" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
         <v>1.37</v>
       </c>
       <c r="P23" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R23" t="n">
         <v>1.31</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T23" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="U23" t="n">
         <v>2.08</v>
       </c>
       <c r="V23" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="W23" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X23" t="n">
         <v>12</v>
@@ -4900,13 +4900,13 @@
         <v>12</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD23" t="n">
         <v>11.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AF23" t="n">
         <v>21</v>
@@ -4918,7 +4918,7 @@
         <v>18.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AJ23" t="n">
         <v>60</v>
@@ -4948,7 +4948,7 @@
         <v>13.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT23" t="n">
         <v>11</v>
@@ -4963,7 +4963,7 @@
         <v>25</v>
       </c>
       <c r="AX23" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AY23" t="n">
         <v>13</v>
@@ -4972,7 +4972,7 @@
         <v>17.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB23" t="n">
         <v>50</v>
@@ -4984,17 +4984,17 @@
         <v>46</v>
       </c>
       <c r="BE23" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="BF23" t="n">
         <v>36</v>
       </c>
       <c r="BG23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -5025,16 +5025,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G24" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H24" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I24" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J24" t="n">
         <v>3.4</v>
@@ -5052,16 +5052,16 @@
         <v>3.5</v>
       </c>
       <c r="O24" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P24" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R24" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -5070,19 +5070,19 @@
         <v>1.87</v>
       </c>
       <c r="U24" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V24" t="n">
         <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X24" t="n">
         <v>12</v>
       </c>
       <c r="Y24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z24" t="n">
         <v>22</v>
@@ -5091,7 +5091,7 @@
         <v>65</v>
       </c>
       <c r="AB24" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC24" t="n">
         <v>7.4</v>
@@ -5109,7 +5109,7 @@
         <v>11.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI24" t="n">
         <v>60</v>
@@ -5127,7 +5127,7 @@
         <v>110</v>
       </c>
       <c r="AN24" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AO24" t="n">
         <v>46</v>
@@ -5136,7 +5136,7 @@
         <v>11</v>
       </c>
       <c r="AQ24" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AR24" t="n">
         <v>20</v>
@@ -5145,37 +5145,37 @@
         <v>30</v>
       </c>
       <c r="AT24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU24" t="n">
         <v>7</v>
       </c>
       <c r="AV24" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="AX24" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY24" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="BA24" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB24" t="n">
         <v>29</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>21</v>
       </c>
       <c r="BC24" t="n">
         <v>24</v>
       </c>
       <c r="BD24" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="BE24" t="n">
         <v>40</v>
@@ -5184,11 +5184,11 @@
         <v>21</v>
       </c>
       <c r="BG24" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -5252,13 +5252,13 @@
         <v>1.97</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
         <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>2.62</v>
+        <v>3.5</v>
       </c>
       <c r="T25" t="n">
         <v>1.77</v>
@@ -5270,13 +5270,13 @@
         <v>1.33</v>
       </c>
       <c r="W25" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X25" t="n">
         <v>14.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="Z25" t="n">
         <v>28</v>
@@ -5285,7 +5285,7 @@
         <v>75</v>
       </c>
       <c r="AB25" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AC25" t="n">
         <v>8</v>
@@ -5303,7 +5303,7 @@
         <v>10.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AI25" t="n">
         <v>55</v>
@@ -5318,25 +5318,25 @@
         <v>36</v>
       </c>
       <c r="AM25" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AN25" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO25" t="n">
         <v>46</v>
       </c>
       <c r="AP25" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ25" t="n">
         <v>13</v>
       </c>
       <c r="AR25" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="AS25" t="n">
-        <v>7.4</v>
+        <v>13.5</v>
       </c>
       <c r="AT25" t="n">
         <v>9.199999999999999</v>
@@ -5345,13 +5345,13 @@
         <v>7.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>8.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="AX25" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AY25" t="n">
         <v>9.800000000000001</v>
@@ -5360,29 +5360,29 @@
         <v>16</v>
       </c>
       <c r="BA25" t="n">
-        <v>7.2</v>
+        <v>14.5</v>
       </c>
       <c r="BB25" t="n">
-        <v>10.5</v>
+        <v>23</v>
       </c>
       <c r="BC25" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>6.6</v>
+        <v>30</v>
       </c>
       <c r="BE25" t="n">
-        <v>7.4</v>
+        <v>14</v>
       </c>
       <c r="BF25" t="n">
         <v>13.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>7</v>
+        <v>13.5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -5416,13 +5416,13 @@
         <v>1.75</v>
       </c>
       <c r="G26" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="H26" t="n">
         <v>5.5</v>
       </c>
       <c r="I26" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J26" t="n">
         <v>3.8</v>
@@ -5431,46 +5431,46 @@
         <v>3.95</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M26" t="n">
         <v>1.07</v>
       </c>
       <c r="N26" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O26" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P26" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R26" t="n">
         <v>1.34</v>
       </c>
       <c r="S26" t="n">
-        <v>2.02</v>
+        <v>3.55</v>
       </c>
       <c r="T26" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U26" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="V26" t="n">
         <v>1.2</v>
       </c>
       <c r="W26" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="X26" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="Y26" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="Z26" t="n">
         <v>42</v>
@@ -5479,10 +5479,10 @@
         <v>150</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC26" t="n">
-        <v>18</v>
+        <v>8.6</v>
       </c>
       <c r="AD26" t="n">
         <v>22</v>
@@ -5494,10 +5494,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AG26" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AH26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI26" t="n">
         <v>90</v>
@@ -5509,28 +5509,28 @@
         <v>18</v>
       </c>
       <c r="AL26" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM26" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN26" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO26" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP26" t="n">
-        <v>4.1</v>
+        <v>13</v>
       </c>
       <c r="AQ26" t="n">
         <v>16</v>
       </c>
       <c r="AR26" t="n">
-        <v>5.2</v>
+        <v>36</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.4</v>
+        <v>20</v>
       </c>
       <c r="AT26" t="n">
         <v>7.6</v>
@@ -5542,7 +5542,7 @@
         <v>19.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>5.5</v>
+        <v>18</v>
       </c>
       <c r="AX26" t="n">
         <v>9</v>
@@ -5554,7 +5554,7 @@
         <v>19</v>
       </c>
       <c r="BA26" t="n">
-        <v>5.5</v>
+        <v>18.5</v>
       </c>
       <c r="BB26" t="n">
         <v>16</v>
@@ -5563,20 +5563,20 @@
         <v>17</v>
       </c>
       <c r="BD26" t="n">
-        <v>15.5</v>
+        <v>34</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.3</v>
+        <v>20</v>
       </c>
       <c r="BF26" t="n">
         <v>10.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.3</v>
+        <v>18.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -5616,16 +5616,16 @@
         <v>16.5</v>
       </c>
       <c r="I27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K27" t="n">
         <v>5.9</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M27" t="n">
         <v>1.08</v>
@@ -5640,19 +5640,19 @@
         <v>1.71</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R27" t="n">
         <v>1.26</v>
       </c>
       <c r="S27" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T27" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="V27" t="n">
         <v>1.04</v>
@@ -5664,7 +5664,7 @@
         <v>14.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Z27" t="n">
         <v>1000</v>
@@ -5673,10 +5673,10 @@
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AD27" t="n">
         <v>85</v>
@@ -5685,10 +5685,10 @@
         <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AG27" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AH27" t="n">
         <v>65</v>
@@ -5697,10 +5697,10 @@
         <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AK27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL27" t="n">
         <v>95</v>
@@ -5709,7 +5709,7 @@
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
@@ -5718,13 +5718,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ27" t="n">
-        <v>7.6</v>
+        <v>4.9</v>
       </c>
       <c r="AR27" t="n">
-        <v>8.800000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="AS27" t="n">
-        <v>9</v>
+        <v>5.3</v>
       </c>
       <c r="AT27" t="n">
         <v>4.5</v>
@@ -5733,10 +5733,10 @@
         <v>10</v>
       </c>
       <c r="AV27" t="n">
-        <v>8.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="AW27" t="n">
-        <v>9</v>
+        <v>5.3</v>
       </c>
       <c r="AX27" t="n">
         <v>4.8</v>
@@ -5745,32 +5745,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ27" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="BA27" t="n">
-        <v>9</v>
+        <v>5.3</v>
       </c>
       <c r="BB27" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="BC27" t="n">
         <v>15</v>
       </c>
       <c r="BD27" t="n">
-        <v>8.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="BE27" t="n">
-        <v>9</v>
+        <v>5.3</v>
       </c>
       <c r="BF27" t="n">
         <v>6.2</v>
       </c>
       <c r="BG27" t="n">
-        <v>9</v>
+        <v>5.3</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
         <v>2.68</v>
       </c>
       <c r="G28" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="H28" t="n">
         <v>2.78</v>
@@ -5819,7 +5819,7 @@
         <v>3.7</v>
       </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M28" t="n">
         <v>1.06</v>
@@ -5834,13 +5834,13 @@
         <v>2.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R28" t="n">
         <v>1.45</v>
       </c>
       <c r="S28" t="n">
-        <v>1.8</v>
+        <v>2.96</v>
       </c>
       <c r="T28" t="n">
         <v>1.65</v>
@@ -5852,13 +5852,13 @@
         <v>1.54</v>
       </c>
       <c r="W28" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X28" t="n">
         <v>17.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Z28" t="n">
         <v>20</v>
@@ -5867,10 +5867,10 @@
         <v>42</v>
       </c>
       <c r="AB28" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
         <v>12.5</v>
@@ -5885,7 +5885,7 @@
         <v>12</v>
       </c>
       <c r="AH28" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI28" t="n">
         <v>38</v>
@@ -5894,10 +5894,10 @@
         <v>40</v>
       </c>
       <c r="AK28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL28" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AM28" t="n">
         <v>75</v>
@@ -5909,16 +5909,16 @@
         <v>22</v>
       </c>
       <c r="AP28" t="n">
-        <v>5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ28" t="n">
         <v>12</v>
       </c>
       <c r="AR28" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AS28" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="AT28" t="n">
         <v>11.5</v>
@@ -5927,13 +5927,13 @@
         <v>7.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="AW28" t="n">
-        <v>9.800000000000001</v>
+        <v>25</v>
       </c>
       <c r="AX28" t="n">
-        <v>8.4</v>
+        <v>17</v>
       </c>
       <c r="AY28" t="n">
         <v>11</v>
@@ -5942,29 +5942,29 @@
         <v>14</v>
       </c>
       <c r="BA28" t="n">
-        <v>5.9</v>
+        <v>32</v>
       </c>
       <c r="BB28" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="BC28" t="n">
-        <v>9.4</v>
+        <v>24</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.9</v>
+        <v>32</v>
       </c>
       <c r="BE28" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="BF28" t="n">
-        <v>5.3</v>
+        <v>18</v>
       </c>
       <c r="BG28" t="n">
-        <v>3.85</v>
+        <v>18.5</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -5995,13 +5995,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G29" t="n">
         <v>1000</v>
       </c>
       <c r="H29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I29" t="n">
         <v>1000</v>
@@ -6010,7 +6010,7 @@
         <v>1.03</v>
       </c>
       <c r="K29" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -6019,13 +6019,13 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="O29" t="n">
         <v>1.23</v>
       </c>
       <c r="P29" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Q29" t="n">
         <v>1.23</v>
@@ -6103,52 +6103,52 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF29" t="n">
         <v>1.01</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -6189,100 +6189,100 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="G30" t="n">
-        <v>1000</v>
+        <v>2.46</v>
       </c>
       <c r="H30" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="I30" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="J30" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="K30" t="n">
-        <v>950</v>
+        <v>3.55</v>
       </c>
       <c r="L30" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="M30" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N30" t="n">
-        <v>1.08</v>
+        <v>2.96</v>
       </c>
       <c r="O30" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="P30" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="R30" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="S30" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="T30" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="U30" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL30" t="n">
         <v>1000</v>
@@ -6291,16 +6291,16 @@
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AR30" t="n">
         <v>1.03</v>
@@ -6309,25 +6309,25 @@
         <v>1.03</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AW30" t="n">
         <v>1.03</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BA30" t="n">
         <v>1.03</v>
@@ -6336,7 +6336,7 @@
         <v>1.03</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BD30" t="n">
         <v>1.03</v>
@@ -6345,14 +6345,14 @@
         <v>1.03</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -6383,13 +6383,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G31" t="n">
         <v>1000</v>
       </c>
       <c r="H31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I31" t="n">
         <v>1000</v>
@@ -6398,7 +6398,7 @@
         <v>1.03</v>
       </c>
       <c r="K31" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
@@ -6407,13 +6407,13 @@
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="O31" t="n">
         <v>1.29</v>
       </c>
       <c r="P31" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Q31" t="n">
         <v>1.29</v>
@@ -6491,52 +6491,52 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF31" t="n">
         <v>1.01</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH31"/>
+  <dimension ref="A1:BH33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,7 +790,7 @@
         <v>1.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R2" t="n">
         <v>1.3</v>
@@ -865,62 +865,62 @@
         <v>220</v>
       </c>
       <c r="AP2" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>15</v>
+        <v>4.7</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS2" t="n">
         <v>4.9</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV2" t="n">
-        <v>21</v>
+        <v>4.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX2" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AY2" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>19</v>
+        <v>4.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>14</v>
+        <v>4.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF2" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG2" t="n">
         <v>4.9</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-08 13:21:28</t>
+          <t>2026-04-08 15:34:35</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="G3" t="n">
         <v>2.74</v>
       </c>
       <c r="H3" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
         <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
         <v>1.36</v>
@@ -999,7 +999,7 @@
         <v>2.26</v>
       </c>
       <c r="V3" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W3" t="n">
         <v>1.58</v>
@@ -1020,7 +1020,7 @@
         <v>13</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3" t="n">
         <v>15</v>
@@ -1080,7 +1080,7 @@
         <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AX3" t="n">
         <v>15</v>
@@ -1092,19 +1092,19 @@
         <v>13.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC3" t="n">
         <v>6</v>
       </c>
-      <c r="BC3" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BD3" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF3" t="n">
         <v>16.5</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-08 13:21:28</t>
+          <t>2026-04-08 15:34:35</t>
         </is>
       </c>
     </row>
@@ -1160,10 +1160,10 @@
         <v>4.9</v>
       </c>
       <c r="K4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
@@ -1178,7 +1178,7 @@
         <v>1.96</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="R4" t="n">
         <v>1.36</v>
@@ -1190,7 +1190,7 @@
         <v>2.32</v>
       </c>
       <c r="U4" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="V4" t="n">
         <v>1.07</v>
@@ -1256,13 +1256,13 @@
         <v>14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT4" t="n">
         <v>6.2</v>
@@ -1271,7 +1271,7 @@
         <v>9</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AW4" t="n">
         <v>4.4</v>
@@ -1283,7 +1283,7 @@
         <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BA4" t="n">
         <v>4.4</v>
@@ -1301,14 +1301,14 @@
         <v>4.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-08 13:21:28</t>
+          <t>2026-04-08 15:34:35</t>
         </is>
       </c>
     </row>
@@ -1339,25 +1339,25 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H5" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="I5" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="J5" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L5" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="M5" t="n">
         <v>1.11</v>
@@ -1369,16 +1369,16 @@
         <v>1.48</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R5" t="n">
         <v>1.21</v>
       </c>
       <c r="S5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T5" t="n">
         <v>1.94</v>
@@ -1387,22 +1387,22 @@
         <v>1.88</v>
       </c>
       <c r="V5" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="W5" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="X5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA5" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AB5" t="n">
         <v>11</v>
@@ -1411,13 +1411,13 @@
         <v>7.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
         <v>38</v>
       </c>
       <c r="AF5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG5" t="n">
         <v>15.5</v>
@@ -1426,7 +1426,7 @@
         <v>21</v>
       </c>
       <c r="AI5" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ5" t="n">
         <v>70</v>
@@ -1441,13 +1441,13 @@
         <v>180</v>
       </c>
       <c r="AN5" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AO5" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AQ5" t="n">
         <v>7.4</v>
@@ -1456,10 +1456,10 @@
         <v>13</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AU5" t="n">
         <v>6</v>
@@ -1468,7 +1468,7 @@
         <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX5" t="n">
         <v>18</v>
@@ -1477,32 +1477,32 @@
         <v>12.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BC5" t="n">
         <v>40</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-08 13:21:28</t>
+          <t>2026-04-08 15:34:35</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="G6" t="n">
         <v>3.55</v>
@@ -1542,13 +1542,13 @@
         <v>2.7</v>
       </c>
       <c r="I6" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="J6" t="n">
         <v>2.78</v>
       </c>
       <c r="K6" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="L6" t="n">
         <v>1.63</v>
@@ -1581,7 +1581,7 @@
         <v>1.78</v>
       </c>
       <c r="V6" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W6" t="n">
         <v>1.39</v>
@@ -1683,7 +1683,7 @@
         <v>9</v>
       </c>
       <c r="BD6" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BE6" t="n">
         <v>10</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-08 13:21:28</t>
+          <t>2026-04-08 15:34:35</t>
         </is>
       </c>
     </row>
@@ -1733,16 +1733,16 @@
         <v>3.2</v>
       </c>
       <c r="H7" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I7" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="J7" t="n">
         <v>3.6</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1775,7 +1775,7 @@
         <v>2.1</v>
       </c>
       <c r="V7" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W7" t="n">
         <v>1.45</v>
@@ -1787,7 +1787,7 @@
         <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AA7" t="n">
         <v>36</v>
@@ -1796,7 +1796,7 @@
         <v>14</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD7" t="n">
         <v>970</v>
@@ -1841,7 +1841,7 @@
         <v>8.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>12</v>
+        <v>5.2</v>
       </c>
       <c r="AS7" t="n">
         <v>6</v>
@@ -1856,7 +1856,7 @@
         <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.7</v>
+        <v>20</v>
       </c>
       <c r="AX7" t="n">
         <v>15.5</v>
@@ -1868,19 +1868,19 @@
         <v>13.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC7" t="n">
         <v>6</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF7" t="n">
         <v>6</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-08 13:21:28</t>
+          <t>2026-04-08 15:34:35</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         <v>4.7</v>
       </c>
       <c r="K8" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L8" t="n">
         <v>1.27</v>
@@ -2035,34 +2035,34 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AS8" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>21</v>
+        <v>4.9</v>
       </c>
       <c r="AU8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV8" t="n">
         <v>8.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX8" t="n">
         <v>4.8</v>
       </c>
       <c r="AY8" t="n">
-        <v>23</v>
+        <v>4.9</v>
       </c>
       <c r="AZ8" t="n">
         <v>19</v>
       </c>
       <c r="BA8" t="n">
-        <v>25</v>
+        <v>4.7</v>
       </c>
       <c r="BB8" t="n">
         <v>5</v>
@@ -2080,11 +2080,11 @@
         <v>4.9</v>
       </c>
       <c r="BG8" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-08 13:21:28</t>
+          <t>2026-04-08 15:34:35</t>
         </is>
       </c>
     </row>
@@ -2115,58 +2115,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.81</v>
+        <v>2.06</v>
       </c>
       <c r="G9" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="H9" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="I9" t="n">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P9" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="R9" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="T9" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U9" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V9" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="W9" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2184,7 +2184,7 @@
         <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.1</v>
+        <v>12</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU9" t="n">
         <v>7.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.8</v>
+        <v>11.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-08 13:21:28</t>
+          <t>2026-04-08 15:34:35</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
         <v>4.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
@@ -2342,7 +2342,7 @@
         <v>2.22</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R10" t="n">
         <v>1.49</v>
@@ -2351,16 +2351,16 @@
         <v>2.72</v>
       </c>
       <c r="T10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U10" t="n">
         <v>2.38</v>
       </c>
       <c r="V10" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W10" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X10" t="n">
         <v>25</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-08 13:21:28</t>
+          <t>2026-04-08 15:34:35</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>MB Rouissat</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.06</v>
+        <v>1.3</v>
       </c>
       <c r="G11" t="n">
-        <v>2.1</v>
+        <v>1.47</v>
       </c>
       <c r="H11" t="n">
-        <v>4.3</v>
+        <v>7.8</v>
       </c>
       <c r="I11" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>3.15</v>
+        <v>2.34</v>
       </c>
       <c r="O11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P11" t="n">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="R11" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="S11" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="T11" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.91</v>
+        <v>3.1</v>
       </c>
       <c r="X11" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-08 13:21:28</t>
+          <t>2026-04-08 15:34:35</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Istanbulspor</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Erzurum BB</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.6</v>
+        <v>2.06</v>
       </c>
       <c r="G12" t="n">
-        <v>5.7</v>
+        <v>2.1</v>
       </c>
       <c r="H12" t="n">
-        <v>1.77</v>
+        <v>4.3</v>
       </c>
       <c r="I12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W12" t="n">
         <v>1.9</v>
       </c>
-      <c r="J12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.21</v>
-      </c>
       <c r="X12" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD12" t="n">
         <v>18</v>
       </c>
-      <c r="Y12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="AE12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH12" t="n">
         <v>21</v>
       </c>
-      <c r="AC12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD12" t="n">
+      <c r="AI12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ12" t="n">
         <v>12</v>
       </c>
-      <c r="AE12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>46</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AR12" t="n">
-        <v>8.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="AS12" t="n">
         <v>15</v>
       </c>
       <c r="AT12" t="n">
-        <v>13.5</v>
+        <v>7.2</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>7.8</v>
+        <v>15.5</v>
       </c>
       <c r="AW12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA12" t="n">
         <v>14.5</v>
       </c>
-      <c r="AX12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ12" t="n">
+      <c r="BB12" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG12" t="n">
         <v>14.5</v>
       </c>
-      <c r="BA12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-08 13:21:28</t>
+          <t>2026-04-08 15:34:35</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Erokspor A.S</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Amed Sportif Faaliyetler</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="G13" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="H13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K13" t="n">
         <v>3.55</v>
       </c>
-      <c r="I13" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N13" t="n">
         <v>3.75</v>
       </c>
-      <c r="L13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N13" t="n">
-        <v>5</v>
-      </c>
       <c r="O13" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="R13" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>2.68</v>
+        <v>3.5</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="U13" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="V13" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="X13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH13" t="n">
         <v>21</v>
       </c>
-      <c r="Y13" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC13" t="n">
+      <c r="AI13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT13" t="n">
         <v>9.6</v>
       </c>
-      <c r="AD13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AU13" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="AX13" t="n">
         <v>13.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ13" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA13" t="n">
         <v>13</v>
       </c>
-      <c r="BA13" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BB13" t="n">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="BC13" t="n">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="BE13" t="n">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-08 13:21:28</t>
+          <t>2026-04-08 15:34:35</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Erokspor A.S</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Amed Sportif Faaliyetler</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="G14" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="H14" t="n">
         <v>3.35</v>
       </c>
       <c r="I14" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="J14" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M14" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="P14" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="R14" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5</v>
+        <v>2.68</v>
       </c>
       <c r="T14" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="U14" t="n">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="V14" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W14" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="X14" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
         <v>14</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ14" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="AR14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT14" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP14" t="n">
+      <c r="AU14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV14" t="n">
         <v>12</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AW14" t="n">
-        <v>32</v>
+        <v>7.4</v>
       </c>
       <c r="AX14" t="n">
         <v>13.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>34</v>
+        <v>7.6</v>
       </c>
       <c r="BB14" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="BC14" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="BD14" t="n">
-        <v>32</v>
+        <v>7.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>13.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF14" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BG14" t="n">
-        <v>12.5</v>
+        <v>7</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-08 13:21:28</t>
+          <t>2026-04-08 15:34:35</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,103 +3270,103 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cukaricki</t>
+          <t>Istanbulspor</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FK Radnicki 1923</t>
+          <t>Erzurum BB</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.16</v>
+        <v>4.6</v>
       </c>
       <c r="G15" t="n">
-        <v>2.36</v>
+        <v>5.5</v>
       </c>
       <c r="H15" t="n">
-        <v>3.35</v>
+        <v>1.84</v>
       </c>
       <c r="I15" t="n">
-        <v>3.9</v>
+        <v>1.91</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="K15" t="n">
         <v>4.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O15" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P15" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="R15" t="n">
         <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>2.82</v>
+        <v>3.2</v>
       </c>
       <c r="T15" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="U15" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="V15" t="n">
-        <v>1.35</v>
+        <v>2.08</v>
       </c>
       <c r="W15" t="n">
-        <v>1.75</v>
+        <v>1.22</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ15" t="n">
         <v>1000</v>
@@ -3384,65 +3384,65 @@
         <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>27</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BF15" t="n">
-        <v>9.6</v>
+        <v>4.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-08 13:21:28</t>
+          <t>2026-04-08 15:34:35</t>
         </is>
       </c>
     </row>
@@ -3464,186 +3464,186 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Crvena Zvezda</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FK Spartak</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.07</v>
+        <v>2.12</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="H16" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="J16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="X16" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF16" t="n">
         <v>17.5</v>
       </c>
-      <c r="K16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N16" t="n">
+      <c r="AG16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF16" t="n">
         <v>12</v>
       </c>
-      <c r="O16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="P16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W16" t="n">
-        <v>11</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>1.62</v>
-      </c>
       <c r="BG16" t="n">
-        <v>3.85</v>
+        <v>30</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-08 13:21:28</t>
+          <t>2026-04-08 15:34:35</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>PFC Levski Sofia</t>
+          <t>Cukaricki</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>FK Radnicki 1923</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.47</v>
+        <v>2.16</v>
       </c>
       <c r="G17" t="n">
-        <v>1.53</v>
+        <v>2.34</v>
       </c>
       <c r="H17" t="n">
-        <v>8.199999999999999</v>
+        <v>3.35</v>
       </c>
       <c r="I17" t="n">
-        <v>10.5</v>
+        <v>3.8</v>
       </c>
       <c r="J17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K17" t="n">
         <v>4.2</v>
       </c>
-      <c r="K17" t="n">
-        <v>5</v>
-      </c>
       <c r="L17" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="M17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="O17" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="P17" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W17" t="n">
         <v>1.75</v>
       </c>
-      <c r="Q17" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S17" t="n">
-        <v>4</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.88</v>
-      </c>
       <c r="X17" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>10.5</v>
+        <v>2.22</v>
       </c>
       <c r="AQ17" t="n">
-        <v>6.4</v>
+        <v>2</v>
       </c>
       <c r="AR17" t="n">
-        <v>8.199999999999999</v>
+        <v>2.08</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.6</v>
+        <v>2.22</v>
       </c>
       <c r="AT17" t="n">
-        <v>5.4</v>
+        <v>1.93</v>
       </c>
       <c r="AU17" t="n">
-        <v>5</v>
+        <v>1.86</v>
       </c>
       <c r="AV17" t="n">
-        <v>7.2</v>
+        <v>2</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.4</v>
+        <v>2.22</v>
       </c>
       <c r="AX17" t="n">
-        <v>6.8</v>
+        <v>2</v>
       </c>
       <c r="AY17" t="n">
-        <v>8.800000000000001</v>
+        <v>1.94</v>
       </c>
       <c r="AZ17" t="n">
-        <v>7</v>
+        <v>2.02</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.4</v>
+        <v>2.22</v>
       </c>
       <c r="BB17" t="n">
-        <v>10</v>
+        <v>2.1</v>
       </c>
       <c r="BC17" t="n">
-        <v>15</v>
+        <v>2.06</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.8</v>
+        <v>2.22</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.6</v>
+        <v>2.22</v>
       </c>
       <c r="BF17" t="n">
-        <v>8.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.6</v>
+        <v>2.22</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-08 13:21:28</t>
+          <t>2026-04-08 15:34:35</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Saudi 1st Division</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14:40:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Al-Adalh</t>
+          <t>Crvena Zvezda</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Batin</t>
+          <t>FK Spartak</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.36</v>
+        <v>1.07</v>
       </c>
       <c r="G18" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="H18" t="n">
-        <v>2.74</v>
+        <v>25</v>
       </c>
       <c r="I18" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>3.15</v>
+        <v>17.5</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>4.1</v>
+        <v>12</v>
       </c>
       <c r="O18" t="n">
-        <v>1.26</v>
+        <v>1.06</v>
       </c>
       <c r="P18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W18" t="n">
+        <v>11</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
         <v>2.06</v>
       </c>
-      <c r="Q18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="X18" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>970</v>
-      </c>
       <c r="AO18" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>13</v>
+        <v>3.85</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>3.9</v>
       </c>
       <c r="AR18" t="n">
-        <v>15.5</v>
+        <v>3.95</v>
       </c>
       <c r="AS18" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AT18" t="n">
-        <v>9.199999999999999</v>
+        <v>3.45</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.6</v>
+        <v>3.7</v>
       </c>
       <c r="AV18" t="n">
-        <v>10</v>
+        <v>3.9</v>
       </c>
       <c r="AW18" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AX18" t="n">
-        <v>12.5</v>
+        <v>4.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>9</v>
+        <v>5.1</v>
       </c>
       <c r="AZ18" t="n">
-        <v>11.5</v>
+        <v>3.8</v>
       </c>
       <c r="BA18" t="n">
         <v>3.95</v>
       </c>
       <c r="BB18" t="n">
-        <v>3.9</v>
+        <v>7.2</v>
       </c>
       <c r="BC18" t="n">
-        <v>18.5</v>
+        <v>4.9</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BF18" t="n">
-        <v>12.5</v>
+        <v>1.66</v>
       </c>
       <c r="BG18" t="n">
-        <v>16.5</v>
+        <v>3.95</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-08 13:21:28</t>
+          <t>2026-04-08 15:34:35</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>PFC Levski Sofia</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ZED FC</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H19" t="n">
+        <v>9</v>
+      </c>
+      <c r="I19" t="n">
+        <v>11</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N19" t="n">
         <v>3.15</v>
       </c>
-      <c r="G19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.4</v>
-      </c>
       <c r="O19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U19" t="n">
         <v>1.62</v>
       </c>
-      <c r="P19" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="V19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3</v>
+      </c>
+      <c r="X19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>260</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>230</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AV19" t="n">
         <v>6.2</v>
       </c>
-      <c r="T19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X19" t="n">
+      <c r="AW19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY19" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Y19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC19" t="n">
+      <c r="AZ19" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA19" t="n">
         <v>7</v>
       </c>
-      <c r="AD19" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>260</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>75</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW19" t="n">
+      <c r="BB19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF19" t="n">
         <v>8.4</v>
       </c>
-      <c r="AX19" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ19" t="n">
+      <c r="BG19" t="n">
         <v>7.2</v>
       </c>
-      <c r="BA19" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>9</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-08 13:21:28</t>
+          <t>2026-04-08 15:34:35</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:40:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al-Adalh</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>Al Batin</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.04</v>
+        <v>2.36</v>
       </c>
       <c r="G20" t="n">
-        <v>2.18</v>
+        <v>2.68</v>
       </c>
       <c r="H20" t="n">
-        <v>5.3</v>
+        <v>2.74</v>
       </c>
       <c r="I20" t="n">
-        <v>5.6</v>
+        <v>3.15</v>
       </c>
       <c r="J20" t="n">
-        <v>2.84</v>
+        <v>3.5</v>
       </c>
       <c r="K20" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="L20" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>2.18</v>
+        <v>4.3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.73</v>
+        <v>1.24</v>
       </c>
       <c r="P20" t="n">
-        <v>1.38</v>
+        <v>2.14</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.13</v>
+        <v>1.45</v>
       </c>
       <c r="S20" t="n">
-        <v>7.2</v>
+        <v>2.76</v>
       </c>
       <c r="T20" t="n">
-        <v>2.52</v>
+        <v>1.61</v>
       </c>
       <c r="U20" t="n">
-        <v>1.56</v>
+        <v>2.3</v>
       </c>
       <c r="V20" t="n">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="W20" t="n">
-        <v>1.84</v>
+        <v>1.59</v>
       </c>
       <c r="X20" t="n">
-        <v>7.6</v>
+        <v>21</v>
       </c>
       <c r="Y20" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Z20" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="AA20" t="n">
-        <v>210</v>
+        <v>55</v>
       </c>
       <c r="AB20" t="n">
-        <v>6.6</v>
+        <v>15</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>29</v>
+        <v>16.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>150</v>
+        <v>38</v>
       </c>
       <c r="AF20" t="n">
-        <v>12.5</v>
+        <v>22</v>
       </c>
       <c r="AG20" t="n">
         <v>15</v>
       </c>
       <c r="AH20" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="AI20" t="n">
-        <v>200</v>
+        <v>46</v>
       </c>
       <c r="AJ20" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AK20" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AL20" t="n">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="AM20" t="n">
-        <v>420</v>
+        <v>80</v>
       </c>
       <c r="AN20" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="AO20" t="n">
-        <v>310</v>
+        <v>26</v>
       </c>
       <c r="AP20" t="n">
-        <v>5.9</v>
+        <v>13</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.8</v>
+        <v>15.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="AT20" t="n">
-        <v>5.1</v>
+        <v>9.4</v>
       </c>
       <c r="AU20" t="n">
         <v>6.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="AX20" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ20" t="n">
-        <v>4.8</v>
+        <v>11.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="BC20" t="n">
-        <v>30</v>
+        <v>18.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.8</v>
+        <v>12.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>5.4</v>
+        <v>16.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-08 13:21:28</t>
+          <t>2026-04-08 15:34:35</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,186 +4434,186 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>ZED FC</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.18</v>
+        <v>3.15</v>
       </c>
       <c r="G21" t="n">
-        <v>2.32</v>
+        <v>3.35</v>
       </c>
       <c r="H21" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="I21" t="n">
-        <v>3.5</v>
+        <v>2.94</v>
       </c>
       <c r="J21" t="n">
-        <v>3.7</v>
+        <v>2.82</v>
       </c>
       <c r="K21" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="M21" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="N21" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="O21" t="n">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>1.47</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.76</v>
+        <v>2.88</v>
       </c>
       <c r="R21" t="n">
-        <v>1.43</v>
+        <v>1.16</v>
       </c>
       <c r="S21" t="n">
-        <v>2.96</v>
+        <v>6.2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.67</v>
+        <v>2.22</v>
       </c>
       <c r="U21" t="n">
-        <v>2.28</v>
+        <v>1.72</v>
       </c>
       <c r="V21" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="W21" t="n">
-        <v>1.8</v>
+        <v>1.42</v>
       </c>
       <c r="X21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ21" t="n">
         <v>22</v>
       </c>
-      <c r="Y21" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC21" t="n">
+      <c r="BA21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB21" t="n">
         <v>9</v>
       </c>
-      <c r="AD21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS21" t="n">
+      <c r="BC21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG21" t="n">
         <v>9</v>
       </c>
-      <c r="AT21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>8</v>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-08 13:21:28</t>
+          <t>2026-04-08 15:34:35</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="G22" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="H22" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="I22" t="n">
-        <v>3.75</v>
+        <v>5.7</v>
       </c>
       <c r="J22" t="n">
-        <v>3.4</v>
+        <v>2.84</v>
       </c>
       <c r="K22" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="M22" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>2.18</v>
       </c>
       <c r="O22" t="n">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="P22" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="S22" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="T22" t="n">
-        <v>1.96</v>
+        <v>2.54</v>
       </c>
       <c r="U22" t="n">
-        <v>1.97</v>
+        <v>1.56</v>
       </c>
       <c r="V22" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="W22" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="X22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>210</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>200</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>420</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>310</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY22" t="n">
         <v>11</v>
       </c>
-      <c r="Y22" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR22" t="n">
+      <c r="AZ22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB22" t="n">
         <v>22</v>
       </c>
-      <c r="AS22" t="n">
-        <v>65</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>42</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>27</v>
-      </c>
       <c r="BC22" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BD22" t="n">
-        <v>42</v>
+        <v>5.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>42</v>
+        <v>5.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="BG22" t="n">
-        <v>50</v>
+        <v>5.6</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-08 13:21:28</t>
+          <t>2026-04-08 15:34:35</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,184 +4817,184 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Al-Ettifaq</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Al Riyadh SC</t>
         </is>
       </c>
       <c r="F23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H23" t="n">
         <v>3.25</v>
       </c>
-      <c r="G23" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="H23" t="n">
-        <v>2.46</v>
-      </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>3.45</v>
       </c>
       <c r="J23" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="K23" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="L23" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="O23" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="P23" t="n">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="R23" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>3.95</v>
+        <v>2.96</v>
       </c>
       <c r="T23" t="n">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="U23" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="V23" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="W23" t="n">
-        <v>1.42</v>
+        <v>1.8</v>
       </c>
       <c r="X23" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Y23" t="n">
-        <v>9.6</v>
+        <v>15</v>
       </c>
       <c r="Z23" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="AA23" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AB23" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AD23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG23" t="n">
         <v>11.5</v>
       </c>
-      <c r="AE23" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>14</v>
-      </c>
       <c r="AH23" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AI23" t="n">
         <v>44</v>
       </c>
       <c r="AJ23" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="AK23" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="AL23" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AM23" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN23" t="n">
-        <v>42</v>
+        <v>15.5</v>
       </c>
       <c r="AO23" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AP23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF23" t="n">
         <v>11</v>
       </c>
-      <c r="AQ23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>50</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>36</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>46</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>85</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>36</v>
-      </c>
       <c r="BG23" t="n">
-        <v>22</v>
+        <v>8.4</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-08 13:21:28</t>
+          <t>2026-04-08 15:34:35</t>
         </is>
       </c>
     </row>
@@ -5016,25 +5016,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Nottm Forest</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="G24" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="H24" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="I24" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="J24" t="n">
         <v>3.4</v>
@@ -5043,94 +5043,94 @@
         <v>3.45</v>
       </c>
       <c r="L24" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="M24" t="n">
         <v>1.09</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="O24" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="P24" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="T24" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="U24" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W24" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="X24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y24" t="n">
         <v>12</v>
       </c>
       <c r="Z24" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA24" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AB24" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AC24" t="n">
         <v>7.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AF24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG24" t="n">
         <v>11.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AI24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO24" t="n">
         <v>60</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>46</v>
       </c>
       <c r="AP24" t="n">
         <v>11</v>
@@ -5139,63 +5139,63 @@
         <v>11</v>
       </c>
       <c r="AR24" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AS24" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AT24" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AU24" t="n">
         <v>7</v>
       </c>
       <c r="AV24" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AW24" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AX24" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AY24" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BB24" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BC24" t="n">
         <v>24</v>
       </c>
       <c r="BD24" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BE24" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BF24" t="n">
         <v>21</v>
       </c>
       <c r="BG24" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-08 13:21:28</t>
+          <t>2026-04-08 15:34:35</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,186 +5210,186 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="G25" t="n">
-        <v>2.16</v>
+        <v>3.45</v>
       </c>
       <c r="H25" t="n">
-        <v>3.85</v>
+        <v>2.42</v>
       </c>
       <c r="I25" t="n">
-        <v>4.1</v>
+        <v>2.44</v>
       </c>
       <c r="J25" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="K25" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M25" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R25" t="n">
         <v>1.31</v>
       </c>
-      <c r="P25" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.38</v>
-      </c>
       <c r="S25" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="T25" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="U25" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="V25" t="n">
-        <v>1.33</v>
+        <v>1.69</v>
       </c>
       <c r="W25" t="n">
-        <v>1.87</v>
+        <v>1.4</v>
       </c>
       <c r="X25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG25" t="n">
         <v>14.5</v>
       </c>
-      <c r="Y25" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AH25" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL25" t="n">
         <v>55</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>36</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
       </c>
       <c r="AN25" t="n">
-        <v>15.5</v>
+        <v>42</v>
       </c>
       <c r="AO25" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="AP25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ25" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AR25" t="n">
-        <v>24</v>
+        <v>13.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>13.5</v>
+        <v>30</v>
       </c>
       <c r="AT25" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AU25" t="n">
         <v>7.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AX25" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AY25" t="n">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>14.5</v>
+        <v>40</v>
       </c>
       <c r="BB25" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="BC25" t="n">
-        <v>19.5</v>
+        <v>36</v>
       </c>
       <c r="BD25" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="BE25" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="BF25" t="n">
-        <v>13.5</v>
+        <v>36</v>
       </c>
       <c r="BG25" t="n">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-08 13:21:28</t>
+          <t>2026-04-08 15:34:35</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,179 +5404,179 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.75</v>
+        <v>2.44</v>
       </c>
       <c r="G26" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P26" t="n">
         <v>1.81</v>
       </c>
-      <c r="H26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I26" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.92</v>
-      </c>
       <c r="Q26" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="S26" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="U26" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="V26" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="W26" t="n">
-        <v>2.24</v>
+        <v>1.68</v>
       </c>
       <c r="X26" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Y26" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="Z26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE26" t="n">
         <v>42</v>
       </c>
-      <c r="AA26" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>80</v>
-      </c>
       <c r="AF26" t="n">
-        <v>9.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AH26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF26" t="n">
         <v>21</v>
       </c>
-      <c r="AI26" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>20</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BG26" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-08 13:21:28</t>
+          <t>2026-04-08 15:34:35</t>
         </is>
       </c>
     </row>
@@ -5619,13 +5619,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="K27" t="n">
         <v>5.9</v>
       </c>
       <c r="L27" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M27" t="n">
         <v>1.08</v>
@@ -5709,7 +5709,7 @@
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
@@ -5718,13 +5718,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ27" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AR27" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AT27" t="n">
         <v>4.5</v>
@@ -5733,10 +5733,10 @@
         <v>10</v>
       </c>
       <c r="AV27" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AX27" t="n">
         <v>4.8</v>
@@ -5745,10 +5745,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ27" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BA27" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BB27" t="n">
         <v>7.4</v>
@@ -5757,20 +5757,20 @@
         <v>15</v>
       </c>
       <c r="BD27" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BE27" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BF27" t="n">
         <v>6.2</v>
       </c>
       <c r="BG27" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-08 13:21:28</t>
+          <t>2026-04-08 15:34:35</t>
         </is>
       </c>
     </row>
@@ -5792,186 +5792,186 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Shakhtar</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.68</v>
+        <v>1.77</v>
       </c>
       <c r="G28" t="n">
-        <v>2.74</v>
+        <v>1.8</v>
       </c>
       <c r="H28" t="n">
-        <v>2.78</v>
+        <v>5.5</v>
       </c>
       <c r="I28" t="n">
-        <v>2.82</v>
+        <v>5.8</v>
       </c>
       <c r="J28" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N28" t="n">
         <v>3.7</v>
       </c>
-      <c r="L28" t="n">
+      <c r="O28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R28" t="n">
         <v>1.35</v>
       </c>
-      <c r="M28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N28" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.45</v>
-      </c>
       <c r="S28" t="n">
-        <v>2.96</v>
+        <v>3.45</v>
       </c>
       <c r="T28" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="U28" t="n">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="V28" t="n">
-        <v>1.54</v>
+        <v>1.2</v>
       </c>
       <c r="W28" t="n">
-        <v>1.57</v>
+        <v>2.26</v>
       </c>
       <c r="X28" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y28" t="n">
         <v>17.5</v>
       </c>
-      <c r="Y28" t="n">
-        <v>13.5</v>
-      </c>
       <c r="Z28" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="AA28" t="n">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="AB28" t="n">
-        <v>13.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>12.5</v>
+        <v>22</v>
       </c>
       <c r="AE28" t="n">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="AF28" t="n">
-        <v>19.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN28" t="n">
         <v>12</v>
       </c>
-      <c r="AH28" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI28" t="n">
+      <c r="AO28" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR28" t="n">
         <v>38</v>
       </c>
-      <c r="AJ28" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR28" t="n">
+      <c r="AS28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>65</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC28" t="n">
         <v>17</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>24</v>
       </c>
       <c r="BD28" t="n">
         <v>32</v>
       </c>
       <c r="BE28" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BF28" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="BG28" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-08 13:21:28</t>
+          <t>2026-04-08 15:34:35</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Juticalpa</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olancho</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="G29" t="n">
-        <v>1000</v>
+        <v>2.16</v>
       </c>
       <c r="H29" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="I29" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="K29" t="n">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N29" t="n">
-        <v>1.3</v>
+        <v>3.85</v>
       </c>
       <c r="O29" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="P29" t="n">
-        <v>1.29</v>
+        <v>1.97</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.23</v>
+        <v>1.98</v>
       </c>
       <c r="R29" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="S29" t="n">
-        <v>1.23</v>
+        <v>3.4</v>
       </c>
       <c r="T29" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="U29" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG29" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL29" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM29" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.03</v>
+        <v>24</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.03</v>
+        <v>23</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-08 13:21:28</t>
+          <t>2026-04-08 15:34:35</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,184 +6175,184 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Union Magdalena</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.18</v>
+        <v>2.68</v>
       </c>
       <c r="G30" t="n">
-        <v>2.46</v>
+        <v>2.78</v>
       </c>
       <c r="H30" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J30" t="n">
         <v>3.6</v>
       </c>
-      <c r="I30" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S30" t="n">
         <v>3.05</v>
       </c>
-      <c r="K30" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P30" t="n">
+      <c r="T30" t="n">
         <v>1.65</v>
       </c>
-      <c r="Q30" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S30" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.9</v>
-      </c>
       <c r="U30" t="n">
-        <v>1.89</v>
+        <v>2.34</v>
       </c>
       <c r="V30" t="n">
-        <v>1.31</v>
+        <v>1.54</v>
       </c>
       <c r="W30" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="X30" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="AA30" t="n">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="AB30" t="n">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="AC30" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD30" t="n">
-        <v>19</v>
+        <v>12.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="AF30" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH30" t="n">
         <v>15.5</v>
       </c>
-      <c r="AG30" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>23</v>
-      </c>
       <c r="AI30" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="AJ30" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL30" t="n">
         <v>38</v>
       </c>
-      <c r="AK30" t="n">
+      <c r="AM30" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA30" t="n">
         <v>32</v>
       </c>
-      <c r="AL30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BB30" t="n">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="BC30" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BF30" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>50</v>
+        <v>18.5</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-08 13:21:28</t>
+          <t>2026-04-08 15:34:35</t>
         </is>
       </c>
     </row>
@@ -6369,17 +6369,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CD Marathon</t>
+          <t>Juticalpa</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CD Motagua</t>
+          <t>Olancho</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -6407,22 +6407,22 @@
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="O31" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="P31" t="n">
         <v>1.29</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="R31" t="n">
         <v>1.18</v>
       </c>
       <c r="S31" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="T31" t="n">
         <v>1.01</v>
@@ -6546,7 +6546,395 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-08 13:21:28</t>
+          <t>2026-04-08 15:34:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Union Magdalena</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="X32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-04-08 15:34:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CD Marathon</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>CD Motagua</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K33" t="n">
+        <v>950</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-04-08 15:34:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH33"/>
+  <dimension ref="A1:BH34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>09:30:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia</t>
+          <t>Guizhou Zhucheng Athletic</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Beroe Stara Za</t>
+          <t>Hubei Istar</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="G2" t="n">
-        <v>1.66</v>
+        <v>44</v>
       </c>
       <c r="H2" t="n">
-        <v>6.8</v>
+        <v>1.5</v>
       </c>
       <c r="I2" t="n">
-        <v>8.199999999999999</v>
+        <v>44</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4</v>
+        <v>32</v>
       </c>
       <c r="L2" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>3.35</v>
+        <v>1.24</v>
       </c>
       <c r="O2" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="P2" t="n">
-        <v>1.81</v>
+        <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.04</v>
+        <v>1.4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>3.75</v>
+        <v>1.4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>2.5</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Lokomotiv Sofia</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Beroe Stara Za</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.62</v>
+        <v>1.58</v>
       </c>
       <c r="G3" t="n">
-        <v>2.74</v>
+        <v>1.66</v>
       </c>
       <c r="H3" t="n">
-        <v>2.74</v>
+        <v>6.8</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="L3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O3" t="n">
         <v>1.36</v>
       </c>
-      <c r="M3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N3" t="n">
-        <v>4</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.27</v>
-      </c>
       <c r="P3" t="n">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="Q3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U3" t="n">
         <v>1.79</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.26</v>
-      </c>
       <c r="V3" t="n">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="W3" t="n">
-        <v>1.58</v>
+        <v>2.5</v>
       </c>
       <c r="X3" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="Z3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>280</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK3" t="n">
         <v>22</v>
       </c>
-      <c r="AA3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="AL3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN3" t="n">
         <v>13</v>
       </c>
-      <c r="AC3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD3" t="n">
+      <c r="AO3" t="n">
+        <v>220</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>15</v>
       </c>
-      <c r="AE3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>11</v>
-      </c>
       <c r="AR3" t="n">
-        <v>17.5</v>
+        <v>4.7</v>
       </c>
       <c r="AS3" t="n">
-        <v>34</v>
+        <v>4.9</v>
       </c>
       <c r="AT3" t="n">
-        <v>10.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU3" t="n">
         <v>7.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AW3" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="AX3" t="n">
-        <v>15</v>
+        <v>6.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13.5</v>
+        <v>19</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="BF3" t="n">
-        <v>16.5</v>
+        <v>8.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>20</v>
+        <v>4.9</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.33</v>
+        <v>2.62</v>
       </c>
       <c r="G4" t="n">
-        <v>1.38</v>
+        <v>2.74</v>
       </c>
       <c r="H4" t="n">
-        <v>12.5</v>
+        <v>2.72</v>
       </c>
       <c r="I4" t="n">
-        <v>14.5</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>5.8</v>
+        <v>3.85</v>
       </c>
       <c r="L4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.32</v>
+        <v>1.66</v>
       </c>
       <c r="U4" t="n">
-        <v>1.74</v>
+        <v>2.26</v>
       </c>
       <c r="V4" t="n">
-        <v>1.07</v>
+        <v>1.5</v>
       </c>
       <c r="W4" t="n">
-        <v>3.6</v>
+        <v>1.57</v>
       </c>
       <c r="X4" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="Z4" t="n">
-        <v>150</v>
+        <v>22</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="AC4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD4" t="n">
         <v>15</v>
       </c>
-      <c r="AD4" t="n">
-        <v>60</v>
-      </c>
       <c r="AE4" t="n">
-        <v>330</v>
+        <v>36</v>
       </c>
       <c r="AF4" t="n">
-        <v>8.6</v>
+        <v>19</v>
       </c>
       <c r="AG4" t="n">
         <v>13</v>
       </c>
       <c r="AH4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>44</v>
       </c>
-      <c r="AI4" t="n">
-        <v>260</v>
-      </c>
-      <c r="AJ4" t="n">
+      <c r="AK4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP4" t="n">
         <v>13</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AQ4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG4" t="n">
         <v>20</v>
       </c>
-      <c r="AL4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>310</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>590</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1330,179 +1330,179 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.65</v>
+        <v>1.33</v>
       </c>
       <c r="G5" t="n">
-        <v>3.8</v>
+        <v>1.38</v>
       </c>
       <c r="H5" t="n">
-        <v>2.46</v>
+        <v>12.5</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6</v>
+        <v>14.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2.88</v>
+        <v>5.1</v>
       </c>
       <c r="K5" t="n">
-        <v>3.15</v>
+        <v>5.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="M5" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>2.84</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.59</v>
+        <v>1.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.44</v>
+        <v>1.89</v>
       </c>
       <c r="R5" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1.94</v>
+        <v>2.32</v>
       </c>
       <c r="U5" t="n">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="V5" t="n">
-        <v>1.62</v>
+        <v>1.07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.35</v>
+        <v>3.6</v>
       </c>
       <c r="X5" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="Y5" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>330</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>260</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>310</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>590</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB5" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Z5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>8</v>
-      </c>
       <c r="BC5" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="BD5" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.6</v>
+        <v>4.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
@@ -1524,186 +1524,186 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="G6" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="I6" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="J6" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="K6" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="L6" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="M6" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.52</v>
+        <v>2.84</v>
       </c>
       <c r="O6" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.78</v>
+        <v>2.46</v>
       </c>
       <c r="R6" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>1.94</v>
       </c>
       <c r="U6" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="V6" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="W6" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="X6" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z6" t="n">
         <v>16</v>
       </c>
       <c r="AA6" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE6" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AF6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AG6" t="n">
         <v>15.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI6" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AJ6" t="n">
         <v>70</v>
       </c>
       <c r="AK6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL6" t="n">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AM6" t="n">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="AN6" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AO6" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AP6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU6" t="n">
         <v>6</v>
       </c>
       <c r="AV6" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AX6" t="n">
         <v>18</v>
       </c>
       <c r="AY6" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BC6" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="BD6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BE6" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>36</v>
+        <v>7.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,186 +1718,186 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FK Novi Pazar</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Partizan Belgrade</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="H7" t="n">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="I7" t="n">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6</v>
+        <v>2.78</v>
       </c>
       <c r="K7" t="n">
-        <v>3.95</v>
+        <v>2.98</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="N7" t="n">
-        <v>3.7</v>
+        <v>2.52</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="P7" t="n">
-        <v>1.94</v>
+        <v>1.49</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.92</v>
+        <v>2.78</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="S7" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="T7" t="n">
-        <v>1.72</v>
+        <v>2.14</v>
       </c>
       <c r="U7" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="V7" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="W7" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="X7" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="Y7" t="n">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AA7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG7" t="n">
         <v>36</v>
       </c>
-      <c r="AB7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>16</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>FK Novi Pazar</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al-Quadisiya (KSA)</t>
+          <t>Partizan Belgrade</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X8" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU8" t="n">
         <v>7.2</v>
       </c>
-      <c r="G8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="AV8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>5.5</v>
       </c>
-      <c r="L8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2</v>
-      </c>
-      <c r="V8" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X8" t="n">
-        <v>26</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA8" t="n">
+      <c r="BA8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG8" t="n">
         <v>16</v>
       </c>
-      <c r="AB8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>80</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>250</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>130</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>140</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Saudi 1st Division</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,184 +2101,184 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13:20:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Al-Ula FC</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>Al-Quadisiya (KSA)</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.06</v>
+        <v>7.2</v>
       </c>
       <c r="G9" t="n">
-        <v>2.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>3.3</v>
+        <v>1.43</v>
       </c>
       <c r="I9" t="n">
-        <v>3.95</v>
+        <v>1.52</v>
       </c>
       <c r="J9" t="n">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="M9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="P9" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="R9" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="S9" t="n">
-        <v>2.84</v>
+        <v>2.58</v>
       </c>
       <c r="T9" t="n">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="U9" t="n">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.34</v>
+        <v>2.92</v>
       </c>
       <c r="W9" t="n">
-        <v>1.77</v>
+        <v>1.12</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AC9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>80</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>250</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>130</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>130</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU9" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AD9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AQ9" t="n">
+      <c r="AV9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW9" t="n">
         <v>12</v>
       </c>
-      <c r="AR9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS9" t="n">
+      <c r="AX9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG9" t="n">
         <v>5.4</v>
       </c>
-      <c r="AT9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Al Orubah</t>
+          <t>Al-Ula FC</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Faisaly ( KSA )</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.98</v>
+        <v>2.08</v>
       </c>
       <c r="G10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H10" t="n">
         <v>3.3</v>
       </c>
-      <c r="H10" t="n">
-        <v>2.24</v>
-      </c>
       <c r="I10" t="n">
-        <v>2.46</v>
+        <v>3.9</v>
       </c>
       <c r="J10" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K10" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="R10" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="T10" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="U10" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="V10" t="n">
-        <v>1.69</v>
+        <v>1.34</v>
       </c>
       <c r="W10" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="X10" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV10" t="n">
         <v>11</v>
       </c>
-      <c r="AD10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AW10" t="n">
-        <v>16.5</v>
+        <v>5.1</v>
       </c>
       <c r="AX10" t="n">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ10" t="n">
-        <v>11.5</v>
+        <v>4.4</v>
       </c>
       <c r="BA10" t="n">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="BE10" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>10.5</v>
+        <v>5.1</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>13:20:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Al Orubah</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouissat</t>
+          <t>Al Faisaly ( KSA )</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.3</v>
+        <v>2.98</v>
       </c>
       <c r="G11" t="n">
-        <v>1.47</v>
+        <v>3.3</v>
       </c>
       <c r="H11" t="n">
-        <v>7.8</v>
+        <v>2.24</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>2.46</v>
       </c>
       <c r="J11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K11" t="n">
         <v>4.2</v>
       </c>
-      <c r="K11" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>2.34</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="P11" t="n">
-        <v>1.54</v>
+        <v>2.22</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.08</v>
+        <v>1.69</v>
       </c>
       <c r="R11" t="n">
-        <v>1.14</v>
+        <v>1.49</v>
       </c>
       <c r="S11" t="n">
-        <v>3.05</v>
+        <v>2.72</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="W11" t="n">
-        <v>3.1</v>
+        <v>1.44</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>MB Rouissat</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.06</v>
+        <v>1.31</v>
       </c>
       <c r="G12" t="n">
-        <v>2.1</v>
+        <v>1.47</v>
       </c>
       <c r="H12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I12" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="K12" t="n">
-        <v>3.45</v>
+        <v>10.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="O12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P12" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="R12" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="S12" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="T12" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="X12" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="G13" t="n">
-        <v>2.44</v>
+        <v>2.14</v>
       </c>
       <c r="H13" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="I13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K13" t="n">
         <v>3.45</v>
       </c>
-      <c r="J13" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.55</v>
-      </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="P13" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="S13" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.71</v>
+        <v>1.97</v>
       </c>
       <c r="U13" t="n">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="X13" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="Y13" t="n">
         <v>13.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AA13" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="AB13" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC13" t="n">
         <v>7.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AE13" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AF13" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH13" t="n">
         <v>21</v>
       </c>
       <c r="AI13" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AJ13" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AK13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL13" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AM13" t="n">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="AN13" t="n">
         <v>20</v>
       </c>
       <c r="AO13" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AP13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AQ13" t="n">
         <v>12</v>
       </c>
       <c r="AR13" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AS13" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AT13" t="n">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU13" t="n">
         <v>7.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AX13" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="AY13" t="n">
         <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BA13" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC13" t="n">
-        <v>10.5</v>
+        <v>22</v>
       </c>
       <c r="BD13" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE13" t="n">
         <v>14</v>
       </c>
-      <c r="BE13" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BF13" t="n">
-        <v>9.4</v>
+        <v>17.5</v>
       </c>
       <c r="BG13" t="n">
         <v>13.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,179 +3076,179 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Erokspor A.S</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Amed Sportif Faaliyetler</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="G14" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="H14" t="n">
         <v>3.35</v>
       </c>
       <c r="I14" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="J14" t="n">
         <v>3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="L14" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="O14" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.68</v>
+        <v>2.02</v>
       </c>
       <c r="R14" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>2.68</v>
+        <v>3.45</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="U14" t="n">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="V14" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="X14" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH14" t="n">
         <v>21</v>
       </c>
-      <c r="Y14" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG14" t="n">
+      <c r="AI14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP14" t="n">
         <v>12</v>
       </c>
-      <c r="AH14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
+      <c r="AQ14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS14" t="n">
         <v>14</v>
       </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
+      <c r="AT14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW14" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>7.4</v>
       </c>
       <c r="AX14" t="n">
         <v>13.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.6</v>
+        <v>13.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="BC14" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BD14" t="n">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="BF14" t="n">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
@@ -3270,186 +3270,186 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Istanbulspor</t>
+          <t>Erokspor A.S</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Erzurum BB</t>
+          <t>Amed Sportif Faaliyetler</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N15" t="n">
         <v>4.6</v>
       </c>
-      <c r="G15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.75</v>
-      </c>
       <c r="O15" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="P15" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2</v>
+        <v>2.68</v>
       </c>
       <c r="T15" t="n">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="U15" t="n">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="V15" t="n">
-        <v>2.08</v>
+        <v>1.38</v>
       </c>
       <c r="W15" t="n">
-        <v>1.22</v>
+        <v>1.73</v>
       </c>
       <c r="X15" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y15" t="n">
         <v>18</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Z15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT15" t="n">
         <v>10.5</v>
       </c>
-      <c r="Z15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD15" t="n">
+      <c r="AU15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV15" t="n">
         <v>12</v>
       </c>
-      <c r="AE15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>46</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ15" t="n">
+      <c r="AW15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB15" t="n">
         <v>7</v>
       </c>
-      <c r="AR15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>27</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BC15" t="n">
-        <v>4.6</v>
+        <v>18</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.6</v>
+        <v>11</v>
       </c>
       <c r="BG15" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,179 +3464,179 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Istanbulspor</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Erzurum BB</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.12</v>
+        <v>4.6</v>
       </c>
       <c r="G16" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="H16" t="n">
-        <v>3.45</v>
+        <v>1.86</v>
       </c>
       <c r="I16" t="n">
-        <v>3.85</v>
+        <v>1.9</v>
       </c>
       <c r="J16" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K16" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O16" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P16" t="n">
         <v>1.94</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="R16" t="n">
         <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T16" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="U16" t="n">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="V16" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.76</v>
+        <v>1.23</v>
       </c>
       <c r="X16" t="n">
         <v>18</v>
       </c>
       <c r="Y16" t="n">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="AA16" t="n">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="AB16" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>18.5</v>
+        <v>12</v>
       </c>
       <c r="AE16" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="AF16" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT16" t="n">
         <v>13.5</v>
       </c>
-      <c r="AH16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AU16" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>10.5</v>
+        <v>4.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>8.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="AZ16" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>27</v>
       </c>
       <c r="BB16" t="n">
-        <v>20</v>
+        <v>4.8</v>
       </c>
       <c r="BC16" t="n">
-        <v>17</v>
+        <v>4.6</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>12</v>
+        <v>4.7</v>
       </c>
       <c r="BG16" t="n">
-        <v>30</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
@@ -3658,179 +3658,179 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cukaricki</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FK Radnicki 1923</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="G17" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="H17" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I17" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J17" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="L17" t="n">
         <v>1.3</v>
       </c>
       <c r="M17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N17" t="n">
         <v>3.75</v>
       </c>
       <c r="O17" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="P17" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="U17" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W17" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.22</v>
+        <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.08</v>
+        <v>19</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.22</v>
+        <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.93</v>
+        <v>7.4</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.86</v>
+        <v>6.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AW17" t="n">
-        <v>2.22</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>2</v>
+        <v>10.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.94</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ17" t="n">
-        <v>2.02</v>
+        <v>12.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.22</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>2.1</v>
+        <v>20</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.06</v>
+        <v>17</v>
       </c>
       <c r="BD17" t="n">
-        <v>2.22</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.22</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.22</v>
+        <v>30</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
@@ -3852,67 +3852,67 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Crvena Zvezda</t>
+          <t>Cukaricki</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FK Spartak</t>
+          <t>FK Radnicki 1923</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.07</v>
+        <v>2.16</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1</v>
+        <v>2.28</v>
       </c>
       <c r="H18" t="n">
-        <v>25</v>
+        <v>3.35</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="J18" t="n">
-        <v>17.5</v>
+        <v>3.35</v>
       </c>
       <c r="K18" t="n">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>12</v>
+        <v>3.75</v>
       </c>
       <c r="O18" t="n">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="P18" t="n">
-        <v>4.7</v>
+        <v>1.99</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.19</v>
+        <v>1.81</v>
       </c>
       <c r="R18" t="n">
-        <v>2.58</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>1.44</v>
+        <v>2.92</v>
       </c>
       <c r="T18" t="n">
-        <v>2.28</v>
+        <v>1.68</v>
       </c>
       <c r="U18" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="W18" t="n">
-        <v>11</v>
+        <v>1.78</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -3963,75 +3963,75 @@
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.06</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.85</v>
+        <v>2.42</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3.9</v>
+        <v>2.22</v>
       </c>
       <c r="AR18" t="n">
-        <v>3.95</v>
+        <v>2.34</v>
       </c>
       <c r="AS18" t="n">
-        <v>3.95</v>
+        <v>2.48</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.45</v>
+        <v>2.14</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.7</v>
+        <v>2.04</v>
       </c>
       <c r="AV18" t="n">
-        <v>3.9</v>
+        <v>2.22</v>
       </c>
       <c r="AW18" t="n">
-        <v>3.95</v>
+        <v>2.48</v>
       </c>
       <c r="AX18" t="n">
-        <v>4.5</v>
+        <v>2.22</v>
       </c>
       <c r="AY18" t="n">
-        <v>5.1</v>
+        <v>2.14</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.8</v>
+        <v>2.24</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.95</v>
+        <v>2.48</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.2</v>
+        <v>2.34</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.9</v>
+        <v>2.3</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.75</v>
+        <v>2.38</v>
       </c>
       <c r="BE18" t="n">
-        <v>3.95</v>
+        <v>2.48</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.66</v>
+        <v>2.22</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.95</v>
+        <v>2.38</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PFC Levski Sofia</t>
+          <t>Crvena Zvezda</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>FK Spartak</t>
         </is>
       </c>
       <c r="F19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H19" t="n">
+        <v>42</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>36</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N19" t="n">
+        <v>12</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S19" t="n">
         <v>1.44</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="H19" t="n">
-        <v>9</v>
-      </c>
-      <c r="I19" t="n">
-        <v>11</v>
-      </c>
-      <c r="J19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.85</v>
       </c>
       <c r="T19" t="n">
         <v>2.28</v>
       </c>
       <c r="U19" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="X19" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>11</v>
+        <v>2.06</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>10.5</v>
+        <v>3.85</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5.7</v>
+        <v>3.9</v>
       </c>
       <c r="AR19" t="n">
-        <v>6.8</v>
+        <v>3.95</v>
       </c>
       <c r="AS19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB19" t="n">
         <v>7.2</v>
       </c>
-      <c r="AT19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>10</v>
-      </c>
       <c r="BC19" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BD19" t="n">
-        <v>40</v>
+        <v>3.75</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.2</v>
+        <v>3.95</v>
       </c>
       <c r="BF19" t="n">
-        <v>8.4</v>
+        <v>1.66</v>
       </c>
       <c r="BG19" t="n">
-        <v>7.2</v>
+        <v>3.95</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Saudi 1st Division</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>14:40:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Al-Adalh</t>
+          <t>PFC Levski Sofia</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Batin</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.36</v>
+        <v>1.46</v>
       </c>
       <c r="G20" t="n">
-        <v>2.68</v>
+        <v>1.51</v>
       </c>
       <c r="H20" t="n">
-        <v>2.74</v>
+        <v>9.4</v>
       </c>
       <c r="I20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N20" t="n">
         <v>3.15</v>
       </c>
-      <c r="J20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N20" t="n">
-        <v>4.3</v>
-      </c>
       <c r="O20" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="P20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q20" t="n">
         <v>2.14</v>
       </c>
-      <c r="Q20" t="n">
-        <v>1.7</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="S20" t="n">
-        <v>2.76</v>
+        <v>3.9</v>
       </c>
       <c r="T20" t="n">
-        <v>1.61</v>
+        <v>2.46</v>
       </c>
       <c r="U20" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="V20" t="n">
-        <v>1.46</v>
+        <v>1.1</v>
       </c>
       <c r="W20" t="n">
-        <v>1.59</v>
+        <v>2.98</v>
       </c>
       <c r="X20" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="Y20" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="Z20" t="n">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="AA20" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>15</v>
+        <v>6.8</v>
       </c>
       <c r="AC20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>260</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>230</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL20" t="n">
+      <c r="AQ20" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD20" t="n">
         <v>40</v>
       </c>
-      <c r="AM20" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>4</v>
-      </c>
       <c r="BE20" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>12.5</v>
+        <v>8.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>16.5</v>
+        <v>7.6</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,184 +4429,184 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:40:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al-Adalh</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ZED FC</t>
+          <t>Al Batin</t>
         </is>
       </c>
       <c r="F21" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I21" t="n">
         <v>3.15</v>
       </c>
-      <c r="G21" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2.94</v>
-      </c>
       <c r="J21" t="n">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="L21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W21" t="n">
         <v>1.59</v>
       </c>
-      <c r="M21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.42</v>
-      </c>
       <c r="X21" t="n">
-        <v>8.6</v>
+        <v>90</v>
       </c>
       <c r="Y21" t="n">
-        <v>8.6</v>
+        <v>17</v>
       </c>
       <c r="Z21" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="AA21" t="n">
         <v>55</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.6</v>
+        <v>15</v>
       </c>
       <c r="AC21" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AE21" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI21" t="n">
         <v>46</v>
       </c>
-      <c r="AF21" t="n">
+      <c r="AJ21" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN21" t="n">
         <v>20</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AO21" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR21" t="n">
         <v>15.5</v>
       </c>
-      <c r="AH21" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>260</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>75</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>15</v>
-      </c>
       <c r="AS21" t="n">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="AT21" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AW21" t="n">
-        <v>8.6</v>
+        <v>4</v>
       </c>
       <c r="AX21" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="AZ21" t="n">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.4</v>
+        <v>4.1</v>
       </c>
       <c r="BB21" t="n">
-        <v>9</v>
+        <v>4.1</v>
       </c>
       <c r="BC21" t="n">
-        <v>8.800000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>9.6</v>
+        <v>4</v>
       </c>
       <c r="BE21" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="BF21" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
@@ -4628,186 +4628,186 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>ZED FC</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.06</v>
+        <v>3.15</v>
       </c>
       <c r="G22" t="n">
-        <v>2.18</v>
+        <v>3.35</v>
       </c>
       <c r="H22" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="I22" t="n">
-        <v>5.7</v>
+        <v>2.94</v>
       </c>
       <c r="J22" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="K22" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="L22" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="M22" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="N22" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="O22" t="n">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="P22" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="R22" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="S22" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="T22" t="n">
-        <v>2.54</v>
+        <v>2.22</v>
       </c>
       <c r="U22" t="n">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="V22" t="n">
-        <v>1.21</v>
+        <v>1.51</v>
       </c>
       <c r="W22" t="n">
-        <v>1.85</v>
+        <v>1.42</v>
       </c>
       <c r="X22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT22" t="n">
         <v>7.6</v>
       </c>
-      <c r="Y22" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>210</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC22" t="n">
+      <c r="AU22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW22" t="n">
         <v>8.6</v>
       </c>
-      <c r="AD22" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>150</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>200</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>420</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>310</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AQ22" t="n">
+      <c r="AX22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BE22" t="n">
         <v>10</v>
       </c>
-      <c r="AR22" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BF22" t="n">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,186 +4822,186 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="F23" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G23" t="n">
         <v>2.18</v>
       </c>
-      <c r="G23" t="n">
-        <v>2.26</v>
-      </c>
       <c r="H23" t="n">
-        <v>3.25</v>
+        <v>5.1</v>
       </c>
       <c r="I23" t="n">
-        <v>3.45</v>
+        <v>5.7</v>
       </c>
       <c r="J23" t="n">
-        <v>3.75</v>
+        <v>2.84</v>
       </c>
       <c r="K23" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="M23" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="N23" t="n">
-        <v>4.2</v>
+        <v>2.18</v>
       </c>
       <c r="O23" t="n">
-        <v>1.26</v>
+        <v>1.79</v>
       </c>
       <c r="P23" t="n">
-        <v>2.12</v>
+        <v>1.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.77</v>
+        <v>3.2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.44</v>
+        <v>1.13</v>
       </c>
       <c r="S23" t="n">
-        <v>2.96</v>
+        <v>7.2</v>
       </c>
       <c r="T23" t="n">
-        <v>1.67</v>
+        <v>2.54</v>
       </c>
       <c r="U23" t="n">
-        <v>2.28</v>
+        <v>1.56</v>
       </c>
       <c r="V23" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="W23" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="X23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>210</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>200</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>420</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>310</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB23" t="n">
         <v>22</v>
       </c>
-      <c r="Y23" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BC23" t="n">
-        <v>7.8</v>
+        <v>30</v>
       </c>
       <c r="BD23" t="n">
-        <v>8.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>9.6</v>
+        <v>5.6</v>
       </c>
       <c r="BF23" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="BG23" t="n">
-        <v>8.4</v>
+        <v>5.6</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,184 +5011,184 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Al-Ettifaq</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>Al Riyadh SC</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="G24" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="H24" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="I24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J24" t="n">
         <v>3.75</v>
       </c>
-      <c r="J24" t="n">
-        <v>3.4</v>
-      </c>
       <c r="K24" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="L24" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="N24" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="O24" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="P24" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="Q24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U24" t="n">
         <v>2.28</v>
       </c>
-      <c r="R24" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.98</v>
-      </c>
       <c r="V24" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="X24" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB24" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y24" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AC24" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AD24" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AF24" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AG24" t="n">
         <v>11.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AI24" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AJ24" t="n">
         <v>29</v>
       </c>
       <c r="AK24" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL24" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN24" t="n">
-        <v>23</v>
+        <v>15.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AP24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF24" t="n">
         <v>11</v>
       </c>
-      <c r="AQ24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>65</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>27</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>42</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>21</v>
-      </c>
       <c r="BG24" t="n">
-        <v>50</v>
+        <v>8.4</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
@@ -5210,179 +5210,179 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Nottm Forest</t>
         </is>
       </c>
       <c r="F25" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J25" t="n">
         <v>3.4</v>
       </c>
-      <c r="G25" t="n">
+      <c r="K25" t="n">
         <v>3.45</v>
       </c>
-      <c r="H25" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="J25" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3.4</v>
-      </c>
       <c r="L25" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="M25" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="O25" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="P25" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="R25" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="T25" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="U25" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="V25" t="n">
-        <v>1.69</v>
+        <v>1.36</v>
       </c>
       <c r="W25" t="n">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="X25" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y25" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="Z25" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="AA25" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AB25" t="n">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC25" t="n">
         <v>7.4</v>
       </c>
       <c r="AD25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG25" t="n">
         <v>11.5</v>
       </c>
-      <c r="AE25" t="n">
+      <c r="AH25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK25" t="n">
         <v>27</v>
       </c>
-      <c r="AF25" t="n">
+      <c r="AL25" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>65</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF25" t="n">
         <v>22</v>
       </c>
-      <c r="AG25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB25" t="n">
+      <c r="BG25" t="n">
         <v>50</v>
       </c>
-      <c r="BC25" t="n">
-        <v>36</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>48</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>38</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>36</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>22</v>
-      </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
@@ -5404,34 +5404,34 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.44</v>
+        <v>3.45</v>
       </c>
       <c r="G26" t="n">
-        <v>2.46</v>
+        <v>3.5</v>
       </c>
       <c r="H26" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="I26" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J26" t="n">
         <v>3.4</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.35</v>
       </c>
       <c r="K26" t="n">
         <v>3.45</v>
       </c>
       <c r="L26" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M26" t="n">
         <v>1.09</v>
@@ -5440,150 +5440,150 @@
         <v>3.5</v>
       </c>
       <c r="O26" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P26" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T26" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U26" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V26" t="n">
-        <v>1.42</v>
+        <v>1.71</v>
       </c>
       <c r="W26" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="X26" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z26" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AA26" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AB26" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="AC26" t="n">
         <v>7.4</v>
       </c>
       <c r="AD26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG26" t="n">
         <v>14.5</v>
       </c>
-      <c r="AE26" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AH26" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI26" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AJ26" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AK26" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="AL26" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AM26" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN26" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="AO26" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="AP26" t="n">
         <v>11</v>
       </c>
       <c r="AQ26" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AR26" t="n">
-        <v>20</v>
+        <v>13.5</v>
       </c>
       <c r="AS26" t="n">
         <v>30</v>
       </c>
       <c r="AT26" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AU26" t="n">
         <v>7</v>
       </c>
       <c r="AV26" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AW26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC26" t="n">
         <v>36</v>
       </c>
-      <c r="AX26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA26" t="n">
+      <c r="BD26" t="n">
         <v>48</v>
       </c>
-      <c r="BB26" t="n">
-        <v>29</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>26</v>
-      </c>
       <c r="BE26" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF26" t="n">
         <v>40</v>
       </c>
-      <c r="BF26" t="n">
+      <c r="BG26" t="n">
         <v>21</v>
       </c>
-      <c r="BG26" t="n">
-        <v>25</v>
-      </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5598,186 +5598,186 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MC El Bayadh</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.28</v>
+        <v>2.42</v>
       </c>
       <c r="G27" t="n">
-        <v>1.34</v>
+        <v>2.46</v>
       </c>
       <c r="H27" t="n">
-        <v>16.5</v>
+        <v>3.35</v>
       </c>
       <c r="I27" t="n">
-        <v>23</v>
+        <v>3.4</v>
       </c>
       <c r="J27" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="K27" t="n">
-        <v>5.9</v>
+        <v>3.45</v>
       </c>
       <c r="L27" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M27" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N27" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="O27" t="n">
         <v>1.38</v>
       </c>
       <c r="P27" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
       </c>
       <c r="T27" t="n">
-        <v>2.88</v>
+        <v>1.87</v>
       </c>
       <c r="U27" t="n">
-        <v>1.43</v>
+        <v>2.08</v>
       </c>
       <c r="V27" t="n">
-        <v>1.04</v>
+        <v>1.41</v>
       </c>
       <c r="W27" t="n">
-        <v>3.9</v>
+        <v>1.68</v>
       </c>
       <c r="X27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD27" t="n">
         <v>14.5</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="AE27" t="n">
         <v>42</v>
       </c>
-      <c r="Z27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>85</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1000</v>
-      </c>
       <c r="AF27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU27" t="n">
         <v>7</v>
       </c>
-      <c r="AG27" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>65</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>10</v>
-      </c>
       <c r="AV27" t="n">
-        <v>5.3</v>
+        <v>12.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.7</v>
+        <v>36</v>
       </c>
       <c r="AX27" t="n">
-        <v>4.8</v>
+        <v>13</v>
       </c>
       <c r="AY27" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>5.3</v>
+        <v>16.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>5.6</v>
+        <v>48</v>
       </c>
       <c r="BB27" t="n">
-        <v>7.4</v>
+        <v>29</v>
       </c>
       <c r="BC27" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="BD27" t="n">
-        <v>5.3</v>
+        <v>26</v>
       </c>
       <c r="BE27" t="n">
-        <v>5.7</v>
+        <v>40</v>
       </c>
       <c r="BF27" t="n">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="BG27" t="n">
-        <v>5.7</v>
+        <v>40</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5792,179 +5792,179 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>MC El Bayadh</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.77</v>
+        <v>1.28</v>
       </c>
       <c r="G28" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="H28" t="n">
-        <v>5.5</v>
+        <v>16.5</v>
       </c>
       <c r="I28" t="n">
-        <v>5.8</v>
+        <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="K28" t="n">
-        <v>3.9</v>
+        <v>5.9</v>
       </c>
       <c r="L28" t="n">
         <v>1.43</v>
       </c>
       <c r="M28" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="O28" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="P28" t="n">
-        <v>1.92</v>
+        <v>1.71</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="R28" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="S28" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="T28" t="n">
-        <v>1.93</v>
+        <v>2.88</v>
       </c>
       <c r="U28" t="n">
-        <v>2.02</v>
+        <v>1.43</v>
       </c>
       <c r="V28" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="W28" t="n">
-        <v>2.26</v>
+        <v>3.9</v>
       </c>
       <c r="X28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>85</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>65</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC28" t="n">
         <v>15</v>
       </c>
-      <c r="Y28" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>38</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>65</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>17</v>
-      </c>
       <c r="BD28" t="n">
-        <v>32</v>
+        <v>5.3</v>
       </c>
       <c r="BE28" t="n">
-        <v>14.5</v>
+        <v>5.7</v>
       </c>
       <c r="BF28" t="n">
-        <v>11</v>
+        <v>6.2</v>
       </c>
       <c r="BG28" t="n">
-        <v>15</v>
+        <v>5.7</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
@@ -5986,179 +5986,179 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.12</v>
+        <v>1.74</v>
       </c>
       <c r="G29" t="n">
-        <v>2.16</v>
+        <v>1.75</v>
       </c>
       <c r="H29" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J29" t="n">
         <v>3.85</v>
       </c>
-      <c r="I29" t="n">
-        <v>4</v>
-      </c>
-      <c r="J29" t="n">
-        <v>3.6</v>
-      </c>
       <c r="K29" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M29" t="n">
         <v>1.07</v>
       </c>
       <c r="N29" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="O29" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P29" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S29" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="T29" t="n">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="U29" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="V29" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="W29" t="n">
-        <v>1.86</v>
+        <v>2.32</v>
       </c>
       <c r="X29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y29" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="AA29" t="n">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="AB29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF29" t="n">
         <v>10</v>
       </c>
-      <c r="AC29" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>13</v>
-      </c>
       <c r="AG29" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH29" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AI29" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AJ29" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="AK29" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AL29" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM29" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO29" t="n">
         <v>110</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>46</v>
       </c>
       <c r="AP29" t="n">
         <v>13</v>
       </c>
       <c r="AQ29" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AS29" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AT29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>75</v>
+      </c>
+      <c r="AX29" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AU29" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>12</v>
-      </c>
       <c r="AY29" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ29" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>70</v>
+      </c>
+      <c r="BB29" t="n">
         <v>16</v>
       </c>
-      <c r="BA29" t="n">
+      <c r="BC29" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>17</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG29" t="n">
         <v>16.5</v>
       </c>
-      <c r="BB29" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>15</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>15</v>
-      </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
@@ -6180,186 +6180,186 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Shakhtar</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.68</v>
+        <v>2.16</v>
       </c>
       <c r="G30" t="n">
-        <v>2.78</v>
+        <v>2.2</v>
       </c>
       <c r="H30" t="n">
-        <v>2.76</v>
+        <v>3.75</v>
       </c>
       <c r="I30" t="n">
-        <v>2.82</v>
+        <v>3.85</v>
       </c>
       <c r="J30" t="n">
         <v>3.6</v>
       </c>
       <c r="K30" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L30" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
         <v>1.06</v>
       </c>
       <c r="N30" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="O30" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="P30" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="R30" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S30" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="T30" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="U30" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="V30" t="n">
-        <v>1.54</v>
+        <v>1.35</v>
       </c>
       <c r="W30" t="n">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="X30" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="Y30" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP30" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z30" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB30" t="n">
+      <c r="AQ30" t="n">
         <v>13.5</v>
       </c>
-      <c r="AC30" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF30" t="n">
+      <c r="AR30" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC30" t="n">
         <v>19.5</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>24</v>
       </c>
       <c r="BD30" t="n">
         <v>32</v>
       </c>
       <c r="BE30" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BF30" t="n">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>18.5</v>
+        <v>38</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,191 +6369,191 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Juticalpa</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olancho</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="G31" t="n">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="H31" t="n">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="I31" t="n">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="J31" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="K31" t="n">
-        <v>950</v>
+        <v>3.65</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M31" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N31" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="O31" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="P31" t="n">
-        <v>1.29</v>
+        <v>2.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.23</v>
+        <v>1.84</v>
       </c>
       <c r="R31" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="S31" t="n">
-        <v>1.23</v>
+        <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="U31" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="X31" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB31" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD31" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF31" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH31" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK31" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL31" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM31" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO31" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.03</v>
+        <v>36</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.03</v>
+        <v>25</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.03</v>
+        <v>24</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.03</v>
+        <v>60</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6568,109 +6568,109 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Union Magdalena</t>
+          <t>Juticalpa</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>Olancho</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.18</v>
+        <v>1.04</v>
       </c>
       <c r="G32" t="n">
-        <v>2.46</v>
+        <v>1000</v>
       </c>
       <c r="H32" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="I32" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="J32" t="n">
-        <v>3.05</v>
+        <v>1.03</v>
       </c>
       <c r="K32" t="n">
-        <v>3.55</v>
+        <v>950</v>
       </c>
       <c r="L32" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>2.96</v>
+        <v>1.3</v>
       </c>
       <c r="O32" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="P32" t="n">
-        <v>1.65</v>
+        <v>1.29</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.24</v>
+        <v>1.23</v>
       </c>
       <c r="R32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S32" t="n">
         <v>1.24</v>
       </c>
-      <c r="S32" t="n">
-        <v>4.2</v>
-      </c>
       <c r="T32" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="U32" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="V32" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y32" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z32" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA32" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC32" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD32" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE32" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG32" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH32" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI32" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK32" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL32" t="n">
         <v>1000</v>
@@ -6679,262 +6679,456 @@
         <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AQ32" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AR32" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AS32" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AT32" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AU32" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV32" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW32" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX32" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AY32" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AZ32" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BA32" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BB32" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BC32" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BD32" t="n">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="BE32" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BF32" t="n">
-        <v>21</v>
+        <v>1.05</v>
       </c>
       <c r="BG32" t="n">
-        <v>5.8</v>
+        <v>1.05</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-08 15:34:35</t>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Union Magdalena</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="X33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-04-08 17:49:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Honduras Liga Nacional</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>22:30:00</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>CD Marathon</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>CD Motagua</t>
         </is>
       </c>
-      <c r="F33" t="n">
+      <c r="F34" t="n">
         <v>1.04</v>
       </c>
-      <c r="G33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H33" t="n">
+      <c r="G34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H34" t="n">
         <v>1.04</v>
       </c>
-      <c r="I33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J33" t="n">
+      <c r="I34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J34" t="n">
         <v>1.03</v>
       </c>
-      <c r="K33" t="n">
+      <c r="K34" t="n">
         <v>950</v>
       </c>
-      <c r="L33" t="n">
+      <c r="L34" t="n">
         <v>1.01</v>
       </c>
-      <c r="M33" t="n">
+      <c r="M34" t="n">
         <v>1.01</v>
       </c>
-      <c r="N33" t="n">
+      <c r="N34" t="n">
         <v>1.01</v>
       </c>
-      <c r="O33" t="n">
+      <c r="O34" t="n">
         <v>1.29</v>
       </c>
-      <c r="P33" t="n">
+      <c r="P34" t="n">
         <v>1.29</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="Q34" t="n">
         <v>1.29</v>
       </c>
-      <c r="R33" t="n">
+      <c r="R34" t="n">
         <v>1.18</v>
       </c>
-      <c r="S33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T33" t="n">
+      <c r="S34" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T34" t="n">
         <v>1.01</v>
       </c>
-      <c r="U33" t="n">
+      <c r="U34" t="n">
         <v>1.01</v>
       </c>
-      <c r="V33" t="n">
+      <c r="V34" t="n">
         <v>1.01</v>
       </c>
-      <c r="W33" t="n">
+      <c r="W34" t="n">
         <v>1.01</v>
       </c>
-      <c r="X33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP33" t="n">
+      <c r="X34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP34" t="n">
         <v>1.03</v>
       </c>
-      <c r="AQ33" t="n">
+      <c r="AQ34" t="n">
         <v>1.03</v>
       </c>
-      <c r="AR33" t="n">
+      <c r="AR34" t="n">
         <v>1.03</v>
       </c>
-      <c r="AS33" t="n">
+      <c r="AS34" t="n">
         <v>1.03</v>
       </c>
-      <c r="AT33" t="n">
+      <c r="AT34" t="n">
         <v>1.03</v>
       </c>
-      <c r="AU33" t="n">
+      <c r="AU34" t="n">
         <v>1.03</v>
       </c>
-      <c r="AV33" t="n">
+      <c r="AV34" t="n">
         <v>1.03</v>
       </c>
-      <c r="AW33" t="n">
+      <c r="AW34" t="n">
         <v>1.03</v>
       </c>
-      <c r="AX33" t="n">
+      <c r="AX34" t="n">
         <v>1.03</v>
       </c>
-      <c r="AY33" t="n">
+      <c r="AY34" t="n">
         <v>1.03</v>
       </c>
-      <c r="AZ33" t="n">
+      <c r="AZ34" t="n">
         <v>1.03</v>
       </c>
-      <c r="BA33" t="n">
+      <c r="BA34" t="n">
         <v>1.03</v>
       </c>
-      <c r="BB33" t="n">
+      <c r="BB34" t="n">
         <v>1.03</v>
       </c>
-      <c r="BC33" t="n">
+      <c r="BC34" t="n">
         <v>1.03</v>
       </c>
-      <c r="BD33" t="n">
+      <c r="BD34" t="n">
         <v>1.03</v>
       </c>
-      <c r="BE33" t="n">
+      <c r="BE34" t="n">
         <v>1.03</v>
       </c>
-      <c r="BF33" t="n">
+      <c r="BF34" t="n">
         <v>1.01</v>
       </c>
-      <c r="BG33" t="n">
+      <c r="BG34" t="n">
         <v>1.01</v>
       </c>
-      <c r="BH33" t="inlineStr">
-        <is>
-          <t>2026-04-08 15:34:35</t>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-04-08 17:49:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH34"/>
+  <dimension ref="A1:BH35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -769,7 +769,7 @@
         <v>44</v>
       </c>
       <c r="J2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K2" t="n">
         <v>32</v>
@@ -781,7 +781,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
         <v>1.4</v>
@@ -865,52 +865,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>1.58</v>
       </c>
       <c r="G3" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="H3" t="n">
         <v>6.8</v>
@@ -963,13 +963,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K3" t="n">
         <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
@@ -987,7 +987,7 @@
         <v>2.06</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S3" t="n">
         <v>3.75</v>
@@ -1002,7 +1002,7 @@
         <v>1.14</v>
       </c>
       <c r="W3" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="X3" t="n">
         <v>15.5</v>
@@ -1011,10 +1011,10 @@
         <v>24</v>
       </c>
       <c r="Z3" t="n">
-        <v>70</v>
+        <v>400</v>
       </c>
       <c r="AA3" t="n">
-        <v>280</v>
+        <v>700</v>
       </c>
       <c r="AB3" t="n">
         <v>8.199999999999999</v>
@@ -1026,10 +1026,10 @@
         <v>32</v>
       </c>
       <c r="AE3" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AF3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG3" t="n">
         <v>12</v>
@@ -1038,10 +1038,10 @@
         <v>29</v>
       </c>
       <c r="AI3" t="n">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AJ3" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK3" t="n">
         <v>22</v>
@@ -1050,13 +1050,13 @@
         <v>55</v>
       </c>
       <c r="AM3" t="n">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="AN3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>220</v>
+        <v>700</v>
       </c>
       <c r="AP3" t="n">
         <v>10</v>
@@ -1065,56 +1065,56 @@
         <v>15</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV3" t="n">
         <v>21</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="n">
         <v>19</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB3" t="n">
         <v>11.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.7</v>
+        <v>19.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BF3" t="n">
         <v>8.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G4" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="H4" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L4" t="n">
         <v>1.32</v>
@@ -1193,22 +1193,22 @@
         <v>2.26</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W4" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="X4" t="n">
         <v>19.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA4" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AB4" t="n">
         <v>13</v>
@@ -1217,10 +1217,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD4" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF4" t="n">
         <v>19</v>
@@ -1232,25 +1232,25 @@
         <v>17</v>
       </c>
       <c r="AI4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>42</v>
       </c>
-      <c r="AJ4" t="n">
-        <v>44</v>
-      </c>
       <c r="AK4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL4" t="n">
         <v>38</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AN4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AP4" t="n">
         <v>13</v>
@@ -1259,7 +1259,7 @@
         <v>11</v>
       </c>
       <c r="AR4" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS4" t="n">
         <v>34</v>
@@ -1274,7 +1274,7 @@
         <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="AX4" t="n">
         <v>15</v>
@@ -1286,29 +1286,29 @@
         <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.2</v>
+        <v>32</v>
       </c>
       <c r="BC4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BG4" t="n">
         <v>20</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="G5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="H5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="I5" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="J5" t="n">
         <v>5.1</v>
@@ -1387,16 +1387,16 @@
         <v>1.74</v>
       </c>
       <c r="V5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W5" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="X5" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="Z5" t="n">
         <v>150</v>
@@ -1405,70 +1405,70 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AD5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AE5" t="n">
         <v>330</v>
       </c>
       <c r="AF5" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AG5" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="AI5" t="n">
         <v>260</v>
       </c>
       <c r="AJ5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AK5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AL5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM5" t="n">
         <v>310</v>
       </c>
       <c r="AN5" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO5" t="n">
-        <v>590</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
         <v>14</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.4</v>
+        <v>24</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="AT5" t="n">
         <v>6.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.2</v>
+        <v>34</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX5" t="n">
         <v>6.2</v>
@@ -1477,32 +1477,32 @@
         <v>9</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.4</v>
+        <v>16</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BC5" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.4</v>
+        <v>30</v>
       </c>
       <c r="BF5" t="n">
         <v>5.9</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.5</v>
+        <v>15</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1536,37 @@
         <v>3.6</v>
       </c>
       <c r="G6" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="H6" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I6" t="n">
         <v>2.6</v>
       </c>
       <c r="J6" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="K6" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="M6" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="O6" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P6" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R6" t="n">
         <v>1.21</v>
@@ -1575,7 +1575,7 @@
         <v>4.8</v>
       </c>
       <c r="T6" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="U6" t="n">
         <v>1.88</v>
@@ -1584,16 +1584,16 @@
         <v>1.62</v>
       </c>
       <c r="W6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="X6" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA6" t="n">
         <v>42</v>
@@ -1602,7 +1602,7 @@
         <v>11</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD6" t="n">
         <v>13</v>
@@ -1611,37 +1611,37 @@
         <v>38</v>
       </c>
       <c r="AF6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG6" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AH6" t="n">
         <v>21</v>
       </c>
       <c r="AI6" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AJ6" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AK6" t="n">
         <v>55</v>
       </c>
       <c r="AL6" t="n">
-        <v>75</v>
+        <v>380</v>
       </c>
       <c r="AM6" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AO6" t="n">
         <v>40</v>
       </c>
       <c r="AP6" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AQ6" t="n">
         <v>7.4</v>
@@ -1650,7 +1650,7 @@
         <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT6" t="n">
         <v>9.4</v>
@@ -1662,7 +1662,7 @@
         <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX6" t="n">
         <v>18</v>
@@ -1671,32 +1671,32 @@
         <v>12.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="BB6" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="BC6" t="n">
         <v>40</v>
       </c>
       <c r="BD6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
@@ -1739,37 +1739,37 @@
         <v>2.8</v>
       </c>
       <c r="J7" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="K7" t="n">
         <v>2.98</v>
       </c>
       <c r="L7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="M7" t="n">
         <v>1.14</v>
       </c>
       <c r="N7" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="O7" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="P7" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="R7" t="n">
         <v>1.17</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="T7" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U7" t="n">
         <v>1.78</v>
@@ -1781,19 +1781,19 @@
         <v>1.39</v>
       </c>
       <c r="X7" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="Y7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z7" t="n">
         <v>16</v>
       </c>
       <c r="AA7" t="n">
-        <v>48</v>
+        <v>220</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC7" t="n">
         <v>6.8</v>
@@ -1802,7 +1802,7 @@
         <v>13.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>50</v>
+        <v>230</v>
       </c>
       <c r="AF7" t="n">
         <v>21</v>
@@ -1811,25 +1811,25 @@
         <v>15.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AJ7" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AK7" t="n">
-        <v>60</v>
+        <v>440</v>
       </c>
       <c r="AL7" t="n">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AM7" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AO7" t="n">
         <v>55</v>
@@ -1838,16 +1838,16 @@
         <v>7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR7" t="n">
         <v>14</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU7" t="n">
         <v>6</v>
@@ -1856,41 +1856,41 @@
         <v>11.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="AX7" t="n">
         <v>18</v>
       </c>
       <c r="AY7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AZ7" t="n">
         <v>20</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.7</v>
+        <v>12</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.7</v>
+        <v>11.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.6</v>
+        <v>11</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.8</v>
+        <v>12</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.9</v>
+        <v>13.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.7</v>
+        <v>12</v>
       </c>
       <c r="BG7" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
@@ -1924,16 +1924,16 @@
         <v>3.05</v>
       </c>
       <c r="G8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H8" t="n">
         <v>2.36</v>
       </c>
       <c r="I8" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="J8" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K8" t="n">
         <v>3.9</v>
@@ -1969,64 +1969,64 @@
         <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W8" t="n">
         <v>1.44</v>
       </c>
       <c r="X8" t="n">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="Y8" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="Z8" t="n">
         <v>970</v>
       </c>
       <c r="AA8" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AB8" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="AC8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AF8" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AG8" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AH8" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AI8" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AJ8" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO8" t="n">
         <v>55</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>22</v>
       </c>
       <c r="AP8" t="n">
         <v>12</v>
@@ -2035,10 +2035,10 @@
         <v>8.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AT8" t="n">
         <v>10</v>
@@ -2050,7 +2050,7 @@
         <v>9</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="AX8" t="n">
         <v>15.5</v>
@@ -2059,32 +2059,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC8" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF8" t="n">
         <v>7</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>6.2</v>
       </c>
       <c r="BG8" t="n">
         <v>16</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
@@ -2121,10 +2121,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="I9" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="J9" t="n">
         <v>4.8</v>
@@ -2133,7 +2133,7 @@
         <v>5.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M9" t="n">
         <v>1.04</v>
@@ -2145,10 +2145,10 @@
         <v>1.21</v>
       </c>
       <c r="P9" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="R9" t="n">
         <v>1.52</v>
@@ -2163,16 +2163,16 @@
         <v>2</v>
       </c>
       <c r="V9" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="W9" t="n">
         <v>1.12</v>
       </c>
       <c r="X9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y9" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z9" t="n">
         <v>9.800000000000001</v>
@@ -2181,40 +2181,40 @@
         <v>14</v>
       </c>
       <c r="AB9" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="AC9" t="n">
         <v>12.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AF9" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AG9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI9" t="n">
         <v>34</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>38</v>
       </c>
       <c r="AJ9" t="n">
         <v>250</v>
       </c>
       <c r="AK9" t="n">
-        <v>130</v>
+        <v>480</v>
       </c>
       <c r="AL9" t="n">
-        <v>110</v>
+        <v>390</v>
       </c>
       <c r="AM9" t="n">
-        <v>130</v>
+        <v>390</v>
       </c>
       <c r="AN9" t="n">
         <v>130</v>
@@ -2235,7 +2235,7 @@
         <v>11.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="AU9" t="n">
         <v>9.800000000000001</v>
@@ -2247,38 +2247,38 @@
         <v>12</v>
       </c>
       <c r="AX9" t="n">
-        <v>6.2</v>
+        <v>50</v>
       </c>
       <c r="AY9" t="n">
-        <v>6</v>
+        <v>15.5</v>
       </c>
       <c r="AZ9" t="n">
         <v>19</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.4</v>
+        <v>28</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="BG9" t="n">
         <v>5.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
@@ -2369,16 +2369,16 @@
         <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD10" t="n">
         <v>1000</v>
@@ -2387,49 +2387,49 @@
         <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="AT10" t="n">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="AU10" t="n">
         <v>7.2</v>
@@ -2438,7 +2438,7 @@
         <v>11</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="AX10" t="n">
         <v>11.5</v>
@@ -2447,32 +2447,32 @@
         <v>9</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="BD10" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BF10" t="n">
         <v>10.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
         <v>3.3</v>
       </c>
       <c r="H11" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I11" t="n">
         <v>2.46</v>
@@ -2593,7 +2593,7 @@
         <v>38</v>
       </c>
       <c r="AJ11" t="n">
-        <v>65</v>
+        <v>280</v>
       </c>
       <c r="AK11" t="n">
         <v>40</v>
@@ -2602,7 +2602,7 @@
         <v>46</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN11" t="n">
         <v>29</v>
@@ -2620,7 +2620,7 @@
         <v>12.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>3.85</v>
+        <v>13</v>
       </c>
       <c r="AT11" t="n">
         <v>11</v>
@@ -2644,16 +2644,16 @@
         <v>11.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>3.85</v>
+        <v>18</v>
       </c>
       <c r="BB11" t="n">
         <v>4</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.9</v>
+        <v>16</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.95</v>
+        <v>20</v>
       </c>
       <c r="BE11" t="n">
         <v>4.1</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
@@ -2697,34 +2697,34 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="G12" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="H12" t="n">
-        <v>4.4</v>
+        <v>13</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="J12" t="n">
         <v>4.4</v>
       </c>
       <c r="K12" t="n">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>2.42</v>
+        <v>2.94</v>
       </c>
       <c r="O12" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P12" t="n">
         <v>1.58</v>
@@ -2736,7 +2736,7 @@
         <v>1.15</v>
       </c>
       <c r="S12" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -2745,10 +2745,10 @@
         <v>1.55</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W12" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2787,7 +2787,7 @@
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK12" t="n">
         <v>1000</v>
@@ -2799,68 +2799,68 @@
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>1.67</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>1.56</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>1.67</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>1.67</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>1.67</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>1.67</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
@@ -2891,170 +2891,170 @@
         </is>
       </c>
       <c r="F13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G13" t="n">
         <v>2.1</v>
       </c>
-      <c r="G13" t="n">
-        <v>2.14</v>
-      </c>
       <c r="H13" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I13" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="J13" t="n">
         <v>3.4</v>
       </c>
       <c r="K13" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M13" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O13" t="n">
         <v>1.41</v>
       </c>
       <c r="P13" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R13" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="U13" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="V13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="X13" t="n">
         <v>11</v>
       </c>
       <c r="Y13" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z13" t="n">
         <v>32</v>
       </c>
       <c r="AA13" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB13" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE13" t="n">
         <v>65</v>
       </c>
       <c r="AF13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG13" t="n">
         <v>11</v>
       </c>
       <c r="AH13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI13" t="n">
         <v>75</v>
       </c>
       <c r="AJ13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AK13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL13" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM13" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN13" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS13" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AT13" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU13" t="n">
         <v>7.2</v>
       </c>
       <c r="AV13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>80</v>
+      </c>
+      <c r="BF13" t="n">
         <v>15.5</v>
       </c>
-      <c r="AW13" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>14</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BG13" t="n">
-        <v>13.5</v>
+        <v>60</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G14" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H14" t="n">
         <v>3.35</v>
@@ -3097,7 +3097,7 @@
         <v>3.45</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K14" t="n">
         <v>3.55</v>
@@ -3115,16 +3115,16 @@
         <v>1.31</v>
       </c>
       <c r="P14" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R14" t="n">
         <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="T14" t="n">
         <v>1.72</v>
@@ -3136,19 +3136,19 @@
         <v>1.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="X14" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y14" t="n">
         <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AA14" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AB14" t="n">
         <v>10.5</v>
@@ -3169,7 +3169,7 @@
         <v>11.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AI14" t="n">
         <v>55</v>
@@ -3181,13 +3181,13 @@
         <v>26</v>
       </c>
       <c r="AL14" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM14" t="n">
-        <v>95</v>
+        <v>320</v>
       </c>
       <c r="AN14" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AO14" t="n">
         <v>36</v>
@@ -3202,7 +3202,7 @@
         <v>20</v>
       </c>
       <c r="AS14" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="AT14" t="n">
         <v>9.6</v>
@@ -3211,10 +3211,10 @@
         <v>7.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW14" t="n">
-        <v>14.5</v>
+        <v>26</v>
       </c>
       <c r="AX14" t="n">
         <v>13.5</v>
@@ -3223,13 +3223,13 @@
         <v>10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BA14" t="n">
-        <v>13.5</v>
+        <v>23</v>
       </c>
       <c r="BB14" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="BC14" t="n">
         <v>22</v>
@@ -3238,17 +3238,17 @@
         <v>32</v>
       </c>
       <c r="BE14" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="BF14" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BG14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
@@ -3282,16 +3282,16 @@
         <v>2.28</v>
       </c>
       <c r="G15" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H15" t="n">
         <v>3.35</v>
       </c>
       <c r="I15" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="K15" t="n">
         <v>3.8</v>
@@ -3327,13 +3327,13 @@
         <v>2.38</v>
       </c>
       <c r="V15" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W15" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y15" t="n">
         <v>18</v>
@@ -3342,19 +3342,19 @@
         <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB15" t="n">
         <v>13</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD15" t="n">
         <v>15.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF15" t="n">
         <v>17</v>
@@ -3363,22 +3363,22 @@
         <v>12</v>
       </c>
       <c r="AH15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK15" t="n">
         <v>23</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN15" t="n">
         <v>14</v>
@@ -3396,7 +3396,7 @@
         <v>21</v>
       </c>
       <c r="AS15" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT15" t="n">
         <v>10.5</v>
@@ -3408,7 +3408,7 @@
         <v>12</v>
       </c>
       <c r="AW15" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX15" t="n">
         <v>13.5</v>
@@ -3420,29 +3420,29 @@
         <v>12.5</v>
       </c>
       <c r="BA15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB15" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>7</v>
       </c>
       <c r="BC15" t="n">
         <v>18</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF15" t="n">
         <v>11</v>
       </c>
       <c r="BG15" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="G16" t="n">
         <v>5.5</v>
       </c>
       <c r="H16" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="J16" t="n">
         <v>3.65</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3497,7 +3497,7 @@
         <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O16" t="n">
         <v>1.29</v>
@@ -3509,7 +3509,7 @@
         <v>1.87</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S16" t="n">
         <v>3.2</v>
@@ -3521,64 +3521,64 @@
         <v>2.02</v>
       </c>
       <c r="V16" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="W16" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X16" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA16" t="n">
         <v>23</v>
       </c>
       <c r="AB16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG16" t="n">
         <v>21</v>
       </c>
-      <c r="AC16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>23</v>
-      </c>
       <c r="AH16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="AJ16" t="n">
         <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AO16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AP16" t="n">
         <v>11.5</v>
@@ -3605,7 +3605,7 @@
         <v>14.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.5</v>
+        <v>16</v>
       </c>
       <c r="AY16" t="n">
         <v>15</v>
@@ -3617,26 +3617,26 @@
         <v>27</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BG16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="H17" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="I17" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="J17" t="n">
         <v>3.45</v>
@@ -3697,10 +3697,10 @@
         <v>1.31</v>
       </c>
       <c r="P17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R17" t="n">
         <v>1.36</v>
@@ -3715,52 +3715,52 @@
         <v>2.24</v>
       </c>
       <c r="V17" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W17" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="X17" t="n">
         <v>18</v>
       </c>
       <c r="Y17" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA17" t="n">
         <v>85</v>
       </c>
       <c r="AB17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE17" t="n">
         <v>55</v>
       </c>
       <c r="AF17" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI17" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL17" t="n">
         <v>46</v>
@@ -3769,7 +3769,7 @@
         <v>110</v>
       </c>
       <c r="AN17" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AO17" t="n">
         <v>55</v>
@@ -3778,59 +3778,59 @@
         <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AR17" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="AX17" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>38</v>
       </c>
       <c r="BB17" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC17" t="n">
         <v>20</v>
       </c>
-      <c r="BC17" t="n">
-        <v>17</v>
-      </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>27</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BG17" t="n">
-        <v>30</v>
+        <v>7.2</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
@@ -3870,10 +3870,10 @@
         <v>3.35</v>
       </c>
       <c r="I18" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J18" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K18" t="n">
         <v>4</v>
@@ -3882,34 +3882,34 @@
         <v>1.3</v>
       </c>
       <c r="M18" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N18" t="n">
-        <v>3.75</v>
+        <v>2.84</v>
       </c>
       <c r="O18" t="n">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="P18" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="T18" t="n">
-        <v>1.68</v>
+        <v>1.11</v>
       </c>
       <c r="U18" t="n">
-        <v>2.2</v>
+        <v>1.11</v>
       </c>
       <c r="V18" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W18" t="n">
         <v>1.78</v>
@@ -3918,19 +3918,19 @@
         <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z18" t="n">
         <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD18" t="n">
         <v>1000</v>
@@ -3939,19 +3939,19 @@
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI18" t="n">
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK18" t="n">
         <v>1000</v>
@@ -3960,71 +3960,71 @@
         <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.42</v>
+        <v>2.68</v>
       </c>
       <c r="AQ18" t="n">
-        <v>2.22</v>
+        <v>8.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.34</v>
+        <v>2.86</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.48</v>
+        <v>3.05</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.14</v>
+        <v>6.2</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.04</v>
+        <v>5.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.22</v>
+        <v>8.4</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.48</v>
+        <v>2.94</v>
       </c>
       <c r="AX18" t="n">
-        <v>2.22</v>
+        <v>7.6</v>
       </c>
       <c r="AY18" t="n">
-        <v>2.14</v>
+        <v>6.4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>2.24</v>
+        <v>9</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="BB18" t="n">
-        <v>2.34</v>
+        <v>2.86</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.3</v>
+        <v>2.82</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.38</v>
+        <v>2.92</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.22</v>
+        <v>3.85</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.38</v>
+        <v>6.8</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
@@ -4067,10 +4067,10 @@
         <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="K19" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4079,22 +4079,22 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O19" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="P19" t="n">
-        <v>4.7</v>
+        <v>2.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="R19" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="S19" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T19" t="n">
         <v>2.28</v>
@@ -4103,10 +4103,10 @@
         <v>1.6</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -4163,62 +4163,62 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="AV19" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AW19" t="n">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="AY19" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BA19" t="n">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="BB19" t="n">
         <v>7.2</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="BE19" t="n">
-        <v>3.95</v>
+        <v>8</v>
       </c>
       <c r="BF19" t="n">
         <v>1.66</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.95</v>
+        <v>10.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
@@ -4249,13 +4249,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="G20" t="n">
         <v>1.51</v>
       </c>
       <c r="H20" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="I20" t="n">
         <v>11.5</v>
@@ -4294,19 +4294,19 @@
         <v>2.46</v>
       </c>
       <c r="U20" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V20" t="n">
         <v>1.1</v>
       </c>
       <c r="W20" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="X20" t="n">
         <v>14</v>
       </c>
       <c r="Y20" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="Z20" t="n">
         <v>110</v>
@@ -4318,10 +4318,10 @@
         <v>6.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD20" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AE20" t="n">
         <v>260</v>
@@ -4333,25 +4333,25 @@
         <v>11</v>
       </c>
       <c r="AH20" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AI20" t="n">
         <v>230</v>
       </c>
       <c r="AJ20" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AK20" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="AL20" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO20" t="n">
         <v>1000</v>
@@ -4360,13 +4360,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AS20" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AT20" t="n">
         <v>5.5</v>
@@ -4375,44 +4375,44 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV20" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AW20" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AX20" t="n">
         <v>6.6</v>
       </c>
       <c r="AY20" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BA20" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB20" t="n">
         <v>10</v>
       </c>
       <c r="BC20" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BD20" t="n">
         <v>40</v>
       </c>
       <c r="BE20" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="BF20" t="n">
         <v>8.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>7.6</v>
+        <v>15</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
@@ -4449,10 +4449,10 @@
         <v>2.68</v>
       </c>
       <c r="H21" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="I21" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J21" t="n">
         <v>3.5</v>
@@ -4479,19 +4479,19 @@
         <v>1.7</v>
       </c>
       <c r="R21" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S21" t="n">
         <v>2.76</v>
       </c>
       <c r="T21" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U21" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V21" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W21" t="n">
         <v>1.59</v>
@@ -4500,67 +4500,67 @@
         <v>90</v>
       </c>
       <c r="Y21" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="Z21" t="n">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="AA21" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN21" t="n">
         <v>55</v>
       </c>
-      <c r="AB21" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>20</v>
-      </c>
       <c r="AO21" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AP21" t="n">
         <v>13</v>
       </c>
       <c r="AQ21" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AR21" t="n">
         <v>15.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="AT21" t="n">
         <v>9.4</v>
@@ -4572,7 +4572,7 @@
         <v>10</v>
       </c>
       <c r="AW21" t="n">
-        <v>4</v>
+        <v>14.5</v>
       </c>
       <c r="AX21" t="n">
         <v>12.5</v>
@@ -4584,19 +4584,19 @@
         <v>11.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.1</v>
+        <v>14.5</v>
       </c>
       <c r="BC21" t="n">
         <v>18.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF21" t="n">
         <v>12.5</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
         <v>3.15</v>
       </c>
       <c r="G22" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H22" t="n">
         <v>2.8</v>
@@ -4658,31 +4658,31 @@
         <v>1.59</v>
       </c>
       <c r="M22" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="N22" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="O22" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="P22" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S22" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="T22" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="U22" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="V22" t="n">
         <v>1.51</v>
@@ -4694,7 +4694,7 @@
         <v>8.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z22" t="n">
         <v>17</v>
@@ -4712,7 +4712,7 @@
         <v>14</v>
       </c>
       <c r="AE22" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AF22" t="n">
         <v>20</v>
@@ -4721,40 +4721,40 @@
         <v>15.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI22" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AJ22" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AK22" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL22" t="n">
         <v>100</v>
       </c>
       <c r="AM22" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AN22" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AO22" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP22" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="AQ22" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AR22" t="n">
         <v>15</v>
       </c>
       <c r="AS22" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AT22" t="n">
         <v>7.6</v>
@@ -4766,7 +4766,7 @@
         <v>12</v>
       </c>
       <c r="AW22" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX22" t="n">
         <v>17.5</v>
@@ -4778,29 +4778,29 @@
         <v>22</v>
       </c>
       <c r="BA22" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD22" t="n">
         <v>9</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BE22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF22" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BD22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BG22" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4840,7 @@
         <v>5.1</v>
       </c>
       <c r="I23" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J23" t="n">
         <v>2.84</v>
@@ -4852,16 +4852,16 @@
         <v>1.67</v>
       </c>
       <c r="M23" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N23" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="O23" t="n">
         <v>1.79</v>
       </c>
       <c r="P23" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Q23" t="n">
         <v>3.2</v>
@@ -4873,10 +4873,10 @@
         <v>7.2</v>
       </c>
       <c r="T23" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="U23" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V23" t="n">
         <v>1.21</v>
@@ -4888,16 +4888,16 @@
         <v>7.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="AA23" t="n">
-        <v>210</v>
+        <v>700</v>
       </c>
       <c r="AB23" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC23" t="n">
         <v>8.6</v>
@@ -4906,37 +4906,37 @@
         <v>29</v>
       </c>
       <c r="AE23" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AF23" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG23" t="n">
         <v>15</v>
       </c>
       <c r="AH23" t="n">
-        <v>36</v>
+        <v>220</v>
       </c>
       <c r="AI23" t="n">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="AJ23" t="n">
         <v>34</v>
       </c>
       <c r="AK23" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="AL23" t="n">
-        <v>110</v>
+        <v>460</v>
       </c>
       <c r="AM23" t="n">
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="AN23" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AO23" t="n">
-        <v>310</v>
+        <v>700</v>
       </c>
       <c r="AP23" t="n">
         <v>5.9</v>
@@ -4945,10 +4945,10 @@
         <v>10</v>
       </c>
       <c r="AR23" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AT23" t="n">
         <v>5.1</v>
@@ -4960,41 +4960,41 @@
         <v>21</v>
       </c>
       <c r="AW23" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AX23" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY23" t="n">
         <v>11</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BB23" t="n">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="BC23" t="n">
         <v>30</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF23" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
@@ -5025,19 +5025,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G24" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H24" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="I24" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="J24" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K24" t="n">
         <v>4.1</v>
@@ -5073,22 +5073,22 @@
         <v>2.28</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W24" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="X24" t="n">
         <v>22</v>
       </c>
       <c r="Y24" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="Z24" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="AA24" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AB24" t="n">
         <v>11.5</v>
@@ -5100,37 +5100,37 @@
         <v>14.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="AF24" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="AG24" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH24" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AI24" t="n">
-        <v>44</v>
+        <v>150</v>
       </c>
       <c r="AJ24" t="n">
-        <v>29</v>
+        <v>900</v>
       </c>
       <c r="AK24" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="AL24" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AM24" t="n">
         <v>95</v>
       </c>
       <c r="AN24" t="n">
-        <v>15.5</v>
+        <v>36</v>
       </c>
       <c r="AO24" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AP24" t="n">
         <v>15.5</v>
@@ -5142,7 +5142,7 @@
         <v>21</v>
       </c>
       <c r="AS24" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="AT24" t="n">
         <v>10</v>
@@ -5154,7 +5154,7 @@
         <v>12.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>8.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="AX24" t="n">
         <v>13.5</v>
@@ -5166,29 +5166,29 @@
         <v>14.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BB24" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BC24" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BE24" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BF24" t="n">
         <v>11</v>
       </c>
       <c r="BG24" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
@@ -5219,16 +5219,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="G25" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="H25" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I25" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="J25" t="n">
         <v>3.4</v>
@@ -5237,40 +5237,40 @@
         <v>3.45</v>
       </c>
       <c r="L25" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="M25" t="n">
         <v>1.1</v>
       </c>
       <c r="N25" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O25" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="P25" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="R25" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="T25" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="U25" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="V25" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W25" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="X25" t="n">
         <v>11</v>
@@ -5279,52 +5279,52 @@
         <v>12</v>
       </c>
       <c r="Z25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA25" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AB25" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC25" t="n">
         <v>7.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AF25" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI25" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK25" t="n">
         <v>27</v>
       </c>
       <c r="AL25" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM25" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AN25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO25" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AP25" t="n">
         <v>10</v>
@@ -5336,10 +5336,10 @@
         <v>23</v>
       </c>
       <c r="AS25" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AT25" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU25" t="n">
         <v>7</v>
@@ -5348,41 +5348,41 @@
         <v>14.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AX25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY25" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA25" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD25" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BE25" t="n">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="BF25" t="n">
         <v>22</v>
       </c>
       <c r="BG25" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="G26" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="H26" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="I26" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="J26" t="n">
         <v>3.4</v>
@@ -5440,43 +5440,43 @@
         <v>3.5</v>
       </c>
       <c r="O26" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P26" t="n">
         <v>1.83</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R26" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S26" t="n">
         <v>3.95</v>
       </c>
       <c r="T26" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U26" t="n">
         <v>2.06</v>
       </c>
       <c r="V26" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="W26" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="X26" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y26" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z26" t="n">
         <v>14</v>
       </c>
       <c r="AA26" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB26" t="n">
         <v>12.5</v>
@@ -5488,64 +5488,64 @@
         <v>11</v>
       </c>
       <c r="AE26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF26" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG26" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH26" t="n">
         <v>18</v>
       </c>
       <c r="AI26" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ26" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AK26" t="n">
         <v>44</v>
       </c>
       <c r="AL26" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM26" t="n">
         <v>100</v>
       </c>
       <c r="AN26" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AO26" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AP26" t="n">
         <v>11</v>
       </c>
       <c r="AQ26" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AR26" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS26" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AT26" t="n">
         <v>11.5</v>
       </c>
       <c r="AU26" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV26" t="n">
         <v>10.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AX26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY26" t="n">
         <v>13.5</v>
@@ -5563,20 +5563,20 @@
         <v>36</v>
       </c>
       <c r="BD26" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BE26" t="n">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="BF26" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BG26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
@@ -5616,13 +5616,13 @@
         <v>3.35</v>
       </c>
       <c r="I27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K27" t="n">
         <v>3.4</v>
-      </c>
-      <c r="J27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3.45</v>
       </c>
       <c r="L27" t="n">
         <v>1.46</v>
@@ -5634,7 +5634,7 @@
         <v>3.45</v>
       </c>
       <c r="O27" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P27" t="n">
         <v>1.81</v>
@@ -5652,7 +5652,7 @@
         <v>1.87</v>
       </c>
       <c r="U27" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V27" t="n">
         <v>1.41</v>
@@ -5733,7 +5733,7 @@
         <v>7</v>
       </c>
       <c r="AV27" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW27" t="n">
         <v>36</v>
@@ -5748,7 +5748,7 @@
         <v>16.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="BB27" t="n">
         <v>29</v>
@@ -5760,24 +5760,24 @@
         <v>26</v>
       </c>
       <c r="BE27" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="BF27" t="n">
         <v>21</v>
       </c>
       <c r="BG27" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5792,179 +5792,179 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MC El Bayadh</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.28</v>
+        <v>2.2</v>
       </c>
       <c r="G28" t="n">
-        <v>1.33</v>
+        <v>2.24</v>
       </c>
       <c r="H28" t="n">
-        <v>16.5</v>
+        <v>3.65</v>
       </c>
       <c r="I28" t="n">
-        <v>23</v>
+        <v>3.75</v>
       </c>
       <c r="J28" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="K28" t="n">
-        <v>5.9</v>
+        <v>3.65</v>
       </c>
       <c r="L28" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>3.05</v>
+        <v>3.85</v>
       </c>
       <c r="O28" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R28" t="n">
         <v>1.38</v>
       </c>
-      <c r="P28" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.26</v>
-      </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.88</v>
+        <v>1.77</v>
       </c>
       <c r="U28" t="n">
-        <v>1.43</v>
+        <v>2.16</v>
       </c>
       <c r="V28" t="n">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="W28" t="n">
-        <v>3.9</v>
+        <v>1.81</v>
       </c>
       <c r="X28" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y28" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="Z28" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB28" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AC28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD28" t="n">
         <v>15.5</v>
       </c>
-      <c r="AD28" t="n">
-        <v>85</v>
-      </c>
       <c r="AE28" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF28" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AG28" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>65</v>
+        <v>17.5</v>
       </c>
       <c r="AI28" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="AK28" t="n">
         <v>23</v>
       </c>
       <c r="AL28" t="n">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="AM28" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN28" t="n">
-        <v>8.4</v>
+        <v>17</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP28" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="AQ28" t="n">
-        <v>5.3</v>
+        <v>13.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>5.5</v>
+        <v>23</v>
       </c>
       <c r="AS28" t="n">
-        <v>5.7</v>
+        <v>28</v>
       </c>
       <c r="AT28" t="n">
-        <v>4.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY28" t="n">
         <v>10</v>
       </c>
-      <c r="AV28" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AZ28" t="n">
-        <v>5.2</v>
+        <v>16</v>
       </c>
       <c r="BA28" t="n">
-        <v>5.6</v>
+        <v>34</v>
       </c>
       <c r="BB28" t="n">
-        <v>7.4</v>
+        <v>23</v>
       </c>
       <c r="BC28" t="n">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.3</v>
+        <v>32</v>
       </c>
       <c r="BE28" t="n">
-        <v>5.7</v>
+        <v>28</v>
       </c>
       <c r="BF28" t="n">
-        <v>6.2</v>
+        <v>13.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>5.7</v>
+        <v>36</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
@@ -5995,16 +5995,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="G29" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="H29" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J29" t="n">
         <v>3.85</v>
@@ -6022,31 +6022,31 @@
         <v>3.7</v>
       </c>
       <c r="O29" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P29" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="T29" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="U29" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="V29" t="n">
         <v>1.19</v>
       </c>
       <c r="W29" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="X29" t="n">
         <v>14</v>
@@ -6055,67 +6055,67 @@
         <v>18.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA29" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AB29" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC29" t="n">
         <v>8.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE29" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI29" t="n">
         <v>95</v>
       </c>
-      <c r="AF29" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>85</v>
-      </c>
       <c r="AJ29" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK29" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL29" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM29" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO29" t="n">
         <v>130</v>
       </c>
-      <c r="AN29" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>110</v>
-      </c>
       <c r="AP29" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ29" t="n">
         <v>16.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AS29" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AT29" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU29" t="n">
         <v>8</v>
@@ -6127,16 +6127,16 @@
         <v>75</v>
       </c>
       <c r="AX29" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY29" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA29" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="BB29" t="n">
         <v>16</v>
@@ -6148,24 +6148,24 @@
         <v>32</v>
       </c>
       <c r="BE29" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="BF29" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6180,179 +6180,179 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>MC El Bayadh</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.16</v>
+        <v>1.28</v>
       </c>
       <c r="G30" t="n">
-        <v>2.2</v>
+        <v>1.33</v>
       </c>
       <c r="H30" t="n">
-        <v>3.75</v>
+        <v>17</v>
       </c>
       <c r="I30" t="n">
-        <v>3.85</v>
+        <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="K30" t="n">
-        <v>3.65</v>
+        <v>5.9</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M30" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N30" t="n">
-        <v>3.95</v>
+        <v>3.05</v>
       </c>
       <c r="O30" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="P30" t="n">
-        <v>1.99</v>
+        <v>1.71</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="R30" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="S30" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>1.77</v>
+        <v>2.88</v>
       </c>
       <c r="U30" t="n">
-        <v>2.16</v>
+        <v>1.43</v>
       </c>
       <c r="V30" t="n">
-        <v>1.35</v>
+        <v>1.05</v>
       </c>
       <c r="W30" t="n">
-        <v>1.83</v>
+        <v>3.9</v>
       </c>
       <c r="X30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>170</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG30" t="n">
         <v>14</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="AH30" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>380</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC30" t="n">
         <v>15</v>
       </c>
-      <c r="Z30" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BD30" t="n">
-        <v>32</v>
+        <v>5.8</v>
       </c>
       <c r="BE30" t="n">
-        <v>16</v>
+        <v>6.2</v>
       </c>
       <c r="BF30" t="n">
-        <v>13.5</v>
+        <v>6.2</v>
       </c>
       <c r="BG30" t="n">
-        <v>38</v>
+        <v>6.4</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
@@ -6383,13 +6383,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="G31" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H31" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I31" t="n">
         <v>2.84</v>
@@ -6401,7 +6401,7 @@
         <v>3.65</v>
       </c>
       <c r="L31" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M31" t="n">
         <v>1.06</v>
@@ -6416,7 +6416,7 @@
         <v>2.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R31" t="n">
         <v>1.44</v>
@@ -6425,7 +6425,7 @@
         <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U31" t="n">
         <v>2.36</v>
@@ -6467,7 +6467,7 @@
         <v>12</v>
       </c>
       <c r="AH31" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI31" t="n">
         <v>38</v>
@@ -6546,14 +6546,14 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6568,186 +6568,186 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Juticalpa</t>
+          <t>Union Magdalena</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olancho</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="G32" t="n">
-        <v>1000</v>
+        <v>2.4</v>
       </c>
       <c r="H32" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="I32" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="J32" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="K32" t="n">
-        <v>950</v>
+        <v>3.45</v>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M32" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N32" t="n">
-        <v>1.3</v>
+        <v>2.96</v>
       </c>
       <c r="O32" t="n">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="P32" t="n">
-        <v>1.29</v>
+        <v>1.66</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.23</v>
+        <v>2.2</v>
       </c>
       <c r="R32" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S32" t="n">
-        <v>1.24</v>
+        <v>4.2</v>
       </c>
       <c r="T32" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="U32" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="W32" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="X32" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA32" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB32" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC32" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF32" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH32" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI32" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK32" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL32" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM32" t="n">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AN32" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO32" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BD32" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.05</v>
+        <v>19</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.05</v>
+        <v>7.8</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6762,109 +6762,109 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Union Magdalena</t>
+          <t>Juticalpa</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>Olancho</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.18</v>
+        <v>2.92</v>
       </c>
       <c r="G33" t="n">
-        <v>2.46</v>
+        <v>1000</v>
       </c>
       <c r="H33" t="n">
-        <v>3.6</v>
+        <v>1.48</v>
       </c>
       <c r="I33" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="J33" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="K33" t="n">
-        <v>3.55</v>
+        <v>950</v>
       </c>
       <c r="L33" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>2.96</v>
+        <v>1.02</v>
       </c>
       <c r="O33" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="P33" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.24</v>
+        <v>1.23</v>
       </c>
       <c r="R33" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S33" t="n">
-        <v>4.2</v>
+        <v>1.23</v>
       </c>
       <c r="T33" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="U33" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>1.31</v>
+        <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.69</v>
+        <v>1.16</v>
       </c>
       <c r="X33" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y33" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z33" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA33" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC33" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD33" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE33" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG33" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH33" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI33" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK33" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL33" t="n">
         <v>1000</v>
@@ -6873,68 +6873,68 @@
         <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>8.199999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="AQ33" t="n">
-        <v>10</v>
+        <v>1.1</v>
       </c>
       <c r="AR33" t="n">
-        <v>22</v>
+        <v>1.14</v>
       </c>
       <c r="AS33" t="n">
-        <v>6</v>
+        <v>1.14</v>
       </c>
       <c r="AT33" t="n">
-        <v>7</v>
+        <v>1.14</v>
       </c>
       <c r="AU33" t="n">
-        <v>6.4</v>
+        <v>1.11</v>
       </c>
       <c r="AV33" t="n">
-        <v>12.5</v>
+        <v>1.11</v>
       </c>
       <c r="AW33" t="n">
-        <v>5.8</v>
+        <v>1.12</v>
       </c>
       <c r="AX33" t="n">
-        <v>10</v>
+        <v>1.14</v>
       </c>
       <c r="AY33" t="n">
-        <v>9.800000000000001</v>
+        <v>1.14</v>
       </c>
       <c r="AZ33" t="n">
-        <v>15</v>
+        <v>1.14</v>
       </c>
       <c r="BA33" t="n">
-        <v>6</v>
+        <v>1.14</v>
       </c>
       <c r="BB33" t="n">
-        <v>6</v>
+        <v>1.14</v>
       </c>
       <c r="BC33" t="n">
-        <v>21</v>
+        <v>1.14</v>
       </c>
       <c r="BD33" t="n">
-        <v>5.7</v>
+        <v>1.14</v>
       </c>
       <c r="BE33" t="n">
-        <v>6</v>
+        <v>1.14</v>
       </c>
       <c r="BF33" t="n">
-        <v>21</v>
+        <v>1.55</v>
       </c>
       <c r="BG33" t="n">
-        <v>5.8</v>
+        <v>1.14</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>
@@ -6951,17 +6951,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>20:15:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CD Marathon</t>
+          <t>Atletico Choloma</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CD Motagua</t>
+          <t>Real Espana</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -6980,7 +6980,7 @@
         <v>1.03</v>
       </c>
       <c r="K34" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
@@ -6989,22 +6989,22 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="O34" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="P34" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="R34" t="n">
         <v>1.18</v>
       </c>
       <c r="S34" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T34" t="n">
         <v>1.01</v>
@@ -7073,52 +7073,52 @@
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF34" t="n">
         <v>1.01</v>
@@ -7128,7 +7128,201 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-08 17:49:17</t>
+          <t>2026-04-08 20:04:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CD Marathon</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>CD Motagua</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K35" t="n">
+        <v>950</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-04-08 20:04:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.2</v>
+        <v>1.54</v>
       </c>
       <c r="G2" t="n">
-        <v>44</v>
+        <v>2.56</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5</v>
+        <v>2.62</v>
       </c>
       <c r="I2" t="n">
         <v>44</v>
       </c>
       <c r="J2" t="n">
-        <v>1.09</v>
+        <v>2.96</v>
       </c>
       <c r="K2" t="n">
-        <v>32</v>
+        <v>9.6</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -781,7 +781,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O2" t="n">
         <v>1.4</v>
@@ -790,25 +790,25 @@
         <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.72</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -826,7 +826,7 @@
         <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD2" t="n">
         <v>1000</v>
@@ -865,62 +865,62 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
         <v>6.8</v>
       </c>
       <c r="I3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
         <v>3.95</v>
@@ -969,7 +969,7 @@
         <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
@@ -1017,10 +1017,10 @@
         <v>700</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD3" t="n">
         <v>32</v>
@@ -1029,13 +1029,13 @@
         <v>700</v>
       </c>
       <c r="AF3" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG3" t="n">
         <v>12</v>
       </c>
       <c r="AH3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI3" t="n">
         <v>700</v>
@@ -1044,7 +1044,7 @@
         <v>17.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL3" t="n">
         <v>55</v>
@@ -1053,22 +1053,22 @@
         <v>700</v>
       </c>
       <c r="AN3" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO3" t="n">
         <v>700</v>
       </c>
       <c r="AP3" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.5</v>
+        <v>23</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
         <v>6.2</v>
@@ -1077,10 +1077,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV3" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AX3" t="n">
         <v>7.8</v>
@@ -1089,32 +1089,32 @@
         <v>9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BC3" t="n">
         <v>16</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>2.6</v>
       </c>
       <c r="G4" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H4" t="n">
         <v>2.68</v>
@@ -1199,7 +1199,7 @@
         <v>1.54</v>
       </c>
       <c r="X4" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y4" t="n">
         <v>13.5</v>
@@ -1238,7 +1238,7 @@
         <v>42</v>
       </c>
       <c r="AK4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL4" t="n">
         <v>38</v>
@@ -1247,13 +1247,13 @@
         <v>320</v>
       </c>
       <c r="AN4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO4" t="n">
         <v>24</v>
       </c>
       <c r="AP4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ4" t="n">
         <v>11</v>
@@ -1286,7 +1286,7 @@
         <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB4" t="n">
         <v>32</v>
@@ -1298,7 +1298,7 @@
         <v>30</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF4" t="n">
         <v>18</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         <v>1.37</v>
       </c>
       <c r="H5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="I5" t="n">
         <v>16</v>
@@ -1378,7 +1378,7 @@
         <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
         <v>2.32</v>
@@ -1450,7 +1450,7 @@
         <v>14</v>
       </c>
       <c r="AQ5" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AR5" t="n">
         <v>7.4</v>
@@ -1468,7 +1468,7 @@
         <v>34</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX5" t="n">
         <v>6.2</v>
@@ -1477,7 +1477,7 @@
         <v>9</v>
       </c>
       <c r="AZ5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA5" t="n">
         <v>7.6</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -1545,13 +1545,13 @@
         <v>2.6</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="K6" t="n">
         <v>3.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="n">
         <v>1.12</v>
@@ -1575,7 +1575,7 @@
         <v>4.8</v>
       </c>
       <c r="T6" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
         <v>1.88</v>
@@ -1623,7 +1623,7 @@
         <v>130</v>
       </c>
       <c r="AJ6" t="n">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="AK6" t="n">
         <v>55</v>
@@ -1635,7 +1635,7 @@
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="AO6" t="n">
         <v>40</v>
@@ -1662,28 +1662,28 @@
         <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY6" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ6" t="n">
         <v>17.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="BB6" t="n">
         <v>20</v>
       </c>
       <c r="BC6" t="n">
-        <v>40</v>
+        <v>8.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE6" t="n">
         <v>9.4</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -1736,10 +1736,10 @@
         <v>2.7</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K7" t="n">
         <v>2.98</v>
@@ -1775,10 +1775,10 @@
         <v>1.78</v>
       </c>
       <c r="V7" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X7" t="n">
         <v>8</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -1924,16 +1924,16 @@
         <v>3.05</v>
       </c>
       <c r="G8" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H8" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I8" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="J8" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
         <v>3.9</v>
@@ -1969,7 +1969,7 @@
         <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W8" t="n">
         <v>1.44</v>
@@ -2002,7 +2002,7 @@
         <v>500</v>
       </c>
       <c r="AG8" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AH8" t="n">
         <v>26</v>
@@ -2035,56 +2035,56 @@
         <v>8.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.2</v>
+        <v>14.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU8" t="n">
         <v>7.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE8" t="n">
         <v>8.4</v>
       </c>
-      <c r="BB8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BF8" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BG8" t="n">
         <v>16</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I9" t="n">
         <v>1.49</v>
@@ -2139,7 +2139,7 @@
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
         <v>1.21</v>
@@ -2169,7 +2169,7 @@
         <v>1.12</v>
       </c>
       <c r="X9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y9" t="n">
         <v>10.5</v>
@@ -2193,7 +2193,7 @@
         <v>15</v>
       </c>
       <c r="AF9" t="n">
-        <v>170</v>
+        <v>540</v>
       </c>
       <c r="AG9" t="n">
         <v>75</v>
@@ -2202,7 +2202,7 @@
         <v>40</v>
       </c>
       <c r="AI9" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="AJ9" t="n">
         <v>250</v>
@@ -2241,13 +2241,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AW9" t="n">
         <v>12</v>
       </c>
       <c r="AX9" t="n">
-        <v>50</v>
+        <v>8.6</v>
       </c>
       <c r="AY9" t="n">
         <v>15.5</v>
@@ -2256,16 +2256,16 @@
         <v>19</v>
       </c>
       <c r="BA9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC9" t="n">
-        <v>28</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD9" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="BE9" t="n">
         <v>8.800000000000001</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
         <v>3.3</v>
       </c>
       <c r="I10" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J10" t="n">
         <v>3.55</v>
@@ -2387,7 +2387,7 @@
         <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="AG10" t="n">
         <v>16.5</v>
@@ -2402,7 +2402,7 @@
         <v>75</v>
       </c>
       <c r="AK10" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AL10" t="n">
         <v>500</v>
@@ -2423,10 +2423,10 @@
         <v>9</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AT10" t="n">
         <v>5.8</v>
@@ -2438,41 +2438,41 @@
         <v>11</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AX10" t="n">
         <v>11.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
         <v>10.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BB10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC10" t="n">
         <v>6.2</v>
       </c>
-      <c r="BC10" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BD10" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BE10" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BF10" t="n">
         <v>10.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
         <v>3.3</v>
       </c>
       <c r="H11" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I11" t="n">
         <v>2.46</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -2715,34 +2715,34 @@
         <v>5.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N12" t="n">
         <v>2.94</v>
       </c>
       <c r="O12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P12" t="n">
         <v>1.58</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="U12" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="V12" t="n">
         <v>1.06</v>
@@ -2751,10 +2751,10 @@
         <v>3.3</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z12" t="n">
         <v>1000</v>
@@ -2763,104 +2763,104 @@
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AE12" t="n">
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>900</v>
+        <v>11</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>29</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.67</v>
+        <v>10</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.2</v>
+        <v>14</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="AX12" t="n">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.56</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.67</v>
+        <v>7.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.67</v>
+        <v>17</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.67</v>
+        <v>7.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.67</v>
+        <v>8</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.86</v>
+        <v>8</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G13" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H13" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I13" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J13" t="n">
         <v>3.4</v>
@@ -2912,43 +2912,43 @@
         <v>1.49</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P13" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R13" t="n">
         <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T13" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U13" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V13" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="X13" t="n">
         <v>11</v>
       </c>
       <c r="Y13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z13" t="n">
         <v>32</v>
@@ -2969,7 +2969,7 @@
         <v>65</v>
       </c>
       <c r="AF13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG13" t="n">
         <v>11</v>
@@ -2981,22 +2981,22 @@
         <v>75</v>
       </c>
       <c r="AJ13" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AK13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL13" t="n">
         <v>44</v>
       </c>
       <c r="AM13" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN13" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP13" t="n">
         <v>10.5</v>
@@ -3005,10 +3005,10 @@
         <v>12.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS13" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AT13" t="n">
         <v>7.6</v>
@@ -3020,41 +3020,41 @@
         <v>15</v>
       </c>
       <c r="AW13" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BA13" t="n">
         <v>55</v>
       </c>
       <c r="BB13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD13" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BE13" t="n">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="BF13" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BG13" t="n">
         <v>60</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
         <v>3.35</v>
       </c>
       <c r="I14" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J14" t="n">
         <v>3.45</v>
@@ -3136,7 +3136,7 @@
         <v>1.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="X14" t="n">
         <v>14.5</v>
@@ -3187,7 +3187,7 @@
         <v>320</v>
       </c>
       <c r="AN14" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AO14" t="n">
         <v>36</v>
@@ -3244,11 +3244,11 @@
         <v>18</v>
       </c>
       <c r="BG14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
         <v>3.35</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L15" t="n">
         <v>1.32</v>
@@ -3390,7 +3390,7 @@
         <v>14.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AR15" t="n">
         <v>21</v>
@@ -3402,13 +3402,13 @@
         <v>10.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV15" t="n">
         <v>12</v>
       </c>
       <c r="AW15" t="n">
-        <v>8.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="AX15" t="n">
         <v>13.5</v>
@@ -3420,7 +3420,7 @@
         <v>12.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="BB15" t="n">
         <v>7.6</v>
@@ -3429,7 +3429,7 @@
         <v>18</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.8</v>
+        <v>25</v>
       </c>
       <c r="BE15" t="n">
         <v>9</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
         <v>1.88</v>
       </c>
       <c r="J16" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K16" t="n">
         <v>4.1</v>
@@ -3494,7 +3494,7 @@
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N16" t="n">
         <v>3.75</v>
@@ -3503,7 +3503,7 @@
         <v>1.29</v>
       </c>
       <c r="P16" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q16" t="n">
         <v>1.87</v>
@@ -3530,13 +3530,13 @@
         <v>16.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z16" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AB16" t="n">
         <v>19</v>
@@ -3578,10 +3578,10 @@
         <v>700</v>
       </c>
       <c r="AO16" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AP16" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AQ16" t="n">
         <v>7</v>
@@ -3617,26 +3617,26 @@
         <v>27</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BC16" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD16" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE16" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BF16" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BG16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G17" t="n">
         <v>2.26</v>
@@ -3676,7 +3676,7 @@
         <v>3.55</v>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J17" t="n">
         <v>3.45</v>
@@ -3697,7 +3697,7 @@
         <v>1.31</v>
       </c>
       <c r="P17" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q17" t="n">
         <v>1.91</v>
@@ -3715,7 +3715,7 @@
         <v>2.24</v>
       </c>
       <c r="V17" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W17" t="n">
         <v>1.79</v>
@@ -3724,43 +3724,43 @@
         <v>18</v>
       </c>
       <c r="Y17" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA17" t="n">
         <v>85</v>
       </c>
       <c r="AB17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD17" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE17" t="n">
         <v>55</v>
       </c>
       <c r="AF17" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI17" t="n">
         <v>55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL17" t="n">
         <v>46</v>
@@ -3769,7 +3769,7 @@
         <v>110</v>
       </c>
       <c r="AN17" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AO17" t="n">
         <v>55</v>
@@ -3784,7 +3784,7 @@
         <v>11.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="AT17" t="n">
         <v>8.800000000000001</v>
@@ -3796,7 +3796,7 @@
         <v>13</v>
       </c>
       <c r="AW17" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="AX17" t="n">
         <v>12.5</v>
@@ -3808,7 +3808,7 @@
         <v>15</v>
       </c>
       <c r="BA17" t="n">
-        <v>38</v>
+        <v>4.5</v>
       </c>
       <c r="BB17" t="n">
         <v>13</v>
@@ -3817,10 +3817,10 @@
         <v>20</v>
       </c>
       <c r="BD17" t="n">
-        <v>27</v>
+        <v>5.1</v>
       </c>
       <c r="BE17" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BF17" t="n">
         <v>14</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -3885,28 +3885,28 @@
         <v>1.03</v>
       </c>
       <c r="N18" t="n">
-        <v>2.84</v>
+        <v>3.95</v>
       </c>
       <c r="O18" t="n">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="P18" t="n">
         <v>2</v>
       </c>
       <c r="Q18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
         <v>1.67</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.11</v>
-      </c>
       <c r="U18" t="n">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="V18" t="n">
         <v>1.35</v>
@@ -3915,7 +3915,7 @@
         <v>1.78</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y18" t="n">
         <v>500</v>
@@ -3969,13 +3969,13 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="AQ18" t="n">
         <v>8.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="AS18" t="n">
         <v>3.05</v>
@@ -3990,7 +3990,7 @@
         <v>8.4</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="AX18" t="n">
         <v>7.6</v>
@@ -4002,19 +4002,19 @@
         <v>9</v>
       </c>
       <c r="BA18" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BB18" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BE18" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BF18" t="n">
         <v>3.85</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
         <v>1.07</v>
       </c>
       <c r="G19" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="H19" t="n">
         <v>42</v>
@@ -4085,7 +4085,7 @@
         <v>1.05</v>
       </c>
       <c r="P19" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="Q19" t="n">
         <v>1.14</v>
@@ -4094,13 +4094,13 @@
         <v>2.62</v>
       </c>
       <c r="S19" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T19" t="n">
         <v>2.28</v>
       </c>
       <c r="U19" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V19" t="n">
         <v>1.02</v>
@@ -4163,13 +4163,13 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="AQ19" t="n">
         <v>4.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="AS19" t="n">
         <v>4.2</v>
@@ -4184,31 +4184,31 @@
         <v>4.2</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="AX19" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AZ19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BE19" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="BF19" t="n">
         <v>1.66</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -4252,19 +4252,19 @@
         <v>1.45</v>
       </c>
       <c r="G20" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="H20" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I20" t="n">
         <v>11.5</v>
       </c>
       <c r="J20" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K20" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L20" t="n">
         <v>1.46</v>
@@ -4300,10 +4300,10 @@
         <v>1.1</v>
       </c>
       <c r="W20" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="X20" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y20" t="n">
         <v>42</v>
@@ -4318,7 +4318,7 @@
         <v>6.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="AD20" t="n">
         <v>95</v>
@@ -4348,7 +4348,7 @@
         <v>500</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AN20" t="n">
         <v>10.5</v>
@@ -4357,49 +4357,49 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ20" t="n">
-        <v>6.6</v>
+        <v>18.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT20" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AU20" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AV20" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AW20" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX20" t="n">
         <v>6.6</v>
       </c>
       <c r="AY20" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BB20" t="n">
         <v>10</v>
       </c>
       <c r="BC20" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BD20" t="n">
-        <v>40</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE20" t="n">
         <v>30</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
         <v>1.59</v>
       </c>
       <c r="X21" t="n">
-        <v>90</v>
+        <v>970</v>
       </c>
       <c r="Y21" t="n">
         <v>970</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -4727,10 +4727,10 @@
         <v>170</v>
       </c>
       <c r="AJ22" t="n">
-        <v>70</v>
+        <v>900</v>
       </c>
       <c r="AK22" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AL22" t="n">
         <v>100</v>
@@ -4742,7 +4742,7 @@
         <v>85</v>
       </c>
       <c r="AO22" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AP22" t="n">
         <v>5.7</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
         <v>2.2</v>
       </c>
       <c r="O23" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="P23" t="n">
         <v>1.39</v>
@@ -4873,7 +4873,7 @@
         <v>7.2</v>
       </c>
       <c r="T23" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="U23" t="n">
         <v>1.57</v>
@@ -4945,7 +4945,7 @@
         <v>10</v>
       </c>
       <c r="AR23" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="AS23" t="n">
         <v>6.2</v>
@@ -4969,7 +4969,7 @@
         <v>11</v>
       </c>
       <c r="AZ23" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BA23" t="n">
         <v>6.2</v>
@@ -4978,7 +4978,7 @@
         <v>11.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="BD23" t="n">
         <v>6</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -5073,7 +5073,7 @@
         <v>2.28</v>
       </c>
       <c r="V24" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W24" t="n">
         <v>1.84</v>
@@ -5124,7 +5124,7 @@
         <v>500</v>
       </c>
       <c r="AM24" t="n">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="AN24" t="n">
         <v>36</v>
@@ -5157,7 +5157,7 @@
         <v>30</v>
       </c>
       <c r="AX24" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY24" t="n">
         <v>9.800000000000001</v>
@@ -5169,7 +5169,7 @@
         <v>10</v>
       </c>
       <c r="BB24" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC24" t="n">
         <v>11.5</v>
@@ -5184,11 +5184,11 @@
         <v>11</v>
       </c>
       <c r="BG24" t="n">
-        <v>9.4</v>
+        <v>26</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         <v>1.1</v>
       </c>
       <c r="N25" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O25" t="n">
         <v>1.45</v>
@@ -5258,7 +5258,7 @@
         <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T25" t="n">
         <v>2.04</v>
@@ -5297,7 +5297,7 @@
         <v>60</v>
       </c>
       <c r="AF25" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG25" t="n">
         <v>11</v>
@@ -5321,7 +5321,7 @@
         <v>150</v>
       </c>
       <c r="AN25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO25" t="n">
         <v>75</v>
@@ -5339,13 +5339,13 @@
         <v>75</v>
       </c>
       <c r="AT25" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU25" t="n">
         <v>7</v>
       </c>
       <c r="AV25" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AW25" t="n">
         <v>50</v>
@@ -5357,7 +5357,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA25" t="n">
         <v>50</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G26" t="n">
         <v>3.7</v>
       </c>
       <c r="H26" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I26" t="n">
         <v>2.3</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2.34</v>
       </c>
       <c r="J26" t="n">
         <v>3.4</v>
@@ -5446,7 +5446,7 @@
         <v>1.83</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R26" t="n">
         <v>1.31</v>
@@ -5458,10 +5458,10 @@
         <v>1.9</v>
       </c>
       <c r="U26" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V26" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="W26" t="n">
         <v>1.37</v>
@@ -5470,13 +5470,13 @@
         <v>12</v>
       </c>
       <c r="Y26" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z26" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AB26" t="n">
         <v>12.5</v>
@@ -5497,7 +5497,7 @@
         <v>15</v>
       </c>
       <c r="AH26" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI26" t="n">
         <v>42</v>
@@ -5545,22 +5545,22 @@
         <v>23</v>
       </c>
       <c r="AX26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AY26" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA26" t="n">
         <v>40</v>
       </c>
       <c r="BB26" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BC26" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BD26" t="n">
         <v>50</v>
@@ -5569,14 +5569,14 @@
         <v>80</v>
       </c>
       <c r="BF26" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BG26" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -5607,10 +5607,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G27" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H27" t="n">
         <v>3.35</v>
@@ -5631,25 +5631,25 @@
         <v>1.09</v>
       </c>
       <c r="N27" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O27" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P27" t="n">
         <v>1.81</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
       </c>
       <c r="T27" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U27" t="n">
         <v>2.1</v>
@@ -5658,7 +5658,7 @@
         <v>1.41</v>
       </c>
       <c r="W27" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X27" t="n">
         <v>12.5</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5816,7 @@
         <v>3.6</v>
       </c>
       <c r="K28" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
@@ -5834,13 +5834,13 @@
         <v>1.97</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R28" t="n">
         <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T28" t="n">
         <v>1.77</v>
@@ -5882,7 +5882,7 @@
         <v>14</v>
       </c>
       <c r="AG28" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH28" t="n">
         <v>17.5</v>
@@ -5903,7 +5903,7 @@
         <v>200</v>
       </c>
       <c r="AN28" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO28" t="n">
         <v>44</v>
@@ -5942,7 +5942,7 @@
         <v>16</v>
       </c>
       <c r="BA28" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="BB28" t="n">
         <v>23</v>
@@ -5954,7 +5954,7 @@
         <v>32</v>
       </c>
       <c r="BE28" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="BF28" t="n">
         <v>13.5</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="F29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G29" t="n">
         <v>1.72</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1.73</v>
       </c>
       <c r="H29" t="n">
         <v>6</v>
@@ -6007,10 +6007,10 @@
         <v>6.4</v>
       </c>
       <c r="J29" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K29" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L29" t="n">
         <v>1.41</v>
@@ -6019,13 +6019,13 @@
         <v>1.07</v>
       </c>
       <c r="N29" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O29" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P29" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q29" t="n">
         <v>2.02</v>
@@ -6034,10 +6034,10 @@
         <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T29" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U29" t="n">
         <v>1.98</v>
@@ -6061,7 +6061,7 @@
         <v>170</v>
       </c>
       <c r="AB29" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC29" t="n">
         <v>8.4</v>
@@ -6079,16 +6079,16 @@
         <v>10</v>
       </c>
       <c r="AH29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI29" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ29" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AK29" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AL29" t="n">
         <v>40</v>
@@ -6097,7 +6097,7 @@
         <v>140</v>
       </c>
       <c r="AN29" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO29" t="n">
         <v>130</v>
@@ -6106,19 +6106,19 @@
         <v>12.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AR29" t="n">
         <v>42</v>
       </c>
       <c r="AS29" t="n">
-        <v>16.5</v>
+        <v>29</v>
       </c>
       <c r="AT29" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU29" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV29" t="n">
         <v>20</v>
@@ -6127,7 +6127,7 @@
         <v>75</v>
       </c>
       <c r="AX29" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY29" t="n">
         <v>9.199999999999999</v>
@@ -6136,29 +6136,29 @@
         <v>20</v>
       </c>
       <c r="BA29" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BB29" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BC29" t="n">
         <v>17</v>
       </c>
       <c r="BD29" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE29" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="BF29" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -6315,7 +6315,7 @@
         <v>10</v>
       </c>
       <c r="AV30" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AW30" t="n">
         <v>6.2</v>
@@ -6327,7 +6327,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ30" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BA30" t="n">
         <v>6</v>
@@ -6348,11 +6348,11 @@
         <v>6.2</v>
       </c>
       <c r="BG30" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -6407,13 +6407,13 @@
         <v>1.06</v>
       </c>
       <c r="N31" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O31" t="n">
         <v>1.27</v>
       </c>
       <c r="P31" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q31" t="n">
         <v>1.86</v>
@@ -6425,7 +6425,7 @@
         <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="U31" t="n">
         <v>2.36</v>
@@ -6488,7 +6488,7 @@
         <v>21</v>
       </c>
       <c r="AO31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP31" t="n">
         <v>15</v>
@@ -6536,7 +6536,7 @@
         <v>32</v>
       </c>
       <c r="BE31" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="BF31" t="n">
         <v>18.5</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -6595,22 +6595,22 @@
         <v>3.45</v>
       </c>
       <c r="L32" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M32" t="n">
         <v>1.09</v>
       </c>
       <c r="N32" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="O32" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P32" t="n">
         <v>1.66</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R32" t="n">
         <v>1.25</v>
@@ -6631,10 +6631,10 @@
         <v>1.72</v>
       </c>
       <c r="X32" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y32" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z32" t="n">
         <v>28</v>
@@ -6643,13 +6643,13 @@
         <v>95</v>
       </c>
       <c r="AB32" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC32" t="n">
         <v>7.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE32" t="n">
         <v>60</v>
@@ -6664,7 +6664,7 @@
         <v>20</v>
       </c>
       <c r="AI32" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AJ32" t="n">
         <v>34</v>
@@ -6679,7 +6679,7 @@
         <v>440</v>
       </c>
       <c r="AN32" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AO32" t="n">
         <v>70</v>
@@ -6694,7 +6694,7 @@
         <v>20</v>
       </c>
       <c r="AS32" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT32" t="n">
         <v>7</v>
@@ -6706,7 +6706,7 @@
         <v>14</v>
       </c>
       <c r="AW32" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX32" t="n">
         <v>10.5</v>
@@ -6718,7 +6718,7 @@
         <v>14.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB32" t="n">
         <v>11.5</v>
@@ -6727,20 +6727,20 @@
         <v>21</v>
       </c>
       <c r="BD32" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE32" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF32" t="n">
         <v>19</v>
       </c>
       <c r="BG32" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -6774,19 +6774,19 @@
         <v>2.92</v>
       </c>
       <c r="G33" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H33" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="I33" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="J33" t="n">
         <v>3.25</v>
       </c>
       <c r="K33" t="n">
-        <v>950</v>
+        <v>10.5</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
@@ -6795,7 +6795,7 @@
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="O33" t="n">
         <v>1.23</v>
@@ -6813,13 +6813,13 @@
         <v>1.23</v>
       </c>
       <c r="T33" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U33" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V33" t="n">
-        <v>1.02</v>
+        <v>1.56</v>
       </c>
       <c r="W33" t="n">
         <v>1.16</v>
@@ -6885,56 +6885,56 @@
         <v>1.1</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AV33" t="n">
         <v>1.11</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BF33" t="n">
         <v>1.55</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -7073,52 +7073,52 @@
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF34" t="n">
         <v>1.01</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -7162,16 +7162,16 @@
         <v>1.04</v>
       </c>
       <c r="G35" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="H35" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I35" t="n">
         <v>1000</v>
       </c>
       <c r="J35" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K35" t="n">
         <v>950</v>
@@ -7207,10 +7207,10 @@
         <v>1.01</v>
       </c>
       <c r="V35" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="X35" t="n">
         <v>1000</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
@@ -760,10 +760,10 @@
         <v>1.54</v>
       </c>
       <c r="G2" t="n">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="H2" t="n">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="I2" t="n">
         <v>44</v>
@@ -808,7 +808,7 @@
         <v>1.12</v>
       </c>
       <c r="W2" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -877,7 +877,7 @@
         <v>1.27</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AU2" t="n">
         <v>1.17</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -954,16 +954,16 @@
         <v>1.58</v>
       </c>
       <c r="G3" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="H3" t="n">
         <v>6.8</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
         <v>4.4</v>
@@ -981,7 +981,7 @@
         <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q3" t="n">
         <v>2.06</v>
@@ -993,7 +993,7 @@
         <v>3.75</v>
       </c>
       <c r="T3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U3" t="n">
         <v>1.79</v>
@@ -1002,7 +1002,7 @@
         <v>1.14</v>
       </c>
       <c r="W3" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="X3" t="n">
         <v>15.5</v>
@@ -1029,7 +1029,7 @@
         <v>700</v>
       </c>
       <c r="AF3" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AG3" t="n">
         <v>12</v>
@@ -1053,7 +1053,7 @@
         <v>700</v>
       </c>
       <c r="AN3" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO3" t="n">
         <v>700</v>
@@ -1068,19 +1068,19 @@
         <v>23</v>
       </c>
       <c r="AS3" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AT3" t="n">
         <v>6.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV3" t="n">
         <v>15</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AX3" t="n">
         <v>7.8</v>
@@ -1092,7 +1092,7 @@
         <v>22</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BB3" t="n">
         <v>13</v>
@@ -1104,17 +1104,17 @@
         <v>20</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF3" t="n">
         <v>9.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -1154,10 +1154,10 @@
         <v>2.68</v>
       </c>
       <c r="I4" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="J4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
         <v>3.9</v>
@@ -1175,16 +1175,16 @@
         <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R4" t="n">
         <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T4" t="n">
         <v>1.66</v>
@@ -1193,7 +1193,7 @@
         <v>2.26</v>
       </c>
       <c r="V4" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W4" t="n">
         <v>1.54</v>
@@ -1220,7 +1220,7 @@
         <v>13.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF4" t="n">
         <v>19</v>
@@ -1277,7 +1277,7 @@
         <v>14.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY4" t="n">
         <v>10</v>
@@ -1292,23 +1292,23 @@
         <v>32</v>
       </c>
       <c r="BC4" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="BD4" t="n">
         <v>30</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF4" t="n">
         <v>18</v>
       </c>
       <c r="BG4" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -1342,10 +1342,10 @@
         <v>1.32</v>
       </c>
       <c r="G5" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="H5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="I5" t="n">
         <v>16</v>
@@ -1354,7 +1354,7 @@
         <v>5.1</v>
       </c>
       <c r="K5" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L5" t="n">
         <v>1.31</v>
@@ -1375,7 +1375,7 @@
         <v>1.89</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S5" t="n">
         <v>3.25</v>
@@ -1384,19 +1384,19 @@
         <v>2.32</v>
       </c>
       <c r="U5" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="V5" t="n">
         <v>1.06</v>
       </c>
       <c r="W5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="X5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y5" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="Z5" t="n">
         <v>150</v>
@@ -1411,7 +1411,7 @@
         <v>13</v>
       </c>
       <c r="AD5" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AE5" t="n">
         <v>330</v>
@@ -1420,7 +1420,7 @@
         <v>7.4</v>
       </c>
       <c r="AG5" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="AH5" t="n">
         <v>70</v>
@@ -1453,10 +1453,10 @@
         <v>28</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT5" t="n">
         <v>6.2</v>
@@ -1465,10 +1465,10 @@
         <v>10.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>34</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW5" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX5" t="n">
         <v>6.2</v>
@@ -1477,10 +1477,10 @@
         <v>9</v>
       </c>
       <c r="AZ5" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB5" t="n">
         <v>8.800000000000001</v>
@@ -1489,7 +1489,7 @@
         <v>13.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="BE5" t="n">
         <v>30</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -1539,40 +1539,40 @@
         <v>3.9</v>
       </c>
       <c r="H6" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="I6" t="n">
         <v>2.6</v>
       </c>
       <c r="J6" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="K6" t="n">
         <v>3.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="M6" t="n">
         <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="O6" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P6" t="n">
         <v>1.56</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="R6" t="n">
         <v>1.21</v>
       </c>
       <c r="S6" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="T6" t="n">
         <v>2</v>
@@ -1605,16 +1605,16 @@
         <v>7</v>
       </c>
       <c r="AD6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF6" t="n">
         <v>25</v>
       </c>
       <c r="AG6" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH6" t="n">
         <v>21</v>
@@ -1623,7 +1623,7 @@
         <v>130</v>
       </c>
       <c r="AJ6" t="n">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AK6" t="n">
         <v>55</v>
@@ -1641,7 +1641,7 @@
         <v>40</v>
       </c>
       <c r="AP6" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AQ6" t="n">
         <v>7.4</v>
@@ -1650,7 +1650,7 @@
         <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT6" t="n">
         <v>9.4</v>
@@ -1662,7 +1662,7 @@
         <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.800000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="AX6" t="n">
         <v>20</v>
@@ -1677,26 +1677,26 @@
         <v>48</v>
       </c>
       <c r="BB6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC6" t="n">
         <v>20</v>
       </c>
-      <c r="BC6" t="n">
+      <c r="BD6" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG6" t="n">
         <v>8.4</v>
       </c>
-      <c r="BD6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -1730,49 +1730,49 @@
         <v>3.4</v>
       </c>
       <c r="G7" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H7" t="n">
         <v>2.7</v>
       </c>
       <c r="I7" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J7" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K7" t="n">
         <v>2.98</v>
       </c>
       <c r="L7" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="M7" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N7" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="O7" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="R7" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="S7" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="T7" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="U7" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="V7" t="n">
         <v>1.56</v>
@@ -1781,7 +1781,7 @@
         <v>1.4</v>
       </c>
       <c r="X7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y7" t="n">
         <v>8.199999999999999</v>
@@ -1793,43 +1793,43 @@
         <v>220</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC7" t="n">
         <v>6.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>230</v>
+        <v>100</v>
       </c>
       <c r="AF7" t="n">
         <v>21</v>
       </c>
       <c r="AG7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI7" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="AJ7" t="n">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
         <v>440</v>
       </c>
       <c r="AL7" t="n">
-        <v>240</v>
+        <v>460</v>
       </c>
       <c r="AM7" t="n">
         <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AO7" t="n">
         <v>55</v>
@@ -1838,13 +1838,13 @@
         <v>7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR7" t="n">
         <v>14</v>
       </c>
       <c r="AS7" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AT7" t="n">
         <v>8.4</v>
@@ -1856,7 +1856,7 @@
         <v>11.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX7" t="n">
         <v>18</v>
@@ -1865,32 +1865,32 @@
         <v>13</v>
       </c>
       <c r="AZ7" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA7" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG7" t="n">
         <v>12</v>
       </c>
-      <c r="BB7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>12</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>11</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -1930,16 +1930,16 @@
         <v>2.34</v>
       </c>
       <c r="I8" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J8" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K8" t="n">
         <v>3.9</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
@@ -1951,13 +1951,13 @@
         <v>1.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
         <v>3.25</v>
@@ -1966,10 +1966,10 @@
         <v>1.72</v>
       </c>
       <c r="U8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W8" t="n">
         <v>1.44</v>
@@ -2002,7 +2002,7 @@
         <v>500</v>
       </c>
       <c r="AG8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AH8" t="n">
         <v>26</v>
@@ -2011,28 +2011,28 @@
         <v>500</v>
       </c>
       <c r="AJ8" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK8" t="n">
         <v>500</v>
       </c>
       <c r="AL8" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AM8" t="n">
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO8" t="n">
         <v>55</v>
       </c>
       <c r="AP8" t="n">
-        <v>12</v>
+        <v>7.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.6</v>
+        <v>5.8</v>
       </c>
       <c r="AR8" t="n">
         <v>8.4</v>
@@ -2041,13 +2041,13 @@
         <v>14.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU8" t="n">
         <v>7.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW8" t="n">
         <v>11.5</v>
@@ -2062,29 +2062,29 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BA8" t="n">
-        <v>20</v>
+        <v>8.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.800000000000001</v>
+        <v>21</v>
       </c>
       <c r="BC8" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BD8" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="BE8" t="n">
         <v>8.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
         <v>18.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR9" t="n">
         <v>8</v>
@@ -2247,16 +2247,16 @@
         <v>12</v>
       </c>
       <c r="AX9" t="n">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="AY9" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AZ9" t="n">
         <v>19</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="BB9" t="n">
         <v>9.199999999999999</v>
@@ -2265,10 +2265,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BD9" t="n">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF9" t="n">
         <v>15</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -2309,58 +2309,58 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.08</v>
+        <v>1.74</v>
       </c>
       <c r="G10" t="n">
-        <v>2.24</v>
+        <v>1.93</v>
       </c>
       <c r="H10" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="I10" t="n">
-        <v>3.95</v>
+        <v>5.2</v>
       </c>
       <c r="J10" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
         <v>1.3</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="O10" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S10" t="n">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="T10" t="n">
         <v>1.64</v>
       </c>
       <c r="U10" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V10" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="W10" t="n">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2369,16 +2369,16 @@
         <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AC10" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AD10" t="n">
         <v>1000</v>
@@ -2387,92 +2387,92 @@
         <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AG10" t="n">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="AH10" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AK10" t="n">
         <v>65</v>
       </c>
       <c r="AL10" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.2</v>
+        <v>4.7</v>
       </c>
       <c r="AV10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AX10" t="n">
-        <v>11.5</v>
+        <v>5.3</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BD10" t="n">
         <v>7</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>1.34</v>
       </c>
       <c r="G12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="H12" t="n">
         <v>13</v>
@@ -2709,37 +2709,37 @@
         <v>16</v>
       </c>
       <c r="J12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K12" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L12" t="n">
         <v>1.4</v>
       </c>
       <c r="M12" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="O12" t="n">
         <v>1.41</v>
       </c>
       <c r="P12" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>1.05</v>
+        <v>4.3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="U12" t="n">
         <v>1.47</v>
@@ -2748,13 +2748,13 @@
         <v>1.06</v>
       </c>
       <c r="W12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="X12" t="n">
         <v>12.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Z12" t="n">
         <v>1000</v>
@@ -2769,13 +2769,13 @@
         <v>12.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AE12" t="n">
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AG12" t="n">
         <v>12</v>
@@ -2790,7 +2790,7 @@
         <v>11</v>
       </c>
       <c r="AK12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL12" t="n">
         <v>90</v>
@@ -2799,7 +2799,7 @@
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
@@ -2811,10 +2811,10 @@
         <v>14</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT12" t="n">
         <v>4.9</v>
@@ -2823,10 +2823,10 @@
         <v>10</v>
       </c>
       <c r="AV12" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AW12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX12" t="n">
         <v>5.6</v>
@@ -2835,10 +2835,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ12" t="n">
-        <v>7.2</v>
+        <v>38</v>
       </c>
       <c r="BA12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB12" t="n">
         <v>9.199999999999999</v>
@@ -2847,20 +2847,20 @@
         <v>17</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BF12" t="n">
         <v>8</v>
       </c>
       <c r="BG12" t="n">
-        <v>8.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="G13" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H13" t="n">
         <v>4.2</v>
       </c>
       <c r="I13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J13" t="n">
         <v>3.4</v>
@@ -2912,58 +2912,58 @@
         <v>1.49</v>
       </c>
       <c r="M13" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N13" t="n">
         <v>3.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P13" t="n">
         <v>1.74</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="R13" t="n">
         <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="U13" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="X13" t="n">
         <v>11</v>
       </c>
       <c r="Y13" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z13" t="n">
         <v>32</v>
       </c>
       <c r="AA13" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB13" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE13" t="n">
         <v>65</v>
@@ -2975,16 +2975,16 @@
         <v>11</v>
       </c>
       <c r="AH13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI13" t="n">
         <v>75</v>
       </c>
       <c r="AJ13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AK13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL13" t="n">
         <v>44</v>
@@ -2993,10 +2993,10 @@
         <v>140</v>
       </c>
       <c r="AN13" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AO13" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP13" t="n">
         <v>10.5</v>
@@ -3005,56 +3005,56 @@
         <v>12.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS13" t="n">
-        <v>17.5</v>
+        <v>28</v>
       </c>
       <c r="AT13" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU13" t="n">
         <v>7.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW13" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AX13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY13" t="n">
         <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA13" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC13" t="n">
         <v>22</v>
       </c>
       <c r="BD13" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BE13" t="n">
         <v>29</v>
       </c>
       <c r="BF13" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BG13" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -3106,7 +3106,7 @@
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N14" t="n">
         <v>3.75</v>
@@ -3124,13 +3124,13 @@
         <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T14" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="U14" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V14" t="n">
         <v>1.4</v>
@@ -3139,7 +3139,7 @@
         <v>1.71</v>
       </c>
       <c r="X14" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y14" t="n">
         <v>13</v>
@@ -3190,7 +3190,7 @@
         <v>40</v>
       </c>
       <c r="AO14" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AP14" t="n">
         <v>12</v>
@@ -3223,7 +3223,7 @@
         <v>10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="BA14" t="n">
         <v>23</v>
@@ -3235,7 +3235,7 @@
         <v>22</v>
       </c>
       <c r="BD14" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="BE14" t="n">
         <v>44</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
         <v>3.75</v>
       </c>
       <c r="L15" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
@@ -3387,7 +3387,7 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AQ15" t="n">
         <v>15</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>4.8</v>
       </c>
       <c r="G16" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H16" t="n">
         <v>1.83</v>
@@ -3494,7 +3494,7 @@
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N16" t="n">
         <v>3.75</v>
@@ -3542,7 +3542,7 @@
         <v>19</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD16" t="n">
         <v>10.5</v>
@@ -3572,7 +3572,7 @@
         <v>320</v>
       </c>
       <c r="AM16" t="n">
-        <v>390</v>
+        <v>580</v>
       </c>
       <c r="AN16" t="n">
         <v>700</v>
@@ -3617,26 +3617,26 @@
         <v>27</v>
       </c>
       <c r="BB16" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD16" t="n">
         <v>8.6</v>
       </c>
-      <c r="BC16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BE16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF16" t="n">
         <v>8.6</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>8.4</v>
       </c>
       <c r="BG16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
         <v>2.26</v>
       </c>
       <c r="H17" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I17" t="n">
         <v>3.9</v>
@@ -3688,7 +3688,7 @@
         <v>1.3</v>
       </c>
       <c r="M17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
         <v>3.75</v>
@@ -3700,16 +3700,16 @@
         <v>1.96</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S17" t="n">
         <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U17" t="n">
         <v>2.24</v>
@@ -3796,10 +3796,10 @@
         <v>13</v>
       </c>
       <c r="AW17" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AX17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY17" t="n">
         <v>9.6</v>
@@ -3808,7 +3808,7 @@
         <v>15</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BB17" t="n">
         <v>13</v>
@@ -3817,7 +3817,7 @@
         <v>20</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE17" t="n">
         <v>4.3</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -3888,10 +3888,10 @@
         <v>3.95</v>
       </c>
       <c r="O18" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="Q18" t="n">
         <v>1.71</v>
@@ -3903,7 +3903,7 @@
         <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U18" t="n">
         <v>2.2</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
         <v>16</v>
       </c>
       <c r="K19" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4082,22 +4082,22 @@
         <v>11</v>
       </c>
       <c r="O19" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="P19" t="n">
-        <v>2.94</v>
+        <v>4.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="R19" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="S19" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="T19" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U19" t="n">
         <v>1.61</v>
@@ -4169,16 +4169,16 @@
         <v>4.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AS19" t="n">
         <v>4.2</v>
       </c>
       <c r="AT19" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AU19" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="AV19" t="n">
         <v>4.2</v>
@@ -4190,35 +4190,35 @@
         <v>6.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AZ19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BA19" t="n">
         <v>4.3</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="BD19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="BG19" t="n">
         <v>10.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -4249,19 +4249,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G20" t="n">
         <v>1.52</v>
       </c>
       <c r="H20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I20" t="n">
         <v>11.5</v>
       </c>
       <c r="J20" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K20" t="n">
         <v>4.5</v>
@@ -4300,10 +4300,10 @@
         <v>1.1</v>
       </c>
       <c r="W20" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="X20" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y20" t="n">
         <v>42</v>
@@ -4348,7 +4348,7 @@
         <v>500</v>
       </c>
       <c r="AM20" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AN20" t="n">
         <v>10.5</v>
@@ -4357,16 +4357,16 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="AQ20" t="n">
         <v>18.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AS20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT20" t="n">
         <v>5.7</v>
@@ -4375,31 +4375,31 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV20" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AW20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX20" t="n">
         <v>6.6</v>
       </c>
       <c r="AY20" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="AZ20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BA20" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BB20" t="n">
         <v>10</v>
       </c>
       <c r="BC20" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE20" t="n">
         <v>30</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -4449,13 +4449,13 @@
         <v>2.68</v>
       </c>
       <c r="H21" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="I21" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J21" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K21" t="n">
         <v>4.1</v>
@@ -4467,13 +4467,13 @@
         <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O21" t="n">
         <v>1.24</v>
       </c>
       <c r="P21" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q21" t="n">
         <v>1.7</v>
@@ -4488,10 +4488,10 @@
         <v>1.62</v>
       </c>
       <c r="U21" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V21" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W21" t="n">
         <v>1.59</v>
@@ -4560,7 +4560,7 @@
         <v>15.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT21" t="n">
         <v>9.4</v>
@@ -4584,7 +4584,7 @@
         <v>11.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB21" t="n">
         <v>14.5</v>
@@ -4596,7 +4596,7 @@
         <v>16</v>
       </c>
       <c r="BE21" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF21" t="n">
         <v>12.5</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -4637,19 +4637,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G22" t="n">
         <v>3.4</v>
       </c>
       <c r="H22" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I22" t="n">
         <v>2.94</v>
       </c>
       <c r="J22" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="K22" t="n">
         <v>3</v>
@@ -4667,7 +4667,7 @@
         <v>1.66</v>
       </c>
       <c r="P22" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q22" t="n">
         <v>3</v>
@@ -4688,13 +4688,13 @@
         <v>1.51</v>
       </c>
       <c r="W22" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X22" t="n">
         <v>8.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="Z22" t="n">
         <v>17</v>
@@ -4718,7 +4718,7 @@
         <v>20</v>
       </c>
       <c r="AG22" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH22" t="n">
         <v>26</v>
@@ -4727,10 +4727,10 @@
         <v>170</v>
       </c>
       <c r="AJ22" t="n">
-        <v>900</v>
+        <v>70</v>
       </c>
       <c r="AK22" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AL22" t="n">
         <v>100</v>
@@ -4742,7 +4742,7 @@
         <v>85</v>
       </c>
       <c r="AO22" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AP22" t="n">
         <v>5.7</v>
@@ -4754,7 +4754,7 @@
         <v>15</v>
       </c>
       <c r="AS22" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT22" t="n">
         <v>7.6</v>
@@ -4766,7 +4766,7 @@
         <v>12</v>
       </c>
       <c r="AW22" t="n">
-        <v>8.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="AX22" t="n">
         <v>17.5</v>
@@ -4778,29 +4778,29 @@
         <v>22</v>
       </c>
       <c r="BA22" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC22" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BB22" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BD22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG22" t="n">
         <v>9</v>
       </c>
-      <c r="BE22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -4843,7 +4843,7 @@
         <v>5.8</v>
       </c>
       <c r="J23" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="K23" t="n">
         <v>3.1</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
         <v>65</v>
       </c>
       <c r="AA24" t="n">
-        <v>130</v>
+        <v>440</v>
       </c>
       <c r="AB24" t="n">
         <v>11.5</v>
@@ -5124,7 +5124,7 @@
         <v>500</v>
       </c>
       <c r="AM24" t="n">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="AN24" t="n">
         <v>36</v>
@@ -5142,7 +5142,7 @@
         <v>21</v>
       </c>
       <c r="AS24" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="AT24" t="n">
         <v>10</v>
@@ -5160,7 +5160,7 @@
         <v>13</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ24" t="n">
         <v>14.5</v>
@@ -5169,7 +5169,7 @@
         <v>10</v>
       </c>
       <c r="BB24" t="n">
-        <v>9.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="BC24" t="n">
         <v>11.5</v>
@@ -5178,7 +5178,7 @@
         <v>10</v>
       </c>
       <c r="BE24" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BF24" t="n">
         <v>11</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -5219,61 +5219,61 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G25" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H25" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I25" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K25" t="n">
         <v>3.4</v>
       </c>
-      <c r="K25" t="n">
-        <v>3.45</v>
-      </c>
       <c r="L25" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M25" t="n">
         <v>1.1</v>
       </c>
       <c r="N25" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="P25" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S25" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="T25" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U25" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="V25" t="n">
         <v>1.33</v>
       </c>
       <c r="W25" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="X25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y25" t="n">
         <v>12</v>
@@ -5282,10 +5282,10 @@
         <v>25</v>
       </c>
       <c r="AA25" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AB25" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC25" t="n">
         <v>7.4</v>
@@ -5300,13 +5300,13 @@
         <v>12</v>
       </c>
       <c r="AG25" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI25" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ25" t="n">
         <v>28</v>
@@ -5315,19 +5315,19 @@
         <v>27</v>
       </c>
       <c r="AL25" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM25" t="n">
-        <v>150</v>
+        <v>440</v>
       </c>
       <c r="AN25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO25" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AP25" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AQ25" t="n">
         <v>11</v>
@@ -5339,13 +5339,13 @@
         <v>75</v>
       </c>
       <c r="AT25" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU25" t="n">
         <v>7</v>
       </c>
       <c r="AV25" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW25" t="n">
         <v>50</v>
@@ -5360,7 +5360,7 @@
         <v>21</v>
       </c>
       <c r="BA25" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BB25" t="n">
         <v>26</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G26" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H26" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I26" t="n">
         <v>2.28</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2.3</v>
       </c>
       <c r="J26" t="n">
         <v>3.4</v>
@@ -5437,7 +5437,7 @@
         <v>1.09</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O26" t="n">
         <v>1.38</v>
@@ -5452,7 +5452,7 @@
         <v>1.31</v>
       </c>
       <c r="S26" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
         <v>1.9</v>
@@ -5461,10 +5461,10 @@
         <v>2.08</v>
       </c>
       <c r="V26" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="W26" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X26" t="n">
         <v>12</v>
@@ -5488,7 +5488,7 @@
         <v>11</v>
       </c>
       <c r="AE26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF26" t="n">
         <v>24</v>
@@ -5497,7 +5497,7 @@
         <v>15</v>
       </c>
       <c r="AH26" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI26" t="n">
         <v>42</v>
@@ -5515,7 +5515,7 @@
         <v>100</v>
       </c>
       <c r="AN26" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AO26" t="n">
         <v>21</v>
@@ -5530,7 +5530,7 @@
         <v>13</v>
       </c>
       <c r="AS26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT26" t="n">
         <v>11.5</v>
@@ -5569,14 +5569,14 @@
         <v>80</v>
       </c>
       <c r="BF26" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BG26" t="n">
         <v>19.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
         <v>3.35</v>
       </c>
       <c r="I27" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J27" t="n">
         <v>3.35</v>
@@ -5637,13 +5637,13 @@
         <v>1.38</v>
       </c>
       <c r="P27" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q27" t="n">
         <v>2.16</v>
       </c>
       <c r="R27" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -5661,7 +5661,7 @@
         <v>1.67</v>
       </c>
       <c r="X27" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y27" t="n">
         <v>12</v>
@@ -5712,7 +5712,7 @@
         <v>24</v>
       </c>
       <c r="AO27" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AP27" t="n">
         <v>11</v>
@@ -5739,7 +5739,7 @@
         <v>36</v>
       </c>
       <c r="AX27" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY27" t="n">
         <v>10.5</v>
@@ -5751,13 +5751,13 @@
         <v>29</v>
       </c>
       <c r="BB27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC27" t="n">
         <v>24</v>
       </c>
       <c r="BD27" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="BE27" t="n">
         <v>60</v>
@@ -5766,11 +5766,11 @@
         <v>21</v>
       </c>
       <c r="BG27" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5816,7 @@
         <v>3.6</v>
       </c>
       <c r="K28" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
@@ -5840,7 +5840,7 @@
         <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T28" t="n">
         <v>1.77</v>
@@ -5855,7 +5855,7 @@
         <v>1.81</v>
       </c>
       <c r="X28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y28" t="n">
         <v>15</v>
@@ -5918,7 +5918,7 @@
         <v>23</v>
       </c>
       <c r="AS28" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="AT28" t="n">
         <v>9.199999999999999</v>
@@ -5948,7 +5948,7 @@
         <v>23</v>
       </c>
       <c r="BC28" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD28" t="n">
         <v>32</v>
@@ -5957,14 +5957,14 @@
         <v>48</v>
       </c>
       <c r="BF28" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG28" t="n">
         <v>36</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -5995,100 +5995,100 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="G29" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="H29" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="I29" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J29" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K29" t="n">
         <v>4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M29" t="n">
         <v>1.07</v>
       </c>
       <c r="N29" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O29" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P29" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S29" t="n">
         <v>3.65</v>
       </c>
       <c r="T29" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="U29" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V29" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W29" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="X29" t="n">
         <v>14</v>
       </c>
       <c r="Y29" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="Z29" t="n">
         <v>55</v>
       </c>
       <c r="AA29" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AB29" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC29" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD29" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH29" t="n">
         <v>23</v>
       </c>
-      <c r="AE29" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>22</v>
-      </c>
       <c r="AI29" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AK29" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL29" t="n">
         <v>40</v>
@@ -6097,22 +6097,22 @@
         <v>140</v>
       </c>
       <c r="AN29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO29" t="n">
-        <v>130</v>
+        <v>410</v>
       </c>
       <c r="AP29" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AS29" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AT29" t="n">
         <v>7.4</v>
@@ -6121,44 +6121,44 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AW29" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AX29" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY29" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ29" t="n">
         <v>20</v>
       </c>
       <c r="BA29" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="BB29" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC29" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE29" t="n">
+        <v>90</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG29" t="n">
         <v>100</v>
       </c>
-      <c r="BF29" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>14</v>
-      </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -6204,16 +6204,16 @@
         <v>5</v>
       </c>
       <c r="K30" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="L30" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
         <v>1.08</v>
       </c>
       <c r="N30" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="O30" t="n">
         <v>1.38</v>
@@ -6231,7 +6231,7 @@
         <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="U30" t="n">
         <v>1.43</v>
@@ -6291,7 +6291,7 @@
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO30" t="n">
         <v>1000</v>
@@ -6315,7 +6315,7 @@
         <v>10</v>
       </c>
       <c r="AV30" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AW30" t="n">
         <v>6.2</v>
@@ -6327,10 +6327,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ30" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BA30" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB30" t="n">
         <v>7.4</v>
@@ -6339,7 +6339,7 @@
         <v>15</v>
       </c>
       <c r="BD30" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE30" t="n">
         <v>6.2</v>
@@ -6348,11 +6348,11 @@
         <v>6.2</v>
       </c>
       <c r="BG30" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -6383,16 +6383,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="G31" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="H31" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="I31" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
         <v>3.6</v>
@@ -6401,43 +6401,43 @@
         <v>3.65</v>
       </c>
       <c r="L31" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M31" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N31" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="O31" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="P31" t="n">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="R31" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T31" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="U31" t="n">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="V31" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="X31" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y31" t="n">
         <v>13.5</v>
@@ -6446,88 +6446,88 @@
         <v>20</v>
       </c>
       <c r="AA31" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AB31" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC31" t="n">
         <v>8</v>
       </c>
       <c r="AD31" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AF31" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AG31" t="n">
         <v>12</v>
       </c>
       <c r="AH31" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI31" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>38</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>40</v>
       </c>
       <c r="AK31" t="n">
         <v>28</v>
       </c>
       <c r="AL31" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM31" t="n">
-        <v>75</v>
+        <v>320</v>
       </c>
       <c r="AN31" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO31" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AP31" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR31" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AT31" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AU31" t="n">
         <v>7.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW31" t="n">
         <v>25</v>
       </c>
       <c r="AX31" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA31" t="n">
         <v>32</v>
       </c>
       <c r="BB31" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC31" t="n">
         <v>24</v>
@@ -6539,14 +6539,14 @@
         <v>36</v>
       </c>
       <c r="BF31" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6583,7 @@
         <v>2.4</v>
       </c>
       <c r="H32" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I32" t="n">
         <v>4.2</v>
@@ -6634,7 +6634,7 @@
         <v>11</v>
       </c>
       <c r="Y32" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z32" t="n">
         <v>28</v>
@@ -6655,7 +6655,7 @@
         <v>60</v>
       </c>
       <c r="AF32" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AG32" t="n">
         <v>12</v>
@@ -6664,7 +6664,7 @@
         <v>20</v>
       </c>
       <c r="AI32" t="n">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AJ32" t="n">
         <v>34</v>
@@ -6679,7 +6679,7 @@
         <v>440</v>
       </c>
       <c r="AN32" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO32" t="n">
         <v>70</v>
@@ -6691,22 +6691,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR32" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AS32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT32" t="n">
         <v>7</v>
       </c>
       <c r="AU32" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV32" t="n">
         <v>14</v>
       </c>
       <c r="AW32" t="n">
-        <v>7.6</v>
+        <v>40</v>
       </c>
       <c r="AX32" t="n">
         <v>10.5</v>
@@ -6718,7 +6718,7 @@
         <v>14.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BB32" t="n">
         <v>11.5</v>
@@ -6727,20 +6727,20 @@
         <v>21</v>
       </c>
       <c r="BD32" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE32" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF32" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BG32" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -6819,7 +6819,7 @@
         <v>1.11</v>
       </c>
       <c r="V33" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="W33" t="n">
         <v>1.16</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -6977,7 +6977,7 @@
         <v>1000</v>
       </c>
       <c r="J34" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K34" t="n">
         <v>1000</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="O35" t="n">
         <v>1.29</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-08 22:19:56</t>
+          <t>2026-04-09 00:39:43</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH35"/>
+  <dimension ref="A1:BH34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,25 +760,25 @@
         <v>1.54</v>
       </c>
       <c r="G2" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="H2" t="n">
-        <v>3.15</v>
+        <v>2.52</v>
       </c>
       <c r="I2" t="n">
-        <v>44</v>
+        <v>8.6</v>
       </c>
       <c r="J2" t="n">
         <v>2.96</v>
       </c>
       <c r="K2" t="n">
-        <v>9.6</v>
+        <v>5.4</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
         <v>1.1</v>
@@ -790,13 +790,13 @@
         <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R2" t="n">
         <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>1.05</v>
+        <v>1.41</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -805,13 +805,13 @@
         <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W2" t="n">
         <v>1.78</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y2" t="n">
         <v>1000</v>
@@ -868,49 +868,49 @@
         <v>1.27</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="BF2" t="n">
         <v>1.55</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -951,61 +951,61 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="G3" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="H3" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="I3" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="M3" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="O3" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="P3" t="n">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="R3" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="U3" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="V3" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="W3" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="X3" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y3" t="n">
         <v>24</v>
@@ -1017,104 +1017,104 @@
         <v>700</v>
       </c>
       <c r="AB3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="AE3" t="n">
         <v>700</v>
       </c>
       <c r="AF3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG3" t="n">
         <v>10</v>
       </c>
-      <c r="AG3" t="n">
-        <v>12</v>
-      </c>
       <c r="AH3" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AI3" t="n">
         <v>700</v>
       </c>
       <c r="AJ3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK3" t="n">
         <v>17.5</v>
       </c>
-      <c r="AK3" t="n">
-        <v>21</v>
-      </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM3" t="n">
         <v>700</v>
       </c>
       <c r="AN3" t="n">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="AO3" t="n">
         <v>700</v>
       </c>
       <c r="AP3" t="n">
-        <v>11.5</v>
+        <v>7.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.5</v>
+        <v>12</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX3" t="n">
         <v>8.4</v>
       </c>
-      <c r="AV3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AY3" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.6</v>
+        <v>11</v>
       </c>
       <c r="BB3" t="n">
         <v>13</v>
       </c>
       <c r="BC3" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.6</v>
+        <v>36</v>
       </c>
       <c r="BF3" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -1145,85 +1145,85 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G4" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="H4" t="n">
         <v>2.68</v>
       </c>
       <c r="I4" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O4" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="R4" t="n">
         <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="V4" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="W4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X4" t="n">
         <v>17.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA4" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AB4" t="n">
         <v>13</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD4" t="n">
         <v>13.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG4" t="n">
         <v>13</v>
@@ -1235,34 +1235,34 @@
         <v>40</v>
       </c>
       <c r="AJ4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL4" t="n">
         <v>42</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>38</v>
       </c>
       <c r="AM4" t="n">
         <v>320</v>
       </c>
       <c r="AN4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AO4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP4" t="n">
         <v>14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AS4" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="AT4" t="n">
         <v>10.5</v>
@@ -1271,44 +1271,44 @@
         <v>7.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX4" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.8</v>
+        <v>32</v>
       </c>
       <c r="BB4" t="n">
         <v>32</v>
       </c>
       <c r="BC4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD4" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="BE4" t="n">
         <v>8.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BG4" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -1339,37 +1339,37 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="G5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H5" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="I5" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="J5" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="K5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="O5" t="n">
         <v>1.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="Q5" t="n">
         <v>1.89</v>
@@ -1378,28 +1378,28 @@
         <v>1.39</v>
       </c>
       <c r="S5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="U5" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="V5" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W5" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="X5" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Y5" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="Z5" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
@@ -1411,22 +1411,22 @@
         <v>13</v>
       </c>
       <c r="AD5" t="n">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="AE5" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="AF5" t="n">
         <v>7.4</v>
       </c>
       <c r="AG5" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AH5" t="n">
         <v>70</v>
       </c>
       <c r="AI5" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AJ5" t="n">
         <v>11</v>
@@ -1435,28 +1435,28 @@
         <v>17</v>
       </c>
       <c r="AL5" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AM5" t="n">
         <v>310</v>
       </c>
       <c r="AN5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="AP5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ5" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="AR5" t="n">
-        <v>8.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT5" t="n">
         <v>6.2</v>
@@ -1465,22 +1465,22 @@
         <v>10.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>8.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="AW5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY5" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9</v>
       </c>
       <c r="AZ5" t="n">
         <v>22</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.800000000000001</v>
+        <v>38</v>
       </c>
       <c r="BB5" t="n">
         <v>8.800000000000001</v>
@@ -1492,7 +1492,7 @@
         <v>23</v>
       </c>
       <c r="BE5" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="BF5" t="n">
         <v>5.9</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -1536,61 +1536,61 @@
         <v>3.6</v>
       </c>
       <c r="G6" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="H6" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="I6" t="n">
         <v>2.6</v>
       </c>
       <c r="J6" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="M6" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N6" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="O6" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="P6" t="n">
         <v>1.56</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="R6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S6" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U6" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="V6" t="n">
         <v>1.62</v>
       </c>
       <c r="W6" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="X6" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z6" t="n">
         <v>15.5</v>
@@ -1626,7 +1626,7 @@
         <v>80</v>
       </c>
       <c r="AK6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL6" t="n">
         <v>380</v>
@@ -1635,22 +1635,22 @@
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>170</v>
+        <v>600</v>
       </c>
       <c r="AO6" t="n">
         <v>40</v>
       </c>
       <c r="AP6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AR6" t="n">
         <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.6</v>
+        <v>19</v>
       </c>
       <c r="AT6" t="n">
         <v>9.4</v>
@@ -1671,32 +1671,32 @@
         <v>13.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA6" t="n">
         <v>48</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BC6" t="n">
         <v>20</v>
       </c>
       <c r="BD6" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="BE6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF6" t="n">
         <v>20</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -1733,34 +1733,34 @@
         <v>3.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="I7" t="n">
         <v>2.76</v>
       </c>
       <c r="J7" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="K7" t="n">
         <v>2.98</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="M7" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N7" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O7" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P7" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R7" t="n">
         <v>1.19</v>
@@ -1769,10 +1769,10 @@
         <v>5.7</v>
       </c>
       <c r="T7" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U7" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V7" t="n">
         <v>1.56</v>
@@ -1817,25 +1817,25 @@
         <v>70</v>
       </c>
       <c r="AJ7" t="n">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AK7" t="n">
         <v>440</v>
       </c>
       <c r="AL7" t="n">
-        <v>460</v>
+        <v>240</v>
       </c>
       <c r="AM7" t="n">
         <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>75</v>
+        <v>600</v>
       </c>
       <c r="AO7" t="n">
-        <v>55</v>
+        <v>600</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AQ7" t="n">
         <v>7.4</v>
@@ -1844,19 +1844,19 @@
         <v>14</v>
       </c>
       <c r="AS7" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AT7" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV7" t="n">
         <v>11.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="AX7" t="n">
         <v>18</v>
@@ -1868,29 +1868,29 @@
         <v>19.5</v>
       </c>
       <c r="BA7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC7" t="n">
         <v>13</v>
       </c>
-      <c r="BB7" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BD7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BE7" t="n">
-        <v>28</v>
+        <v>15.5</v>
       </c>
       <c r="BF7" t="n">
         <v>13.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -1921,58 +1921,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H8" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I8" t="n">
         <v>2.42</v>
       </c>
       <c r="J8" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L8" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O8" t="n">
         <v>1.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="R8" t="n">
         <v>1.37</v>
       </c>
       <c r="S8" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="U8" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="V8" t="n">
         <v>1.7</v>
       </c>
       <c r="W8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X8" t="n">
         <v>90</v>
@@ -2002,7 +2002,7 @@
         <v>500</v>
       </c>
       <c r="AG8" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AH8" t="n">
         <v>26</v>
@@ -2032,13 +2032,13 @@
         <v>7.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.8</v>
+        <v>9.6</v>
       </c>
       <c r="AR8" t="n">
         <v>8.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AT8" t="n">
         <v>9.800000000000001</v>
@@ -2050,7 +2050,7 @@
         <v>9.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX8" t="n">
         <v>10.5</v>
@@ -2062,29 +2062,29 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.4</v>
+        <v>17.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC8" t="n">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="BD8" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.4</v>
+        <v>29</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -2115,100 +2115,100 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="G9" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="H9" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="I9" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="J9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K9" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="L9" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M9" t="n">
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O9" t="n">
         <v>1.21</v>
       </c>
       <c r="P9" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="R9" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="S9" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="T9" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="U9" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="V9" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="W9" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X9" t="n">
         <v>24</v>
       </c>
       <c r="Y9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z9" t="n">
         <v>10.5</v>
       </c>
-      <c r="Z9" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AA9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB9" t="n">
         <v>70</v>
       </c>
       <c r="AC9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>540</v>
+        <v>170</v>
       </c>
       <c r="AG9" t="n">
         <v>75</v>
       </c>
       <c r="AH9" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="AI9" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="AJ9" t="n">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="AK9" t="n">
-        <v>480</v>
+        <v>260</v>
       </c>
       <c r="AL9" t="n">
         <v>390</v>
@@ -2217,7 +2217,7 @@
         <v>390</v>
       </c>
       <c r="AN9" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AO9" t="n">
         <v>6.4</v>
@@ -2226,43 +2226,43 @@
         <v>18.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AS9" t="n">
         <v>11.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="AU9" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AV9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AW9" t="n">
         <v>12</v>
       </c>
       <c r="AX9" t="n">
-        <v>28</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA9" t="n">
         <v>16</v>
       </c>
-      <c r="AZ9" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BB9" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BD9" t="n">
         <v>28</v>
@@ -2271,14 +2271,14 @@
         <v>10</v>
       </c>
       <c r="BF9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -2309,58 +2309,58 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1.74</v>
       </c>
-      <c r="G10" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="H10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.67</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="T10" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U10" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V10" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="W10" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2375,13 +2375,13 @@
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AC10" t="n">
         <v>14</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE10" t="n">
         <v>1000</v>
@@ -2390,7 +2390,7 @@
         <v>26</v>
       </c>
       <c r="AG10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AH10" t="n">
         <v>500</v>
@@ -2399,80 +2399,80 @@
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AK10" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="AR10" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.2</v>
+        <v>9.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AV10" t="n">
         <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX10" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AY10" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BA10" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.4</v>
+        <v>16.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="BF10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG10" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BG10" t="n">
-        <v>6</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -2506,46 +2506,46 @@
         <v>2.98</v>
       </c>
       <c r="G11" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H11" t="n">
         <v>2.28</v>
       </c>
       <c r="I11" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J11" t="n">
         <v>3.65</v>
       </c>
       <c r="K11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L11" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="M11" t="n">
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P11" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="R11" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S11" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="T11" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="U11" t="n">
         <v>2.38</v>
@@ -2560,10 +2560,10 @@
         <v>24</v>
       </c>
       <c r="Y11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA11" t="n">
         <v>38</v>
@@ -2575,7 +2575,7 @@
         <v>11</v>
       </c>
       <c r="AD11" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE11" t="n">
         <v>28</v>
@@ -2593,7 +2593,7 @@
         <v>38</v>
       </c>
       <c r="AJ11" t="n">
-        <v>280</v>
+        <v>900</v>
       </c>
       <c r="AK11" t="n">
         <v>40</v>
@@ -2602,71 +2602,71 @@
         <v>46</v>
       </c>
       <c r="AM11" t="n">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="AN11" t="n">
         <v>29</v>
       </c>
       <c r="AO11" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AP11" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AR11" t="n">
-        <v>12.5</v>
+        <v>8.4</v>
       </c>
       <c r="AS11" t="n">
         <v>13</v>
       </c>
       <c r="AT11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AX11" t="n">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>18</v>
+        <v>4.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BC11" t="n">
         <v>16</v>
       </c>
       <c r="BD11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF11" t="n">
         <v>20</v>
       </c>
-      <c r="BE11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>17</v>
-      </c>
       <c r="BG11" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="G12" t="n">
         <v>1.41</v>
@@ -2706,55 +2706,55 @@
         <v>13</v>
       </c>
       <c r="I12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="J12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K12" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="M12" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="O12" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P12" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T12" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="U12" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V12" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W12" t="n">
         <v>3.4</v>
       </c>
       <c r="X12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y12" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Z12" t="n">
         <v>1000</v>
@@ -2763,13 +2763,13 @@
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD12" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AE12" t="n">
         <v>1000</v>
@@ -2778,10 +2778,10 @@
         <v>6.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
@@ -2790,16 +2790,16 @@
         <v>11</v>
       </c>
       <c r="AK12" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AL12" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
@@ -2808,28 +2808,28 @@
         <v>10</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AU12" t="n">
         <v>10</v>
       </c>
       <c r="AV12" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AY12" t="n">
         <v>9.800000000000001</v>
@@ -2838,7 +2838,7 @@
         <v>38</v>
       </c>
       <c r="BA12" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BB12" t="n">
         <v>9.199999999999999</v>
@@ -2847,10 +2847,10 @@
         <v>17</v>
       </c>
       <c r="BD12" t="n">
-        <v>8.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="BE12" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BF12" t="n">
         <v>8</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -2891,73 +2891,73 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G13" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H13" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I13" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K13" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L13" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M13" t="n">
         <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O13" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P13" t="n">
         <v>1.74</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S13" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="T13" t="n">
         <v>1.97</v>
       </c>
       <c r="U13" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V13" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="X13" t="n">
         <v>11</v>
       </c>
       <c r="Y13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z13" t="n">
         <v>32</v>
       </c>
       <c r="AA13" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC13" t="n">
         <v>7.4</v>
@@ -2978,10 +2978,10 @@
         <v>21</v>
       </c>
       <c r="AI13" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AJ13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK13" t="n">
         <v>24</v>
@@ -2993,7 +2993,7 @@
         <v>140</v>
       </c>
       <c r="AN13" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="AO13" t="n">
         <v>80</v>
@@ -3008,10 +3008,10 @@
         <v>27</v>
       </c>
       <c r="AS13" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AT13" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU13" t="n">
         <v>7.2</v>
@@ -3023,19 +3023,19 @@
         <v>50</v>
       </c>
       <c r="AX13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY13" t="n">
         <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA13" t="n">
         <v>60</v>
       </c>
       <c r="BB13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC13" t="n">
         <v>22</v>
@@ -3044,17 +3044,17 @@
         <v>38</v>
       </c>
       <c r="BE13" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="BF13" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BG13" t="n">
         <v>65</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="G14" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="H14" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="I14" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="J14" t="n">
         <v>3.45</v>
@@ -3103,82 +3103,82 @@
         <v>3.55</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M14" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P14" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W14" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="X14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y14" t="n">
         <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="AA14" t="n">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AB14" t="n">
         <v>10.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF14" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG14" t="n">
         <v>11.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI14" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AJ14" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AK14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL14" t="n">
         <v>40</v>
@@ -3187,7 +3187,7 @@
         <v>320</v>
       </c>
       <c r="AN14" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="AO14" t="n">
         <v>500</v>
@@ -3196,10 +3196,10 @@
         <v>12</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS14" t="n">
         <v>23</v>
@@ -3211,44 +3211,44 @@
         <v>7.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW14" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AX14" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AY14" t="n">
         <v>10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BA14" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="BB14" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="BC14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BD14" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="BE14" t="n">
         <v>44</v>
       </c>
       <c r="BF14" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -3279,64 +3279,64 @@
         </is>
       </c>
       <c r="F15" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G15" t="n">
         <v>2.28</v>
       </c>
-      <c r="G15" t="n">
-        <v>2.38</v>
-      </c>
       <c r="H15" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I15" t="n">
         <v>3.7</v>
       </c>
       <c r="J15" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K15" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L15" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="O15" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="R15" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="S15" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="T15" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="U15" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V15" t="n">
         <v>1.37</v>
       </c>
       <c r="W15" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="X15" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z15" t="n">
         <v>1000</v>
@@ -3345,10 +3345,10 @@
         <v>900</v>
       </c>
       <c r="AB15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD15" t="n">
         <v>15.5</v>
@@ -3363,7 +3363,7 @@
         <v>12</v>
       </c>
       <c r="AH15" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI15" t="n">
         <v>500</v>
@@ -3381,10 +3381,10 @@
         <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP15" t="n">
         <v>16</v>
@@ -3396,16 +3396,16 @@
         <v>21</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.800000000000001</v>
+        <v>42</v>
       </c>
       <c r="AT15" t="n">
         <v>10.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW15" t="n">
         <v>29</v>
@@ -3417,13 +3417,13 @@
         <v>9.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA15" t="n">
         <v>32</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="BC15" t="n">
         <v>18</v>
@@ -3432,17 +3432,17 @@
         <v>25</v>
       </c>
       <c r="BE15" t="n">
-        <v>9</v>
+        <v>19.5</v>
       </c>
       <c r="BF15" t="n">
         <v>11</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.6</v>
+        <v>22</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -3473,46 +3473,46 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="G16" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="H16" t="n">
         <v>1.83</v>
       </c>
       <c r="I16" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K16" t="n">
         <v>4.1</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M16" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P16" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="R16" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T16" t="n">
         <v>1.81</v>
@@ -3521,16 +3521,16 @@
         <v>2.02</v>
       </c>
       <c r="V16" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="W16" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X16" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z16" t="n">
         <v>11.5</v>
@@ -3542,7 +3542,7 @@
         <v>19</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD16" t="n">
         <v>10.5</v>
@@ -3551,7 +3551,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="AG16" t="n">
         <v>21</v>
@@ -3560,7 +3560,7 @@
         <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="AJ16" t="n">
         <v>1000</v>
@@ -3569,7 +3569,7 @@
         <v>700</v>
       </c>
       <c r="AL16" t="n">
-        <v>320</v>
+        <v>160</v>
       </c>
       <c r="AM16" t="n">
         <v>580</v>
@@ -3584,59 +3584,59 @@
         <v>13</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AR16" t="n">
         <v>9.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT16" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AV16" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW16" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AX16" t="n">
         <v>16</v>
       </c>
       <c r="AY16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BA16" t="n">
-        <v>27</v>
+        <v>18.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BC16" t="n">
-        <v>8.4</v>
+        <v>34</v>
       </c>
       <c r="BD16" t="n">
-        <v>8.6</v>
+        <v>29</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="BG16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -3673,40 +3673,40 @@
         <v>2.26</v>
       </c>
       <c r="H17" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I17" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J17" t="n">
         <v>3.45</v>
       </c>
       <c r="K17" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="M17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="O17" t="n">
         <v>1.31</v>
       </c>
       <c r="P17" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R17" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T17" t="n">
         <v>1.76</v>
@@ -3715,7 +3715,7 @@
         <v>2.24</v>
       </c>
       <c r="V17" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W17" t="n">
         <v>1.79</v>
@@ -3724,43 +3724,43 @@
         <v>18</v>
       </c>
       <c r="Y17" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z17" t="n">
         <v>32</v>
       </c>
       <c r="AA17" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE17" t="n">
         <v>55</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI17" t="n">
         <v>55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL17" t="n">
         <v>46</v>
@@ -3769,13 +3769,13 @@
         <v>110</v>
       </c>
       <c r="AN17" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO17" t="n">
         <v>55</v>
       </c>
       <c r="AP17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AQ17" t="n">
         <v>12</v>
@@ -3784,7 +3784,7 @@
         <v>11.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.4</v>
+        <v>23</v>
       </c>
       <c r="AT17" t="n">
         <v>8.800000000000001</v>
@@ -3796,7 +3796,7 @@
         <v>13</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AX17" t="n">
         <v>12</v>
@@ -3808,7 +3808,7 @@
         <v>15</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BB17" t="n">
         <v>13</v>
@@ -3817,20 +3817,20 @@
         <v>20</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.2</v>
+        <v>30</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BF17" t="n">
         <v>14</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.2</v>
+        <v>36</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -3861,58 +3861,58 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G18" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H18" t="n">
         <v>3.35</v>
       </c>
       <c r="I18" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="J18" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="M18" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="O18" t="n">
         <v>1.27</v>
       </c>
       <c r="P18" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="R18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V18" t="n">
         <v>1.39</v>
       </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.35</v>
-      </c>
       <c r="W18" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X18" t="n">
         <v>90</v>
@@ -3924,19 +3924,19 @@
         <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE18" t="n">
         <v>500</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1000</v>
       </c>
       <c r="AF18" t="n">
         <v>500</v>
@@ -3948,10 +3948,10 @@
         <v>38</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ18" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK18" t="n">
         <v>1000</v>
@@ -3969,62 +3969,62 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.72</v>
+        <v>7.6</v>
       </c>
       <c r="AQ18" t="n">
         <v>8.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.88</v>
+        <v>7.4</v>
       </c>
       <c r="AS18" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AV18" t="n">
         <v>8.4</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.98</v>
+        <v>8</v>
       </c>
       <c r="AX18" t="n">
         <v>7.6</v>
       </c>
       <c r="AY18" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AZ18" t="n">
         <v>9</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.05</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB18" t="n">
-        <v>2.9</v>
+        <v>7.6</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.84</v>
+        <v>7.2</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.94</v>
+        <v>8</v>
       </c>
       <c r="BE18" t="n">
-        <v>3.05</v>
+        <v>4.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.85</v>
+        <v>6.2</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
         <v>1.07</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="H19" t="n">
         <v>42</v>
@@ -4067,46 +4067,46 @@
         <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="K19" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="M19" t="n">
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O19" t="n">
         <v>1.06</v>
       </c>
       <c r="P19" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="R19" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="S19" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="T19" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U19" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="V19" t="n">
         <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -4163,25 +4163,25 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR19" t="n">
         <v>4.2</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>4.4</v>
       </c>
       <c r="AS19" t="n">
         <v>4.2</v>
       </c>
       <c r="AT19" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AU19" t="n">
         <v>4.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AW19" t="n">
         <v>4.2</v>
@@ -4190,35 +4190,35 @@
         <v>6.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="AZ19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA19" t="n">
         <v>4.2</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>4.3</v>
       </c>
       <c r="BB19" t="n">
         <v>7.2</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="BE19" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BG19" t="n">
         <v>10.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -4252,43 +4252,43 @@
         <v>1.46</v>
       </c>
       <c r="G20" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="H20" t="n">
         <v>9.4</v>
       </c>
       <c r="I20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J20" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="K20" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L20" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M20" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N20" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O20" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P20" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="R20" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="T20" t="n">
         <v>2.46</v>
@@ -4297,10 +4297,10 @@
         <v>1.64</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W20" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="X20" t="n">
         <v>13</v>
@@ -4315,7 +4315,7 @@
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC20" t="n">
         <v>42</v>
@@ -4324,7 +4324,7 @@
         <v>95</v>
       </c>
       <c r="AE20" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AF20" t="n">
         <v>8</v>
@@ -4336,7 +4336,7 @@
         <v>75</v>
       </c>
       <c r="AI20" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AJ20" t="n">
         <v>21</v>
@@ -4351,34 +4351,34 @@
         <v>300</v>
       </c>
       <c r="AN20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS20" t="n">
         <v>10.5</v>
       </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AT20" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AU20" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AV20" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AW20" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AX20" t="n">
         <v>6.6</v>
@@ -4387,19 +4387,19 @@
         <v>9</v>
       </c>
       <c r="AZ20" t="n">
-        <v>7.6</v>
+        <v>19.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BB20" t="n">
         <v>10</v>
       </c>
       <c r="BC20" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BD20" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BE20" t="n">
         <v>30</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="G21" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H21" t="n">
         <v>2.76</v>
       </c>
       <c r="I21" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J21" t="n">
         <v>3.55</v>
@@ -4461,46 +4461,46 @@
         <v>4.1</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M21" t="n">
         <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P21" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q21" t="n">
         <v>1.7</v>
       </c>
       <c r="R21" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S21" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="T21" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="U21" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V21" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W21" t="n">
         <v>1.59</v>
       </c>
       <c r="X21" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="Y21" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="Z21" t="n">
         <v>60</v>
@@ -4509,7 +4509,7 @@
         <v>900</v>
       </c>
       <c r="AB21" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AC21" t="n">
         <v>9.199999999999999</v>
@@ -4518,19 +4518,19 @@
         <v>22</v>
       </c>
       <c r="AE21" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AF21" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG21" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AI21" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AJ21" t="n">
         <v>500</v>
@@ -4539,7 +4539,7 @@
         <v>500</v>
       </c>
       <c r="AL21" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AM21" t="n">
         <v>580</v>
@@ -4548,65 +4548,65 @@
         <v>55</v>
       </c>
       <c r="AO21" t="n">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AP21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ21" t="n">
         <v>13</v>
       </c>
-      <c r="AQ21" t="n">
-        <v>12</v>
-      </c>
       <c r="AR21" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="AT21" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW21" t="n">
         <v>14.5</v>
       </c>
       <c r="AX21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ21" t="n">
         <v>12.5</v>
       </c>
-      <c r="AY21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BA21" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="BC21" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BD21" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="BE21" t="n">
-        <v>7.8</v>
+        <v>50</v>
       </c>
       <c r="BF21" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BG21" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -4640,49 +4640,49 @@
         <v>3.2</v>
       </c>
       <c r="G22" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H22" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I22" t="n">
         <v>2.94</v>
       </c>
       <c r="J22" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="L22" t="n">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="M22" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N22" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="O22" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="P22" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="R22" t="n">
         <v>1.15</v>
       </c>
       <c r="S22" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="T22" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="U22" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="V22" t="n">
         <v>1.51</v>
@@ -4691,10 +4691,10 @@
         <v>1.41</v>
       </c>
       <c r="X22" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="Y22" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="Z22" t="n">
         <v>17</v>
@@ -4703,104 +4703,104 @@
         <v>55</v>
       </c>
       <c r="AB22" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC22" t="n">
         <v>7</v>
       </c>
       <c r="AD22" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE22" t="n">
         <v>500</v>
       </c>
       <c r="AF22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG22" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI22" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AJ22" t="n">
-        <v>70</v>
+        <v>220</v>
       </c>
       <c r="AK22" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AL22" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AM22" t="n">
         <v>500</v>
       </c>
       <c r="AN22" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AO22" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AP22" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AQ22" t="n">
         <v>6.6</v>
       </c>
       <c r="AR22" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU22" t="n">
         <v>6.2</v>
       </c>
       <c r="AV22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BB22" t="n">
         <v>12</v>
       </c>
-      <c r="AW22" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>9</v>
-      </c>
       <c r="BC22" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="BF22" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -4834,10 +4834,10 @@
         <v>2.06</v>
       </c>
       <c r="G23" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H23" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I23" t="n">
         <v>5.8</v>
@@ -4846,43 +4846,43 @@
         <v>2.86</v>
       </c>
       <c r="K23" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="L23" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="M23" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="N23" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="O23" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="P23" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S23" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="T23" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="U23" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="V23" t="n">
         <v>1.21</v>
       </c>
       <c r="W23" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="X23" t="n">
         <v>7.6</v>
@@ -4939,7 +4939,7 @@
         <v>700</v>
       </c>
       <c r="AP23" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AQ23" t="n">
         <v>10</v>
@@ -4948,10 +4948,10 @@
         <v>13</v>
       </c>
       <c r="AS23" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AT23" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AU23" t="n">
         <v>6.6</v>
@@ -4960,7 +4960,7 @@
         <v>21</v>
       </c>
       <c r="AW23" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AX23" t="n">
         <v>9.199999999999999</v>
@@ -4972,7 +4972,7 @@
         <v>5.9</v>
       </c>
       <c r="BA23" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BB23" t="n">
         <v>11.5</v>
@@ -4981,10 +4981,10 @@
         <v>6</v>
       </c>
       <c r="BD23" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE23" t="n">
         <v>6</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>6.2</v>
       </c>
       <c r="BF23" t="n">
         <v>7.8</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -5025,58 +5025,58 @@
         </is>
       </c>
       <c r="F24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G24" t="n">
         <v>2.16</v>
       </c>
-      <c r="G24" t="n">
-        <v>2.2</v>
-      </c>
       <c r="H24" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="I24" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J24" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K24" t="n">
         <v>4.1</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M24" t="n">
         <v>1.05</v>
       </c>
       <c r="N24" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O24" t="n">
         <v>1.26</v>
       </c>
       <c r="P24" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="R24" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S24" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="T24" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U24" t="n">
         <v>2.28</v>
       </c>
       <c r="V24" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W24" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X24" t="n">
         <v>22</v>
@@ -5088,22 +5088,22 @@
         <v>65</v>
       </c>
       <c r="AA24" t="n">
-        <v>440</v>
+        <v>900</v>
       </c>
       <c r="AB24" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC24" t="n">
         <v>9</v>
       </c>
       <c r="AD24" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE24" t="n">
         <v>90</v>
       </c>
       <c r="AF24" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="AG24" t="n">
         <v>11</v>
@@ -5115,10 +5115,10 @@
         <v>150</v>
       </c>
       <c r="AJ24" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AK24" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AL24" t="n">
         <v>500</v>
@@ -5127,68 +5127,68 @@
         <v>95</v>
       </c>
       <c r="AN24" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="AO24" t="n">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="AP24" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR24" t="n">
         <v>21</v>
       </c>
       <c r="AS24" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AT24" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU24" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW24" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AX24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ24" t="n">
         <v>14.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="BB24" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="BC24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF24" t="n">
         <v>11.5</v>
       </c>
-      <c r="BD24" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>11</v>
-      </c>
       <c r="BG24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -5219,64 +5219,64 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="G25" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="H25" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I25" t="n">
         <v>3.95</v>
       </c>
-      <c r="I25" t="n">
-        <v>4</v>
-      </c>
       <c r="J25" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K25" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L25" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="M25" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="O25" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="P25" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="S25" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="T25" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="U25" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="V25" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W25" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="X25" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z25" t="n">
         <v>25</v>
@@ -5285,16 +5285,16 @@
         <v>90</v>
       </c>
       <c r="AB25" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD25" t="n">
         <v>16.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF25" t="n">
         <v>12</v>
@@ -5306,31 +5306,31 @@
         <v>24</v>
       </c>
       <c r="AI25" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ25" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AK25" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AL25" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM25" t="n">
-        <v>440</v>
+        <v>180</v>
       </c>
       <c r="AN25" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AO25" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AP25" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR25" t="n">
         <v>23</v>
@@ -5339,7 +5339,7 @@
         <v>75</v>
       </c>
       <c r="AT25" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AU25" t="n">
         <v>7</v>
@@ -5348,7 +5348,7 @@
         <v>15.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX25" t="n">
         <v>11</v>
@@ -5357,32 +5357,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA25" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BB25" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>150</v>
+      </c>
+      <c r="BF25" t="n">
         <v>26</v>
       </c>
-      <c r="BC25" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>120</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>22</v>
-      </c>
       <c r="BG25" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="G26" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="H26" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="I26" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="J26" t="n">
         <v>3.4</v>
@@ -5431,7 +5431,7 @@
         <v>3.45</v>
       </c>
       <c r="L26" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="M26" t="n">
         <v>1.09</v>
@@ -5440,7 +5440,7 @@
         <v>3.45</v>
       </c>
       <c r="O26" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P26" t="n">
         <v>1.83</v>
@@ -5449,34 +5449,34 @@
         <v>2.18</v>
       </c>
       <c r="R26" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T26" t="n">
         <v>1.9</v>
       </c>
       <c r="U26" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V26" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="W26" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="X26" t="n">
         <v>12</v>
       </c>
       <c r="Y26" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AB26" t="n">
         <v>12.5</v>
@@ -5491,31 +5491,31 @@
         <v>25</v>
       </c>
       <c r="AF26" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AG26" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI26" t="n">
         <v>42</v>
       </c>
       <c r="AJ26" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AK26" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AL26" t="n">
         <v>60</v>
       </c>
       <c r="AM26" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN26" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO26" t="n">
         <v>21</v>
@@ -5524,16 +5524,16 @@
         <v>11</v>
       </c>
       <c r="AQ26" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT26" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU26" t="n">
         <v>7.2</v>
@@ -5545,13 +5545,13 @@
         <v>23</v>
       </c>
       <c r="AX26" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AY26" t="n">
         <v>14.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA26" t="n">
         <v>40</v>
@@ -5560,23 +5560,23 @@
         <v>65</v>
       </c>
       <c r="BC26" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BD26" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>90</v>
+      </c>
+      <c r="BF26" t="n">
         <v>50</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>80</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>48</v>
       </c>
       <c r="BG26" t="n">
         <v>19.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -5607,94 +5607,94 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="G27" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="H27" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K27" t="n">
         <v>3.35</v>
       </c>
-      <c r="I27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J27" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3.4</v>
-      </c>
       <c r="L27" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="M27" t="n">
         <v>1.09</v>
       </c>
       <c r="N27" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="O27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V27" t="n">
         <v>1.38</v>
       </c>
-      <c r="P27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S27" t="n">
-        <v>4</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.41</v>
-      </c>
       <c r="W27" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="X27" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA27" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB27" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC27" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD27" t="n">
         <v>14.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AF27" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG27" t="n">
         <v>11.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AJ27" t="n">
         <v>34</v>
@@ -5703,81 +5703,81 @@
         <v>28</v>
       </c>
       <c r="AL27" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM27" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AN27" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW27" t="n">
         <v>42</v>
       </c>
-      <c r="AP27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV27" t="n">
+      <c r="AX27" t="n">
         <v>13</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>13.5</v>
       </c>
       <c r="AY27" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BA27" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="BB27" t="n">
         <v>30</v>
       </c>
       <c r="BC27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD27" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BE27" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="BF27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BG27" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5792,179 +5792,179 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>MC El Bayadh</t>
         </is>
       </c>
       <c r="F28" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H28" t="n">
+        <v>19</v>
+      </c>
+      <c r="I28" t="n">
+        <v>23</v>
+      </c>
+      <c r="J28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>6</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q28" t="n">
         <v>2.2</v>
       </c>
-      <c r="G28" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="H28" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="I28" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J28" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K28" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.98</v>
-      </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="S28" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="T28" t="n">
-        <v>1.77</v>
+        <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>2.16</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="W28" t="n">
-        <v>1.81</v>
+        <v>4</v>
       </c>
       <c r="X28" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>290</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>380</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC28" t="n">
         <v>15</v>
       </c>
-      <c r="Y28" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>44</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>20</v>
-      </c>
       <c r="BD28" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="BE28" t="n">
-        <v>48</v>
+        <v>7.6</v>
       </c>
       <c r="BF28" t="n">
-        <v>14.5</v>
+        <v>6.2</v>
       </c>
       <c r="BG28" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -5995,40 +5995,40 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G29" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="H29" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I29" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J29" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K29" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L29" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M29" t="n">
         <v>1.07</v>
       </c>
       <c r="N29" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O29" t="n">
         <v>1.33</v>
       </c>
       <c r="P29" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q29" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R29" t="n">
         <v>1.35</v>
@@ -6037,28 +6037,28 @@
         <v>3.65</v>
       </c>
       <c r="T29" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="U29" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V29" t="n">
         <v>1.17</v>
       </c>
       <c r="W29" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="X29" t="n">
         <v>14</v>
       </c>
       <c r="Y29" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z29" t="n">
         <v>55</v>
       </c>
       <c r="AA29" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AB29" t="n">
         <v>8.199999999999999</v>
@@ -6067,28 +6067,28 @@
         <v>8.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE29" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF29" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AG29" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AH29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI29" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ29" t="n">
         <v>16.5</v>
       </c>
       <c r="AK29" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL29" t="n">
         <v>40</v>
@@ -6100,19 +6100,19 @@
         <v>11</v>
       </c>
       <c r="AO29" t="n">
-        <v>410</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR29" t="n">
         <v>46</v>
       </c>
       <c r="AS29" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AT29" t="n">
         <v>7.4</v>
@@ -6127,16 +6127,16 @@
         <v>85</v>
       </c>
       <c r="AX29" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY29" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA29" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BB29" t="n">
         <v>14.5</v>
@@ -6148,24 +6148,24 @@
         <v>36</v>
       </c>
       <c r="BE29" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="BF29" t="n">
         <v>9.6</v>
       </c>
       <c r="BG29" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6180,179 +6180,179 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MC El Bayadh</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.28</v>
+        <v>2.2</v>
       </c>
       <c r="G30" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O30" t="n">
         <v>1.33</v>
       </c>
-      <c r="H30" t="n">
-        <v>17</v>
-      </c>
-      <c r="I30" t="n">
+      <c r="P30" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="X30" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC30" t="n">
         <v>21</v>
       </c>
-      <c r="J30" t="n">
-        <v>5</v>
-      </c>
-      <c r="K30" t="n">
-        <v>6</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S30" t="n">
-        <v>4</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W30" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="X30" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y30" t="n">
+      <c r="BD30" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>75</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG30" t="n">
         <v>38</v>
       </c>
-      <c r="Z30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>170</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>11</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>380</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -6383,76 +6383,76 @@
         </is>
       </c>
       <c r="F31" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="G31" t="n">
         <v>2.56</v>
       </c>
-      <c r="G31" t="n">
-        <v>2.64</v>
-      </c>
       <c r="H31" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J31" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K31" t="n">
         <v>3.6</v>
       </c>
-      <c r="K31" t="n">
-        <v>3.65</v>
-      </c>
       <c r="L31" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M31" t="n">
         <v>1.07</v>
       </c>
       <c r="N31" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="O31" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P31" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="R31" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S31" t="n">
         <v>3.4</v>
       </c>
       <c r="T31" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U31" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V31" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W31" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="X31" t="n">
         <v>14.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA31" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB31" t="n">
         <v>11.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD31" t="n">
         <v>13.5</v>
@@ -6461,7 +6461,7 @@
         <v>34</v>
       </c>
       <c r="AF31" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AG31" t="n">
         <v>12</v>
@@ -6470,40 +6470,40 @@
         <v>16.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ31" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL31" t="n">
         <v>38</v>
       </c>
-      <c r="AK31" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>40</v>
-      </c>
       <c r="AM31" t="n">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="AN31" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO31" t="n">
         <v>30</v>
       </c>
       <c r="AP31" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ31" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR31" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AS31" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AT31" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU31" t="n">
         <v>7.4</v>
@@ -6512,48 +6512,48 @@
         <v>11.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AX31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ31" t="n">
         <v>15.5</v>
       </c>
-      <c r="AY31" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BA31" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BB31" t="n">
         <v>32</v>
       </c>
       <c r="BC31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD31" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE31" t="n">
         <v>36</v>
       </c>
       <c r="BF31" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BG31" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6568,186 +6568,186 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Union Magdalena</t>
+          <t>Juticalpa</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>Olancho</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.16</v>
+        <v>2.92</v>
       </c>
       <c r="G32" t="n">
-        <v>2.4</v>
+        <v>110</v>
       </c>
       <c r="H32" t="n">
-        <v>3.65</v>
+        <v>1.5</v>
       </c>
       <c r="I32" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="J32" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K32" t="n">
-        <v>3.45</v>
+        <v>10.5</v>
       </c>
       <c r="L32" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>2.92</v>
+        <v>1.1</v>
       </c>
       <c r="O32" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="P32" t="n">
-        <v>1.66</v>
+        <v>1.24</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.22</v>
+        <v>1.23</v>
       </c>
       <c r="R32" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S32" t="n">
-        <v>4.2</v>
+        <v>1.23</v>
       </c>
       <c r="T32" t="n">
-        <v>1.9</v>
+        <v>1.11</v>
       </c>
       <c r="U32" t="n">
-        <v>1.9</v>
+        <v>1.11</v>
       </c>
       <c r="V32" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="W32" t="n">
-        <v>1.72</v>
+        <v>1.16</v>
       </c>
       <c r="X32" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y32" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z32" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA32" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC32" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD32" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE32" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AG32" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH32" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI32" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK32" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL32" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM32" t="n">
-        <v>440</v>
+        <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>8.199999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="AQ32" t="n">
-        <v>9.199999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="AR32" t="n">
-        <v>22</v>
+        <v>1.15</v>
       </c>
       <c r="AS32" t="n">
-        <v>9</v>
+        <v>1.15</v>
       </c>
       <c r="AT32" t="n">
-        <v>7</v>
+        <v>1.15</v>
       </c>
       <c r="AU32" t="n">
-        <v>6.4</v>
+        <v>1.12</v>
       </c>
       <c r="AV32" t="n">
-        <v>14</v>
+        <v>1.11</v>
       </c>
       <c r="AW32" t="n">
-        <v>40</v>
+        <v>1.13</v>
       </c>
       <c r="AX32" t="n">
-        <v>10.5</v>
+        <v>1.15</v>
       </c>
       <c r="AY32" t="n">
-        <v>8.800000000000001</v>
+        <v>1.15</v>
       </c>
       <c r="AZ32" t="n">
-        <v>14.5</v>
+        <v>1.15</v>
       </c>
       <c r="BA32" t="n">
-        <v>10.5</v>
+        <v>1.15</v>
       </c>
       <c r="BB32" t="n">
-        <v>11.5</v>
+        <v>1.15</v>
       </c>
       <c r="BC32" t="n">
-        <v>21</v>
+        <v>1.15</v>
       </c>
       <c r="BD32" t="n">
-        <v>8</v>
+        <v>1.15</v>
       </c>
       <c r="BE32" t="n">
-        <v>9</v>
+        <v>1.15</v>
       </c>
       <c r="BF32" t="n">
-        <v>21</v>
+        <v>1.55</v>
       </c>
       <c r="BG32" t="n">
-        <v>8.6</v>
+        <v>1.15</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6762,179 +6762,179 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Juticalpa</t>
+          <t>Union Magdalena</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olancho</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.92</v>
+        <v>2.22</v>
       </c>
       <c r="G33" t="n">
-        <v>110</v>
+        <v>2.34</v>
       </c>
       <c r="H33" t="n">
-        <v>1.5</v>
+        <v>3.65</v>
       </c>
       <c r="I33" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="J33" t="n">
         <v>3.25</v>
       </c>
       <c r="K33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="X33" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>440</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX33" t="n">
         <v>10.5</v>
       </c>
-      <c r="L33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S33" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AY33" t="n">
-        <v>1.15</v>
+        <v>9.6</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.15</v>
+        <v>14.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.15</v>
+        <v>11</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.15</v>
+        <v>26</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.15</v>
+        <v>21</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.15</v>
+        <v>9</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.15</v>
+        <v>10</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.55</v>
+        <v>21</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.15</v>
+        <v>9.4</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -6951,17 +6951,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>20:15:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Atletico Choloma</t>
+          <t>CD Marathon</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Real Espana</t>
+          <t>CD Motagua</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -6971,16 +6971,16 @@
         <v>1000</v>
       </c>
       <c r="H34" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I34" t="n">
         <v>1000</v>
       </c>
       <c r="J34" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K34" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
@@ -6989,22 +6989,22 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="O34" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="P34" t="n">
         <v>1.24</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="R34" t="n">
         <v>1.18</v>
       </c>
       <c r="S34" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T34" t="n">
         <v>1.01</v>
@@ -7016,7 +7016,7 @@
         <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -7128,201 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Honduras Liga Nacional</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>22:30:00</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>CD Marathon</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>CD Motagua</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G35" t="n">
-        <v>240</v>
-      </c>
-      <c r="H35" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J35" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K35" t="n">
-        <v>950</v>
-      </c>
-      <c r="L35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P35" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH35" t="inlineStr">
-        <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH34"/>
+  <dimension ref="A1:BH33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,10 +760,10 @@
         <v>1.54</v>
       </c>
       <c r="G2" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.52</v>
+        <v>3.6</v>
       </c>
       <c r="I2" t="n">
         <v>8.6</v>
@@ -784,19 +784,19 @@
         <v>1.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>1.41</v>
+        <v>1.05</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -808,7 +808,7 @@
         <v>1.13</v>
       </c>
       <c r="W2" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="X2" t="n">
         <v>18</v>
@@ -865,62 +865,62 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU2" t="n">
         <v>1.27</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AV2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AX2" t="n">
         <v>1.37</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AY2" t="n">
         <v>1.36</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="AZ2" t="n">
         <v>1.37</v>
       </c>
-      <c r="AT2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AW2" t="n">
+      <c r="BA2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BC2" t="n">
         <v>1.37</v>
       </c>
-      <c r="AX2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1.34</v>
-      </c>
       <c r="BD2" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
@@ -951,58 +951,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="G3" t="n">
         <v>1.65</v>
       </c>
       <c r="H3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I3" t="n">
         <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="R3" t="n">
         <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="U3" t="n">
         <v>1.94</v>
       </c>
       <c r="V3" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W3" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="X3" t="n">
         <v>16</v>
@@ -1017,13 +1017,13 @@
         <v>700</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AE3" t="n">
         <v>700</v>
@@ -1035,16 +1035,16 @@
         <v>10</v>
       </c>
       <c r="AH3" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AI3" t="n">
         <v>700</v>
       </c>
       <c r="AJ3" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AK3" t="n">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="AL3" t="n">
         <v>120</v>
@@ -1059,62 +1059,62 @@
         <v>700</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AS3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AV3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="BA3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="BD3" t="n">
         <v>21</v>
       </c>
       <c r="BE3" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H4" t="n">
         <v>2.68</v>
@@ -1160,7 +1160,7 @@
         <v>3.45</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L4" t="n">
         <v>1.4</v>
@@ -1169,28 +1169,28 @@
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R4" t="n">
         <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U4" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V4" t="n">
         <v>1.56</v>
@@ -1208,7 +1208,7 @@
         <v>19</v>
       </c>
       <c r="AA4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AB4" t="n">
         <v>13</v>
@@ -1217,19 +1217,19 @@
         <v>8.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
         <v>29</v>
       </c>
       <c r="AF4" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG4" t="n">
         <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI4" t="n">
         <v>40</v>
@@ -1241,28 +1241,28 @@
         <v>32</v>
       </c>
       <c r="AL4" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="AM4" t="n">
         <v>320</v>
       </c>
       <c r="AN4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO4" t="n">
         <v>25</v>
       </c>
       <c r="AP4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>10</v>
       </c>
       <c r="AR4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT4" t="n">
         <v>10.5</v>
@@ -1277,38 +1277,38 @@
         <v>15</v>
       </c>
       <c r="AX4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AY4" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC4" t="n">
         <v>13.5</v>
       </c>
-      <c r="BA4" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>23</v>
-      </c>
       <c r="BD4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.6</v>
+        <v>60</v>
       </c>
       <c r="BF4" t="n">
         <v>19</v>
       </c>
       <c r="BG4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
@@ -1339,70 +1339,70 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="G5" t="n">
         <v>1.34</v>
       </c>
-      <c r="G5" t="n">
-        <v>1.36</v>
-      </c>
       <c r="H5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="I5" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="J5" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="K5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L5" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P5" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="R5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="U5" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="V5" t="n">
         <v>1.07</v>
       </c>
       <c r="W5" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="X5" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="Z5" t="n">
         <v>140</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>830</v>
       </c>
       <c r="AB5" t="n">
         <v>7.4</v>
@@ -1411,98 +1411,98 @@
         <v>13</v>
       </c>
       <c r="AD5" t="n">
-        <v>200</v>
+        <v>55</v>
       </c>
       <c r="AE5" t="n">
         <v>310</v>
       </c>
       <c r="AF5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AG5" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH5" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AI5" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AJ5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AR5" t="n">
         <v>17</v>
       </c>
-      <c r="AL5" t="n">
-        <v>130</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>310</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>550</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>29</v>
-      </c>
       <c r="AS5" t="n">
-        <v>10</v>
+        <v>19.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW5" t="n">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="AX5" t="n">
         <v>6.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="BA5" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="BB5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BC5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD5" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="BE5" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BG5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
@@ -1536,13 +1536,13 @@
         <v>3.6</v>
       </c>
       <c r="G6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H6" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I6" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="J6" t="n">
         <v>2.92</v>
@@ -1557,16 +1557,16 @@
         <v>1.13</v>
       </c>
       <c r="N6" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="O6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P6" t="n">
         <v>1.56</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="R6" t="n">
         <v>1.2</v>
@@ -1575,10 +1575,10 @@
         <v>5.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U6" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V6" t="n">
         <v>1.62</v>
@@ -1587,19 +1587,19 @@
         <v>1.37</v>
       </c>
       <c r="X6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y6" t="n">
         <v>8.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AB6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC6" t="n">
         <v>7</v>
@@ -1620,16 +1620,16 @@
         <v>21</v>
       </c>
       <c r="AI6" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AJ6" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AK6" t="n">
         <v>60</v>
       </c>
       <c r="AL6" t="n">
-        <v>380</v>
+        <v>85</v>
       </c>
       <c r="AM6" t="n">
         <v>500</v>
@@ -1641,19 +1641,19 @@
         <v>40</v>
       </c>
       <c r="AP6" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="AQ6" t="n">
         <v>7</v>
       </c>
       <c r="AR6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS6" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="AT6" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU6" t="n">
         <v>6</v>
@@ -1662,7 +1662,7 @@
         <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AX6" t="n">
         <v>20</v>
@@ -1677,26 +1677,26 @@
         <v>48</v>
       </c>
       <c r="BB6" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BD6" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BE6" t="n">
         <v>10.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>20</v>
+        <v>9.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         <v>3.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I7" t="n">
         <v>2.76</v>
@@ -1757,22 +1757,22 @@
         <v>1.56</v>
       </c>
       <c r="P7" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="R7" t="n">
         <v>1.19</v>
       </c>
       <c r="S7" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="T7" t="n">
         <v>2.1</v>
       </c>
       <c r="U7" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V7" t="n">
         <v>1.56</v>
@@ -1781,28 +1781,28 @@
         <v>1.4</v>
       </c>
       <c r="X7" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y7" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Z7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="AB7" t="n">
         <v>9.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AD7" t="n">
         <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="AF7" t="n">
         <v>21</v>
@@ -1811,7 +1811,7 @@
         <v>15</v>
       </c>
       <c r="AH7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
         <v>70</v>
@@ -1820,7 +1820,7 @@
         <v>160</v>
       </c>
       <c r="AK7" t="n">
-        <v>440</v>
+        <v>130</v>
       </c>
       <c r="AL7" t="n">
         <v>240</v>
@@ -1832,10 +1832,10 @@
         <v>600</v>
       </c>
       <c r="AO7" t="n">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="AP7" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ7" t="n">
         <v>7.4</v>
@@ -1844,7 +1844,7 @@
         <v>14</v>
       </c>
       <c r="AS7" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AT7" t="n">
         <v>8.6</v>
@@ -1856,7 +1856,7 @@
         <v>11.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX7" t="n">
         <v>18</v>
@@ -1868,29 +1868,29 @@
         <v>19.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>13.5</v>
+        <v>28</v>
       </c>
       <c r="BB7" t="n">
-        <v>13.5</v>
+        <v>23</v>
       </c>
       <c r="BC7" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>15</v>
+      </c>
+      <c r="BF7" t="n">
         <v>13</v>
       </c>
-      <c r="BD7" t="n">
-        <v>14</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BG7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O8" t="n">
         <v>1.3</v>
@@ -1954,7 +1954,7 @@
         <v>1.96</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R8" t="n">
         <v>1.37</v>
@@ -1975,49 +1975,49 @@
         <v>1.43</v>
       </c>
       <c r="X8" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>280</v>
+      </c>
+      <c r="AK8" t="n">
         <v>90</v>
       </c>
-      <c r="Y8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>500</v>
-      </c>
       <c r="AL8" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AM8" t="n">
         <v>580</v>
@@ -2026,65 +2026,65 @@
         <v>600</v>
       </c>
       <c r="AO8" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="AP8" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ8" t="n">
         <v>9.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="AS8" t="n">
         <v>15</v>
       </c>
       <c r="AT8" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AU8" t="n">
         <v>7.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>12</v>
+        <v>18.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY8" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AZ8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BA8" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BB8" t="n">
         <v>20</v>
       </c>
       <c r="BC8" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="BE8" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="BF8" t="n">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="G9" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="H9" t="n">
         <v>1.49</v>
       </c>
       <c r="I9" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="J9" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="K9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L9" t="n">
         <v>1.33</v>
@@ -2139,49 +2139,49 @@
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O9" t="n">
         <v>1.21</v>
       </c>
       <c r="P9" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R9" t="n">
         <v>1.56</v>
       </c>
       <c r="S9" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="T9" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U9" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V9" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="W9" t="n">
         <v>1.15</v>
       </c>
       <c r="X9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y9" t="n">
         <v>11</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AA9" t="n">
         <v>15</v>
       </c>
       <c r="AB9" t="n">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="AC9" t="n">
         <v>12</v>
@@ -2190,37 +2190,37 @@
         <v>10</v>
       </c>
       <c r="AE9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AF9" t="n">
-        <v>170</v>
+        <v>540</v>
       </c>
       <c r="AG9" t="n">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="AH9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI9" t="n">
         <v>32</v>
       </c>
       <c r="AJ9" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AK9" t="n">
-        <v>260</v>
+        <v>100</v>
       </c>
       <c r="AL9" t="n">
         <v>390</v>
       </c>
       <c r="AM9" t="n">
-        <v>390</v>
+        <v>100</v>
       </c>
       <c r="AN9" t="n">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="AO9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AP9" t="n">
         <v>18.5</v>
@@ -2232,53 +2232,53 @@
         <v>8.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="AU9" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AV9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AW9" t="n">
         <v>12</v>
       </c>
       <c r="AX9" t="n">
-        <v>9.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="AY9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA9" t="n">
         <v>16</v>
       </c>
       <c r="BB9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC9" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="BD9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BE9" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="BF9" t="n">
         <v>16</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
@@ -2312,25 +2312,25 @@
         <v>1.94</v>
       </c>
       <c r="G10" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="H10" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="I10" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N10" t="n">
         <v>4.5</v>
@@ -2339,19 +2339,19 @@
         <v>1.24</v>
       </c>
       <c r="P10" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="R10" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S10" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="T10" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U10" t="n">
         <v>2.3</v>
@@ -2360,10 +2360,10 @@
         <v>1.32</v>
       </c>
       <c r="W10" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y10" t="n">
         <v>1000</v>
@@ -2372,7 +2372,7 @@
         <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
         <v>16.5</v>
@@ -2381,13 +2381,13 @@
         <v>14</v>
       </c>
       <c r="AD10" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
         <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG10" t="n">
         <v>20</v>
@@ -2399,16 +2399,16 @@
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="AK10" t="n">
         <v>46</v>
       </c>
       <c r="AL10" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AM10" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
         <v>55</v>
@@ -2417,69 +2417,69 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>8.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.6</v>
+        <v>28</v>
       </c>
       <c r="AT10" t="n">
         <v>9.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AW10" t="n">
-        <v>8.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="AX10" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AY10" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.6</v>
+        <v>29</v>
       </c>
       <c r="BB10" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="BD10" t="n">
-        <v>23</v>
+        <v>7.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="BG10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Saudi 1st Division</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13:20:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Al Orubah</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Faisaly ( KSA )</t>
+          <t>MB Rouissat</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.98</v>
+        <v>1.38</v>
       </c>
       <c r="G11" t="n">
-        <v>3.25</v>
+        <v>1.42</v>
       </c>
       <c r="H11" t="n">
-        <v>2.28</v>
+        <v>13.5</v>
       </c>
       <c r="I11" t="n">
-        <v>2.44</v>
+        <v>16.5</v>
       </c>
       <c r="J11" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="K11" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="L11" t="n">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>4.5</v>
+        <v>2.86</v>
       </c>
       <c r="O11" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.24</v>
+        <v>1.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.71</v>
+        <v>2.46</v>
       </c>
       <c r="R11" t="n">
-        <v>1.48</v>
+        <v>1.21</v>
       </c>
       <c r="S11" t="n">
-        <v>2.78</v>
+        <v>5</v>
       </c>
       <c r="T11" t="n">
-        <v>1.63</v>
+        <v>2.96</v>
       </c>
       <c r="U11" t="n">
-        <v>2.38</v>
+        <v>1.41</v>
       </c>
       <c r="V11" t="n">
-        <v>1.69</v>
+        <v>1.06</v>
       </c>
       <c r="W11" t="n">
-        <v>1.44</v>
+        <v>3.3</v>
       </c>
       <c r="X11" t="n">
-        <v>24</v>
+        <v>10.5</v>
       </c>
       <c r="Y11" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>150</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG11" t="n">
         <v>15</v>
       </c>
-      <c r="Z11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>260</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>20</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>13</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouissat</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.38</v>
+        <v>2.06</v>
       </c>
       <c r="G12" t="n">
-        <v>1.41</v>
+        <v>2.08</v>
       </c>
       <c r="H12" t="n">
-        <v>13</v>
+        <v>4.3</v>
       </c>
       <c r="I12" t="n">
-        <v>15.5</v>
+        <v>4.5</v>
       </c>
       <c r="J12" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="L12" t="n">
         <v>1.5</v>
       </c>
       <c r="M12" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O12" t="n">
         <v>1.43</v>
       </c>
       <c r="P12" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="Q12" t="n">
         <v>2.3</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S12" t="n">
         <v>4.4</v>
       </c>
       <c r="T12" t="n">
-        <v>2.74</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.48</v>
+        <v>1.96</v>
       </c>
       <c r="V12" t="n">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>3.4</v>
+        <v>1.92</v>
       </c>
       <c r="X12" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ12" t="n">
         <v>12</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AR12" t="n">
         <v>28</v>
       </c>
-      <c r="Z12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>150</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>120</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN12" t="n">
+      <c r="AS12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY12" t="n">
         <v>10</v>
       </c>
-      <c r="AO12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AZ12" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="BA12" t="n">
-        <v>11.5</v>
+        <v>60</v>
       </c>
       <c r="BB12" t="n">
-        <v>9.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="BC12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="BD12" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="BE12" t="n">
-        <v>11.5</v>
+        <v>70</v>
       </c>
       <c r="BF12" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="BG12" t="n">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="G13" t="n">
-        <v>2.08</v>
+        <v>2.58</v>
       </c>
       <c r="H13" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="I13" t="n">
-        <v>4.4</v>
+        <v>3.15</v>
       </c>
       <c r="J13" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K13" t="n">
         <v>3.55</v>
       </c>
       <c r="L13" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="P13" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="R13" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="S13" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="T13" t="n">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="U13" t="n">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="V13" t="n">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="W13" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="X13" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB13" t="n">
         <v>11</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AC13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD13" t="n">
         <v>13</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AE13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO13" t="n">
         <v>32</v>
       </c>
-      <c r="AA13" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF13" t="n">
+      <c r="AP13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>11.5</v>
       </c>
-      <c r="AG13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL13" t="n">
+      <c r="AR13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS13" t="n">
         <v>44</v>
       </c>
-      <c r="AM13" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>20</v>
-      </c>
       <c r="AT13" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="AU13" t="n">
         <v>7.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AW13" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AX13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY13" t="n">
         <v>10.5</v>
       </c>
-      <c r="AY13" t="n">
-        <v>10</v>
-      </c>
       <c r="AZ13" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="BA13" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="BB13" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="BC13" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BD13" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BE13" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BF13" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BG13" t="n">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,179 +3076,179 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Erokspor A.S</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Amed Sportif Faaliyetler</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="G14" t="n">
-        <v>2.56</v>
+        <v>2.26</v>
       </c>
       <c r="H14" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="I14" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="J14" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K14" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="L14" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="M14" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>3.85</v>
+        <v>4.9</v>
       </c>
       <c r="O14" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="P14" t="n">
-        <v>1.96</v>
+        <v>2.26</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="R14" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V14" t="n">
         <v>1.37</v>
       </c>
-      <c r="S14" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.45</v>
-      </c>
       <c r="W14" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="X14" t="n">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="Y14" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB14" t="n">
         <v>13</v>
       </c>
-      <c r="Z14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AC14" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AE14" t="n">
         <v>36</v>
       </c>
       <c r="AF14" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG14" t="n">
         <v>11.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="AJ14" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AK14" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AL14" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AM14" t="n">
-        <v>320</v>
+        <v>75</v>
       </c>
       <c r="AN14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR14" t="n">
         <v>22</v>
       </c>
-      <c r="AO14" t="n">
-        <v>500</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ14" t="n">
+      <c r="AS14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT14" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AU14" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW14" t="n">
         <v>30</v>
       </c>
       <c r="AX14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY14" t="n">
         <v>10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA14" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BB14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC14" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="BD14" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="BE14" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="BF14" t="n">
-        <v>19.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
@@ -3270,186 +3270,186 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Erokspor A.S</t>
+          <t>Istanbulspor</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Amed Sportif Faaliyetler</t>
+          <t>Erzurum BB</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.22</v>
+        <v>4.7</v>
       </c>
       <c r="G15" t="n">
-        <v>2.28</v>
+        <v>5.2</v>
       </c>
       <c r="H15" t="n">
-        <v>3.4</v>
+        <v>1.83</v>
       </c>
       <c r="I15" t="n">
-        <v>3.7</v>
+        <v>1.89</v>
       </c>
       <c r="J15" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="P15" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="R15" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.78</v>
+        <v>3.25</v>
       </c>
       <c r="T15" t="n">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="U15" t="n">
-        <v>2.44</v>
+        <v>2.06</v>
       </c>
       <c r="V15" t="n">
-        <v>1.37</v>
+        <v>2.12</v>
       </c>
       <c r="W15" t="n">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="X15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG15" t="n">
         <v>19.5</v>
       </c>
-      <c r="Y15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE15" t="n">
+      <c r="AH15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI15" t="n">
         <v>85</v>
       </c>
-      <c r="AF15" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>500</v>
-      </c>
       <c r="AJ15" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="AL15" t="n">
-        <v>75</v>
+        <v>700</v>
       </c>
       <c r="AM15" t="n">
         <v>580</v>
       </c>
       <c r="AN15" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP15" t="n">
         <v>13.5</v>
       </c>
-      <c r="AO15" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP15" t="n">
+      <c r="AQ15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW15" t="n">
         <v>16</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>29</v>
-      </c>
       <c r="AX15" t="n">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.6</v>
+        <v>16</v>
       </c>
       <c r="AZ15" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BA15" t="n">
-        <v>32</v>
+        <v>18.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="BC15" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="BD15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BE15" t="n">
-        <v>19.5</v>
+        <v>9.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="BG15" t="n">
-        <v>22</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,179 +3464,179 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Istanbulspor</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Erzurum BB</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.9</v>
+        <v>2.18</v>
       </c>
       <c r="G16" t="n">
-        <v>5.2</v>
+        <v>2.32</v>
       </c>
       <c r="H16" t="n">
-        <v>1.83</v>
+        <v>3.6</v>
       </c>
       <c r="I16" t="n">
+        <v>4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P16" t="n">
         <v>1.86</v>
       </c>
-      <c r="J16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N16" t="n">
-        <v>4</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.02</v>
-      </c>
       <c r="Q16" t="n">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="R16" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="S16" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="T16" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="U16" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V16" t="n">
-        <v>2.16</v>
+        <v>1.33</v>
       </c>
       <c r="W16" t="n">
-        <v>1.23</v>
+        <v>1.76</v>
       </c>
       <c r="X16" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="Z16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG16" t="n">
         <v>11.5</v>
       </c>
-      <c r="AA16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD16" t="n">
+      <c r="AH16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP16" t="n">
         <v>10.5</v>
       </c>
-      <c r="AE16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>46</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>700</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>700</v>
-      </c>
-      <c r="AO16" t="n">
+      <c r="AQ16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE16" t="n">
         <v>12</v>
       </c>
-      <c r="AP16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ16" t="n">
+      <c r="BF16" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG16" t="n">
         <v>11</v>
       </c>
-      <c r="BA16" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>34</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
@@ -3658,127 +3658,127 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Cukaricki</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>FK Radnicki 1923</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G17" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="H17" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="I17" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="J17" t="n">
         <v>3.45</v>
       </c>
       <c r="K17" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M17" t="n">
         <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O17" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P17" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S17" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="T17" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U17" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="V17" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W17" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="X17" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="Y17" t="n">
-        <v>16.5</v>
+        <v>34</v>
       </c>
       <c r="Z17" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AB17" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="AD17" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN17" t="n">
         <v>55</v>
       </c>
-      <c r="AF17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>19</v>
-      </c>
       <c r="AO17" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>13</v>
+        <v>7.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="AR17" t="n">
         <v>11.5</v>
@@ -3787,50 +3787,50 @@
         <v>23</v>
       </c>
       <c r="AT17" t="n">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="AV17" t="n">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.8</v>
+        <v>16</v>
       </c>
       <c r="AX17" t="n">
-        <v>12</v>
+        <v>7.6</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.6</v>
+        <v>6.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.8</v>
+        <v>34</v>
       </c>
       <c r="BB17" t="n">
         <v>13</v>
       </c>
       <c r="BC17" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>30</v>
+        <v>17.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BF17" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="BG17" t="n">
-        <v>36</v>
+        <v>8.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
@@ -3852,186 +3852,186 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cukaricki</t>
+          <t>Crvena Zvezda</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FK Radnicki 1923</t>
+          <t>FK Spartak</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.18</v>
+        <v>1.07</v>
       </c>
       <c r="G18" t="n">
-        <v>2.3</v>
+        <v>1.09</v>
       </c>
       <c r="H18" t="n">
-        <v>3.35</v>
+        <v>44</v>
       </c>
       <c r="I18" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>3.55</v>
+        <v>15.5</v>
       </c>
       <c r="K18" t="n">
+        <v>32</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N18" t="n">
+        <v>12</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="P18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W18" t="n">
+        <v>12</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC18" t="n">
         <v>3.95</v>
       </c>
-      <c r="L18" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="X18" t="n">
-        <v>90</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>500</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BD18" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>6.2</v>
+        <v>1.69</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Crvena Zvezda</t>
+          <t>PFC Levski Sofia</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FK Spartak</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.07</v>
+        <v>1.46</v>
       </c>
       <c r="G19" t="n">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
       <c r="H19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I19" t="n">
+        <v>11</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3</v>
+      </c>
+      <c r="X19" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y19" t="n">
         <v>42</v>
       </c>
-      <c r="I19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J19" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="K19" t="n">
-        <v>32</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N19" t="n">
-        <v>12</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="P19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W19" t="n">
-        <v>12</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1000</v>
-      </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.06</v>
+        <v>10.5</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.95</v>
+        <v>7.8</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5.2</v>
+        <v>11.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="AT19" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV19" t="n">
-        <v>5.1</v>
+        <v>30</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY19" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3.9</v>
+        <v>26</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BC19" t="n">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.2</v>
+        <v>30</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.68</v>
+        <v>8.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:40:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>PFC Levski Sofia</t>
+          <t>Al-Adalh</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Al Batin</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.46</v>
+        <v>2.42</v>
       </c>
       <c r="G20" t="n">
-        <v>1.5</v>
+        <v>2.66</v>
       </c>
       <c r="H20" t="n">
-        <v>9.4</v>
+        <v>2.8</v>
       </c>
       <c r="I20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X20" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV20" t="n">
         <v>11</v>
       </c>
-      <c r="J20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S20" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="X20" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>42</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>110</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>42</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>95</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>250</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>75</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>220</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU20" t="n">
+      <c r="AW20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE20" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AV20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>30</v>
-      </c>
       <c r="BF20" t="n">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Saudi 1st Division</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,184 +4429,184 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>14:40:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Al-Adalh</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Batin</t>
+          <t>ZED FC</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.42</v>
+        <v>3.2</v>
       </c>
       <c r="G21" t="n">
-        <v>2.7</v>
+        <v>3.35</v>
       </c>
       <c r="H21" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="I21" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="J21" t="n">
-        <v>3.55</v>
+        <v>2.84</v>
       </c>
       <c r="K21" t="n">
-        <v>4.1</v>
+        <v>2.98</v>
       </c>
       <c r="L21" t="n">
-        <v>1.34</v>
+        <v>1.68</v>
       </c>
       <c r="M21" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>2.46</v>
       </c>
       <c r="O21" t="n">
-        <v>1.23</v>
+        <v>1.64</v>
       </c>
       <c r="P21" t="n">
-        <v>2.22</v>
+        <v>1.47</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.7</v>
+        <v>2.96</v>
       </c>
       <c r="R21" t="n">
-        <v>1.48</v>
+        <v>1.16</v>
       </c>
       <c r="S21" t="n">
-        <v>2.74</v>
+        <v>6.4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.6</v>
+        <v>2.24</v>
       </c>
       <c r="U21" t="n">
-        <v>2.36</v>
+        <v>1.73</v>
       </c>
       <c r="V21" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W21" t="n">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="X21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF21" t="n">
         <v>21</v>
       </c>
-      <c r="Y21" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD21" t="n">
+      <c r="AG21" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>220</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ21" t="n">
         <v>22</v>
       </c>
-      <c r="AE21" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR21" t="n">
+      <c r="BA21" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG21" t="n">
         <v>11.5</v>
       </c>
-      <c r="AS21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>24</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>14</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
@@ -4628,186 +4628,186 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ZED FC</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="G22" t="n">
-        <v>3.45</v>
+        <v>2.18</v>
       </c>
       <c r="H22" t="n">
-        <v>2.84</v>
+        <v>5.3</v>
       </c>
       <c r="I22" t="n">
-        <v>2.94</v>
+        <v>5.8</v>
       </c>
       <c r="J22" t="n">
         <v>2.76</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="L22" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="M22" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="N22" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="O22" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="P22" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="S22" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="T22" t="n">
-        <v>2.32</v>
+        <v>2.7</v>
       </c>
       <c r="U22" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="V22" t="n">
-        <v>1.51</v>
+        <v>1.21</v>
       </c>
       <c r="W22" t="n">
-        <v>1.41</v>
+        <v>1.84</v>
       </c>
       <c r="X22" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="AA22" t="n">
-        <v>55</v>
+        <v>700</v>
       </c>
       <c r="AB22" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG22" t="n">
         <v>14.5</v>
       </c>
-      <c r="AE22" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AH22" t="n">
-        <v>27</v>
+        <v>220</v>
       </c>
       <c r="AI22" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AJ22" t="n">
-        <v>220</v>
+        <v>34</v>
       </c>
       <c r="AK22" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AL22" t="n">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="AM22" t="n">
         <v>500</v>
       </c>
       <c r="AN22" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="AO22" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AP22" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="AQ22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS22" t="n">
         <v>6.6</v>
       </c>
-      <c r="AR22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AT22" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="AW22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY22" t="n">
         <v>11</v>
       </c>
-      <c r="AX22" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AZ22" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>12.5</v>
+        <v>6.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="BC22" t="n">
-        <v>11.5</v>
+        <v>32</v>
       </c>
       <c r="BD22" t="n">
-        <v>12.5</v>
+        <v>6.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>16</v>
+        <v>6.8</v>
       </c>
       <c r="BF22" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG22" t="n">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,186 +4822,186 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al-Ettifaq</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>Al Riyadh SC</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G23" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H23" t="n">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="I23" t="n">
-        <v>5.8</v>
+        <v>3.75</v>
       </c>
       <c r="J23" t="n">
-        <v>2.86</v>
+        <v>3.85</v>
       </c>
       <c r="K23" t="n">
+        <v>4</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S23" t="n">
         <v>3</v>
       </c>
-      <c r="L23" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S23" t="n">
-        <v>7.8</v>
-      </c>
       <c r="T23" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="U23" t="n">
-        <v>1.54</v>
+        <v>2.26</v>
       </c>
       <c r="V23" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="W23" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X23" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU23" t="n">
         <v>7.6</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AV23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX23" t="n">
         <v>12.5</v>
       </c>
-      <c r="Z23" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>700</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>700</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>220</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>460</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>500</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>700</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV23" t="n">
+      <c r="AY23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA23" t="n">
         <v>21</v>
       </c>
-      <c r="AW23" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>6</v>
-      </c>
       <c r="BB23" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF23" t="n">
         <v>11.5</v>
       </c>
-      <c r="BC23" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BG23" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,184 +5011,184 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>Nottm Forest</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="G24" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="H24" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="J24" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="K24" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="L24" t="n">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
       <c r="M24" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="N24" t="n">
-        <v>4.4</v>
+        <v>2.86</v>
       </c>
       <c r="O24" t="n">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="P24" t="n">
-        <v>2.18</v>
+        <v>1.6</v>
       </c>
       <c r="Q24" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W24" t="n">
         <v>1.8</v>
       </c>
-      <c r="R24" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.86</v>
-      </c>
       <c r="X24" t="n">
-        <v>22</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y24" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z24" t="n">
         <v>25</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AA24" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE24" t="n">
         <v>65</v>
       </c>
-      <c r="AA24" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB24" t="n">
+      <c r="AF24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>75</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX24" t="n">
         <v>11</v>
       </c>
-      <c r="AC24" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE24" t="n">
+      <c r="AY24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>75</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>150</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>26</v>
+      </c>
+      <c r="BG24" t="n">
         <v>90</v>
       </c>
-      <c r="AF24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>190</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>28</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>27</v>
-      </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
@@ -5210,179 +5210,179 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.26</v>
+        <v>3.85</v>
       </c>
       <c r="G25" t="n">
-        <v>2.28</v>
+        <v>3.9</v>
       </c>
       <c r="H25" t="n">
-        <v>3.85</v>
+        <v>2.22</v>
       </c>
       <c r="I25" t="n">
-        <v>3.95</v>
+        <v>2.24</v>
       </c>
       <c r="J25" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K25" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="L25" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="M25" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>2.86</v>
+        <v>3.45</v>
       </c>
       <c r="O25" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="P25" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="R25" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="T25" t="n">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="U25" t="n">
-        <v>1.84</v>
+        <v>2.06</v>
       </c>
       <c r="V25" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="W25" t="n">
         <v>1.34</v>
       </c>
-      <c r="W25" t="n">
-        <v>1.78</v>
-      </c>
       <c r="X25" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="Z25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF25" t="n">
         <v>25</v>
       </c>
-      <c r="AA25" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>12</v>
-      </c>
       <c r="AG25" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AJ25" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="AK25" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="AL25" t="n">
         <v>60</v>
       </c>
       <c r="AM25" t="n">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="AN25" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AO25" t="n">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="AP25" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AQ25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV25" t="n">
         <v>10</v>
       </c>
-      <c r="AR25" t="n">
+      <c r="AW25" t="n">
         <v>23</v>
       </c>
-      <c r="AS25" t="n">
-        <v>75</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>55</v>
-      </c>
       <c r="AX25" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="AY25" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AZ25" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="BB25" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="BC25" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BD25" t="n">
         <v>55</v>
       </c>
       <c r="BE25" t="n">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="BF25" t="n">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="BG25" t="n">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
@@ -5404,186 +5404,186 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.85</v>
+        <v>2.38</v>
       </c>
       <c r="G26" t="n">
-        <v>3.95</v>
+        <v>2.4</v>
       </c>
       <c r="H26" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="I26" t="n">
-        <v>2.24</v>
+        <v>3.6</v>
       </c>
       <c r="J26" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K26" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L26" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M26" t="n">
         <v>1.09</v>
       </c>
       <c r="N26" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="O26" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="P26" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S26" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T26" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U26" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V26" t="n">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="W26" t="n">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="X26" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="AA26" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK26" t="n">
         <v>28</v>
       </c>
-      <c r="AB26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE26" t="n">
+      <c r="AL26" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN26" t="n">
         <v>25</v>
       </c>
-      <c r="AF26" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI26" t="n">
+      <c r="AO26" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW26" t="n">
         <v>42</v>
       </c>
-      <c r="AJ26" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>26</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV26" t="n">
+      <c r="AX26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY26" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>24</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>14.5</v>
       </c>
       <c r="AZ26" t="n">
         <v>17.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BB26" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="BC26" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="BD26" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="BE26" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BF26" t="n">
+        <v>24</v>
+      </c>
+      <c r="BG26" t="n">
         <v>50</v>
       </c>
-      <c r="BG26" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5598,186 +5598,186 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>MC El Bayadh</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.36</v>
+        <v>1.27</v>
       </c>
       <c r="G27" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="H27" t="n">
-        <v>3.55</v>
+        <v>22</v>
       </c>
       <c r="I27" t="n">
-        <v>3.6</v>
+        <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="K27" t="n">
-        <v>3.35</v>
+        <v>6</v>
       </c>
       <c r="L27" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="M27" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N27" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O27" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="P27" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="R27" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W27" t="n">
         <v>4.3</v>
       </c>
-      <c r="T27" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.71</v>
-      </c>
       <c r="X27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>380</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>36</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY27" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y27" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>26</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS27" t="n">
+      <c r="AZ27" t="n">
         <v>60</v>
       </c>
-      <c r="AT27" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>42</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>18</v>
-      </c>
       <c r="BA27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="BB27" t="n">
-        <v>30</v>
+        <v>7.4</v>
       </c>
       <c r="BC27" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="BD27" t="n">
-        <v>42</v>
+        <v>9.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="BF27" t="n">
-        <v>23</v>
+        <v>6.4</v>
       </c>
       <c r="BG27" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5792,179 +5792,179 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MC El Bayadh</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.31</v>
+        <v>1.67</v>
       </c>
       <c r="G28" t="n">
-        <v>1.33</v>
+        <v>1.69</v>
       </c>
       <c r="H28" t="n">
-        <v>19</v>
+        <v>6.2</v>
       </c>
       <c r="I28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="X28" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH28" t="n">
         <v>23</v>
       </c>
-      <c r="J28" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>6</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W28" t="n">
-        <v>4</v>
-      </c>
-      <c r="X28" t="n">
+      <c r="AI28" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP28" t="n">
         <v>13</v>
       </c>
-      <c r="Y28" t="n">
-        <v>40</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>290</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AK28" t="n">
+      <c r="AQ28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>46</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>150</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV28" t="n">
         <v>21</v>
       </c>
-      <c r="AL28" t="n">
-        <v>380</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AW28" t="n">
-        <v>7.6</v>
+        <v>85</v>
       </c>
       <c r="AX28" t="n">
-        <v>5.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY28" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ28" t="n">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="BA28" t="n">
-        <v>7.6</v>
+        <v>80</v>
       </c>
       <c r="BB28" t="n">
-        <v>7.4</v>
+        <v>14.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD28" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="BE28" t="n">
-        <v>7.6</v>
+        <v>110</v>
       </c>
       <c r="BF28" t="n">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
@@ -5986,31 +5986,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.67</v>
+        <v>2.28</v>
       </c>
       <c r="G29" t="n">
-        <v>1.69</v>
+        <v>2.32</v>
       </c>
       <c r="H29" t="n">
-        <v>6.2</v>
+        <v>3.45</v>
       </c>
       <c r="I29" t="n">
-        <v>6.6</v>
+        <v>3.55</v>
       </c>
       <c r="J29" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="K29" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="L29" t="n">
         <v>1.42</v>
@@ -6019,146 +6019,146 @@
         <v>1.07</v>
       </c>
       <c r="N29" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O29" t="n">
         <v>1.33</v>
       </c>
       <c r="P29" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q29" t="n">
         <v>2.02</v>
       </c>
       <c r="R29" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S29" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T29" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="U29" t="n">
-        <v>1.97</v>
+        <v>2.22</v>
       </c>
       <c r="V29" t="n">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="W29" t="n">
-        <v>2.44</v>
+        <v>1.75</v>
       </c>
       <c r="X29" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD29" t="n">
         <v>14</v>
       </c>
-      <c r="Y29" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Z29" t="n">
+      <c r="AE29" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI29" t="n">
         <v>55</v>
       </c>
-      <c r="AA29" t="n">
-        <v>200</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD29" t="n">
+      <c r="AJ29" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK29" t="n">
         <v>24</v>
       </c>
-      <c r="AE29" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AL29" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM29" t="n">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="AN29" t="n">
-        <v>11</v>
+        <v>18.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP29" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>80</v>
+      </c>
+      <c r="BF29" t="n">
         <v>17</v>
       </c>
-      <c r="AR29" t="n">
-        <v>46</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>24</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>22</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>85</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>85</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>36</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BG29" t="n">
-        <v>95</v>
+        <v>34</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
@@ -6180,25 +6180,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="G30" t="n">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="H30" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="I30" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="J30" t="n">
         <v>3.6</v>
@@ -6213,153 +6213,153 @@
         <v>1.07</v>
       </c>
       <c r="N30" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O30" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P30" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="R30" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S30" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T30" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="U30" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V30" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W30" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="X30" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z30" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AA30" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AB30" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AC30" t="n">
         <v>7.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AE30" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AF30" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AG30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH30" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AJ30" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AK30" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AL30" t="n">
         <v>38</v>
       </c>
       <c r="AM30" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AN30" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AO30" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AP30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV30" t="n">
         <v>12.5</v>
       </c>
-      <c r="AQ30" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR30" t="n">
+      <c r="AW30" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC30" t="n">
         <v>23</v>
       </c>
-      <c r="AS30" t="n">
-        <v>48</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>25</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>21</v>
-      </c>
       <c r="BD30" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE30" t="n">
         <v>75</v>
       </c>
       <c r="BF30" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BG30" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,191 +6369,191 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Shakhtar</t>
+          <t>Juticalpa</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>Olancho</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.52</v>
+        <v>5</v>
       </c>
       <c r="G31" t="n">
-        <v>2.56</v>
+        <v>8</v>
       </c>
       <c r="H31" t="n">
-        <v>3.05</v>
+        <v>1.56</v>
       </c>
       <c r="I31" t="n">
-        <v>3.1</v>
+        <v>1.72</v>
       </c>
       <c r="J31" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K31" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="L31" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="M31" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="N31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG31" t="n">
         <v>4</v>
       </c>
-      <c r="O31" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="X31" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>46</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>36</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>19</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>27</v>
-      </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6568,186 +6568,186 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Juticalpa</t>
+          <t>Union Magdalena</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olancho</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.92</v>
+        <v>2.22</v>
       </c>
       <c r="G32" t="n">
-        <v>110</v>
+        <v>2.34</v>
       </c>
       <c r="H32" t="n">
-        <v>1.5</v>
+        <v>3.65</v>
       </c>
       <c r="I32" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="J32" t="n">
         <v>3.25</v>
       </c>
       <c r="K32" t="n">
-        <v>10.5</v>
+        <v>3.5</v>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M32" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>1.1</v>
+        <v>3.15</v>
       </c>
       <c r="O32" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="P32" t="n">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.23</v>
+        <v>2.28</v>
       </c>
       <c r="R32" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S32" t="n">
-        <v>1.23</v>
+        <v>4.3</v>
       </c>
       <c r="T32" t="n">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="U32" t="n">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="V32" t="n">
-        <v>1.67</v>
+        <v>1.34</v>
       </c>
       <c r="W32" t="n">
-        <v>1.16</v>
+        <v>1.75</v>
       </c>
       <c r="X32" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y32" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA32" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB32" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE32" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF32" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG32" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH32" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI32" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK32" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL32" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM32" t="n">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AN32" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO32" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.1</v>
+        <v>10</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.15</v>
+        <v>22</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.15</v>
+        <v>9.6</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.15</v>
+        <v>7</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.12</v>
+        <v>6.4</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.11</v>
+        <v>14</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.15</v>
+        <v>11.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.15</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.15</v>
+        <v>16.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.15</v>
+        <v>12.5</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.15</v>
+        <v>11.5</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.15</v>
+        <v>13</v>
       </c>
       <c r="BD32" t="n">
-        <v>1.15</v>
+        <v>9</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.15</v>
+        <v>10</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.55</v>
+        <v>21</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.15</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,378 +6757,184 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Union Magdalena</t>
+          <t>CD Marathon</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>CD Motagua</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.22</v>
+        <v>1.04</v>
       </c>
       <c r="G33" t="n">
-        <v>2.34</v>
+        <v>240</v>
       </c>
       <c r="H33" t="n">
-        <v>3.65</v>
+        <v>1.09</v>
       </c>
       <c r="I33" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="J33" t="n">
-        <v>3.25</v>
+        <v>1.09</v>
       </c>
       <c r="K33" t="n">
-        <v>3.5</v>
+        <v>950</v>
       </c>
       <c r="L33" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>3.1</v>
+        <v>1.02</v>
       </c>
       <c r="O33" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="P33" t="n">
-        <v>1.69</v>
+        <v>1.24</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.3</v>
+        <v>1.29</v>
       </c>
       <c r="R33" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S33" t="n">
-        <v>4.4</v>
+        <v>1.29</v>
       </c>
       <c r="T33" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="U33" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.76</v>
+        <v>1.54</v>
       </c>
       <c r="X33" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y33" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z33" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA33" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC33" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD33" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE33" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AG33" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH33" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI33" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK33" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL33" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM33" t="n">
-        <v>440</v>
+        <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AQ33" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AR33" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AS33" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AT33" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AU33" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV33" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AW33" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AX33" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY33" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ33" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA33" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BB33" t="n">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="BC33" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BD33" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="BE33" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BF33" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BG33" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-09 02:58:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Honduras Liga Nacional</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>22:30:00</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>CD Marathon</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>CD Motagua</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H34" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="I34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="K34" t="n">
-        <v>950</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S34" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH34" t="inlineStr">
-        <is>
-          <t>2026-04-09 02:58:28</t>
+          <t>2026-04-09 05:17:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
@@ -757,64 +757,64 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.54</v>
+        <v>1.76</v>
       </c>
       <c r="G2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W2" t="n">
         <v>2.08</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.94</v>
       </c>
       <c r="X2" t="n">
         <v>18</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z2" t="n">
         <v>1000</v>
@@ -823,34 +823,34 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AC2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG2" t="n">
         <v>42</v>
       </c>
-      <c r="AD2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1000</v>
-      </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL2" t="n">
         <v>1000</v>
@@ -859,68 +859,68 @@
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.39</v>
+        <v>4.3</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.39</v>
+        <v>3.05</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.4</v>
+        <v>2.52</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.35</v>
+        <v>4.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.27</v>
+        <v>4.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.39</v>
+        <v>2.74</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.37</v>
+        <v>5.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.36</v>
+        <v>5.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.37</v>
+        <v>7.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.39</v>
+        <v>7.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.37</v>
+        <v>7.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.39</v>
+        <v>5</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.56</v>
+        <v>2.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -960,43 +960,43 @@
         <v>6.4</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K3" t="n">
         <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="P3" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="R3" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T3" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="U3" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="V3" t="n">
         <v>1.16</v>
@@ -1005,116 +1005,116 @@
         <v>2.52</v>
       </c>
       <c r="X3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y3" t="n">
         <v>24</v>
       </c>
       <c r="Z3" t="n">
-        <v>400</v>
+        <v>55</v>
       </c>
       <c r="AA3" t="n">
-        <v>700</v>
+        <v>190</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC3" t="n">
         <v>9.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="AE3" t="n">
-        <v>700</v>
+        <v>240</v>
       </c>
       <c r="AF3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AG3" t="n">
-        <v>10</v>
-      </c>
       <c r="AH3" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>700</v>
+        <v>90</v>
       </c>
       <c r="AJ3" t="n">
         <v>17</v>
       </c>
       <c r="AK3" t="n">
-        <v>25</v>
+        <v>16.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="AM3" t="n">
-        <v>700</v>
+        <v>190</v>
       </c>
       <c r="AN3" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AO3" t="n">
         <v>700</v>
       </c>
       <c r="AP3" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="AR3" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AS3" t="n">
-        <v>12.5</v>
+        <v>36</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU3" t="n">
         <v>8.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AW3" t="n">
-        <v>11.5</v>
+        <v>55</v>
       </c>
       <c r="AX3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC3" t="n">
         <v>15</v>
       </c>
-      <c r="BA3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>10</v>
-      </c>
       <c r="BD3" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BE3" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="BF3" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="G4" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="H4" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="J4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.4</v>
@@ -1178,10 +1178,10 @@
         <v>2.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
         <v>3.25</v>
@@ -1196,43 +1196,43 @@
         <v>1.56</v>
       </c>
       <c r="W4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X4" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Y4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB4" t="n">
         <v>13</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF4" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AG4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ4" t="n">
         <v>44</v>
@@ -1241,74 +1241,74 @@
         <v>32</v>
       </c>
       <c r="AL4" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="AM4" t="n">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="AN4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO4" t="n">
         <v>24</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>25</v>
       </c>
       <c r="AP4" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>36</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>22</v>
+      </c>
+      <c r="BG4" t="n">
         <v>21</v>
       </c>
-      <c r="AT4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>60</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>19</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>20</v>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="G5" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="H5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="I5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="J5" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="K5" t="n">
         <v>5.9</v>
@@ -1360,7 +1360,7 @@
         <v>1.38</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
         <v>4.2</v>
@@ -1375,34 +1375,34 @@
         <v>1.86</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="U5" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="V5" t="n">
         <v>1.07</v>
       </c>
       <c r="W5" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="X5" t="n">
         <v>18.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="Z5" t="n">
         <v>140</v>
       </c>
       <c r="AA5" t="n">
-        <v>830</v>
+        <v>660</v>
       </c>
       <c r="AB5" t="n">
         <v>7.4</v>
@@ -1417,16 +1417,16 @@
         <v>310</v>
       </c>
       <c r="AF5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AG5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AH5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI5" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AJ5" t="n">
         <v>10</v>
@@ -1444,19 +1444,19 @@
         <v>6.4</v>
       </c>
       <c r="AO5" t="n">
-        <v>500</v>
+        <v>430</v>
       </c>
       <c r="AP5" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AR5" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AT5" t="n">
         <v>6.6</v>
@@ -1465,10 +1465,10 @@
         <v>11.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW5" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AX5" t="n">
         <v>6.4</v>
@@ -1477,16 +1477,16 @@
         <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BA5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC5" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD5" t="n">
         <v>34</v>
@@ -1495,14 +1495,14 @@
         <v>30</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -1533,25 +1533,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="G6" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="I6" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="J6" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="L6" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="M6" t="n">
         <v>1.13</v>
@@ -1560,13 +1560,13 @@
         <v>2.8</v>
       </c>
       <c r="O6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P6" t="n">
         <v>1.56</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R6" t="n">
         <v>1.2</v>
@@ -1575,128 +1575,128 @@
         <v>5.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U6" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V6" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="W6" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="X6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC6" t="n">
         <v>7</v>
       </c>
       <c r="AD6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE6" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF6" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AG6" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="AJ6" t="n">
         <v>160</v>
       </c>
       <c r="AK6" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AL6" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AM6" t="n">
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>600</v>
+        <v>95</v>
       </c>
       <c r="AO6" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AT6" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW6" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AX6" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AY6" t="n">
         <v>13.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA6" t="n">
         <v>48</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.6</v>
+        <v>20</v>
       </c>
       <c r="BC6" t="n">
-        <v>25</v>
+        <v>11.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="BE6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF6" t="n">
         <v>10.5</v>
       </c>
-      <c r="BF6" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BG6" t="n">
-        <v>29</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -1727,58 +1727,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="H7" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="I7" t="n">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="J7" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="K7" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="M7" t="n">
         <v>1.14</v>
       </c>
       <c r="N7" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="O7" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="P7" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="R7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="T7" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="U7" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="V7" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="X7" t="n">
         <v>8</v>
@@ -1787,34 +1787,34 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Z7" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AA7" t="n">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AC7" t="n">
         <v>7</v>
       </c>
       <c r="AD7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AF7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG7" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH7" t="n">
         <v>23</v>
       </c>
       <c r="AI7" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AJ7" t="n">
         <v>160</v>
@@ -1823,37 +1823,37 @@
         <v>130</v>
       </c>
       <c r="AL7" t="n">
-        <v>240</v>
+        <v>80</v>
       </c>
       <c r="AM7" t="n">
         <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>600</v>
+        <v>70</v>
       </c>
       <c r="AO7" t="n">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AP7" t="n">
         <v>7.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS7" t="n">
         <v>21</v>
       </c>
       <c r="AT7" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AU7" t="n">
         <v>6.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW7" t="n">
         <v>19</v>
@@ -1874,23 +1874,23 @@
         <v>23</v>
       </c>
       <c r="BC7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD7" t="n">
         <v>34</v>
       </c>
       <c r="BE7" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="BF7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -1924,16 +1924,16 @@
         <v>3.1</v>
       </c>
       <c r="G8" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H8" t="n">
         <v>2.36</v>
       </c>
       <c r="I8" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="J8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K8" t="n">
         <v>3.85</v>
@@ -1945,16 +1945,16 @@
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O8" t="n">
         <v>1.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="R8" t="n">
         <v>1.37</v>
@@ -1966,13 +1966,13 @@
         <v>1.7</v>
       </c>
       <c r="U8" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="V8" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W8" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X8" t="n">
         <v>24</v>
@@ -1984,13 +1984,13 @@
         <v>30</v>
       </c>
       <c r="AA8" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AB8" t="n">
         <v>23</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD8" t="n">
         <v>17</v>
@@ -2011,7 +2011,7 @@
         <v>95</v>
       </c>
       <c r="AJ8" t="n">
-        <v>280</v>
+        <v>120</v>
       </c>
       <c r="AK8" t="n">
         <v>90</v>
@@ -2023,22 +2023,22 @@
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="AP8" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR8" t="n">
         <v>13.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="AT8" t="n">
         <v>11</v>
@@ -2047,13 +2047,13 @@
         <v>7.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW8" t="n">
         <v>18.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AY8" t="n">
         <v>11.5</v>
@@ -2071,20 +2071,20 @@
         <v>16.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="BE8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>18</v>
+        <v>8.6</v>
       </c>
       <c r="BG8" t="n">
         <v>11</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="G9" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="H9" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="I9" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="J9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K9" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L9" t="n">
         <v>1.33</v>
@@ -2142,37 +2142,37 @@
         <v>5.3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q9" t="n">
         <v>1.64</v>
       </c>
       <c r="R9" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S9" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T9" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="U9" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V9" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z9" t="n">
         <v>11</v>
@@ -2181,7 +2181,7 @@
         <v>15</v>
       </c>
       <c r="AB9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AC9" t="n">
         <v>12</v>
@@ -2193,46 +2193,46 @@
         <v>15</v>
       </c>
       <c r="AF9" t="n">
-        <v>540</v>
+        <v>75</v>
       </c>
       <c r="AG9" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AH9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI9" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AJ9" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AK9" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AL9" t="n">
-        <v>390</v>
+        <v>240</v>
       </c>
       <c r="AM9" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>160</v>
+        <v>90</v>
       </c>
       <c r="AO9" t="n">
         <v>6.6</v>
       </c>
       <c r="AP9" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR9" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AT9" t="n">
         <v>24</v>
@@ -2241,13 +2241,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AW9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AY9" t="n">
         <v>20</v>
@@ -2259,26 +2259,26 @@
         <v>16</v>
       </c>
       <c r="BB9" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC9" t="n">
-        <v>30</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD9" t="n">
         <v>30</v>
       </c>
       <c r="BE9" t="n">
-        <v>29</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
         <v>1.94</v>
       </c>
       <c r="G10" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H10" t="n">
         <v>3.7</v>
@@ -2324,16 +2324,16 @@
         <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O10" t="n">
         <v>1.24</v>
@@ -2342,64 +2342,64 @@
         <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R10" t="n">
         <v>1.46</v>
       </c>
       <c r="S10" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T10" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="U10" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="V10" t="n">
         <v>1.32</v>
       </c>
       <c r="W10" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X10" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>500</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>300</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH10" t="n">
         <v>24</v>
       </c>
-      <c r="Y10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>500</v>
-      </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ10" t="n">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="AK10" t="n">
         <v>46</v>
@@ -2411,10 +2411,10 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP10" t="n">
         <v>9.800000000000001</v>
@@ -2432,13 +2432,13 @@
         <v>9.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV10" t="n">
         <v>14</v>
       </c>
       <c r="AW10" t="n">
-        <v>20</v>
+        <v>8.6</v>
       </c>
       <c r="AX10" t="n">
         <v>11</v>
@@ -2447,7 +2447,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA10" t="n">
         <v>29</v>
@@ -2456,23 +2456,23 @@
         <v>18.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="BD10" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BE10" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BF10" t="n">
         <v>10</v>
       </c>
       <c r="BG10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -2512,31 +2512,31 @@
         <v>13.5</v>
       </c>
       <c r="I11" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="J11" t="n">
         <v>4.3</v>
       </c>
       <c r="K11" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
         <v>1.54</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="O11" t="n">
         <v>1.5</v>
       </c>
       <c r="P11" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R11" t="n">
         <v>1.21</v>
@@ -2545,10 +2545,10 @@
         <v>5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="U11" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="V11" t="n">
         <v>1.06</v>
@@ -2557,10 +2557,10 @@
         <v>3.3</v>
       </c>
       <c r="X11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y11" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Z11" t="n">
         <v>1000</v>
@@ -2572,7 +2572,7 @@
         <v>5.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD11" t="n">
         <v>150</v>
@@ -2584,7 +2584,7 @@
         <v>6.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
         <v>60</v>
@@ -2599,7 +2599,7 @@
         <v>23</v>
       </c>
       <c r="AL11" t="n">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
@@ -2614,13 +2614,13 @@
         <v>8.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AT11" t="n">
         <v>4.4</v>
@@ -2629,22 +2629,22 @@
         <v>10.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>40</v>
+        <v>10.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AX11" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB11" t="n">
         <v>9.4</v>
@@ -2656,17 +2656,17 @@
         <v>28</v>
       </c>
       <c r="BE11" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="BG11" t="n">
         <v>15</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="H12" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I12" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J12" t="n">
         <v>3.4</v>
@@ -2727,10 +2727,10 @@
         <v>1.43</v>
       </c>
       <c r="P12" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R12" t="n">
         <v>1.27</v>
@@ -2739,25 +2739,25 @@
         <v>4.4</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U12" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W12" t="n">
         <v>1.96</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.92</v>
       </c>
       <c r="X12" t="n">
         <v>11</v>
       </c>
       <c r="Y12" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA12" t="n">
         <v>110</v>
@@ -2766,7 +2766,7 @@
         <v>7.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD12" t="n">
         <v>17.5</v>
@@ -2790,7 +2790,7 @@
         <v>25</v>
       </c>
       <c r="AK12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL12" t="n">
         <v>44</v>
@@ -2799,10 +2799,10 @@
         <v>140</v>
       </c>
       <c r="AN12" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AP12" t="n">
         <v>10.5</v>
@@ -2811,25 +2811,25 @@
         <v>12</v>
       </c>
       <c r="AR12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS12" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AT12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU12" t="n">
         <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW12" t="n">
         <v>55</v>
       </c>
       <c r="AX12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY12" t="n">
         <v>10</v>
@@ -2838,29 +2838,29 @@
         <v>18</v>
       </c>
       <c r="BA12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BB12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD12" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BE12" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="BF12" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>2.5</v>
       </c>
       <c r="G13" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H13" t="n">
         <v>3.05</v>
@@ -2903,13 +2903,13 @@
         <v>3.15</v>
       </c>
       <c r="J13" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K13" t="n">
         <v>3.55</v>
       </c>
       <c r="L13" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M13" t="n">
         <v>1.07</v>
@@ -2918,7 +2918,7 @@
         <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
@@ -2936,7 +2936,7 @@
         <v>1.75</v>
       </c>
       <c r="U13" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V13" t="n">
         <v>1.46</v>
@@ -2963,7 +2963,7 @@
         <v>7.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE13" t="n">
         <v>34</v>
@@ -2975,28 +2975,28 @@
         <v>11.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AJ13" t="n">
         <v>36</v>
       </c>
       <c r="AK13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL13" t="n">
         <v>40</v>
       </c>
       <c r="AM13" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP13" t="n">
         <v>13</v>
@@ -3008,13 +3008,13 @@
         <v>19</v>
       </c>
       <c r="AS13" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AT13" t="n">
         <v>10</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV13" t="n">
         <v>12</v>
@@ -3032,10 +3032,10 @@
         <v>15</v>
       </c>
       <c r="BA13" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BC13" t="n">
         <v>24</v>
@@ -3044,7 +3044,7 @@
         <v>34</v>
       </c>
       <c r="BE13" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BF13" t="n">
         <v>19</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="G14" t="n">
-        <v>2.26</v>
+        <v>2.78</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="I14" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K14" t="n">
         <v>3.65</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.8</v>
       </c>
       <c r="L14" t="n">
         <v>1.35</v>
@@ -3109,13 +3109,13 @@
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O14" t="n">
         <v>1.23</v>
       </c>
       <c r="P14" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q14" t="n">
         <v>1.74</v>
@@ -3127,128 +3127,128 @@
         <v>2.8</v>
       </c>
       <c r="T14" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U14" t="n">
         <v>2.44</v>
       </c>
       <c r="V14" t="n">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="W14" t="n">
-        <v>1.79</v>
+        <v>1.56</v>
       </c>
       <c r="X14" t="n">
         <v>18</v>
       </c>
       <c r="Y14" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AA14" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AB14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD14" t="n">
         <v>13</v>
       </c>
-      <c r="AC14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>15</v>
-      </c>
       <c r="AE14" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AF14" t="n">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="AG14" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AH14" t="n">
         <v>14.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AJ14" t="n">
         <v>65</v>
       </c>
       <c r="AK14" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AL14" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM14" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN14" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AO14" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="AP14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AR14" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AT14" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AX14" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AY14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ14" t="n">
         <v>13</v>
       </c>
       <c r="BA14" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BB14" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BC14" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BD14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE14" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="BF14" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="BG14" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -3279,91 +3279,91 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="G15" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="I15" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="J15" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="K15" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O15" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P15" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="U15" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="V15" t="n">
-        <v>2.12</v>
+        <v>2.46</v>
       </c>
       <c r="W15" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X15" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH15" t="n">
         <v>21</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>46</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>19.5</v>
       </c>
       <c r="AI15" t="n">
         <v>85</v>
@@ -3372,7 +3372,7 @@
         <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AL15" t="n">
         <v>700</v>
@@ -3381,68 +3381,68 @@
         <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP15" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AR15" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT15" t="n">
         <v>16.5</v>
       </c>
-      <c r="AT15" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AU15" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AV15" t="n">
         <v>9</v>
       </c>
       <c r="AW15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX15" t="n">
         <v>16</v>
       </c>
-      <c r="AX15" t="n">
-        <v>20</v>
-      </c>
       <c r="AY15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AZ15" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BA15" t="n">
         <v>18.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>36</v>
+        <v>10.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BD15" t="n">
         <v>27</v>
       </c>
       <c r="BE15" t="n">
-        <v>9.4</v>
+        <v>28</v>
       </c>
       <c r="BF15" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="BG15" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -3497,34 +3497,34 @@
         <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O16" t="n">
         <v>1.38</v>
       </c>
       <c r="P16" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="R16" t="n">
         <v>1.32</v>
       </c>
       <c r="S16" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V16" t="n">
         <v>1.33</v>
       </c>
       <c r="W16" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X16" t="n">
         <v>12.5</v>
@@ -3536,7 +3536,7 @@
         <v>26</v>
       </c>
       <c r="AA16" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AB16" t="n">
         <v>8.800000000000001</v>
@@ -3551,7 +3551,7 @@
         <v>55</v>
       </c>
       <c r="AF16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG16" t="n">
         <v>11.5</v>
@@ -3560,25 +3560,25 @@
         <v>19.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ16" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AK16" t="n">
         <v>27</v>
       </c>
       <c r="AL16" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AM16" t="n">
         <v>320</v>
       </c>
       <c r="AN16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO16" t="n">
-        <v>600</v>
+        <v>60</v>
       </c>
       <c r="AP16" t="n">
         <v>10.5</v>
@@ -3599,10 +3599,10 @@
         <v>6.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="AW16" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="AX16" t="n">
         <v>11.5</v>
@@ -3626,17 +3626,17 @@
         <v>36</v>
       </c>
       <c r="BE16" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BF16" t="n">
         <v>18</v>
       </c>
       <c r="BG16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G17" t="n">
         <v>2.32</v>
       </c>
       <c r="H17" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I17" t="n">
         <v>3.75</v>
@@ -3691,13 +3691,13 @@
         <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P17" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
         <v>1.94</v>
@@ -3712,16 +3712,16 @@
         <v>1.75</v>
       </c>
       <c r="U17" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V17" t="n">
         <v>1.37</v>
       </c>
       <c r="W17" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X17" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="Y17" t="n">
         <v>34</v>
@@ -3733,37 +3733,37 @@
         <v>500</v>
       </c>
       <c r="AB17" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AC17" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE17" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AF17" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AG17" t="n">
-        <v>36</v>
+        <v>17.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AI17" t="n">
         <v>500</v>
       </c>
       <c r="AJ17" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM17" t="n">
         <v>580</v>
@@ -3778,16 +3778,16 @@
         <v>7.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="AR17" t="n">
         <v>11.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>23</v>
+        <v>9.4</v>
       </c>
       <c r="AT17" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU17" t="n">
         <v>6</v>
@@ -3820,17 +3820,17 @@
         <v>17.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BF17" t="n">
         <v>7</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -3873,10 +3873,10 @@
         <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="K18" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="L18" t="n">
         <v>1.14</v>
@@ -3903,16 +3903,16 @@
         <v>1.52</v>
       </c>
       <c r="T18" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U18" t="n">
         <v>1.65</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -3969,62 +3969,62 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AQ18" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AS18" t="n">
         <v>4.2</v>
       </c>
       <c r="AT18" t="n">
-        <v>4.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU18" t="n">
-        <v>5.9</v>
+        <v>17.5</v>
       </c>
       <c r="AV18" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AX18" t="n">
         <v>6.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="BB18" t="n">
         <v>5.1</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.95</v>
+        <v>7.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>8.6</v>
+        <v>20</v>
       </c>
       <c r="BE18" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="BG18" t="n">
         <v>10.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="G19" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H19" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="I19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L19" t="n">
         <v>1.48</v>
@@ -4079,16 +4079,16 @@
         <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O19" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P19" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R19" t="n">
         <v>1.27</v>
@@ -4100,7 +4100,7 @@
         <v>2.46</v>
       </c>
       <c r="U19" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="V19" t="n">
         <v>1.1</v>
@@ -4109,116 +4109,116 @@
         <v>3</v>
       </c>
       <c r="X19" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="Z19" t="n">
         <v>110</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="AB19" t="n">
         <v>6.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD19" t="n">
         <v>95</v>
       </c>
       <c r="AE19" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AF19" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AG19" t="n">
         <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="AI19" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AJ19" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="AK19" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AL19" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AM19" t="n">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="AN19" t="n">
         <v>10.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AP19" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="AQ19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS19" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="AT19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>34</v>
+      </c>
+      <c r="AW19" t="n">
         <v>11</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="AX19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>30</v>
+      </c>
+      <c r="BA19" t="n">
         <v>11</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>30</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>26</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>10.5</v>
       </c>
       <c r="BB19" t="n">
         <v>10</v>
       </c>
       <c r="BC19" t="n">
-        <v>8.4</v>
+        <v>16.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>9.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BE19" t="n">
         <v>30</v>
       </c>
       <c r="BF19" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.42</v>
+        <v>2.68</v>
       </c>
       <c r="G20" t="n">
-        <v>2.66</v>
+        <v>2.86</v>
       </c>
       <c r="H20" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I20" t="n">
         <v>2.8</v>
       </c>
-      <c r="I20" t="n">
-        <v>3.15</v>
-      </c>
       <c r="J20" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K20" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L20" t="n">
         <v>1.35</v>
@@ -4291,97 +4291,97 @@
         <v>2.78</v>
       </c>
       <c r="T20" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="U20" t="n">
         <v>2.38</v>
       </c>
       <c r="V20" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="W20" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="X20" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="Y20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z20" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AA20" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB20" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC20" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD20" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE20" t="n">
         <v>75</v>
       </c>
       <c r="AF20" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AG20" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH20" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="AJ20" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AK20" t="n">
         <v>500</v>
       </c>
       <c r="AL20" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM20" t="n">
         <v>580</v>
       </c>
       <c r="AN20" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="AO20" t="n">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AP20" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AR20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV20" t="n">
         <v>10</v>
       </c>
-      <c r="AS20" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>11</v>
-      </c>
       <c r="AW20" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AX20" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AY20" t="n">
         <v>10</v>
@@ -4390,29 +4390,29 @@
         <v>12.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB20" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="BD20" t="n">
         <v>20</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="BF20" t="n">
-        <v>14.5</v>
+        <v>6.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -4449,58 +4449,58 @@
         <v>3.35</v>
       </c>
       <c r="H21" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="I21" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K21" t="n">
         <v>2.92</v>
       </c>
-      <c r="J21" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2.98</v>
-      </c>
       <c r="L21" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="M21" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N21" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="O21" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="P21" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="R21" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="S21" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="T21" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="U21" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="V21" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W21" t="n">
         <v>1.42</v>
       </c>
       <c r="X21" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y21" t="n">
         <v>7.4</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>7.6</v>
       </c>
       <c r="Z21" t="n">
         <v>17</v>
@@ -4509,16 +4509,16 @@
         <v>55</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC21" t="n">
         <v>7</v>
       </c>
       <c r="AD21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE21" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF21" t="n">
         <v>21</v>
@@ -4527,13 +4527,13 @@
         <v>16</v>
       </c>
       <c r="AH21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI21" t="n">
         <v>500</v>
       </c>
       <c r="AJ21" t="n">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="AK21" t="n">
         <v>120</v>
@@ -4551,7 +4551,7 @@
         <v>600</v>
       </c>
       <c r="AP21" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ21" t="n">
         <v>6.6</v>
@@ -4563,7 +4563,7 @@
         <v>24</v>
       </c>
       <c r="AT21" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU21" t="n">
         <v>6.2</v>
@@ -4584,29 +4584,29 @@
         <v>22</v>
       </c>
       <c r="BA21" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="BB21" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BC21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BD21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BE21" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BG21" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -4637,64 +4637,64 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G22" t="n">
         <v>2.18</v>
       </c>
       <c r="H22" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I22" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J22" t="n">
         <v>2.76</v>
       </c>
       <c r="K22" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="L22" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="M22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V22" t="n">
         <v>1.2</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S22" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.21</v>
       </c>
       <c r="W22" t="n">
         <v>1.84</v>
       </c>
       <c r="X22" t="n">
-        <v>7.6</v>
+        <v>5.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z22" t="n">
         <v>85</v>
@@ -4703,37 +4703,37 @@
         <v>700</v>
       </c>
       <c r="AB22" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AE22" t="n">
         <v>700</v>
       </c>
       <c r="AF22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG22" t="n">
         <v>14.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>220</v>
+        <v>70</v>
       </c>
       <c r="AI22" t="n">
         <v>700</v>
       </c>
       <c r="AJ22" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AK22" t="n">
         <v>80</v>
       </c>
       <c r="AL22" t="n">
-        <v>460</v>
+        <v>240</v>
       </c>
       <c r="AM22" t="n">
         <v>500</v>
@@ -4745,62 +4745,62 @@
         <v>700</v>
       </c>
       <c r="AP22" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR22" t="n">
         <v>24</v>
       </c>
       <c r="AS22" t="n">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="AT22" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AU22" t="n">
         <v>6.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="AX22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ22" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA22" t="n">
-        <v>6.6</v>
+        <v>80</v>
       </c>
       <c r="BB22" t="n">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BD22" t="n">
-        <v>6.6</v>
+        <v>28</v>
       </c>
       <c r="BE22" t="n">
-        <v>6.8</v>
+        <v>46</v>
       </c>
       <c r="BF22" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -4834,19 +4834,19 @@
         <v>2.08</v>
       </c>
       <c r="G23" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H23" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I23" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J23" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L23" t="n">
         <v>1.37</v>
@@ -4855,16 +4855,16 @@
         <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O23" t="n">
         <v>1.26</v>
       </c>
       <c r="P23" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R23" t="n">
         <v>1.46</v>
@@ -4873,19 +4873,19 @@
         <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U23" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V23" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W23" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y23" t="n">
         <v>16</v>
@@ -4894,13 +4894,13 @@
         <v>28</v>
       </c>
       <c r="AA23" t="n">
-        <v>900</v>
+        <v>70</v>
       </c>
       <c r="AB23" t="n">
         <v>11.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD23" t="n">
         <v>15.5</v>
@@ -4912,7 +4912,7 @@
         <v>14.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH23" t="n">
         <v>16.5</v>
@@ -4921,43 +4921,43 @@
         <v>46</v>
       </c>
       <c r="AJ23" t="n">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="AK23" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="AL23" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AM23" t="n">
         <v>80</v>
       </c>
       <c r="AN23" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO23" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP23" t="n">
         <v>16</v>
       </c>
       <c r="AQ23" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR23" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AS23" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AT23" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU23" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW23" t="n">
         <v>34</v>
@@ -4972,29 +4972,29 @@
         <v>14.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="BB23" t="n">
         <v>22</v>
       </c>
       <c r="BC23" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>16.5</v>
+        <v>28</v>
       </c>
       <c r="BE23" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="BF23" t="n">
         <v>11.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="G24" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="I24" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="J24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K24" t="n">
         <v>3.25</v>
-      </c>
-      <c r="K24" t="n">
-        <v>3.3</v>
       </c>
       <c r="L24" t="n">
         <v>1.58</v>
@@ -5049,61 +5049,61 @@
         <v>1.12</v>
       </c>
       <c r="N24" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="O24" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="P24" t="n">
         <v>1.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="R24" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S24" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="T24" t="n">
         <v>2.14</v>
       </c>
       <c r="U24" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V24" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W24" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="X24" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z24" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA24" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AB24" t="n">
         <v>7.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE24" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG24" t="n">
         <v>11.5</v>
@@ -5112,13 +5112,13 @@
         <v>24</v>
       </c>
       <c r="AI24" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ24" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AK24" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AL24" t="n">
         <v>60</v>
@@ -5127,40 +5127,40 @@
         <v>180</v>
       </c>
       <c r="AN24" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AO24" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ24" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AR24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS24" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AT24" t="n">
         <v>6.8</v>
       </c>
       <c r="AU24" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW24" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AX24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY24" t="n">
         <v>11</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>10.5</v>
       </c>
       <c r="AZ24" t="n">
         <v>23</v>
@@ -5172,23 +5172,23 @@
         <v>28</v>
       </c>
       <c r="BC24" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BD24" t="n">
         <v>50</v>
       </c>
       <c r="BE24" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="BF24" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BG24" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="H25" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="I25" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="J25" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K25" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L25" t="n">
         <v>1.49</v>
@@ -5243,13 +5243,13 @@
         <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="O25" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P25" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q25" t="n">
         <v>2.2</v>
@@ -5261,28 +5261,28 @@
         <v>4.1</v>
       </c>
       <c r="T25" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="U25" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V25" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="W25" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="X25" t="n">
         <v>11.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z25" t="n">
         <v>12.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AB25" t="n">
         <v>12.5</v>
@@ -5297,10 +5297,10 @@
         <v>24</v>
       </c>
       <c r="AF25" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AG25" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH25" t="n">
         <v>18.5</v>
@@ -5309,7 +5309,7 @@
         <v>42</v>
       </c>
       <c r="AJ25" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AK25" t="n">
         <v>48</v>
@@ -5321,7 +5321,7 @@
         <v>110</v>
       </c>
       <c r="AN25" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AO25" t="n">
         <v>21</v>
@@ -5333,10 +5333,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR25" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT25" t="n">
         <v>12</v>
@@ -5351,19 +5351,19 @@
         <v>23</v>
       </c>
       <c r="AX25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY25" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA25" t="n">
         <v>40</v>
       </c>
       <c r="BB25" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BC25" t="n">
         <v>44</v>
@@ -5372,17 +5372,17 @@
         <v>55</v>
       </c>
       <c r="BE25" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BF25" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BG25" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -5413,28 +5413,28 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="G26" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H26" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I26" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J26" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K26" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L26" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M26" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N26" t="n">
         <v>3.25</v>
@@ -5452,19 +5452,19 @@
         <v>1.28</v>
       </c>
       <c r="S26" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T26" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="U26" t="n">
         <v>2.04</v>
       </c>
       <c r="V26" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W26" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="X26" t="n">
         <v>11.5</v>
@@ -5473,37 +5473,37 @@
         <v>11.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA26" t="n">
         <v>70</v>
       </c>
       <c r="AB26" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD26" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE26" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF26" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG26" t="n">
         <v>11.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI26" t="n">
         <v>65</v>
       </c>
       <c r="AJ26" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK26" t="n">
         <v>28</v>
@@ -5512,7 +5512,7 @@
         <v>46</v>
       </c>
       <c r="AM26" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN26" t="n">
         <v>25</v>
@@ -5533,34 +5533,34 @@
         <v>60</v>
       </c>
       <c r="AT26" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU26" t="n">
         <v>6.8</v>
       </c>
       <c r="AV26" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW26" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX26" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY26" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA26" t="n">
         <v>50</v>
       </c>
       <c r="BB26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD26" t="n">
         <v>42</v>
@@ -5569,14 +5569,14 @@
         <v>95</v>
       </c>
       <c r="BF26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BG26" t="n">
         <v>50</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -5616,10 +5616,10 @@
         <v>22</v>
       </c>
       <c r="I27" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="K27" t="n">
         <v>6</v>
@@ -5628,16 +5628,16 @@
         <v>1.47</v>
       </c>
       <c r="M27" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N27" t="n">
         <v>3.15</v>
       </c>
       <c r="O27" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P27" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q27" t="n">
         <v>2.24</v>
@@ -5652,19 +5652,19 @@
         <v>3.2</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V27" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W27" t="n">
         <v>4.3</v>
       </c>
       <c r="X27" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y27" t="n">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="Z27" t="n">
         <v>1000</v>
@@ -5676,7 +5676,7 @@
         <v>5.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AD27" t="n">
         <v>1000</v>
@@ -5685,13 +5685,13 @@
         <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AG27" t="n">
         <v>14</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AI27" t="n">
         <v>1000</v>
@@ -5721,56 +5721,56 @@
         <v>36</v>
       </c>
       <c r="AR27" t="n">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="AS27" t="n">
-        <v>100</v>
+        <v>11.5</v>
       </c>
       <c r="AT27" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AU27" t="n">
         <v>13</v>
       </c>
       <c r="AV27" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX27" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AY27" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>60</v>
+        <v>10.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BB27" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC27" t="n">
         <v>17</v>
       </c>
       <c r="BD27" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BE27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BF27" t="n">
         <v>6.4</v>
       </c>
       <c r="BG27" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5810,7 @@
         <v>6.2</v>
       </c>
       <c r="I28" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J28" t="n">
         <v>4</v>
@@ -5819,37 +5819,37 @@
         <v>4.1</v>
       </c>
       <c r="L28" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M28" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="O28" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P28" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="R28" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S28" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="T28" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="V28" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W28" t="n">
         <v>2.44</v>
@@ -5858,10 +5858,10 @@
         <v>14</v>
       </c>
       <c r="Y28" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z28" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA28" t="n">
         <v>180</v>
@@ -5876,7 +5876,7 @@
         <v>24</v>
       </c>
       <c r="AE28" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AF28" t="n">
         <v>9.4</v>
@@ -5888,46 +5888,46 @@
         <v>23</v>
       </c>
       <c r="AI28" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ28" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK28" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AL28" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AM28" t="n">
         <v>140</v>
       </c>
       <c r="AN28" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AO28" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AP28" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ28" t="n">
         <v>17</v>
       </c>
       <c r="AR28" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AS28" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AT28" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW28" t="n">
         <v>85</v>
@@ -5948,7 +5948,7 @@
         <v>14.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD28" t="n">
         <v>36</v>
@@ -5957,14 +5957,14 @@
         <v>110</v>
       </c>
       <c r="BF28" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BG28" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -5995,22 +5995,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="G29" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="H29" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="I29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K29" t="n">
         <v>3.55</v>
-      </c>
-      <c r="J29" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K29" t="n">
-        <v>3.6</v>
       </c>
       <c r="L29" t="n">
         <v>1.42</v>
@@ -6019,7 +6019,7 @@
         <v>1.07</v>
       </c>
       <c r="N29" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O29" t="n">
         <v>1.33</v>
@@ -6028,7 +6028,7 @@
         <v>1.96</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R29" t="n">
         <v>1.36</v>
@@ -6037,16 +6037,16 @@
         <v>3.6</v>
       </c>
       <c r="T29" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U29" t="n">
         <v>2.22</v>
       </c>
       <c r="V29" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W29" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="X29" t="n">
         <v>13.5</v>
@@ -6055,64 +6055,64 @@
         <v>13</v>
       </c>
       <c r="Z29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA29" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB29" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD29" t="n">
         <v>14</v>
       </c>
       <c r="AE29" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF29" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG29" t="n">
         <v>11</v>
       </c>
       <c r="AH29" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI29" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ29" t="n">
         <v>32</v>
       </c>
       <c r="AK29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL29" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO29" t="n">
         <v>38</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>42</v>
       </c>
       <c r="AP29" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR29" t="n">
         <v>21</v>
       </c>
       <c r="AS29" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AT29" t="n">
         <v>9.4</v>
@@ -6121,13 +6121,13 @@
         <v>7.2</v>
       </c>
       <c r="AV29" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AX29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY29" t="n">
         <v>10</v>
@@ -6136,10 +6136,10 @@
         <v>16</v>
       </c>
       <c r="BA29" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BB29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC29" t="n">
         <v>22</v>
@@ -6154,11 +6154,11 @@
         <v>17</v>
       </c>
       <c r="BG29" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -6189,16 +6189,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="G30" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="H30" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="I30" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="J30" t="n">
         <v>3.6</v>
@@ -6213,16 +6213,16 @@
         <v>1.07</v>
       </c>
       <c r="N30" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O30" t="n">
         <v>1.31</v>
       </c>
       <c r="P30" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R30" t="n">
         <v>1.39</v>
@@ -6231,46 +6231,46 @@
         <v>3.4</v>
       </c>
       <c r="T30" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="U30" t="n">
         <v>2.24</v>
       </c>
       <c r="V30" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="W30" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="X30" t="n">
         <v>14.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AA30" t="n">
         <v>55</v>
       </c>
       <c r="AB30" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC30" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE30" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF30" t="n">
         <v>16</v>
       </c>
       <c r="AG30" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH30" t="n">
         <v>16.5</v>
@@ -6279,10 +6279,10 @@
         <v>44</v>
       </c>
       <c r="AJ30" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL30" t="n">
         <v>38</v>
@@ -6291,22 +6291,22 @@
         <v>85</v>
       </c>
       <c r="AN30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO30" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AP30" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR30" t="n">
         <v>19.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AT30" t="n">
         <v>10</v>
@@ -6324,7 +6324,7 @@
         <v>14.5</v>
       </c>
       <c r="AY30" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ30" t="n">
         <v>15</v>
@@ -6333,10 +6333,10 @@
         <v>38</v>
       </c>
       <c r="BB30" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BC30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD30" t="n">
         <v>32</v>
@@ -6345,14 +6345,14 @@
         <v>75</v>
       </c>
       <c r="BF30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BG30" t="n">
         <v>27</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -6383,10 +6383,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="G31" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="H31" t="n">
         <v>1.56</v>
@@ -6395,28 +6395,28 @@
         <v>1.72</v>
       </c>
       <c r="J31" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="K31" t="n">
         <v>4.9</v>
       </c>
       <c r="L31" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="M31" t="n">
         <v>1.04</v>
       </c>
       <c r="N31" t="n">
-        <v>1.3</v>
+        <v>3.9</v>
       </c>
       <c r="O31" t="n">
         <v>1.22</v>
       </c>
       <c r="P31" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="R31" t="n">
         <v>1.47</v>
@@ -6437,10 +6437,10 @@
         <v>1.17</v>
       </c>
       <c r="X31" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y31" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z31" t="n">
         <v>13</v>
@@ -6491,62 +6491,62 @@
         <v>29</v>
       </c>
       <c r="AP31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AQ31" t="n">
         <v>4.4</v>
       </c>
-      <c r="AQ31" t="n">
+      <c r="AR31" t="n">
         <v>4.6</v>
       </c>
-      <c r="AR31" t="n">
+      <c r="AS31" t="n">
         <v>5</v>
       </c>
-      <c r="AS31" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AT31" t="n">
-        <v>2.96</v>
+        <v>5.6</v>
       </c>
       <c r="AU31" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AV31" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AX31" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="AY31" t="n">
-        <v>2.76</v>
+        <v>5.6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.84</v>
+        <v>6</v>
       </c>
       <c r="BB31" t="n">
-        <v>2.22</v>
+        <v>7</v>
       </c>
       <c r="BC31" t="n">
-        <v>3</v>
+        <v>6.6</v>
       </c>
       <c r="BD31" t="n">
-        <v>3</v>
+        <v>6.6</v>
       </c>
       <c r="BE31" t="n">
-        <v>2.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF31" t="n">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="BG31" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -6577,170 +6577,170 @@
         </is>
       </c>
       <c r="F32" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G32" t="n">
         <v>2.22</v>
       </c>
-      <c r="G32" t="n">
-        <v>2.34</v>
-      </c>
       <c r="H32" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="I32" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="J32" t="n">
         <v>3.25</v>
       </c>
       <c r="K32" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="L32" t="n">
         <v>1.49</v>
       </c>
       <c r="M32" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N32" t="n">
         <v>3.15</v>
       </c>
       <c r="O32" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P32" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R32" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S32" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T32" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U32" t="n">
         <v>1.92</v>
       </c>
-      <c r="U32" t="n">
-        <v>1.9</v>
-      </c>
       <c r="V32" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W32" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="X32" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y32" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="Z32" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AA32" t="n">
         <v>900</v>
       </c>
       <c r="AB32" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC32" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD32" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ32" t="n">
         <v>17</v>
       </c>
-      <c r="AE32" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH32" t="n">
+      <c r="BA32" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC32" t="n">
         <v>20</v>
       </c>
-      <c r="AI32" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>440</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>26</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ32" t="n">
+      <c r="BD32" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BF32" t="n">
         <v>16.5</v>
       </c>
-      <c r="BA32" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>21</v>
-      </c>
       <c r="BG32" t="n">
-        <v>9.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>
@@ -6774,10 +6774,10 @@
         <v>1.04</v>
       </c>
       <c r="G33" t="n">
-        <v>240</v>
+        <v>600</v>
       </c>
       <c r="H33" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I33" t="n">
         <v>1000</v>
@@ -6795,13 +6795,13 @@
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="O33" t="n">
         <v>1.29</v>
       </c>
       <c r="P33" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="Q33" t="n">
         <v>1.29</v>
@@ -6810,13 +6810,13 @@
         <v>1.18</v>
       </c>
       <c r="S33" t="n">
-        <v>1.29</v>
+        <v>1.05</v>
       </c>
       <c r="T33" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U33" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V33" t="n">
         <v>1.01</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-09 05:17:51</t>
+          <t>2026-04-09 07:38:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH15"/>
+  <dimension ref="A1:BH11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,36 +743,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>MC El Bayadh</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -793,141 +793,141 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-09 15:50:53</t>
+          <t>2026-04-09 18:22:54</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,36 +937,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MB Rouissat</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -987,10 +987,10 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -999,129 +999,129 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>930</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>990</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-09 15:50:53</t>
+          <t>2026-04-09 18:22:54</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cukaricki</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FK Radnicki 1923</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-09 15:50:53</t>
+          <t>2026-04-09 18:22:54</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>610</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>820</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-09 15:50:53</t>
+          <t>2026-04-09 18:22:54</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,36 +1519,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Crvena Zvezda</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FK Spartak</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>650</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1581,129 +1581,129 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-09 15:50:53</t>
+          <t>2026-04-09 18:22:54</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PFC Levski Sofia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-09 15:50:53</t>
+          <t>2026-04-09 18:22:54</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Saudi 1st Division</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,36 +1907,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:40:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Al-Adalh</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Batin</t>
+          <t>Nottm Forest</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1945,153 +1945,153 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-09 15:50:53</t>
+          <t>2026-04-09 18:22:54</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Union Magdalena</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ZED FC</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="G9" t="n">
-        <v>3.3</v>
+        <v>2.36</v>
       </c>
       <c r="H9" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="I9" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="J9" t="n">
-        <v>2.64</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>2.74</v>
+        <v>3.5</v>
       </c>
       <c r="L9" t="n">
-        <v>2.6</v>
+        <v>1.53</v>
       </c>
       <c r="M9" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>1.92</v>
+        <v>3.15</v>
       </c>
       <c r="O9" t="n">
-        <v>2.04</v>
+        <v>1.44</v>
       </c>
       <c r="P9" t="n">
-        <v>1.29</v>
+        <v>1.73</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.2</v>
+        <v>2.32</v>
       </c>
       <c r="R9" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>4.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.82</v>
+        <v>1.94</v>
       </c>
       <c r="U9" t="n">
-        <v>1.45</v>
+        <v>1.93</v>
       </c>
       <c r="V9" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="W9" t="n">
-        <v>1.41</v>
+        <v>1.73</v>
       </c>
       <c r="X9" t="n">
-        <v>5.2</v>
+        <v>11.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="Z9" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AA9" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AC9" t="n">
         <v>7.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="AF9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH9" t="n">
         <v>21</v>
       </c>
-      <c r="AG9" t="n">
-        <v>990</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>46</v>
-      </c>
       <c r="AI9" t="n">
-        <v>210</v>
+        <v>65</v>
       </c>
       <c r="AJ9" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="AK9" t="n">
-        <v>95</v>
+        <v>29</v>
       </c>
       <c r="AL9" t="n">
-        <v>210</v>
+        <v>48</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN9" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="AO9" t="n">
-        <v>180</v>
+        <v>65</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.9</v>
+        <v>10</v>
       </c>
       <c r="AR9" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AS9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>25</v>
+      </c>
+      <c r="BG9" t="n">
         <v>48</v>
       </c>
-      <c r="AT9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>34</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>120</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>55</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>65</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>130</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>450</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>110</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>90</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-09 15:50:53</t>
+          <t>2026-04-09 18:22:54</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Juticalpa</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>Olancho</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.31</v>
+        <v>5.2</v>
       </c>
       <c r="G10" t="n">
-        <v>1.32</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>18.5</v>
+        <v>1.48</v>
       </c>
       <c r="I10" t="n">
-        <v>21</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="K10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N10" t="n">
         <v>5.5</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.9</v>
-      </c>
       <c r="O10" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="P10" t="n">
-        <v>1.64</v>
+        <v>2.68</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.48</v>
+        <v>1.56</v>
       </c>
       <c r="R10" t="n">
-        <v>1.19</v>
+        <v>1.63</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.12</v>
+        <v>1.06</v>
       </c>
       <c r="U10" t="n">
-        <v>1.69</v>
+        <v>1.02</v>
       </c>
       <c r="V10" t="n">
-        <v>1.05</v>
+        <v>3</v>
       </c>
       <c r="W10" t="n">
-        <v>4</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z10" t="n">
         <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.4</v>
+        <v>990</v>
       </c>
       <c r="AD10" t="n">
-        <v>34</v>
+        <v>990</v>
       </c>
       <c r="AE10" t="n">
         <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>5.3</v>
+        <v>85</v>
       </c>
       <c r="AG10" t="n">
-        <v>11.5</v>
+        <v>990</v>
       </c>
       <c r="AH10" t="n">
         <v>990</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ10" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
         <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP10" t="n">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR10" t="n">
-        <v>11</v>
+        <v>4.1</v>
       </c>
       <c r="AS10" t="n">
-        <v>11</v>
+        <v>3.45</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.8</v>
+        <v>8.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="AV10" t="n">
-        <v>22</v>
+        <v>3.45</v>
       </c>
       <c r="AW10" t="n">
-        <v>22</v>
+        <v>3.85</v>
       </c>
       <c r="AX10" t="n">
-        <v>4.5</v>
+        <v>1.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="AZ10" t="n">
-        <v>23</v>
+        <v>4.1</v>
       </c>
       <c r="BA10" t="n">
-        <v>22</v>
+        <v>2.9</v>
       </c>
       <c r="BB10" t="n">
-        <v>11.5</v>
+        <v>1.63</v>
       </c>
       <c r="BC10" t="n">
-        <v>18.5</v>
+        <v>4</v>
       </c>
       <c r="BD10" t="n">
-        <v>22</v>
+        <v>4.7</v>
       </c>
       <c r="BE10" t="n">
-        <v>220</v>
+        <v>4.9</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.6</v>
+        <v>2.08</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-09 15:50:53</t>
+          <t>2026-04-09 18:22:54</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,93 +2489,93 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>CD Marathon</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>CD Motagua</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.46</v>
+        <v>3.6</v>
       </c>
       <c r="G11" t="n">
-        <v>1.49</v>
+        <v>5.4</v>
       </c>
       <c r="H11" t="n">
-        <v>8.6</v>
+        <v>1.97</v>
       </c>
       <c r="I11" t="n">
-        <v>9.4</v>
+        <v>2.24</v>
       </c>
       <c r="J11" t="n">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R11" t="n">
-        <v>8</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>1.13</v>
+        <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.12</v>
+        <v>1.63</v>
       </c>
       <c r="W11" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z11" t="n">
         <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE11" t="n">
         <v>1000</v>
@@ -2584,865 +2584,89 @@
         <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>8.4</v>
+        <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
         <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
         <v>23</v>
       </c>
       <c r="AP11" t="n">
-        <v>250</v>
+        <v>4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>250</v>
+        <v>3.7</v>
       </c>
       <c r="AR11" t="n">
-        <v>250</v>
+        <v>4.1</v>
       </c>
       <c r="AS11" t="n">
-        <v>250</v>
+        <v>4.9</v>
       </c>
       <c r="AT11" t="n">
-        <v>17</v>
+        <v>4.1</v>
       </c>
       <c r="AU11" t="n">
-        <v>15</v>
+        <v>3.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>17</v>
+        <v>3.8</v>
       </c>
       <c r="AW11" t="n">
-        <v>17</v>
+        <v>4.6</v>
       </c>
       <c r="AX11" t="n">
-        <v>17</v>
+        <v>4.7</v>
       </c>
       <c r="AY11" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="AZ11" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="BA11" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="BB11" t="n">
-        <v>17</v>
+        <v>5.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE11" t="n">
-        <v>13</v>
+        <v>5.3</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.35</v>
+        <v>5.1</v>
       </c>
       <c r="BG11" t="n">
-        <v>18.5</v>
+        <v>4.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-09 15:50:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Algerian Ligue 1</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>16:00:00</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>MC Alger</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>MC El Bayadh</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="H12" t="n">
-        <v>20</v>
-      </c>
-      <c r="I12" t="n">
-        <v>24</v>
-      </c>
-      <c r="J12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="X12" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>44</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>110</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>80</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>910</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>28</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>95</v>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>2026-04-09 15:50:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Colombian Primera B</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>18:00:00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Union Magdalena</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Envigado</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="H13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="X13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>190</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>500</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>26</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>20</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>25</v>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>2026-04-09 15:50:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Honduras Liga Nacional</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>18:00:00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Juticalpa</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Olancho</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N14" t="n">
-        <v>4</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V14" t="n">
-        <v>2</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X14" t="n">
-        <v>90</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>700</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>700</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>29</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>7</v>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>2026-04-09 15:50:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Honduras Liga Nacional</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>22:30:00</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>CD Marathon</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CD Motagua</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="G15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="I15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>2026-04-09 15:50:53</t>
+          <t>2026-04-09 18:22:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-09.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.15</v>
+        <v>1.47</v>
       </c>
       <c r="G2" t="n">
-        <v>3.75</v>
+        <v>1.48</v>
       </c>
       <c r="H2" t="n">
-        <v>2.36</v>
+        <v>10</v>
       </c>
       <c r="I2" t="n">
-        <v>2.64</v>
+        <v>12.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>3.55</v>
+        <v>4.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="T2" t="n">
         <v>1.73</v>
       </c>
       <c r="U2" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="V2" t="n">
-        <v>1.61</v>
+        <v>1.09</v>
       </c>
       <c r="W2" t="n">
-        <v>1.37</v>
+        <v>3.1</v>
       </c>
       <c r="X2" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>13.5</v>
+        <v>5.3</v>
       </c>
       <c r="AC2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>290</v>
+      </c>
+      <c r="AP2" t="n">
         <v>7.8</v>
       </c>
-      <c r="AD2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI2" t="n">
+      <c r="AQ2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD2" t="n">
         <v>42</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>32</v>
-      </c>
       <c r="BE2" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="BF2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="BG2" t="n">
-        <v>17.5</v>
+        <v>110</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-09 20:55:11</t>
+          <t>2026-04-09 23:27:12</t>
         </is>
       </c>
     </row>
